--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=event ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=doclist ; https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB2/document.pdf</t>
+          <t>https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=event ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=doclist ; https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB1/document.pdf ; https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB2/document.pdf</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -857,7 +857,7 @@
     <row r="7" ht="78" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Saksan mitätöintikanne hylättiin 14.1.2026, mutta valitus on vireillä.</t>
+          <t>Saksan virallinen tapahtuma: Mitätöintikanne hylättiin; valitus vireillä (14.1.2026).</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Väite rajataan Saksan osaan ja nykyiseen prosessitilaan.</t>
+          <t>Maantieteellinen ja prosessuaalinen rajaus: Saksa. Ei lainvoimainen BGH-valituksen ollessa vireillä.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -897,14 +897,14 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Seuraa BGH-valituksen X ZR 21/26 etenemistä ja lopputulosta.</t>
+          <t>Seuraa muutoksenhakua X ZR 21/26, sen lopputulosta, täytäntöönpanoa ja mahdollisia maksettuja korvauksia.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Münchenin tuomioistuin totesi tarkasteltujen tuotteiden loukkaavan vaatimuksia 1 ja 6.</t>
+          <t>Saksan virallinen tapahtuma koski vaatimuksia 1 ja 6: Tarkasteltujen tuotteiden todettiin loukkaavan patenttia.</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Ei yleistetä muihin tuotteisiin, yhtiöihin tai maihin.</t>
+          <t>Maantieteellinen ja prosessuaalinen rajaus: Saksa. Virallinen tuomio on saatavilla; valitustilaa, lainvoimaisuutta ja täytäntöönpanoa ei ole tässä julkaisussa riippumattomasti vahvistettu.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -944,14 +944,14 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Valitustila, lainvoimaisuus, täytäntöönpano ja maksetut korvaukset on vahvistettava.</t>
+          <t>Vahvista valitustila, lainvoimaisuus, täytäntöönpano ja maksetut korvaukset.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Kiinan tunnistettu asia on hakijapuolen uudelleentarkastus, ei loukkausoikeudenkäynti.</t>
+          <t>Kiinan tunnistettu menettely: Kiinan hakijapuolen uudelleentarkastus tunnistettu; perusteluja ei saatu.</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://litigation.rpxcorp.com/china/prb/5153434-picsen-company-v-pixan-oy-of-365 ; https://www.cnipa.gov.cn/art/2020/6/5/art_1517_92474.html</t>
+          <t>https://litigation.rpxcorp.com/china/prb/5153434-picsen-company-v-pixan-oy-of-365 ; https://www.cnipa.gov.cn/art/2020/6/5/art_1517_92474.html ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=family</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Kolme yksittäistä verkkokauppahintaa; vuosiero; vain verotettu neste.</t>
+          <t>Kolme yksittäistä verkkokauppahintaa; syötevuodet 2025 ja 2026; vain verotettu neste.</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan edustava hintakori, tuotemix, kanavamarginaalit ja saman vuoden hinnat.</t>
+          <t>Tarvitaan edustava hintakori, tuotemix ja kanavamarginaalit sekä mallivuoden 2025 hinnat.</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Neljä rekisteritarkistusta ei kata koko perhettä.</t>
+          <t>Neljä kansallista rekisterijurisdiktiota ei kata koko perhettä.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923 ; https://patentcenter.uspto.gov/applications/14911851</t>
+          <t>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923 ; https://patentcenter.uspto.gov/applications/14911851 ; https://assignment.uspto.gov/patent/index.html#/patent/search/resultFilter?searchInput=10306923</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.22-7</t>
+          <t>2026.07.22-8</t>
         </is>
       </c>
     </row>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.22-8</t>
+          <t>2026.07.22-9</t>
         </is>
       </c>
     </row>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.22-9</t>
+          <t>2026.07.23-10</t>
         </is>
       </c>
     </row>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.23-10</t>
+          <t>2026.07.23-11</t>
         </is>
       </c>
     </row>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.23-11</t>
+          <t>2026.07.23-12</t>
         </is>
       </c>
     </row>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.23-12</t>
+          <t>2026.07.23-13</t>
         </is>
       </c>
     </row>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.23-13</t>
+          <t>2026.07.23-14</t>
         </is>
       </c>
     </row>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.23-14</t>
+          <t>2026.07.23-15</t>
         </is>
       </c>
     </row>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.23-15</t>
+          <t>2026.07.23-16</t>
         </is>
       </c>
     </row>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence Register'!$A$1:$I$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence Register'!$A$1:$I$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Evidence Register'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Lähteet'!$A$1:$E$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Lähteet'!$A$1:$E$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Lähteet'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -252,8 +252,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EvidenceRegister" displayName="EvidenceRegister" ref="A1:I46" headerRowCount="1">
-  <autoFilter ref="A1:I46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EvidenceRegister" displayName="EvidenceRegister" ref="A1:I50" headerRowCount="1">
+  <autoFilter ref="A1:I50"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Väite"/>
     <tableColumn id="2" name="Dia/osio"/>
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -642,7 +642,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="11" ht="78" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Hyväksyttyjä vuosittaisia virallisia määrähavaintoja on viidestä maasta.</t>
+          <t>Hyväksyttyjä vuosittaisia virallisia määrähavaintoja on kuudesta maasta.</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Maat: Kanada, Saksa, Suomi, Puola ja Ruotsi.</t>
+          <t>Hyväksytyt maat ovat Kanada, Saksa, Suomi, Uusi-Seelanti, Puola ja Ruotsi. 20 virallista tietuetta sisältävät eri tapahtumatasoja, valuuttoja ja tuoterajauksia.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Uniikit maat virallisiksi luokitelluista vuosihavainnoista.</t>
+          <t>Uniikit maat vuosihavainnoista, joiden evidenceStatus alkaa official_.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Mittarit eivät ole keskenään samanlaisia.</t>
+          <t>Virallinen julkaisu ei tee mittareista automaattisesti vertailukelpoisia maiden välillä.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1102,27 +1102,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>comparableFullYearMarketValueDonors = 0.</t>
+          <t>comparableFullYearMarketValueDonors = 0. Neljä ehdokastestiä on julkaistu saman 10 ehdon protokollan mukaan.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>site/data/market-values.json (modelReadiness)</t>
+          <t>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Yhteensopivien koko vuoden kuluttajavähittäisarvojen hyväksyntäkriteeri.</t>
+          <t>Ehdokas lasketaan luovuttajaksi vain, jos D1–D10 täyttyvät kaikki; hylätty tai avoin ehto pitää sen lukumäärän ulkopuolella.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Toimitus-, vero- ja määräluvut eivät ole vähittäisarvoja.</t>
+          <t>Virallisia alarajoja, institutionaalisia vertailuarvoja, toimitusarvoja, verotuloja, fyysisiä määriä ja malleja ei nimetä uudelleen täydelliseksi kuluttajavähittäisarvoksi.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Hanki vähintään kolme yhteensopivaa luovuttajamarkkinaa sekä alue- ja sääntelytyyppien peitto.</t>
+          <t>Tarvitaan vähintään kolme hyväksyttyä luovuttajaa sekä alue- ja sääntelytyyppien peitto.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="78" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Kanadan vuoden 2024 valmistaja- ja maahantuojatoimitusten arvo oli 1,16075379678 mrd CAD.</t>
+          <t>Uuden-Seelannin vuoden 2024 erikoistuneiden sähkötupakkakauppiaiden myynniksi ilmoitettiin vähintään 280 milj. NZD.</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Virallinen koko vuoden toimitusarvo tukku- tai vähittäismyyjille kaikissa neljässä raportoidussa tuoteryhmässä. Kyse ei ole kuluttajien vähittäisostoista, ja Health Canada voi tarkistaa tietoa.</t>
+          <t>Terveysministeriö julkaisee virallisen kuluttajavähittäismyynnin alarajan, joka perustuu vain puutteellisiin erikoistuneiden sähkötupakkakauppiaiden myynteihin. Yleisvähittäiskauppa puuttuu, viereisiä ilmoitusvelvollisia tuotteita sisältyy eikä ministeriö suosittele aineistoa perusteelliseen tutkimukseen.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://health-infobase.canada.ca/substance-use/vaping/sales/</t>
+          <t>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Health Canadan neljän raportoidun tuoteryhmän toimitusarvon summa.</t>
+          <t>Virallista vähintään-otsikkolukua käytetään suoraan; ei ekstrapolointia eikä muiden palautustyyppien yhteenlaskua.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Ei kuluttajavähittäismyyntiä.</t>
+          <t>Luku on alaraja, ei koko maan sähkötupakkamarkkinan arvo.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1179,14 +1179,14 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan vähittäismarginaali-, kanava- ja varastomuutostäsmäytys.</t>
+          <t>Hanki täydellinen valtakunnallinen vain sähkötupakkatuotteita koskeva vähittäiskaupan koonti, GST-perusta ja riippumaton täsmäytys.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="78" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Kanadan vuoden 2024 raportoidut toimitukset sisälsivät 1 251 843 litraa nestettä.</t>
+          <t>Uuden-Seelannin 29 virallisen vuoden 2024 XLSX-tiedoston 612 765 numeerisen Total sales -solun raakasumma on 280 684 512,81 NZD.</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1196,44 +1196,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Höyrystettävää ainetta sisältävien tuoteryhmien ilmoitettu määrä. Se on fyysinen määrä, ei vähittäismarkkina-arvo.</t>
+          <t>Raakasumma täsmää ministeriön vähintään 280 milj. NZD otsikkolukuun. Aineistossa on 95 144 täsmälleen toistuvaa riviallekirjoitusta; niiden ensimmäisen esiintymän jälkeinen poistaminen antaisi 264 561 055,05 NZD, mutta toistojen merkitystä ei ole vahvistettu.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://health-infobase.canada.ca/substance-use/vaping/sales/</t>
+          <t>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_ANNUAL_RETURNS_RECONCILIATION.md</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Raportoitujen nestettä sisältävien tuoteryhmien summa.</t>
+          <t>Kaikkien 29 virallisen XLSX-tiedoston numeeristen Total sales -solujen suora summa; ei deduplikointia, puhdistusta tai ekstrapolointia.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Fyysinen määrä, ei markkina-arvo.</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Vahvistettu</t>
+          <t>Toistuvat rivit säilytetään raakasummassa, koska niiden liiketoiminnallista merkitystä ei tunneta.</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Tuettu</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan tuotemixin, keskihinnan ja vähittäiskanavan tiedot.</t>
+          <t>Raakasumma ei ole puhdistettu kansallinen markkina-arvo. Yleisvähittäiskauppa, puuttuvat ilmoitukset ja GST-käsittely ovat avoimia.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="78" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Saksan verotettu nestemäärä kasvoi 1.241 milj. l:sta 1.518 milj. l:aan vuosina 2023–2025.</t>
+          <t>Varovainen tekstiluokitus tunnistaa Uuden-Seelannin vuoden 2024 sähkötupakkatuoterivien raakasummaksi 274 180 410,21 NZD.</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1243,44 +1243,44 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2023 ja 2024 lopullisia; 2025 alustava.</t>
+          <t>Viereisiksi ilmoitusvelvollisiksi tuotteiksi tunnistettiin 2 137 085,24 NZD ja ratkaisemattomaksi tuotetyypiksi 4 367 017,37 NZD. Sähkötupakkarivien toistorivien poistamisen herkkyys on 258 327 110,88 NZD, mutta se ei ole korjattu estimaatti.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</t>
+          <t>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_ANNUAL_RETURNS_RECONCILIATION.md</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2023–2025</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Destatis-taulukon nettomäärät, ei ekstrapolointia.</t>
+          <t>Konservatiivinen Product type -tekstiluokitus virallisten XLSX-tiedostojen tuoteriveille; luokittelu- ja toistoriviherkkyys raportoidaan erikseen.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Mittaa verotettua nestettä, ei laitteita tai laitonta myyntiä.</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Vahvistettu</t>
+          <t>Tuotetyyppikentän virheet ja ratkaisemattomat rivit estävät kattavan sähkötupakkamarkkinan tulkinnan.</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Tuettu</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Vuoden 2025 lopullinen luku ja vähittäismyyntitiedot puuttuvat.</t>
+          <t>Hanki viranomaisen tuotekoodisanasto, toistorivien semantiikka, täydellinen kanavapeitto ja GST-perusta. Luku ei kelpaa luovuttajaksi.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="78" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Saksan tupakankorvikkeiden valmisteverotulot olivat 404 milj. euroa vuonna 2025 (alustava).</t>
+          <t>Euroopan komissio julkaisee vuoden 2023 EU:n sähkötupakkamarkkinan 4,99 mrd euron vertailuarvon.</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1290,44 +1290,44 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Alustavat viralliset kassaperusteiset valmisteverotulot. Verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</t>
+          <t>SWD(2026) 111:n fyysisen PDF:n sivun 25 alaviite 83 nimeää seuraavien sivujen taulukoiden lähteeksi Euromonitor International Tobacco 2025 -aineiston; fyysisen sivun 27 taulukko 4 raportoi 4,99 mrd euroa. SWD(2025) 560:n fyysinen sivu 161 kuvaa lähes 5 mrd euron koonnin, joka sisältää laitteet ja nesteet, myös nikotiinittomat; sivu 162 ilmoittaa Kyproksen, Luxemburgin ja Maltan tiedot puuttuviksi.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2025%3A0560%3AFIN ; https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2026%3A111%3AFIN</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Virallinen kassaperusteinen verohavainto.</t>
+          <t>Kahden Euroopan komission valmisteluasiakirjan taulukko-, sivu- ja lähdeviitteiden ristiinvertailu; lukuja ei summata.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Verotulo ei ole myyntitulo tai vähittäismarkkina-arvo.</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Vahvistettu</t>
+          <t>Komissio julkaisee vertailuarvon, mutta sen pohjana on kaupallinen Euromonitor-aineisto. Täysi menetelmä, veroperusta ja uudelleenkäytettävä maadata eivät ole julkisia, ja kolmesta EU-maasta ei ole tietoa.</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Tuettu</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan lopullinen 2025 tilasto ja tuoteryhmäkohtainen veropohja.</t>
+          <t>Hanki lisensoitu maataulukko ja menetelmä, tapahtumamääritelmä, kanavapeitto, veroperusta sekä riippumaton täsmäytys; täydennä Kypros, Luxemburg ja Malta.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="78" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Suomessa verotettiin 11 801,062 litraa nikotiininestettä vuonna 2025.</t>
+          <t>Kanadan vuoden 2024 valmistaja- ja maahantuojatoimitusten arvo oli 1,16075379678 mrd CAD.</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1337,27 +1337,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Virallinen koko vuoden nikotiinillisen sähkösavukenesteen määrä. Nikotiinittoman nesteen koko vuoden arvo on salattu; fyysinen määrä ei sisällä laitteita eikä ole vähittäismarkkina-arvo.</t>
+          <t>Virallinen koko vuoden toimitusarvo tukku- tai vähittäismyyjille kaikissa neljässä raportoidussa tuoteryhmässä. Kyse ei ole kuluttajien vähittäisostoista, ja Health Canada voi tarkistaa tietoa.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</t>
+          <t>https://health-infobase.canada.ca/substance-use/vaping/sales/</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Verohallinnon PXWeb-havainto.</t>
+          <t>Health Canadan neljän raportoidun tuoteryhmän toimitusarvon summa.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Verotettu nikotiinineste ei kata koko sähkötupakkamarkkinaa.</t>
+          <t>Ei kuluttajavähittäismyyntiä.</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1367,14 +1367,14 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Laitteet, nikotiinittomat tuotteet, veroton ja laiton kauppa puuttuvat.</t>
+          <t>Tarvitaan vähittäismarginaali-, kanava- ja varastomuutostäsmäytys.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="78" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Suomen nikotiininesteiden valmisteverotulot olivat 3 540 319 euroa vuonna 2025.</t>
+          <t>Kanadan vuoden 2024 raportoidut toimitukset sisälsivät 1 251 843 litraa nestettä.</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1384,27 +1384,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Viralliset koko vuoden nikotiinillisen sähkösavukenesteen valmisteverotulot. Nikotiinittoman nesteen koko vuoden arvo on salattu; verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</t>
+          <t>Höyrystettävää ainetta sisältävien tuoteryhmien ilmoitettu määrä. Se on fyysinen määrä, ei vähittäismarkkina-arvo.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</t>
+          <t>https://health-infobase.canada.ca/substance-use/vaping/sales/</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Verohallinnon PXWeb-havainto.</t>
+          <t>Raportoitujen nestettä sisältävien tuoteryhmien summa.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Verotulo ei ole kuluttajamyynti.</t>
+          <t>Fyysinen määrä, ei markkina-arvo.</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan vähittäismyynti- ja hintadata.</t>
+          <t>Tarvitaan tuotemixin, keskihinnan ja vähittäiskanavan tiedot.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="78" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Puolassa raportoitu sähkötupakkanesteiden määrä oli 805 441 litraa vuonna 2023.</t>
+          <t>Saksan verotettu nestemäärä kasvoi 1.241 milj. l:sta 1.518 milj. l:aan vuosina 2023–2025.</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Virallisessa parlamenttivastauksessa ilmoitettu nestemäärä. Se on fyysinen määrä, ei sisällä laitteiden arvoa eikä ole havaittu vähittäismarkkina-arvo.</t>
+          <t>2023 ja 2024 lopullisia; 2025 alustava.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDDEJZ5/i07255-o1.pdf</t>
+          <t>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023–2025</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Parlamentaariseen vastaukseen raportoitu määrä.</t>
+          <t>Destatis-taulukon nettomäärät, ei ekstrapolointia.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Mittarin kattavuus on luettava alkuperäislähteen rajauksin.</t>
+          <t>Mittaa verotettua nestettä, ei laitteita tai laitonta myyntiä.</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1461,14 +1461,14 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan uudempi vuosisarja ja vähittäisarvo.</t>
+          <t>Vuoden 2025 lopullinen luku ja vähittäismyyntitiedot puuttuvat.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="78" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Puolan vuoden 2025 ilmoitettu e-nestevalmisteveron määrä oli 993,1 milj. PLN.</t>
+          <t>Saksan tupakankorvikkeiden valmisteverotulot olivat 404 milj. euroa vuonna 2025 (alustava).</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Virallisessa parlamenttivastauksessa ilmoitettu veromäärä. Se ei ole myyntituloa eikä vähittäismarkkina-arvoa, ja se pidetään erillään laitteiden ja osasarjojen veromääristä.</t>
+          <t>Alustavat viralliset kassaperusteiset valmisteverotulot. Verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf</t>
+          <t>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Parlamentaariseen vastaukseen raportoitu veromäärä.</t>
+          <t>Virallinen kassaperusteinen verohavainto.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Veromäärä ei ole vähittäismyynti.</t>
+          <t>Verotulo ei ole myyntitulo tai vähittäismarkkina-arvo.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1508,14 +1508,14 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan toteuman lopullisuus ja veropohjan täsmäytys.</t>
+          <t>Tarvitaan lopullinen 2025 tilasto ja tuoteryhmäkohtainen veropohja.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="78" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Ruotsissa verotettiin 26 000 litraa nikotiininestettä vuonna 2024.</t>
+          <t>Suomessa verotettiin 11 801,062 litraa nikotiininestettä vuonna 2025.</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Taulukon 7.5 pyöristetty virallinen määrä. Se kattaa nikotiinillisen sähkösavukenesteen, ei sisällä laitteita tai nikotiinitonta nestettä eikä ole vähittäismarkkina-arvo.</t>
+          <t>Virallinen koko vuoden nikotiinillisen sähkösavukenesteen määrä. Nikotiinittoman nesteen koko vuoden arvo on salattu; fyysinen määrä ei sisällä laitteita eikä ole vähittäismarkkina-arvo.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf</t>
+          <t>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Hallituksen laskentaperusteessa ilmoitettu määrä.</t>
+          <t>Verohallinnon PXWeb-havainto.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1555,14 +1555,14 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan toteutunut vähittäismyynti ja laitedata.</t>
+          <t>Laitteet, nikotiinittomat tuotteet, veroton ja laiton kauppa puuttuvat.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="78" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Kolme kaupallista vuoden 2025 globaaliarviota muodostavat 26,0–46,32 mrd USD haarukan.</t>
+          <t>Suomen nikotiininesteiden valmisteverotulot olivat 3 540 319 euroa vuonna 2025.</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>IMARC 26,0; Grand View Research 45,7; Fortune Business Insights 46,32 mrd USD.</t>
+          <t>Viralliset koko vuoden nikotiinillisen sähkösavukenesteen valmisteverotulot. Nikotiinittoman nesteen koko vuoden arvo on salattu; verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://www.imarcgroup.com/e-cigarette-market ; https://www.grandviewresearch.com/industry-analysis/e-cigarette-vaping-market ; https://www.fortunebusinessinsights.com/e-cigarette-and-vaping-market-114882</t>
+          <t>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1587,106 +1587,106 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Minimi 26000000000, maksimi 46320000000; arvioita verrataan, ei summata.</t>
+          <t>Verohallinnon PXWeb-havainto.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tuoterajaukset ja menetelmät eivät välttämättä ole yhteismitallisia.</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Tuettu</t>
+          <t>Verotulo ei ole kuluttajamyynti.</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Hanki raporttien täydet metodit ja harmonisoi tuoterajaus.</t>
+          <t>Tarvitaan vähittäismyynti- ja hintadata.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="78" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Saksan vuoden 2025 verotetun nesteen vähittäismyyntivastaavuuden mallihaitari on 667,92–1 654,62 milj. euroa.</t>
+          <t>Puolassa raportoitu sähkötupakkanesteiden määrä oli 805 441 litraa vuonna 2023.</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Taloudellinen malli</t>
+          <t>Markkinan koko</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ei havaittua myyntiä. Laskelma kertoo vuoden 2025 alustavan verotetun nestemäärän kolmella yksittäisellä saksalaisen verkkokaupan vuoden 2026 hinnalla. Vuosiero, yhden kaupan hintakori, tuotejakauma ja pois rajatut tuoteryhmät tekevät luottamustasosta matalan.</t>
+          <t>Virallisessa parlamenttivastauksessa ilmoitettu nestemäärä. Se on fyysinen määrä, ei sisällä laitteiden arvoa eikä ole havaittu vähittäismarkkina-arvo.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003 ; https://www.intaste.de/pfefferminz-liquid-germanflavours-liquid ; https://www.intaste.de/anstand-liquid-samurai-liquid ; https://www.intaste.de/tobacco-vanilla-nikotinsalz-revoltage-liquid</t>
+          <t>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDDEJZ5/i07255-o1.pdf</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2025 määrä / 2026 hinnat</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>volume_litres * 1000 * retail_price_eur_per_ml</t>
+          <t>Parlamentaariseen vastaukseen raportoitu määrä.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Kolme yksittäistä verkkokauppahintaa; syötevuodet 2025 ja 2026; vain verotettu neste.</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Oletus</t>
+          <t>Mittarin kattavuus on luettava alkuperäislähteen rajauksin.</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan edustava hintakori, tuotemix ja kanavamarginaalit sekä mallivuoden 2025 hinnat.</t>
+          <t>Tarvitaan uudempi vuosisarja ja vähittäisarvo.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="78" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Atlas ei ole vielä lainanantajavalmis markkina-arvio.</t>
+          <t>Puolan vuoden 2025 ilmoitettu e-nestevalmisteveron määrä oli 993,1 milj. PLN.</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Rahoitusteesi</t>
+          <t>Markkinan koko</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>research_dataset_not_valuation: Useimmista maista puuttuu virallinen vuosittainen laite- ja nestemyynti Markkinaevidenssiä ei ole vielä sidottu maakohtaiseen patenttistatukseen ja claim charteihin Aineisto ei sisällä riippumatonta IVS-arvonmääritystä eikä realisoitunutta lisenssi- tai vahingonkorvauskassavirtaa</t>
+          <t>Virallisessa parlamenttivastauksessa ilmoitettu veromäärä. Se ei ole myyntituloa eikä vähittäismarkkina-arvoa, ja se pidetään erillään laitteiden ja osasarjojen veromääristä.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>site/data/atlas.json (readiness)</t>
+          <t>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Julkisen datasetin oma readiness-luokitus.</t>
+          <t>Parlamentaariseen vastaukseen raportoitu veromäärä.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Markkinadata ja IP-arvo pidetään erillään.</t>
+          <t>Veromäärä ei ole vähittäismyynti.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1696,232 +1696,232 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Täytä blocker-lista ennen vakuusarvo- tai yritysarvopäätelmää.</t>
+          <t>Tarvitaan toteuman lopullisuus ja veropohjan täsmäytys.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="78" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei sisällä riippumatonta IVS-arvonmääritystä.</t>
+          <t>Ruotsissa verotettiin 26 000 litraa nikotiininestettä vuonna 2024.</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Taloudellinen malli</t>
+          <t>Markkinan koko</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Readiness-blocker ilmoittaa riippumattoman arvonmäärityksen puuttuvan.</t>
+          <t>Taulukon 7.5 pyöristetty virallinen määrä. Se kattaa nikotiinillisen sähkösavukenesteen, ei sisällä laitteita tai nikotiinitonta nestettä eikä ole vähittäismarkkina-arvo.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>site/data/atlas.json (readiness.blockers)</t>
+          <t>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Aineiston puute.</t>
+          <t>Hallituksen laskentaperusteessa ilmoitettu määrä.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Ei oletuksia.</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Puuttuu</t>
+          <t>Verotettu nikotiinineste ei kata koko sähkötupakkamarkkinaa.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Tilaa riippumaton IP- ja tarvittaessa yritysarvonmääritys skenaarioineen.</t>
+          <t>Tarvitaan toteutunut vähittäismyynti ja laitedata.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="78" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei osoita toteutunutta lisenssi- tai vahingonkorvauskassavirtaa.</t>
+          <t>Kolme kaupallista vuoden 2025 globaaliarviota muodostavat 26,0–46,32 mrd USD haarukan.</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Kaupallistamismalli</t>
+          <t>Markkinan koko</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Readiness-blocker ilmoittaa realisoituneen kassavirran puuttuvan.</t>
+          <t>IMARC 26,0; Grand View Research 45,7; Fortune Business Insights 46,32 mrd USD.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>site/data/atlas.json (readiness.blockers)</t>
+          <t>https://www.imarcgroup.com/e-cigarette-market ; https://www.grandviewresearch.com/industry-analysis/e-cigarette-vaping-market ; https://www.fortunebusinessinsights.com/e-cigarette-and-vaping-market-114882</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Aineiston puute.</t>
+          <t>Minimi 26000000000, maksimi 46320000000; arvioita verrataan, ei summata.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Ei oletuksia.</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Puuttuu</t>
+          <t>Tuoterajaukset ja menetelmät eivät välttämättä ole yhteismitallisia.</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Tuettu</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Lisää allekirjoitetut sopimukset, laskut, maksutositteet ja saamisten täsmäytys.</t>
+          <t>Hanki raporttien täydet metodit ja harmonisoi tuoterajaus.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="78" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei vahvista testituloksia tai riippumatonta teknistä validointia.</t>
+          <t>Saksan vuoden 2025 verotetun nesteen vähittäismyyntivastaavuuden mallihaitari on 667,92–1 654,62 milj. euroa.</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Tekninen erottautuminen</t>
+          <t>Taloudellinen malli</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Patenttiselitys kuvaa ratkaisun; erillistä testirekisteriä ei ole julkisessa datassa.</t>
+          <t>Ei havaittua myyntiä. Laskelma kertoo vuoden 2025 alustavan verotetun nestemäärän kolmella yksittäisellä saksalaisen verkkokaupan vuoden 2026 hinnalla. Vuosiero, yhden kaupan hintakori, tuotejakauma ja pois rajatut tuoteryhmät tekevät luottamustasosta matalan.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>site/data/patent-history.json</t>
+          <t>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003 ; https://www.intaste.de/pfefferminz-liquid-germanflavours-liquid ; https://www.intaste.de/anstand-liquid-samurai-liquid ; https://www.intaste.de/tobacco-vanilla-nikotinsalz-revoltage-liquid</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025 määrä / 2026 hinnat</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Aineiston puute suhteessa tekniseen suorituskykyväitteeseen.</t>
+          <t>volume_litres * 1000 * retail_price_eur_per_ml</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Patenttijulkaisu ei ole tuotetestiraportti.</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Puuttuu</t>
+          <t>Kolme yksittäistä verkkokauppahintaa; syötevuodet 2025 ja 2026; vain verotettu neste.</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Oletus</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Hanki testiprotokolla, riippumaton laboratorio, tulokset ja raakadata.</t>
+          <t>Tarvitaan edustava hintakori, tuotemix ja kanavamarginaalit sekä mallivuoden 2025 hinnat.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="78" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei vahvista piloteja tai nimettyä asiakasnäyttöä.</t>
+          <t>Atlas ei ole vielä lainanantajavalmis markkina-arvio.</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Validointi</t>
+          <t>Rahoitusteesi</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Julkisessa evidenssirekisterissä ei ole pilotti- tai asiakasvalidointia.</t>
+          <t>research_dataset_not_valuation: Useimmista maista puuttuu virallinen vuosittainen laite- ja nestemyynti Markkinaevidenssiä ei ole vielä sidottu maakohtaiseen patenttistatukseen ja claim charteihin Aineisto ei sisällä riippumatonta IVS-arvonmääritystä eikä realisoitunutta lisenssi- tai vahingonkorvauskassavirtaa</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>site/data/evidence.csv</t>
+          <t>site/data/atlas.json (readiness)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Aineiston puute.</t>
+          <t>Julkisen datasetin oma readiness-luokitus.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Ei päätellä asiakkaiden olemassaoloa tai puuttumista yhtiötasolla.</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Puuttuu</t>
+          <t>Markkinadata ja IP-arvo pidetään erillään.</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Lisää allekirjoitetut pilotit, toimitusnäyttö, asiakasreferenssit ja käyttödata.</t>
+          <t>Täytä blocker-lista ennen vakuusarvo- tai yritysarvopäätelmää.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="78" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei vahvista nykyistä maakohtaista omistusta, vuosimaksuja ja rasitteettomuutta koko perheessä.</t>
+          <t>Julkinen aineisto ei sisällä riippumatonta IVS-arvonmääritystä.</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>IP-status</t>
+          <t>Taloudellinen malli</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Perhejulkaisut eivät yksin osoita kansallista post-grant-tilaa.</t>
+          <t>Readiness-blocker ilmoittaa riippumattoman arvonmäärityksen puuttuvan.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=family ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=legal ; https://www.epo.org/en/applying/european/validation</t>
+          <t>site/data/atlas.json (readiness.blockers)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Diligence-rajaus.</t>
+          <t>Aineiston puute.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Neljä kansallista rekisterijurisdiktiota ei kata koko perhettä.</t>
+          <t>Ei oletuksia.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -1931,44 +1931,44 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Laadi asiamiehen allekirjoittama maamatriisi ja liitä tuoreet rekisteriotteet sekä maksukuitit.</t>
+          <t>Tilaa riippumaton IP- ja tarvittaessa yritysarvonmääritys skenaarioineen.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="78" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei sisällä maakohtaisia tuote–vaatimusvertailuja.</t>
+          <t>Julkinen aineisto ei osoita toteutunutta lisenssi- tai vahingonkorvauskassavirtaa.</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Tekninen erottautuminen</t>
+          <t>Kaupallistamismalli</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Patenttihistorian guardrail edellyttää counsel-reviewed claim chartia.</t>
+          <t>Readiness-blocker ilmoittaa realisoituneen kassavirran puuttuvan.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB2/document.pdf ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</t>
+          <t>site/data/atlas.json (readiness.blockers)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Vaatimuspiirteiden tuotekohtainen kartoitus puuttuu.</t>
+          <t>Aineiston puute.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Samankaltaisuus ei ole loukkaus.</t>
+          <t>Ei oletuksia.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1978,232 +1978,232 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Hanki tuotteet, säilytä hallussapitoketju, tee teardown ja asiamiehen tarkastama claim chart.</t>
+          <t>Lisää allekirjoitetut sopimukset, laskut, maksutositteet ja saamisten täsmäytys.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="78" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Markkinan kokonaisarvo ei ole automaattisesti rojaltipohja.</t>
+          <t>Julkinen aineisto ei vahvista testituloksia tai riippumatonta teknistä validointia.</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Taloudellinen malli</t>
+          <t>Tekninen erottautuminen</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Patenttihistorian kaupallistamisrajaus erottaa markkinan, kohdistettavan myynnin ja kassavirran.</t>
+          <t>Patenttiselitys kuvaa ratkaisun; erillistä testirekisteriä ei ole julkisessa datassa.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/en/web/business/ip-valuation</t>
+          <t>site/data/patent-history.json</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Arvonmäärityksen perusrajaus.</t>
+          <t>Aineiston puute suhteessa tekniseen suorituskykyväitteeseen.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Rojaltipohja vaatii patentin maantieteellisen, ajallisen ja tuotekohtaisen osuvuuden.</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Vahvistettu</t>
+          <t>Patenttijulkaisu ei ole tuotetestiraportti.</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Puuttuu</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan addressable/in-scope/claim-mapped sales -silta.</t>
+          <t>Hanki testiprotokolla, riippumaton laboratorio, tulokset ja raakadata.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="78" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Patenttiarvo, yritysarvo, osakearvo ja vakuusarvo ovat eri mittareita.</t>
+          <t>Julkinen aineisto ei vahvista piloteja tai nimettyä asiakasnäyttöä.</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Rahoitusteesi</t>
+          <t>Validointi</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>WIPO:n IP-arvonmääritys- ja rahoituskehys sekä aineiston oma guardrail.</t>
+          <t>Julkisessa evidenssirekisterissä ei ole pilotti- tai asiakasvalidointia.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/en/web/business/ip-valuation ; https://www.wipo.int/en/web/ip-financing</t>
+          <t>site/data/evidence.csv</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Arvokäsitteiden erottelu.</t>
+          <t>Aineiston puute.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Ei oletuksia.</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Vahvistettu</t>
+          <t>Ei päätellä asiakkaiden olemassaoloa tai puuttumista yhtiötasolla.</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Puuttuu</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Rahoitusrakenne ja vakuusarvo vaativat erillisen oikeudellisen ja taloudellisen analyysin.</t>
+          <t>Lisää allekirjoitetut pilotit, toimitusnäyttö, asiakasreferenssit ja käyttödata.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="78" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Asiantuntijavetoinen rajattu lisensointi- tai sovintopilotti on mahdollinen kaupallistamishypoteesi.</t>
+          <t>Julkinen aineisto ei vahvista nykyistä maakohtaista omistusta, vuosimaksuja ja rasitteettomuutta koko perheessä.</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Kaupallistamismalli</t>
+          <t>IP-status</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Patenttihistorian vaiheistus suosittelee kovia portteja, claim chartia ja auditoitavaa yhteydenottoa.</t>
+          <t>Perhejulkaisut eivät yksin osoita kansallista post-grant-tilaa.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/business/settle-ip-disputes ; https://www.epo.org/en/searching-for-patents/business/ipscore</t>
+          <t>https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=family ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=legal ; https://www.epo.org/en/applying/european/validation</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Hypoteesi, ei toteutunut kaupallinen näyttö.</t>
+          <t>Diligence-rajaus.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Kohdemaat ja vastapuolet valitaan vasta oikeus- ja evidenssiporttien jälkeen.</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Oletus</t>
+          <t>Neljä kansallista rekisterijurisdiktiota ei kata koko perhettä.</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Puuttuu</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Hyväksytä pilottimalli johdolla ja patenttiasiantuntijalla; dokumentoi kustannus, vasteet ja termit.</t>
+          <t>Laadi asiamiehen allekirjoittama maamatriisi ja liitä tuoreet rekisteriotteet sekä maksukuitit.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="78" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Patenttivakuudellinen rahoitus on arvioitava vain vahvistettujen oikeuksien ja kassavirtojen pohjalta.</t>
+          <t>Julkinen aineisto ei sisällä maakohtaisia tuote–vaatimusvertailuja.</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Rahoitusteesi</t>
+          <t>Tekninen erottautuminen</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>WIPO IP Finance ja patenttihistorian vaihe 5.</t>
+          <t>Patenttihistorian guardrail edellyttää counsel-reviewed claim chartia.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/en/web/ip-financing ; https://www.wipo.int/en/web/business/ip-valuation</t>
+          <t>https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB2/document.pdf ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Rahoitusperiaate.</t>
+          <t>Vaatimuspiirteiden tuotekohtainen kartoitus puuttuu.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Ei näyttöä olemassa olevasta vakuusarvosta.</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Tuettu</t>
+          <t>Samankaltaisuus ei ole loukkaus.</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Puuttuu</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Tarvitaan riippumaton arvonmääritys, oikeuksien due diligence, toteutuneet tai sopimuspohjaiset kassavirrat ja downside-analyysi.</t>
+          <t>Hanki tuotteet, säilytä hallussapitoketju, tee teardown ja asiamiehen tarkastama claim chart.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="78" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Australian oikeuden seuraava uusiminen on vahvistettava välittömästi.</t>
+          <t>Markkinan kokonaisarvo ei ole automaattisesti rojaltipohja.</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Riskit</t>
+          <t>Taloudellinen malli</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>IP Australian API näyttää GRANTED-tilan, viimeisen uusimismaksun 18.7.2025 ja in-force date -päivän 14.8.2026.</t>
+          <t>Patenttihistorian kaupallistamisrajaus erottaa markkinan, kohdistettavan myynnin ja kassavirran.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://production.api.ipaustralia.gov.au/public/ipright-search-api/v1/patents/2014307829</t>
+          <t>https://www.wipo.int/en/web/business/ip-valuation</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Virallisen API-tiedon diligence-hälytys.</t>
+          <t>Arvonmäärityksen perusrajaus.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>API:n in-force-through-päivä ei ole tässä lakisääteinen eräpäiväväite.</t>
+          <t>Rojaltipohja vaatii patentin maantieteellisen, ajallisen ja tuotekohtaisen osuvuuden.</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2213,44 +2213,44 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Patenttihallinto ja Australian asiamies: vahvistakaa lakisääteinen maksupäivä, summa, maksuvaltuus ja suoritettu maksu; arkistoikaa kuitti ja tuore rekisteriote.</t>
+          <t>Tarvitaan addressable/in-scope/claim-mapped sales -silta.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="78" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Suomen 14. vuosimaksun eräpäiväksi on rekisteröity 31.8.2026.</t>
+          <t>Patenttiarvo, yritysarvo, osakearvo ja vakuusarvo ovat eri mittareita.</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Riskit</t>
+          <t>Rahoitusteesi</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PRH kirjaa 14. vuoden 670 euron maksun eräpäiväksi 31.8.2026 ja myöhäisen maksukauden päättymispäiväksi 28.2.2027.</t>
+          <t>WIPO:n IP-arvonmääritys- ja rahoituskehys sekä aineiston oma guardrail.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://patenttitietopalvelu.prh.fi/en/patent/20135829</t>
+          <t>https://www.wipo.int/en/web/business/ip-valuation ; https://www.wipo.int/en/web/ip-financing</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>PRH:n rekisterihavainto.</t>
+          <t>Arvokäsitteiden erottelu.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Tavoite on maksaa normaalina eräpäivänä.</t>
+          <t>Ei oletuksia.</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2260,296 +2260,296 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Patenttihallinto: maksakaa ennen normaalia eräpäivää ja säilyttäkää maksukuitti sekä päivitetty PRH-ote.</t>
+          <t>Rahoitusrakenne ja vakuusarvo vaativat erillisen oikeudellisen ja taloudellisen analyysin.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="78" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Yhdysvaltain 7,5 vuoden ylläpitomaksun tila on vahvistettava.</t>
+          <t>Asiantuntijavetoinen rajattu lisensointi- tai sovintopilotti on mahdollinen kaupallistamishypoteesi.</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Riskit</t>
+          <t>Kaupallistamismalli</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>USPTO:n ylläpitomaksureitti näyttää normaalimaksuikkunan päättyvän 4.12.2026; maksutilaa ei vahvistettu riippumattomasti tässä julkaisussa.</t>
+          <t>Patenttihistorian vaiheistus suosittelee kovia portteja, claim chartia ja auditoitavaa yhteydenottoa.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923 ; https://patentcenter.uspto.gov/applications/14911851 ; https://assignment.uspto.gov/patent/index.html#/patent/search/resultFilter?searchInput=10306923</t>
+          <t>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/business/settle-ip-disputes ; https://www.epo.org/en/searching-for-patents/business/ipscore</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Virallisen maksuikkunan tarkistus.</t>
+          <t>Hypoteesi, ei toteutunut kaupallinen näyttö.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Julkaisu ei väitä, että maksu on tai ei ole suoritettu.</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Vahvistettu</t>
+          <t>Kohdemaat ja vastapuolet valitaan vasta oikeus- ja evidenssiporttien jälkeen.</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Oletus</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Yhdysvaltain patenttiasiamies: vahvistakaa entity status, summa ja maksu sekä arkistoikaa virallinen kuitti ja tuoreet ylläpito- ja siirtotiedot.</t>
+          <t>Hyväksytä pilottimalli johdolla ja patenttiasiantuntijalla; dokumentoi kustannus, vasteet ja termit.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="78" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei sisällä auditoituja historiallisia tilinpäätöksiä tai kassavirtaennustetta.</t>
+          <t>Patenttivakuudellinen rahoitus on arvioitava vain vahvistettujen oikeuksien ja kassavirtojen pohjalta.</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Taloudellinen malli</t>
+          <t>Rahoitusteesi</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Markkina- ja patenttiaineisto ei ole yhtiön talousaineisto.</t>
+          <t>WIPO IP Finance ja patenttihistorian vaihe 5.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Julkisen paketin rajaus</t>
+          <t>https://www.wipo.int/en/web/ip-financing ; https://www.wipo.int/en/web/business/ip-valuation</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Aineiston puute.</t>
+          <t>Rahoitusperiaate.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Yhtiön taloudellisesta tilanteesta ei tehdä päätelmää.</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>Puuttuu</t>
+          <t>Ei näyttöä olemassa olevasta vakuusarvosta.</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Tuettu</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Lisää 3–5 vuoden tilinpäätökset, tuore pääkirja, budjetti, kassavirta, velat ja verovelkatodistus.</t>
+          <t>Tarvitaan riippumaton arvonmääritys, oikeuksien due diligence, toteutuneet tai sopimuspohjaiset kassavirrat ja downside-analyysi.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei yksilöi rahoitustarvetta, käyttötarkoitusta tai takaisinmaksulähdettä.</t>
+          <t>Australian oikeuden seuraava uusiminen on vahvistettava välittömästi.</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Rahoitusteesi</t>
+          <t>Riskit</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Rahoitusparametreja ei ole markkina- tai patenttidatassa.</t>
+          <t>IP Australian API näyttää GRANTED-tilan, viimeisen uusimismaksun 18.7.2025 ja in-force date -päivän 14.8.2026.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Julkisen paketin rajaus</t>
+          <t>https://production.api.ipaustralia.gov.au/public/ipright-search-api/v1/patents/2014307829</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Aineiston puute.</t>
+          <t>Virallisen API-tiedon diligence-hälytys.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Ei oleteta lainamäärää, maturiteettia tai vakuusrakennetta.</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>Puuttuu</t>
+          <t>API:n in-force-through-päivä ei ole tässä lakisääteinen eräpäiväväite.</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Määritä lainamäärä, käyttötarkoitus, maturiteetti, lyhennysprofiili, takaisinmaksu ja kovenantit.</t>
+          <t>Patenttihallinto ja Australian asiamies: vahvistakaa lakisääteinen maksupäivä, summa, maksuvaltuus ja suoritettu maksu; arkistoikaa kuitti ja tuore rekisteriote.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="78" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei osoita osakekantaa, cap tablea tai osakkeiden rasitteita.</t>
+          <t>Suomen 14. vuosimaksun eräpäiväksi on rekisteröity 31.8.2026.</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Rahoitusteesi</t>
+          <t>Riskit</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Julkinen paketti on rajattu markkina- ja patenttievidenssiin.</t>
+          <t>PRH kirjaa 14. vuoden 670 euron maksun eräpäiväksi 31.8.2026 ja myöhäisen maksukauden päättymispäiväksi 28.2.2027.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Julkisen paketin rajaus</t>
+          <t>https://patenttitietopalvelu.prh.fi/en/patent/20135829</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Aineiston puute.</t>
+          <t>PRH:n rekisterihavainto.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Ei oleteta omistusosuuksia tai vakuuskelpoisuutta.</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>Puuttuu</t>
+          <t>Tavoite on maksaa normaalina eräpäivänä.</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Toimita varmennettu osakasluettelo, yhtiöjärjestys, päätökset, panttaus- ja rasiteselvitys suljettuun datahuoneeseen.</t>
+          <t>Patenttihallinto: maksakaa ennen normaalia eräpäivää ja säilyttäkää maksukuitti sekä päivitetty PRH-ote.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="78" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Julkinen aineisto ei sisällä vertailukelpoista kilpailija- ja vaihtoehtoanalyysiä.</t>
+          <t>Yhdysvaltain 7,5 vuoden ylläpitomaksun tila on vahvistettava.</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Kilpailu</t>
+          <t>Riskit</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Patenttiselitys ja oikeustapaukset eivät yksin muodosta markkinakilpailukarttaa.</t>
+          <t>USPTO:n ylläpitomaksureitti näyttää normaalimaksuikkunan päättyvän 4.12.2026; maksutilaa ei vahvistettu riippumattomasti tässä julkaisussa.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>site/data/patent-history.json</t>
+          <t>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923 ; https://patentcenter.uspto.gov/applications/14911851 ; https://assignment.uspto.gov/patent/index.html#/patent/search/resultFilter?searchInput=10306923</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Aineiston puute.</t>
+          <t>Virallisen maksuikkunan tarkistus.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Kilpailu on erotettava patenttien päällekkäisyydestä ja ei-patentoiduista vaihtoehdoista.</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>Puuttuu</t>
+          <t>Julkaisu ei väitä, että maksu on tai ei ole suoritettu.</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Laadi tuotteet, valmistajat, vaihtoehtoiset teknologiat, patenttiperheet, hinnat ja claim-map-status kattava vertailu.</t>
+          <t>Yhdysvaltain patenttiasiamies: vahvistakaa entity status, summa ja maksu sekä arkistoikaa virallinen kuitti ja tuoreet ylläpito- ja siirtotiedot.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="78" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Asiakassegmentit voidaan alustavasti jäsentää valmistajiin, teknologiatoimittajiin ja IP-rahoittajiin.</t>
+          <t>Julkinen aineisto ei sisällä auditoituja historiallisia tilinpäätöksiä tai kassavirtaennustetta.</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Asiakkaat</t>
+          <t>Taloudellinen malli</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Patenttihistorian kaupallistamisreitit sisältävät lisensoinnin, luovutuksen ja IP-rahoituksen.</t>
+          <t>Markkina- ja patenttiaineisto ei ole yhtiön talousaineisto.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/ip-financing</t>
+          <t>Julkisen paketin rajaus</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Segmentointihypoteesi kaupallistamisreiteistä.</t>
+          <t>Aineiston puute.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Ei todennettua ostoaikomusta tai asiakaskantaa.</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>Oletus</t>
+          <t>Yhtiön taloudellisesta tilanteesta ei tehdä päätelmää.</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Puuttuu</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Validoi 10–15 strukturoitua ostaja- ja rahoittajahaastattelua sekä dokumentoi päätöskriteerit.</t>
+          <t>Lisää 3–5 vuoden tilinpäätökset, tuore pääkirja, budjetti, kassavirta, velat ja verovelkatodistus.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="78" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Saksan ratkaisut voivat toimia evidenssiankkurina, mutta eivät maailmanlaajuisena loukkausratkaisuna.</t>
+          <t>Julkinen aineisto ei yksilöi rahoitustarvetta, käyttötarkoitusta tai takaisinmaksulähdettä.</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2559,185 +2559,373 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Ratkaisut ovat kansallisia, tuote-, osapuoli- ja ajanjaksokohtaisia.</t>
+          <t>Rahoitusparametreja ei ole markkina- tai patenttidatassa.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://www.rechtsprechung-im-internet.de/jportal/?quelle=jlink&amp;docid=JURE269032275&amp;psml=bsjrsprod.psml ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</t>
+          <t>Julkisen paketin rajaus</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Oikeudellisen vaikutuksen alueellinen rajaus.</t>
+          <t>Aineiston puute.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Muiden maiden tulokset riippuvat paikallisista oikeuksista ja tuotteista.</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Vahvistettu</t>
+          <t>Ei oleteta lainamäärää, maturiteettia tai vakuusrakennetta.</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Puuttuu</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Laadi maakohtaiset oikeus- ja claim chart -paketit ennen yhteydenottoja.</t>
+          <t>Määritä lainamäärä, käyttötarkoitus, maturiteetti, lyhennysprofiili, takaisinmaksu ja kovenantit.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="78" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Aineiston A-luokan maita on viisi, mutta 158 maata on D-luokassa.</t>
+          <t>Julkinen aineisto ei osoita osakekantaa, cap tablea tai osakkeiden rasitteita.</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Markkinan koko</t>
+          <t>Rahoitusteesi</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Luokat: A 5, B 13, C 19, D 158.</t>
+          <t>Julkinen paketti on rajattu markkina- ja patenttievidenssiin.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>site/data/atlas.json (summary.gradeCounts)</t>
+          <t>Julkisen paketin rajaus</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Maakohtaisten evidenssiluokkien laskenta.</t>
+          <t>Aineiston puute.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Luokka mittaa evidenssikypsyyttä, ei markkinan houkuttelevuutta.</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Vahvistettu</t>
+          <t>Ei oleteta omistusosuuksia tai vakuuskelpoisuutta.</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Puuttuu</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Priorisoi D-maiden tietopyynnöt talouskoon, patenttistatuksen ja sääntelyn mukaan.</t>
+          <t>Toimita varmennettu osakasluettelo, yhtiöjärjestys, päätökset, panttaus- ja rasiteselvitys suljettuun datahuoneeseen.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="78" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Maailmanlaajuista atlasestimaattia ei ole hyväksytty julkaistavaksi.</t>
+          <t>Julkinen aineisto ei sisällä vertailukelpoista kilpailija- ja vaihtoehtoanalyysiä.</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Markkinan koko</t>
+          <t>Kilpailu</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nolla vertailukelpoista vähittäisarvoluovuttajaa alittaa kolmen luovuttajan minimikynnyksen.</t>
+          <t>Patenttiselitys ja oikeustapaukset eivät yksin muodosta markkinakilpailukarttaa.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>site/data/market-values.json (modelReadiness)</t>
+          <t>site/data/patent-history.json</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Hard gate: vähintään kolme yhteensopivaa luovuttajaa + alueellinen validointi.</t>
+          <t>Aineiston puute.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Kaupallisia globaaliarvioita käytetään vain sanity check -haarukkana.</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Vahvistettu</t>
+          <t>Kilpailu on erotettava patenttien päällekkäisyydestä ja ei-patentoiduista vaihtoehdoista.</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Puuttuu</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Älä esitä yhtä maailmanlukua ennen metodin porttien täyttymistä.</t>
+          <t>Laadi tuotteet, valmistajat, vaihtoehtoiset teknologiat, patenttiperheet, hinnat ja claim-map-status kattava vertailu.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="78" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>Asiakassegmentit voidaan alustavasti jäsentää valmistajiin, teknologiatoimittajiin ja IP-rahoittajiin.</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Asiakkaat</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Patenttihistorian kaupallistamisreitit sisältävät lisensoinnin, luovutuksen ja IP-rahoituksen.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/ip-financing</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Segmentointihypoteesi kaupallistamisreiteistä.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Ei todennettua ostoaikomusta tai asiakaskantaa.</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Oletus</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Validoi 10–15 strukturoitua ostaja- ja rahoittajahaastattelua sekä dokumentoi päätöskriteerit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="78" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Saksan ratkaisut voivat toimia evidenssiankkurina, mutta eivät maailmanlaajuisena loukkausratkaisuna.</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Rahoitusteesi</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Ratkaisut ovat kansallisia, tuote-, osapuoli- ja ajanjaksokohtaisia.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rechtsprechung-im-internet.de/jportal/?quelle=jlink&amp;docid=JURE269032275&amp;psml=bsjrsprod.psml ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Oikeudellisen vaikutuksen alueellinen rajaus.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Muiden maiden tulokset riippuvat paikallisista oikeuksista ja tuotteista.</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Laadi maakohtaiset oikeus- ja claim chart -paketit ennen yhteydenottoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="78" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Aineiston A-luokan maita on viisi, mutta 158 maata on D-luokassa.</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Markkinan koko</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Luokat: A 5, B 13, C 19, D 158.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>site/data/atlas.json (summary.gradeCounts)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Maakohtaisten evidenssiluokkien laskenta.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Luokka mittaa evidenssikypsyyttä, ei markkinan houkuttelevuutta.</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Priorisoi D-maiden tietopyynnöt talouskoon, patenttistatuksen ja sääntelyn mukaan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="78" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Maailmanlaajuista atlasestimaattia ei ole hyväksytty julkaistavaksi.</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Markkinan koko</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Nolla hyväksyttyä luovuttajamarkkinaa alittaa kolmen luovuttajan minimikynnyksen. Julkaistuissa Uuden-Seelannin, EU:n, Kanadan ja Saksan ehdokastesteissä jokaisessa on vähintään yksi hylätty ehto.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Hard gate: jokaisen luovuttajan on läpäistävä D1–D10, ja lisäksi tarvitaan vähintään kolme yhteensopivaa luovuttajaa sekä alueellinen validointi.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Viralliset alarajat ja ulkoiset vertailuarvot ovat hyödyllisiä ristiintarkistuksia mutta niitä ei lasketa hyväksytyiksi luovuttajiksi.</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Vahvistettu</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Älä esitä yhtä maailmanlukua ennen metodin porttien täyttymistä.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="78" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>Korkean luottamuksen rahoituspaketti vaatii suljetun datahuoneen julkisen paketin rinnalle.</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Seuraavat vaiheet</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Julkinen paketti osoittaa lähteet ja puutteet mutta ei sisällä luottamuksellista talous-, sopimus- tai omistusaineistoa.</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Julkisen paketin rajaus</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Diligence-arkkitehtuurin suositus.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Pääsy rajataan ja lokitetaan.</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>Tuettu</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>Perusta indeksoitu datahuone: Corporate, IP, Legal, Commercial, Finance, Valuation, Security.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I46"/>
+  <autoFilter ref="A1:I50"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Vahvistettu,Tuettu,Oletus,Puuttuu"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2779,7 +2967,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026.07.23-16</t>
+          <t>2026.07.24-17</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2979,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -2814,7 +3002,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" ht="23" customHeight="1"/>
@@ -2833,7 +3021,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" ht="23" customHeight="1">
@@ -2843,7 +3031,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
@@ -3114,7 +3302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3586,7 +3774,7 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>EU-TPLF-MAPPING</t>
+          <t>EU-EC-SWD-2025-560</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -3596,66 +3784,66 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>official_policy_study</t>
+          <t>official_secondary</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/strategy-and-policy/policies/justice-and-fundamental-rights/civil-justice/civil-and-commercial-law/third-party-litigation-funding-tplf_en</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2025%3A0560%3AFIN</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>FI-TAX-EXCISE-VVT-010-2025</t>
+          <t>EU-EC-SWD-2026-111</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Finnish Tax Administration</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>official_secondary</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2026%3A111%3AFIN</t>
         </is>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>FORTUNE-GLOBAL-2025</t>
+          <t>EU-TPLF-MAPPING</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Fortune Business Insights</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>commercial_estimate</t>
+          <t>official_policy_study</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>https://www.fortunebusinessinsights.com/e-cigarette-and-vaping-market-114882</t>
+          <t>https://commission.europa.eu/strategy-and-policy/policies/justice-and-fundamental-rights/civil-justice/civil-and-commercial-law/third-party-litigation-funding-tplf_en</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
@@ -3667,22 +3855,22 @@
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>GVR-GLOBAL-2025</t>
+          <t>FI-TAX-EXCISE-VVT-010-2025</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Grand View Research</t>
+          <t>Finnish Tax Administration</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>commercial_estimate</t>
+          <t>official</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>https://www.grandviewresearch.com/industry-analysis/e-cigarette-vaping-market</t>
+          <t>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
@@ -3694,12 +3882,12 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>IMARC-GLOBAL-2025</t>
+          <t>FORTUNE-GLOBAL-2025</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>IMARC Group</t>
+          <t>Fortune Business Insights</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -3709,7 +3897,7 @@
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>https://www.imarcgroup.com/e-cigarette-market</t>
+          <t>https://www.fortunebusinessinsights.com/e-cigarette-and-vaping-market-114882</t>
         </is>
       </c>
       <c r="E22" s="18" t="inlineStr">
@@ -3721,22 +3909,22 @@
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>INTASTE-GERMANFLAVOURS-2026</t>
+          <t>GVR-GLOBAL-2025</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>inTaste.de</t>
+          <t>Grand View Research</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>retail_listing</t>
+          <t>commercial_estimate</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>https://www.intaste.de/pfefferminz-liquid-germanflavours-liquid</t>
+          <t>https://www.grandviewresearch.com/industry-analysis/e-cigarette-vaping-market</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
@@ -3748,22 +3936,22 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>INTASTE-REVOLTAGE-2026</t>
+          <t>IMARC-GLOBAL-2025</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>inTaste.de</t>
+          <t>IMARC Group</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>retail_listing</t>
+          <t>commercial_estimate</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>https://www.intaste.de/tobacco-vanilla-nikotinsalz-revoltage-liquid</t>
+          <t>https://www.imarcgroup.com/e-cigarette-market</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
@@ -3775,7 +3963,7 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>INTASTE-SAMURAI-2026</t>
+          <t>INTASTE-GERMANFLAVOURS-2026</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
@@ -3790,7 +3978,7 @@
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>https://www.intaste.de/anstand-liquid-samurai-liquid</t>
+          <t>https://www.intaste.de/pfefferminz-liquid-germanflavours-liquid</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
@@ -3802,22 +3990,22 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>IPAU-PATENT-API</t>
+          <t>INTASTE-REVOLTAGE-2026</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>IP Australia</t>
+          <t>inTaste.de</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>official_national_api</t>
+          <t>retail_listing</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>https://production.api.ipaustralia.gov.au/public/ipright-search-api/v1/patents/2014307829</t>
+          <t>https://www.intaste.de/tobacco-vanilla-nikotinsalz-revoltage-liquid</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
@@ -3829,22 +4017,22 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>KIPRIS-REGISTER</t>
+          <t>INTASTE-SAMURAI-2026</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>Korean Intellectual Property Office / KIPRIS</t>
+          <t>inTaste.de</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>official_national_register</t>
+          <t>retail_listing</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>https://www.kipris.or.kr/khome/search/searchResult.do</t>
+          <t>https://www.intaste.de/anstand-liquid-samurai-liquid</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
@@ -3856,22 +4044,22 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>PL-SEJM-I07255-O1</t>
+          <t>IPAU-PATENT-API</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Sejm of the Republic of Poland</t>
+          <t>IP Australia</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>official_national_api</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDDEJZ5/i07255-o1.pdf</t>
+          <t>https://production.api.ipaustralia.gov.au/public/ipright-search-api/v1/patents/2014307829</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
@@ -3883,22 +4071,22 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>PL-SEJM-I17526-O1</t>
+          <t>KIPRIS-REGISTER</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Sejm of the Republic of Poland</t>
+          <t>Korean Intellectual Property Office / KIPRIS</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>official_national_register</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr">
         <is>
-          <t>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf</t>
+          <t>https://www.kipris.or.kr/khome/search/searchResult.do</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
@@ -3910,103 +4098,103 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>PRH-FI-REGISTER</t>
+          <t>NZ-MOH-ANNUAL-RETURNS-2022</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Finnish Patent and Registration Office</t>
+          <t>New Zealand Ministry of Health</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>official_national_register</t>
+          <t>official</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>https://patenttitietopalvelu.prh.fi/en/patent/20135829</t>
+          <t>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2022</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>ROSPATENT-REGISTER</t>
+          <t>NZ-MOH-ANNUAL-RETURNS-2023</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>Federal Service for Intellectual Property (Rospatent)</t>
+          <t>New Zealand Ministry of Health</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>official_national_register</t>
+          <t>official</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
         <is>
-          <t>https://new.fips.ru/registers-doc-view/fips_servlet?DB=RUPAT&amp;DocNumber=2600093&amp;TypeFile=html</t>
+          <t>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2023</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>RPAD-KANANEN-2013</t>
+          <t>NZ-MOH-ANNUAL-RETURNS-2024</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>RPad.tv</t>
+          <t>New Zealand Ministry of Health</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>secondary_interview</t>
+          <t>official</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>https://rpad.tv/2013/09/23/vaping-diaries-108-electric-angel-owner-mika-kananen-interview/</t>
+          <t>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>RPX-CN-225669</t>
+          <t>PL-SEJM-I07255-O1</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>RPX Insight</t>
+          <t>Sejm of the Republic of Poland</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>secondary_litigation_database</t>
+          <t>official</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
         <is>
-          <t>https://litigation.rpxcorp.com/china/prb/5153434-picsen-company-v-pixan-oy-of-365</t>
+          <t>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDDEJZ5/i07255-o1.pdf</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
@@ -4018,12 +4206,12 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>SE-GOV-BERAKNINGSKONVENTIONER-2026</t>
+          <t>PL-SEJM-I17526-O1</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Government Offices of Sweden</t>
+          <t>Sejm of the Republic of Poland</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
@@ -4033,7 +4221,7 @@
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf</t>
+          <t>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
@@ -4045,22 +4233,22 @@
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>UPCA-ARTICLE-83</t>
+          <t>PRH-FI-REGISTER</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>European Patent Office / Agreement on a Unified Patent Court</t>
+          <t>Finnish Patent and Registration Office</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>official_treaty_text</t>
+          <t>official_national_register</t>
         </is>
       </c>
       <c r="D35" s="18" t="inlineStr">
         <is>
-          <t>https://www.epo.org/en/legal/up-upc/2022/upca_83.html</t>
+          <t>https://patenttitietopalvelu.prh.fi/en/patent/20135829</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr">
@@ -4072,22 +4260,22 @@
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>USPTO-ASSIGNMENT</t>
+          <t>ROSPATENT-REGISTER</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>United States Patent and Trademark Office</t>
+          <t>Federal Service for Intellectual Property (Rospatent)</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>official_national_assignment_route</t>
+          <t>official_national_register</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
         <is>
-          <t>https://assignment.uspto.gov/patent/index.html#/patent/search/resultFilter?searchInput=10306923</t>
+          <t>https://new.fips.ru/registers-doc-view/fips_servlet?DB=RUPAT&amp;DocNumber=2600093&amp;TypeFile=html</t>
         </is>
       </c>
       <c r="E36" s="18" t="inlineStr">
@@ -4099,22 +4287,22 @@
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>USPTO-MAINTENANCE</t>
+          <t>RPAD-KANANEN-2013</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>United States Patent and Trademark Office</t>
+          <t>RPad.tv</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>official_national_fee_route</t>
+          <t>secondary_interview</t>
         </is>
       </c>
       <c r="D37" s="18" t="inlineStr">
         <is>
-          <t>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923</t>
+          <t>https://rpad.tv/2013/09/23/vaping-diaries-108-electric-angel-owner-mika-kananen-interview/</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr">
@@ -4126,22 +4314,22 @@
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>USPTO-PATENT-CENTER</t>
+          <t>RPX-CN-225669</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>United States Patent and Trademark Office</t>
+          <t>RPX Insight</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>official_national_register_route</t>
+          <t>secondary_litigation_database</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
         <is>
-          <t>https://patentcenter.uspto.gov/applications/14911851</t>
+          <t>https://litigation.rpxcorp.com/china/prb/5153434-picsen-company-v-pixan-oy-of-365</t>
         </is>
       </c>
       <c r="E38" s="18" t="inlineStr">
@@ -4153,22 +4341,22 @@
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>WAYBACK-EA-ABOUT-2012</t>
+          <t>SE-GOV-BERAKNINGSKONVENTIONER-2026</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Electric Angel Oy webpage archived by Internet Archive</t>
+          <t>Government Offices of Sweden</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>archived_company_statement</t>
+          <t>official</t>
         </is>
       </c>
       <c r="D39" s="18" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20121206055248/http://www.electricangel.fi:80/page/4/about-us</t>
+          <t>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr">
@@ -4180,22 +4368,22 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>WAYBACK-EA-INVICTUS-2013</t>
+          <t>UPCA-ARTICLE-83</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Electric Angel Oy webpage archived by Internet Archive</t>
+          <t>European Patent Office / Agreement on a Unified Patent Court</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>archived_company_statement</t>
+          <t>official_treaty_text</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20131216064916/http://www.electricangel.fi:80/news/3/ea-invictus</t>
+          <t>https://www.epo.org/en/legal/up-upc/2022/upca_83.html</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr">
@@ -4207,22 +4395,22 @@
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>WIPO-ASSIGNMENT-LICENSING</t>
+          <t>USPTO-ASSIGNMENT</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>World Intellectual Property Organization</t>
+          <t>United States Patent and Trademark Office</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>official_guidance</t>
+          <t>official_national_assignment_route</t>
         </is>
       </c>
       <c r="D41" s="18" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/ja/web/business/assignment-licensing</t>
+          <t>https://assignment.uspto.gov/patent/index.html#/patent/search/resultFilter?searchInput=10306923</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr">
@@ -4234,22 +4422,22 @@
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>WIPO-DISPUTE-RESOLUTION</t>
+          <t>USPTO-MAINTENANCE</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>World Intellectual Property Organization</t>
+          <t>United States Patent and Trademark Office</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>official_guidance</t>
+          <t>official_national_fee_route</t>
         </is>
       </c>
       <c r="D42" s="18" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/en/web/business/settle-ip-disputes</t>
+          <t>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923</t>
         </is>
       </c>
       <c r="E42" s="18" t="inlineStr">
@@ -4261,22 +4449,22 @@
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>WIPO-IP-FINANCE</t>
+          <t>USPTO-PATENT-CENTER</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>World Intellectual Property Organization</t>
+          <t>United States Patent and Trademark Office</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>official_guidance</t>
+          <t>official_national_register_route</t>
         </is>
       </c>
       <c r="D43" s="18" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/en/web/ip-financing</t>
+          <t>https://patentcenter.uspto.gov/applications/14911851</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr">
@@ -4288,22 +4476,22 @@
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>WIPO-IP-VALUATION</t>
+          <t>WAYBACK-EA-ABOUT-2012</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>World Intellectual Property Organization</t>
+          <t>Electric Angel Oy webpage archived by Internet Archive</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>official_guidance</t>
+          <t>archived_company_statement</t>
         </is>
       </c>
       <c r="D44" s="18" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/en/web/business/ip-valuation</t>
+          <t>https://web.archive.org/web/20121206055248/http://www.electricangel.fi:80/page/4/about-us</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
@@ -4315,22 +4503,22 @@
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>WIPO-PCT-NATIONAL-PHASE</t>
+          <t>WAYBACK-EA-INVICTUS-2013</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>World Intellectual Property Organization</t>
+          <t>Electric Angel Oy webpage archived by Internet Archive</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>official_guidance</t>
+          <t>archived_company_statement</t>
         </is>
       </c>
       <c r="D45" s="18" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/en/web/pct-system/national-phase</t>
+          <t>https://web.archive.org/web/20131216064916/http://www.electricangel.fi:80/news/3/ea-invictus</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
@@ -4342,22 +4530,22 @@
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>YTJ-ELECTRIC-ANGEL</t>
+          <t>WIPO-ASSIGNMENT-LICENSING</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Finnish Patent and Registration Office / Finnish Tax Administration</t>
+          <t>World Intellectual Property Organization</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>official_company_register</t>
+          <t>official_guidance</t>
         </is>
       </c>
       <c r="D46" s="18" t="inlineStr">
         <is>
-          <t>https://avoindata.prh.fi/opendata-ytj-api/v3/companies?businessId=2498114-9</t>
+          <t>https://www.wipo.int/ja/web/business/assignment-licensing</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
@@ -4369,32 +4557,167 @@
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
+          <t>WIPO-DISPUTE-RESOLUTION</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>World Intellectual Property Organization</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>official_guidance</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/en/web/business/settle-ip-disputes</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>WIPO-IP-FINANCE</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>World Intellectual Property Organization</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>official_guidance</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/en/web/ip-financing</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>WIPO-IP-VALUATION</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>World Intellectual Property Organization</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>official_guidance</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/en/web/business/ip-valuation</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>WIPO-PCT-NATIONAL-PHASE</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>World Intellectual Property Organization</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>official_guidance</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/en/web/pct-system/national-phase</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>YTJ-ELECTRIC-ANGEL</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>Finnish Patent and Registration Office / Finnish Tax Administration</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>official_company_register</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>https://avoindata.prh.fi/opendata-ytj-api/v3/companies?businessId=2498114-9</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
           <t>YTJ-PIXAN</t>
         </is>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>Finnish Patent and Registration Office / Finnish Tax Administration</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>official_company_register</t>
         </is>
       </c>
-      <c r="D47" s="18" t="inlineStr">
+      <c r="D52" s="18" t="inlineStr">
         <is>
           <t>https://avoindata.prh.fi/opendata-ytj-api/v3/companies?businessId=2632380-1</t>
         </is>
       </c>
-      <c r="E47" s="18" t="inlineStr">
+      <c r="E52" s="18" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E47"/>
+  <autoFilter ref="A1:E52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Re13344a066a34cb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R7b0f29e6c2eb4edf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R1fe349cd88e243ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R4412913f29a3435f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rbf794580a5734dbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rd6b5ab7867574097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R5076fed3b7614897"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R8a1f085f61b54e98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R81ac2e9ea3404516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Re752d0bb70ee4157"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E72" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EurEquivalentsFI" displayName="EurEquivalentsFI" ref="A1:N38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EurEquivalentsFI" displayName="EurEquivalentsFI" ref="A1:N45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Tietuetyyppi"/>
     <x:tableColumn id="2" name="Tunniste"/>
@@ -870,7 +870,7 @@
     </x:row>
     <x:row r="11" ht="58.5" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>Julkinen paketti sisältää 27 virallisista reiteistä johdettua vuosihavaintoa 7 maasta.</x:v>
+        <x:v>Julkinen paketti sisältää 34 virallisista reiteistä johdettua vuosihavaintoa 7 maasta.</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>Markkinakoko</x:v>
@@ -1160,31 +1160,31 @@
     </x:row>
     <x:row r="21" ht="58.5" customHeight="1">
       <x:c r="A21" s="14" t="str">
-        <x:v>Kanadan vuoden 2024 valmistaja- ja maahantuojatoimitusten arvo oli 1,16075379678 mrd CAD.</x:v>
+        <x:v>Kanadan Statistics Canada -sarja sisältää seitsemän koko vuoden kuluttajavähittäismyyntiestimaattia 2019–2025; vuoden 2024 arvo on 1 219 160 000 CAD.</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Virallinen koko vuoden toimitusarvo tukku- tai vähittäismyyjille kaikissa neljässä raportoidussa tuoteryhmässä. Kyse ei ole kuluttajien vähittäisostoista, ja Health Canada voi tarkistaa tietoa.</x:v>
+        <x:v>Vuosisumma on neljän RCS-vuosineljänneksen summa NAPCS 5619122 -tuoteryhmälle. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusarvo on 1 160 753 796,78 CAD.</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>https://health-infobase.canada.ca/substance-use/vaping/sales/</x:v>
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_RCS_2019_2025_RETAIL_SALES.md</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>Health Canadan neljän raportoidun tuoteryhmän toimitusarvon summa.</x:v>
+        <x:v>1 219 160 000 − 1 160 753 796,78 = 58 406 203,22 CAD; RCS / Health Canada = 1,0503175 eli +5,03 %.</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
-        <x:v>Ei kuluttajavähittäismyyntiä.</x:v>
+        <x:v>Kaikilla vuoden 2024 neljänneksillä on E-laatuvaroitus. Sähkötupakkakohtaista kanavapeittoa ei ole määrällistetty eikä valmisteveroperustaa vahvistettu.</x:v>
       </x:c>
       <x:c r="H21" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
-        <x:v>Tarvitaan vähittäismarginaali-, kanava- ja varastomuutostäsmäytys.</x:v>
+        <x:v>Retail–toimitus-silta ei vielä selitä katetta, varastoa, palautuksia, ajoitusta, tuoterajausta eikä verokäsittelyä; Kanada ei ole hyväksytty donor.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="58.5" customHeight="1">
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc90d9afa03c745a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf468af55f1a048bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.24-18</x:v>
+        <x:v>2026.07.24-19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2257,7 +2257,7 @@
       </x:c>
       <x:c r="B11" s="13" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$54,A11)</x:f>
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20.25" customHeight="1">
@@ -2266,7 +2266,7 @@
       </x:c>
       <x:c r="B12" s="14" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$54,A12)</x:f>
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20.25" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9343ce01ce384432"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26322b30c6ef4fa0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3370,7 +3370,7 @@
     </x:row>
     <x:row r="53" ht="31.5" customHeight="1">
       <x:c r="A53" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-E8408060156E</x:v>
+        <x:v>REGISTER-REFERENCE-BC2CDD0708D5</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3379,7 +3379,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3387,7 +3387,7 @@
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
       <x:c r="A54" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-2FB6E2117AD7</x:v>
+        <x:v>REGISTER-REFERENCE-7264539499F0</x:v>
       </x:c>
       <x:c r="B54" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3396,7 +3396,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3404,7 +3404,7 @@
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
       <x:c r="A55" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-8FEBAD85B03E</x:v>
+        <x:v>REGISTER-REFERENCE-2580DD0733C9</x:v>
       </x:c>
       <x:c r="B55" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3413,7 +3413,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3421,7 +3421,7 @@
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
       <x:c r="A56" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-37CBB91A050A</x:v>
+        <x:v>REGISTER-REFERENCE-38DD93023815</x:v>
       </x:c>
       <x:c r="B56" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3430,7 +3430,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D56" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3438,7 +3438,7 @@
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
       <x:c r="A57" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-54AB30A87D3D</x:v>
+        <x:v>REGISTER-REFERENCE-72D82058EA8A</x:v>
       </x:c>
       <x:c r="B57" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3447,7 +3447,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3455,7 +3455,7 @@
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
       <x:c r="A58" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-4B9D48C385C9</x:v>
+        <x:v>REGISTER-REFERENCE-E8408060156E</x:v>
       </x:c>
       <x:c r="B58" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3464,7 +3464,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D58" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3472,7 +3472,7 @@
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
       <x:c r="A59" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-97704C5CE7D4</x:v>
+        <x:v>REGISTER-REFERENCE-ACB549D404B8</x:v>
       </x:c>
       <x:c r="B59" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3481,7 +3481,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3489,7 +3489,7 @@
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
       <x:c r="A60" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-EF5511CEAE3C</x:v>
+        <x:v>REGISTER-REFERENCE-2FB6E2117AD7</x:v>
       </x:c>
       <x:c r="B60" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3498,7 +3498,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D60" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3506,7 +3506,7 @@
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
       <x:c r="A61" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-15452EF50F15</x:v>
+        <x:v>REGISTER-REFERENCE-8FEBAD85B03E</x:v>
       </x:c>
       <x:c r="B61" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3515,7 +3515,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3523,7 +3523,7 @@
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
       <x:c r="A62" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-9C7C0F0FD33F</x:v>
+        <x:v>REGISTER-REFERENCE-37CBB91A050A</x:v>
       </x:c>
       <x:c r="B62" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3532,7 +3532,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3540,7 +3540,7 @@
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
       <x:c r="A63" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-82A9C0A0E9C4</x:v>
+        <x:v>REGISTER-REFERENCE-54AB30A87D3D</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3549,7 +3549,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3557,7 +3557,7 @@
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
       <x:c r="A64" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-25E2E410922F</x:v>
+        <x:v>REGISTER-REFERENCE-4B9D48C385C9</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3566,7 +3566,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3574,7 +3574,7 @@
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
       <x:c r="A65" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-74211110370B</x:v>
+        <x:v>REGISTER-REFERENCE-97704C5CE7D4</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3583,7 +3583,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3591,7 +3591,7 @@
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
       <x:c r="A66" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
+        <x:v>REGISTER-REFERENCE-EF5511CEAE3C</x:v>
       </x:c>
       <x:c r="B66" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3600,7 +3600,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3608,16 +3608,16 @@
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
       <x:c r="A67" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
+        <x:v>REGISTER-REFERENCE-15452EF50F15</x:v>
       </x:c>
       <x:c r="B67" s="14" t="str">
-        <x:v>data.ecb.europa.eu</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3625,16 +3625,16 @@
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
       <x:c r="A68" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+        <x:v>REGISTER-REFERENCE-9C7C0F0FD33F</x:v>
       </x:c>
       <x:c r="B68" s="14" t="str">
-        <x:v>ecb.europa.eu</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3642,16 +3642,16 @@
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
       <x:c r="A69" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>REGISTER-REFERENCE-82A9C0A0E9C4</x:v>
       </x:c>
       <x:c r="B69" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3659,16 +3659,16 @@
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
       <x:c r="A70" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>REGISTER-REFERENCE-25E2E410922F</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3676,42 +3676,161 @@
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
       <x:c r="A71" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-74211110370B</x:v>
+      </x:c>
+      <x:c r="B71" s="14" t="str">
+        <x:v>data-api.ecb.europa.eu</x:v>
+      </x:c>
+      <x:c r="C71" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D71" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="E71" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="31.5" customHeight="1">
+      <x:c r="A72" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
+      </x:c>
+      <x:c r="B72" s="14" t="str">
+        <x:v>data-api.ecb.europa.eu</x:v>
+      </x:c>
+      <x:c r="C72" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D72" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="E72" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="31.5" customHeight="1">
+      <x:c r="A73" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
+      </x:c>
+      <x:c r="B73" s="14" t="str">
+        <x:v>data.ecb.europa.eu</x:v>
+      </x:c>
+      <x:c r="C73" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D73" s="14" t="str">
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+      </x:c>
+      <x:c r="E73" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="31.5" customHeight="1">
+      <x:c r="A74" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+      </x:c>
+      <x:c r="B74" s="14" t="str">
+        <x:v>ecb.europa.eu</x:v>
+      </x:c>
+      <x:c r="C74" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D74" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="E74" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="31.5" customHeight="1">
+      <x:c r="A75" s="14" t="str">
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+      </x:c>
+      <x:c r="B75" s="14" t="str">
+        <x:v>Federal Trade Commission</x:v>
+      </x:c>
+      <x:c r="C75" s="14" t="str">
+        <x:v>official_report</x:v>
+      </x:c>
+      <x:c r="D75" s="14" t="str">
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+      </x:c>
+      <x:c r="E75" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="31.5" customHeight="1">
+      <x:c r="A76" s="14" t="str">
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="str">
+        <x:v>Federal Trade Commission</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="str">
+        <x:v>official_report</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="str">
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+      </x:c>
+      <x:c r="E76" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="31.5" customHeight="1">
+      <x:c r="A77" s="14" t="str">
         <x:v>UN-MEMBER-STATES</x:v>
       </x:c>
-      <x:c r="B71" s="14" t="str">
+      <x:c r="B77" s="14" t="str">
         <x:v>United Nations</x:v>
       </x:c>
-      <x:c r="C71" s="14" t="str">
+      <x:c r="C77" s="14" t="str">
         <x:v>official_reference</x:v>
       </x:c>
-      <x:c r="D71" s="14" t="str">
+      <x:c r="D77" s="14" t="str">
         <x:v>https://www.un.org/en/about-us/member-states</x:v>
       </x:c>
-      <x:c r="E71" s="14" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" ht="31.5" customHeight="1">
-      <x:c r="A72" s="15" t="str">
+      <x:c r="E77" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="31.5" customHeight="1">
+      <x:c r="A78" s="14" t="str">
         <x:v>UN-NON-MEMBER-STATES</x:v>
       </x:c>
-      <x:c r="B72" s="15" t="str">
+      <x:c r="B78" s="14" t="str">
         <x:v>United Nations</x:v>
       </x:c>
-      <x:c r="C72" s="15" t="str">
+      <x:c r="C78" s="14" t="str">
         <x:v>official_reference</x:v>
       </x:c>
-      <x:c r="D72" s="15" t="str">
+      <x:c r="D78" s="14" t="str">
         <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
       </x:c>
-      <x:c r="E72" s="15" t="str">
+      <x:c r="E78" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="31.5" customHeight="1">
+      <x:c r="A79" s="15" t="str">
+        <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
+      </x:c>
+      <x:c r="B79" s="15" t="str">
+        <x:v>www150.statcan.gc.ca</x:v>
+      </x:c>
+      <x:c r="C79" s="15" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D79" s="15" t="str">
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
+      </x:c>
+      <x:c r="E79" s="15" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e4c21d659424553"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73adae9b0b1d4460"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3830,38 +3949,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>NZ-2022-NOTIFIABLE-PRODUCT-REPORTED-REVENUE</x:v>
+        <x:v>CA-2019-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>official_reported_revenue_mixed_supply_stages</x:v>
+        <x:v>statcan_rcs_vaping_retail_sales</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Canada</x:v>
       </x:c>
       <x:c r="E3" s="14" t="n">
-        <x:v>2022</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G3" s="45" t="n">
-        <x:v>404000000</x:v>
+        <x:v>477077000</x:v>
       </x:c>
       <x:c r="H3" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>CAD</x:v>
       </x:c>
       <x:c r="I3" s="45" t="n">
-        <x:v>1.6582474708171</x:v>
+        <x:v>1.485477254902</x:v>
       </x:c>
       <x:c r="J3" s="45" t="n">
         <x:f>G3/I3</x:f>
-        <x:v>243630704.7710613</x:v>
+        <x:v>321160757.20827764</x:v>
       </x:c>
       <x:c r="K3" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2022</x:v>
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2019</x:v>
       </x:c>
       <x:c r="L3" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M3" s="14" t="str">
         <x:v>computed</x:v>
@@ -3875,38 +3994,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>NZ-2023-NOTIFIABLE-PRODUCT-REPORTED-REVENUE-LOWER-BOUND</x:v>
+        <x:v>CA-2020-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>official_reported_revenue_mixed_supply_stages</x:v>
+        <x:v>statcan_rcs_vaping_retail_sales</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Canada</x:v>
       </x:c>
       <x:c r="E4" s="14" t="n">
-        <x:v>2023</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G4" s="45" t="n">
-        <x:v>374000000</x:v>
+        <x:v>520647000</x:v>
       </x:c>
       <x:c r="H4" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>CAD</x:v>
       </x:c>
       <x:c r="I4" s="45" t="n">
-        <x:v>1.762151372549</x:v>
+        <x:v>1.5299926070039</x:v>
       </x:c>
       <x:c r="J4" s="45" t="n">
         <x:f>G4/I4</x:f>
-        <x:v>212240563.33991262</x:v>
+        <x:v>340293801.1704215</x:v>
       </x:c>
       <x:c r="K4" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2023</x:v>
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2020</x:v>
       </x:c>
       <x:c r="L4" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M4" s="14" t="str">
         <x:v>computed</x:v>
@@ -3920,38 +4039,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>NZ-2024-SPECIALIST-RETAIL-SALES-LOWER-BOUND</x:v>
+        <x:v>CA-2021-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>official_specialist_retail_sales_lower_bound</x:v>
+        <x:v>statcan_rcs_vaping_retail_sales</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Canada</x:v>
       </x:c>
       <x:c r="E5" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G5" s="45" t="n">
-        <x:v>280000000</x:v>
+        <x:v>992732000</x:v>
       </x:c>
       <x:c r="H5" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>CAD</x:v>
       </x:c>
       <x:c r="I5" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.4825689922481</x:v>
       </x:c>
       <x:c r="J5" s="45" t="n">
         <x:f>G5/I5</x:f>
-        <x:v>156595276.14445302</x:v>
+        <x:v>669602565.0008142</x:v>
       </x:c>
       <x:c r="K5" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2021</x:v>
       </x:c>
       <x:c r="L5" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M5" s="14" t="str">
         <x:v>computed</x:v>
@@ -3965,38 +4084,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>NZ-2024-SPECIALIST-RETAIL-PRODUCT-SALES-RAW-FILE-SUM</x:v>
+        <x:v>CA-2022-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>derived_official_workbook_sales_raw_sum</x:v>
+        <x:v>statcan_rcs_vaping_retail_sales</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Canada</x:v>
       </x:c>
       <x:c r="E6" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G6" s="45" t="n">
-        <x:v>280684512.81</x:v>
+        <x:v>1277158000</x:v>
       </x:c>
       <x:c r="H6" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>CAD</x:v>
       </x:c>
       <x:c r="I6" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.3694910505837</x:v>
       </x:c>
       <x:c r="J6" s="45" t="n">
         <x:f>G6/I6</x:f>
-        <x:v>156978102.83197576</x:v>
+        <x:v>932578565.924658</x:v>
       </x:c>
       <x:c r="K6" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2022</x:v>
       </x:c>
       <x:c r="L6" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M6" s="14" t="str">
         <x:v>computed</x:v>
@@ -4010,38 +4129,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>NZ-2024-IDENTIFIED-VAPING-PRODUCT-SALES-RAW-SUM</x:v>
+        <x:v>CA-2023-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>derived_identified_vaping_product_sales_raw_sum</x:v>
+        <x:v>statcan_rcs_vaping_retail_sales</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Canada</x:v>
       </x:c>
       <x:c r="E7" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G7" s="45" t="n">
-        <x:v>274180410.21</x:v>
+        <x:v>1530758000</x:v>
       </x:c>
       <x:c r="H7" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>CAD</x:v>
       </x:c>
       <x:c r="I7" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.459468627451</x:v>
       </x:c>
       <x:c r="J7" s="45" t="n">
         <x:f>G7/I7</x:f>
-        <x:v>153340560.89369413</x:v>
+        <x:v>1048846115.091565</x:v>
       </x:c>
       <x:c r="K7" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2023</x:v>
       </x:c>
       <x:c r="L7" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M7" s="14" t="str">
         <x:v>computed</x:v>
@@ -4055,44 +4174,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>EU-2023-EC-E-CIGARETTE-MARKET-BENCHMARK</x:v>
+        <x:v>CA-2024-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>institutional_market_value_benchmark</x:v>
+        <x:v>statcan_rcs_vaping_retail_sales</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
-        <x:v>European Union</x:v>
+        <x:v>Canada</x:v>
       </x:c>
       <x:c r="E8" s="14" t="n">
-        <x:v>2023</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G8" s="45" t="n">
-        <x:v>4990000000</x:v>
+        <x:v>1219160000</x:v>
       </x:c>
       <x:c r="H8" s="45" t="str">
-        <x:v>EUR</x:v>
+        <x:v>CAD</x:v>
       </x:c>
       <x:c r="I8" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>1.482110546875</x:v>
       </x:c>
       <x:c r="J8" s="45" t="n">
-        <x:f>G8</x:f>
-        <x:v>4990000000</x:v>
+        <x:f>G8/I8</x:f>
+        <x:v>822583715.2097555</x:v>
       </x:c>
       <x:c r="K8" s="14" t="str">
-        <x:v>EUR-IDENTITY</x:v>
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L8" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M8" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>computed</x:v>
       </x:c>
       <x:c r="N8" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="25.5" customHeight="1">
@@ -4100,44 +4219,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
-        <x:v>DE-2023-SUBSTITUTES-EXCISE-RECEIPTS</x:v>
+        <x:v>CA-2025-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>substitutes_excise_receipts</x:v>
+        <x:v>statcan_rcs_vaping_retail_sales</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Canada</x:v>
       </x:c>
       <x:c r="E9" s="14" t="n">
-        <x:v>2023</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G9" s="45" t="n">
-        <x:v>201000000</x:v>
+        <x:v>1266567000</x:v>
       </x:c>
       <x:c r="H9" s="45" t="str">
-        <x:v>EUR</x:v>
+        <x:v>CAD</x:v>
       </x:c>
       <x:c r="I9" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>1.5787262745098</x:v>
       </x:c>
       <x:c r="J9" s="45" t="n">
-        <x:f>G9</x:f>
-        <x:v>201000000</x:v>
+        <x:f>G9/I9</x:f>
+        <x:v>802271438.9758753</x:v>
       </x:c>
       <x:c r="K9" s="14" t="str">
-        <x:v>EUR-IDENTITY</x:v>
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L9" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M9" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>computed</x:v>
       </x:c>
       <x:c r="N9" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="25.5" customHeight="1">
@@ -4145,44 +4264,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>DE-2024-SUBSTITUTES-EXCISE-RECEIPTS</x:v>
+        <x:v>NZ-2022-NOTIFIABLE-PRODUCT-REPORTED-REVENUE</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>substitutes_excise_receipts</x:v>
+        <x:v>official_reported_revenue_mixed_supply_stages</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>New Zealand</x:v>
       </x:c>
       <x:c r="E10" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G10" s="45" t="n">
-        <x:v>266000000</x:v>
+        <x:v>404000000</x:v>
       </x:c>
       <x:c r="H10" s="45" t="str">
-        <x:v>EUR</x:v>
+        <x:v>NZD</x:v>
       </x:c>
       <x:c r="I10" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>1.6582474708171</x:v>
       </x:c>
       <x:c r="J10" s="45" t="n">
-        <x:f>G10</x:f>
-        <x:v>266000000</x:v>
+        <x:f>G10/I10</x:f>
+        <x:v>243630704.7710613</x:v>
       </x:c>
       <x:c r="K10" s="14" t="str">
-        <x:v>EUR-IDENTITY</x:v>
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2022</x:v>
       </x:c>
       <x:c r="L10" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M10" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>computed</x:v>
       </x:c>
       <x:c r="N10" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="25.5" customHeight="1">
@@ -4190,44 +4309,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>DE-2025-SUBSTITUTES-EXCISE-RECEIPTS</x:v>
+        <x:v>NZ-2023-NOTIFIABLE-PRODUCT-REPORTED-REVENUE-LOWER-BOUND</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>substitutes_excise_receipts</x:v>
+        <x:v>official_reported_revenue_mixed_supply_stages</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>New Zealand</x:v>
       </x:c>
       <x:c r="E11" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G11" s="45" t="n">
-        <x:v>404000000</x:v>
+        <x:v>374000000</x:v>
       </x:c>
       <x:c r="H11" s="45" t="str">
-        <x:v>EUR</x:v>
+        <x:v>NZD</x:v>
       </x:c>
       <x:c r="I11" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>1.762151372549</x:v>
       </x:c>
       <x:c r="J11" s="45" t="n">
-        <x:f>G11</x:f>
-        <x:v>404000000</x:v>
+        <x:f>G11/I11</x:f>
+        <x:v>212240563.33991262</x:v>
       </x:c>
       <x:c r="K11" s="14" t="str">
-        <x:v>EUR-IDENTITY</x:v>
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2023</x:v>
       </x:c>
       <x:c r="L11" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M11" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>computed</x:v>
       </x:c>
       <x:c r="N11" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="25.5" customHeight="1">
@@ -4235,44 +4354,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
-        <x:v>FI-2025-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
+        <x:v>NZ-2024-SPECIALIST-RETAIL-SALES-LOWER-BOUND</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>nicotine_e_liquid_excise_receipts</x:v>
+        <x:v>official_specialist_retail_sales_lower_bound</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>Finland</x:v>
+        <x:v>New Zealand</x:v>
       </x:c>
       <x:c r="E12" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G12" s="45" t="n">
-        <x:v>3540319</x:v>
+        <x:v>280000000</x:v>
       </x:c>
       <x:c r="H12" s="45" t="str">
-        <x:v>EUR</x:v>
+        <x:v>NZD</x:v>
       </x:c>
       <x:c r="I12" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>1.788048828125</x:v>
       </x:c>
       <x:c r="J12" s="45" t="n">
-        <x:f>G12</x:f>
-        <x:v>3540319</x:v>
+        <x:f>G12/I12</x:f>
+        <x:v>156595276.14445302</x:v>
       </x:c>
       <x:c r="K12" s="14" t="str">
-        <x:v>EUR-IDENTITY</x:v>
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L12" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M12" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>computed</x:v>
       </x:c>
       <x:c r="N12" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="25.5" customHeight="1">
@@ -4280,38 +4399,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>PL-2025-E-LIQUID-EXCISE-AMOUNT</x:v>
+        <x:v>NZ-2024-SPECIALIST-RETAIL-PRODUCT-SALES-RAW-FILE-SUM</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>e_liquid_excise_amount</x:v>
+        <x:v>derived_official_workbook_sales_raw_sum</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>New Zealand</x:v>
       </x:c>
       <x:c r="E13" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G13" s="45" t="n">
-        <x:v>993100000</x:v>
+        <x:v>280684512.81</x:v>
       </x:c>
       <x:c r="H13" s="45" t="str">
-        <x:v>PLN</x:v>
+        <x:v>NZD</x:v>
       </x:c>
       <x:c r="I13" s="45" t="n">
-        <x:v>4.2396576470588</x:v>
+        <x:v>1.788048828125</x:v>
       </x:c>
       <x:c r="J13" s="45" t="n">
         <x:f>G13/I13</x:f>
-        <x:v>234240611.54771507</x:v>
+        <x:v>156978102.83197576</x:v>
       </x:c>
       <x:c r="K13" s="14" t="str">
-        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L13" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M13" s="14" t="str">
         <x:v>computed</x:v>
@@ -4325,38 +4444,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>PL-2025-VAPING-DEVICE-EXCISE-AMOUNT</x:v>
+        <x:v>NZ-2024-IDENTIFIED-VAPING-PRODUCT-SALES-RAW-SUM</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>vaping_device_excise_amount</x:v>
+        <x:v>derived_identified_vaping_product_sales_raw_sum</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>New Zealand</x:v>
       </x:c>
       <x:c r="E14" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G14" s="45" t="n">
-        <x:v>175300000</x:v>
+        <x:v>274180410.21</x:v>
       </x:c>
       <x:c r="H14" s="45" t="str">
-        <x:v>PLN</x:v>
+        <x:v>NZD</x:v>
       </x:c>
       <x:c r="I14" s="45" t="n">
-        <x:v>4.2396576470588</x:v>
+        <x:v>1.788048828125</x:v>
       </x:c>
       <x:c r="J14" s="45" t="n">
         <x:f>G14/I14</x:f>
-        <x:v>41347678.183782555</x:v>
+        <x:v>153340560.89369413</x:v>
       </x:c>
       <x:c r="K14" s="14" t="str">
-        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L14" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M14" s="14" t="str">
         <x:v>computed</x:v>
@@ -4370,44 +4489,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>PL-2025-VAPING-COMPONENT-SETS-EXCISE-AMOUNT</x:v>
+        <x:v>EU-2023-EC-E-CIGARETTE-MARKET-BENCHMARK</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>vaping_component_sets_excise_amount</x:v>
+        <x:v>institutional_market_value_benchmark</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>European Union</x:v>
       </x:c>
       <x:c r="E15" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G15" s="45" t="n">
-        <x:v>2500000</x:v>
+        <x:v>4990000000</x:v>
       </x:c>
       <x:c r="H15" s="45" t="str">
-        <x:v>PLN</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I15" s="45" t="n">
-        <x:v>4.2396576470588</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="45" t="n">
-        <x:f>G15/I15</x:f>
-        <x:v>589670.2536192606</x:v>
+        <x:f>G15</x:f>
+        <x:v>4990000000</x:v>
       </x:c>
       <x:c r="K15" s="14" t="str">
-        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L15" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M15" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N15" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="25.5" customHeight="1">
@@ -4415,44 +4534,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>SE-2024-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
+        <x:v>DE-2023-SUBSTITUTES-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>nicotine_e_liquid_excise_receipts</x:v>
+        <x:v>substitutes_excise_receipts</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>Sweden</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="E16" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G16" s="45" t="n">
-        <x:v>80000000</x:v>
+        <x:v>201000000</x:v>
       </x:c>
       <x:c r="H16" s="45" t="str">
-        <x:v>SEK</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I16" s="45" t="n">
-        <x:v>11.432519140625</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J16" s="45" t="n">
-        <x:f>G16/I16</x:f>
-        <x:v>6997582.861306848</x:v>
+        <x:f>G16</x:f>
+        <x:v>201000000</x:v>
       </x:c>
       <x:c r="K16" s="14" t="str">
-        <x:v>ECB-EXR-A-SEK-EUR-SP00-A-2024</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L16" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M16" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N16" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="25.5" customHeight="1">
@@ -4460,44 +4579,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>GLOBAL-2025-IMARC-COMMERCIAL-ESTIMATE</x:v>
+        <x:v>DE-2024-SUBSTITUTES-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>commercial_market_estimate</x:v>
+        <x:v>substitutes_excise_receipts</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>Global</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="E17" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>calendar_year_estimate</x:v>
+        <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G17" s="45" t="n">
-        <x:v>26000000000</x:v>
+        <x:v>266000000</x:v>
       </x:c>
       <x:c r="H17" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I17" s="45" t="n">
-        <x:v>1.1299831372549</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J17" s="45" t="n">
-        <x:f>G17/I17</x:f>
-        <x:v>23009192918.721367</x:v>
+        <x:f>G17</x:f>
+        <x:v>266000000</x:v>
       </x:c>
       <x:c r="K17" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L17" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M17" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N17" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="25.5" customHeight="1">
@@ -4505,44 +4624,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>GLOBAL-2025-GVR-COMMERCIAL-ESTIMATE</x:v>
+        <x:v>DE-2025-SUBSTITUTES-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>commercial_market_estimate</x:v>
+        <x:v>substitutes_excise_receipts</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:v>Global</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="E18" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>calendar_year_estimate</x:v>
+        <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G18" s="45" t="n">
-        <x:v>45700000000</x:v>
+        <x:v>404000000</x:v>
       </x:c>
       <x:c r="H18" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I18" s="45" t="n">
-        <x:v>1.1299831372549</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J18" s="45" t="n">
-        <x:f>G18/I18</x:f>
-        <x:v>40443081399.44486</x:v>
+        <x:f>G18</x:f>
+        <x:v>404000000</x:v>
       </x:c>
       <x:c r="K18" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L18" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M18" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N18" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="25.5" customHeight="1">
@@ -4550,44 +4669,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>GLOBAL-2025-FORTUNE-COMMERCIAL-ESTIMATE</x:v>
+        <x:v>FI-2025-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>commercial_market_estimate</x:v>
+        <x:v>nicotine_e_liquid_excise_receipts</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>Global</x:v>
+        <x:v>Finland</x:v>
       </x:c>
       <x:c r="E19" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>calendar_year_estimate</x:v>
+        <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G19" s="45" t="n">
-        <x:v>46320000000</x:v>
+        <x:v>3540319</x:v>
       </x:c>
       <x:c r="H19" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I19" s="45" t="n">
-        <x:v>1.1299831372549</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J19" s="45" t="n">
-        <x:f>G19/I19</x:f>
-        <x:v>40991762153.66052</x:v>
+        <x:f>G19</x:f>
+        <x:v>3540319</x:v>
       </x:c>
       <x:c r="K19" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L19" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M19" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N19" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="25.5" customHeight="1">
@@ -4595,38 +4714,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>US-2015-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2025-E-LIQUID-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>e_liquid_excise_amount</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E20" s="14" t="n">
-        <x:v>2015</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G20" s="45" t="n">
-        <x:v>304170046</x:v>
+        <x:v>993100000</x:v>
       </x:c>
       <x:c r="H20" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I20" s="45" t="n">
-        <x:v>1.109512890625</x:v>
+        <x:v>4.2396576470588</x:v>
       </x:c>
       <x:c r="J20" s="45" t="n">
         <x:f>G20/I20</x:f>
-        <x:v>274147374.5552049</x:v>
+        <x:v>234240611.54771507</x:v>
       </x:c>
       <x:c r="K20" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2015</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L20" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M20" s="14" t="str">
         <x:v>computed</x:v>
@@ -4640,38 +4759,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>US-2016-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2025-VAPING-DEVICE-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>vaping_device_excise_amount</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E21" s="14" t="n">
-        <x:v>2016</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G21" s="45" t="n">
-        <x:v>485707484</x:v>
+        <x:v>175300000</x:v>
       </x:c>
       <x:c r="H21" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I21" s="45" t="n">
-        <x:v>1.1069031128405</x:v>
+        <x:v>4.2396576470588</x:v>
       </x:c>
       <x:c r="J21" s="45" t="n">
         <x:f>G21/I21</x:f>
-        <x:v>438798552.7961817</x:v>
+        <x:v>41347678.183782555</x:v>
       </x:c>
       <x:c r="K21" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2016</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L21" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M21" s="14" t="str">
         <x:v>computed</x:v>
@@ -4685,38 +4804,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>US-2017-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2025-VAPING-COMPONENT-SETS-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>vaping_component_sets_excise_amount</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E22" s="14" t="n">
-        <x:v>2017</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G22" s="45" t="n">
-        <x:v>779836399</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="H22" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I22" s="45" t="n">
-        <x:v>1.1296811764706</x:v>
+        <x:v>4.2396576470588</x:v>
       </x:c>
       <x:c r="J22" s="45" t="n">
         <x:f>G22/I22</x:f>
-        <x:v>690315475.943752</x:v>
+        <x:v>589670.2536192606</x:v>
       </x:c>
       <x:c r="K22" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2017</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L22" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M22" s="14" t="str">
         <x:v>computed</x:v>
@@ -4730,38 +4849,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>US-2018-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>SE-2024-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>nicotine_e_liquid_excise_receipts</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Sweden</x:v>
       </x:c>
       <x:c r="E23" s="14" t="n">
-        <x:v>2018</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G23" s="45" t="n">
-        <x:v>2043703005</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="H23" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>SEK</x:v>
       </x:c>
       <x:c r="I23" s="45" t="n">
-        <x:v>1.1809545098039</x:v>
+        <x:v>11.432519140625</x:v>
       </x:c>
       <x:c r="J23" s="45" t="n">
         <x:f>G23/I23</x:f>
-        <x:v>1730551844.3207107</x:v>
+        <x:v>6997582.861306848</x:v>
       </x:c>
       <x:c r="K23" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2018</x:v>
+        <x:v>ECB-EXR-A-SEK-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L23" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M23" s="14" t="str">
         <x:v>computed</x:v>
@@ -4775,38 +4894,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>US-2019-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>GLOBAL-2025-IMARC-COMMERCIAL-ESTIMATE</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>commercial_market_estimate</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Global</x:v>
       </x:c>
       <x:c r="E24" s="14" t="n">
-        <x:v>2019</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>calendar_year_estimate</x:v>
       </x:c>
       <x:c r="G24" s="45" t="n">
-        <x:v>2702608307</x:v>
+        <x:v>26000000000</x:v>
       </x:c>
       <x:c r="H24" s="45" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="I24" s="45" t="n">
-        <x:v>1.1194745098039</x:v>
+        <x:v>1.1299831372549</x:v>
       </x:c>
       <x:c r="J24" s="45" t="n">
         <x:f>G24/I24</x:f>
-        <x:v>2414175832.796246</x:v>
+        <x:v>23009192918.721367</x:v>
       </x:c>
       <x:c r="K24" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2019</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L24" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M24" s="14" t="str">
         <x:v>computed</x:v>
@@ -4820,38 +4939,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>US-2020-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>GLOBAL-2025-GVR-COMMERCIAL-ESTIMATE</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>commercial_market_estimate</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Global</x:v>
       </x:c>
       <x:c r="E25" s="14" t="n">
-        <x:v>2020</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>calendar_year_estimate</x:v>
       </x:c>
       <x:c r="G25" s="45" t="n">
-        <x:v>2394423105</x:v>
+        <x:v>45700000000</x:v>
       </x:c>
       <x:c r="H25" s="45" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="I25" s="45" t="n">
-        <x:v>1.1421961089494</x:v>
+        <x:v>1.1299831372549</x:v>
       </x:c>
       <x:c r="J25" s="45" t="n">
         <x:f>G25/I25</x:f>
-        <x:v>2096332745.523365</x:v>
+        <x:v>40443081399.44486</x:v>
       </x:c>
       <x:c r="K25" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2020</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L25" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M25" s="14" t="str">
         <x:v>computed</x:v>
@@ -4865,38 +4984,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>US-2021-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>GLOBAL-2025-FORTUNE-COMMERCIAL-ESTIMATE</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>commercial_market_estimate</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Global</x:v>
       </x:c>
       <x:c r="E26" s="14" t="n">
-        <x:v>2021</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>calendar_year_estimate</x:v>
       </x:c>
       <x:c r="G26" s="45" t="n">
-        <x:v>2763284338</x:v>
+        <x:v>46320000000</x:v>
       </x:c>
       <x:c r="H26" s="45" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="I26" s="45" t="n">
-        <x:v>1.1827403100775</x:v>
+        <x:v>1.1299831372549</x:v>
       </x:c>
       <x:c r="J26" s="45" t="n">
         <x:f>G26/I26</x:f>
-        <x:v>2336340711.866778</x:v>
+        <x:v>40991762153.66052</x:v>
       </x:c>
       <x:c r="K26" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2021</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L26" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M26" s="14" t="str">
         <x:v>computed</x:v>
@@ -4907,41 +5026,41 @@
     </x:row>
     <x:row r="27" ht="25.5" customHeight="1">
       <x:c r="A27" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2015-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>low.specialistRetailNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E27" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="F27" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G27" s="45" t="n">
-        <x:v>258327110.88</x:v>
+        <x:v>304170046</x:v>
       </x:c>
       <x:c r="H27" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I27" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.109512890625</x:v>
       </x:c>
       <x:c r="J27" s="45" t="n">
         <x:f>G27/I27</x:f>
-        <x:v>144474304.51375833</x:v>
+        <x:v>274147374.5552049</x:v>
       </x:c>
       <x:c r="K27" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2015</x:v>
       </x:c>
       <x:c r="L27" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M27" s="14" t="str">
         <x:v>computed</x:v>
@@ -4952,41 +5071,41 @@
     </x:row>
     <x:row r="28" ht="25.5" customHeight="1">
       <x:c r="A28" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2016-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>low.generalRetailRpsNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E28" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G28" s="45" t="n">
-        <x:v>275335272.8</x:v>
+        <x:v>485707484</x:v>
       </x:c>
       <x:c r="H28" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I28" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1069031128405</x:v>
       </x:c>
       <x:c r="J28" s="45" t="n">
         <x:f>G28/I28</x:f>
-        <x:v>153986439.55865824</x:v>
+        <x:v>438798552.7961817</x:v>
       </x:c>
       <x:c r="K28" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2016</x:v>
       </x:c>
       <x:c r="L28" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M28" s="14" t="str">
         <x:v>computed</x:v>
@@ -4997,41 +5116,41 @@
     </x:row>
     <x:row r="29" ht="25.5" customHeight="1">
       <x:c r="A29" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2017-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>low.combinedNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E29" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G29" s="45" t="n">
-        <x:v>533662383.68</x:v>
+        <x:v>779836399</x:v>
       </x:c>
       <x:c r="H29" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I29" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1296811764706</x:v>
       </x:c>
       <x:c r="J29" s="45" t="n">
         <x:f>G29/I29</x:f>
-        <x:v>298460744.0724166</x:v>
+        <x:v>690315475.943752</x:v>
       </x:c>
       <x:c r="K29" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2017</x:v>
       </x:c>
       <x:c r="L29" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M29" s="14" t="str">
         <x:v>computed</x:v>
@@ -5042,41 +5161,41 @@
     </x:row>
     <x:row r="30" ht="25.5" customHeight="1">
       <x:c r="A30" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2018-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>base.specialistRetailNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E30" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="F30" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G30" s="45" t="n">
-        <x:v>274180410.21</x:v>
+        <x:v>2043703005</x:v>
       </x:c>
       <x:c r="H30" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I30" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1809545098039</x:v>
       </x:c>
       <x:c r="J30" s="45" t="n">
         <x:f>G30/I30</x:f>
-        <x:v>153340560.89369413</x:v>
+        <x:v>1730551844.3207107</x:v>
       </x:c>
       <x:c r="K30" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2018</x:v>
       </x:c>
       <x:c r="L30" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M30" s="14" t="str">
         <x:v>computed</x:v>
@@ -5087,41 +5206,41 @@
     </x:row>
     <x:row r="31" ht="25.5" customHeight="1">
       <x:c r="A31" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2019-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>base.generalRetailRpsNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E31" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="F31" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G31" s="45" t="n">
-        <x:v>367631277.68</x:v>
+        <x:v>2702608307</x:v>
       </x:c>
       <x:c r="H31" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I31" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1194745098039</x:v>
       </x:c>
       <x:c r="J31" s="45" t="n">
         <x:f>G31/I31</x:f>
-        <x:v>205604719.4558489</x:v>
+        <x:v>2414175832.796246</x:v>
       </x:c>
       <x:c r="K31" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2019</x:v>
       </x:c>
       <x:c r="L31" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M31" s="14" t="str">
         <x:v>computed</x:v>
@@ -5132,41 +5251,41 @@
     </x:row>
     <x:row r="32" ht="25.5" customHeight="1">
       <x:c r="A32" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2020-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>base.combinedNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E32" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="F32" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G32" s="45" t="n">
-        <x:v>641811687.89</x:v>
+        <x:v>2394423105</x:v>
       </x:c>
       <x:c r="H32" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I32" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1421961089494</x:v>
       </x:c>
       <x:c r="J32" s="45" t="n">
         <x:f>G32/I32</x:f>
-        <x:v>358945280.34954304</x:v>
+        <x:v>2096332745.523365</x:v>
       </x:c>
       <x:c r="K32" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2020</x:v>
       </x:c>
       <x:c r="L32" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M32" s="14" t="str">
         <x:v>computed</x:v>
@@ -5177,41 +5296,41 @@
     </x:row>
     <x:row r="33" ht="25.5" customHeight="1">
       <x:c r="A33" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2021-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>high.specialistRetailNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E33" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="F33" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G33" s="45" t="n">
-        <x:v>274180410.21</x:v>
+        <x:v>2763284338</x:v>
       </x:c>
       <x:c r="H33" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I33" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1827403100775</x:v>
       </x:c>
       <x:c r="J33" s="45" t="n">
         <x:f>G33/I33</x:f>
-        <x:v>153340560.89369413</x:v>
+        <x:v>2336340711.866778</x:v>
       </x:c>
       <x:c r="K33" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2021</x:v>
       </x:c>
       <x:c r="L33" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M33" s="14" t="str">
         <x:v>computed</x:v>
@@ -5228,7 +5347,7 @@
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>high.generalRetailRpsNzd</x:v>
+        <x:v>low.specialistRetailNzd</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
         <x:v>New Zealand</x:v>
@@ -5240,7 +5359,7 @@
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G34" s="45" t="n">
-        <x:v>456995382.29</x:v>
+        <x:v>258327110.88</x:v>
       </x:c>
       <x:c r="H34" s="45" t="str">
         <x:v>NZD</x:v>
@@ -5250,7 +5369,7 @@
       </x:c>
       <x:c r="J34" s="45" t="n">
         <x:f>G34/I34</x:f>
-        <x:v>255583278.88015154</x:v>
+        <x:v>144474304.51375833</x:v>
       </x:c>
       <x:c r="K34" s="14" t="str">
         <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
@@ -5273,7 +5392,7 @@
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>high.combinedNzd</x:v>
+        <x:v>low.generalRetailRpsNzd</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
         <x:v>New Zealand</x:v>
@@ -5285,7 +5404,7 @@
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G35" s="45" t="n">
-        <x:v>731175792.5</x:v>
+        <x:v>275335272.8</x:v>
       </x:c>
       <x:c r="H35" s="45" t="str">
         <x:v>NZD</x:v>
@@ -5295,7 +5414,7 @@
       </x:c>
       <x:c r="J35" s="45" t="n">
         <x:f>G35/I35</x:f>
-        <x:v>408923839.7738457</x:v>
+        <x:v>153986439.55865824</x:v>
       </x:c>
       <x:c r="K35" s="14" t="str">
         <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
@@ -5312,137 +5431,452 @@
     </x:row>
     <x:row r="36" ht="25.5" customHeight="1">
       <x:c r="A36" s="14" t="str">
-        <x:v>model</x:v>
+        <x:v>scenario_component</x:v>
       </x:c>
       <x:c r="B36" s="14" t="str">
-        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>low</x:v>
-      </x:c>
-      <x:c r="D36" s="14"/>
+        <x:v>low.combinedNzd</x:v>
+      </x:c>
+      <x:c r="D36" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
       <x:c r="E36" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G36" s="45" t="n">
-        <x:v>667920000</x:v>
+        <x:v>533662383.68</x:v>
       </x:c>
       <x:c r="H36" s="45" t="str">
-        <x:v>EUR</x:v>
+        <x:v>NZD</x:v>
       </x:c>
       <x:c r="I36" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>1.788048828125</x:v>
       </x:c>
       <x:c r="J36" s="45" t="n">
-        <x:f>G36</x:f>
-        <x:v>667920000</x:v>
+        <x:f>G36/I36</x:f>
+        <x:v>298460744.0724166</x:v>
       </x:c>
       <x:c r="K36" s="14" t="str">
-        <x:v>EUR-IDENTITY</x:v>
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L36" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M36" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>computed</x:v>
       </x:c>
       <x:c r="N36" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="25.5" customHeight="1">
       <x:c r="A37" s="14" t="str">
-        <x:v>model</x:v>
+        <x:v>scenario_component</x:v>
       </x:c>
       <x:c r="B37" s="14" t="str">
-        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>central</x:v>
-      </x:c>
-      <x:c r="D37" s="14"/>
+        <x:v>base.specialistRetailNzd</x:v>
+      </x:c>
+      <x:c r="D37" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
       <x:c r="E37" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F37" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G37" s="45" t="n">
+        <x:v>274180410.21</x:v>
+      </x:c>
+      <x:c r="H37" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I37" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J37" s="45" t="n">
+        <x:f>G37/I37</x:f>
+        <x:v>153340560.89369413</x:v>
+      </x:c>
+      <x:c r="K37" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L37" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N37" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="25.5" customHeight="1">
+      <x:c r="A38" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B38" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="str">
+        <x:v>base.generalRetailRpsNzd</x:v>
+      </x:c>
+      <x:c r="D38" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G38" s="45" t="n">
+        <x:v>367631277.68</x:v>
+      </x:c>
+      <x:c r="H38" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I38" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J38" s="45" t="n">
+        <x:f>G38/I38</x:f>
+        <x:v>205604719.4558489</x:v>
+      </x:c>
+      <x:c r="K38" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L38" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N38" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="25.5" customHeight="1">
+      <x:c r="A39" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B39" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="str">
+        <x:v>base.combinedNzd</x:v>
+      </x:c>
+      <x:c r="D39" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G39" s="45" t="n">
+        <x:v>641811687.89</x:v>
+      </x:c>
+      <x:c r="H39" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I39" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J39" s="45" t="n">
+        <x:f>G39/I39</x:f>
+        <x:v>358945280.34954304</x:v>
+      </x:c>
+      <x:c r="K39" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L39" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N39" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="25.5" customHeight="1">
+      <x:c r="A40" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B40" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="str">
+        <x:v>high.specialistRetailNzd</x:v>
+      </x:c>
+      <x:c r="D40" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G40" s="45" t="n">
+        <x:v>274180410.21</x:v>
+      </x:c>
+      <x:c r="H40" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I40" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J40" s="45" t="n">
+        <x:f>G40/I40</x:f>
+        <x:v>153340560.89369413</x:v>
+      </x:c>
+      <x:c r="K40" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L40" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N40" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="25.5" customHeight="1">
+      <x:c r="A41" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B41" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="str">
+        <x:v>high.generalRetailRpsNzd</x:v>
+      </x:c>
+      <x:c r="D41" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G41" s="45" t="n">
+        <x:v>456995382.29</x:v>
+      </x:c>
+      <x:c r="H41" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I41" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J41" s="45" t="n">
+        <x:f>G41/I41</x:f>
+        <x:v>255583278.88015154</x:v>
+      </x:c>
+      <x:c r="K41" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L41" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M41" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N41" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="25.5" customHeight="1">
+      <x:c r="A42" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B42" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="str">
+        <x:v>high.combinedNzd</x:v>
+      </x:c>
+      <x:c r="D42" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G42" s="45" t="n">
+        <x:v>731175792.5</x:v>
+      </x:c>
+      <x:c r="H42" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I42" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J42" s="45" t="n">
+        <x:f>G42/I42</x:f>
+        <x:v>408923839.7738457</x:v>
+      </x:c>
+      <x:c r="K42" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L42" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N42" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="25.5" customHeight="1">
+      <x:c r="A43" s="14" t="str">
+        <x:v>model</x:v>
+      </x:c>
+      <x:c r="B43" s="14" t="str">
+        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="str">
+        <x:v>low</x:v>
+      </x:c>
+      <x:c r="D43" s="14"/>
+      <x:c r="E43" s="14" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G43" s="45" t="n">
+        <x:v>667920000</x:v>
+      </x:c>
+      <x:c r="H43" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I43" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J43" s="45" t="n">
+        <x:f>G43</x:f>
+        <x:v>667920000</x:v>
+      </x:c>
+      <x:c r="K43" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L43" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N43" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="25.5" customHeight="1">
+      <x:c r="A44" s="14" t="str">
+        <x:v>model</x:v>
+      </x:c>
+      <x:c r="B44" s="14" t="str">
+        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="str">
+        <x:v>central</x:v>
+      </x:c>
+      <x:c r="D44" s="14"/>
+      <x:c r="E44" s="14" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G44" s="45" t="n">
         <x:v>1199220000</x:v>
       </x:c>
-      <x:c r="H37" s="45" t="str">
+      <x:c r="H44" s="45" t="str">
         <x:v>EUR</x:v>
       </x:c>
-      <x:c r="I37" s="45" t="n">
+      <x:c r="I44" s="45" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J37" s="45" t="n">
-        <x:f>G37</x:f>
+      <x:c r="J44" s="45" t="n">
+        <x:f>G44</x:f>
         <x:v>1199220000</x:v>
       </x:c>
-      <x:c r="K37" s="14" t="str">
+      <x:c r="K44" s="14" t="str">
         <x:v>EUR-IDENTITY</x:v>
       </x:c>
-      <x:c r="L37" s="14" t="str">
+      <x:c r="L44" s="14" t="str">
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
-      <x:c r="M37" s="14" t="str">
+      <x:c r="M44" s="14" t="str">
         <x:v>already_eur</x:v>
       </x:c>
-      <x:c r="N37" s="14" t="str">
+      <x:c r="N44" s="14" t="str">
         <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="25.5" customHeight="1">
-      <x:c r="A38" s="15" t="str">
+    <x:row r="45" ht="25.5" customHeight="1">
+      <x:c r="A45" s="15" t="str">
         <x:v>model</x:v>
       </x:c>
-      <x:c r="B38" s="15" t="str">
+      <x:c r="B45" s="15" t="str">
         <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="str">
+      <x:c r="C45" s="15" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="D38" s="15"/>
-      <x:c r="E38" s="15" t="n">
+      <x:c r="D45" s="15"/>
+      <x:c r="E45" s="15" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F38" s="15" t="str">
+      <x:c r="F45" s="15" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
-      <x:c r="G38" s="46" t="n">
+      <x:c r="G45" s="46" t="n">
         <x:v>1654620000</x:v>
       </x:c>
-      <x:c r="H38" s="46" t="str">
+      <x:c r="H45" s="46" t="str">
         <x:v>EUR</x:v>
       </x:c>
-      <x:c r="I38" s="46" t="n">
+      <x:c r="I45" s="46" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J38" s="46" t="n">
-        <x:f>G38</x:f>
+      <x:c r="J45" s="46" t="n">
+        <x:f>G45</x:f>
         <x:v>1654620000</x:v>
       </x:c>
-      <x:c r="K38" s="15" t="str">
+      <x:c r="K45" s="15" t="str">
         <x:v>EUR-IDENTITY</x:v>
       </x:c>
-      <x:c r="L38" s="15" t="str">
+      <x:c r="L45" s="15" t="str">
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
-      <x:c r="M38" s="15" t="str">
+      <x:c r="M45" s="15" t="str">
         <x:v>already_eur</x:v>
       </x:c>
-      <x:c r="N38" s="15" t="str">
+      <x:c r="N45" s="15" t="str">
         <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22f2d13c12a44f51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d031557710e4a7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rd6b5ab7867574097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R5076fed3b7614897"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R8a1f085f61b54e98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R81ac2e9ea3404516"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Re752d0bb70ee4157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Recba4cb624b848a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Ra59949488f1c4c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R72f74df590134cbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R9451f709bf79421e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rc98af35b5ee04eac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf468af55f1a048bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1542ba2196094ebb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.24-19</x:v>
+        <x:v>2026.07.24-20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26322b30c6ef4fa0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf96d9af5b9d4fd0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3830,7 +3830,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73adae9b0b1d4460"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R303ebb6150f94ba9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5876,7 +5876,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d031557710e4a7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda67d7e029ff4d91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Recba4cb624b848a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Ra59949488f1c4c3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R72f74df590134cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R9451f709bf79421e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rc98af35b5ee04eac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R2198bceac1c1425b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Rbc950aa267804c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R3816da610ea248ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R65e0d948c27843d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R0c56caf21d404bf2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1542ba2196094ebb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde5cadb1e5ca49e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.24-20</x:v>
+        <x:v>2026.07.24-21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf96d9af5b9d4fd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R616976a2123e4324"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3830,7 +3830,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R303ebb6150f94ba9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R447ef1127c5547fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5876,7 +5876,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda67d7e029ff4d91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa167a56e4ba4443"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R2198bceac1c1425b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Rbc950aa267804c2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R3816da610ea248ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R65e0d948c27843d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R0c56caf21d404bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rac01b668fec14551"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R9457bcb3dba74471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R085be5525a8548b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rfad7af1819c84cc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Ra630f39d2e0c4b16"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -870,13 +870,13 @@
     </x:row>
     <x:row r="11" ht="58.5" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>Julkinen paketti sisältää 34 virallisista reiteistä johdettua vuosihavaintoa 7 maasta.</x:v>
+        <x:v>Julkinen markkina-aineisto sisältää 79 havaintoa 21 lähteestä; 70 virallista havaintoa jakautuvat 34 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>Maat ovat Kanada, Saksa, Suomi, Uusi-Seelanti, Puola, Ruotsi ja Yhdysvallat. Havaintojen transaktiotasot, valuutat ja tuoterajaukset eroavat.</x:v>
+        <x:v>Markkinamittarit kattavat Kanadan, Saksan, Suomen, Uuden-Seelannin, Puolan, Ruotsin ja Yhdysvallat. FHM-luvut kuvaavat vuosien 2018–2026 raportoivia toimijoita sekä ilmoitettuja, aktiivisia ja markkinoilta poistettuja tuotteita; ne eivät ole myyntiä tai markkina-arvoa.</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
         <x:v>site/data/market-values.json (julkisen sivuston koneellisesti luettava lähdetiedosto)</x:v>
@@ -885,10 +885,10 @@
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>Niiden vuosihavaintojen määrä, joiden evidenceStatus alkaa official_-tunnisteella.</x:v>
+        <x:v>79 = 43 aiempaa havaintoa + 36 FHM-rakennelukua; 70 virallista = 34 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>Virallinen julkaisu ei tee mittareista automaattisesti yhteismitallisia.</x:v>
+        <x:v>Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja kalenterivuoden virtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva, ei valmis vuosijakso. Virallinen lähde ei tee eri mittareista yhteismitallisia.</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str">
         <x:v>Vahvistettu</x:v>
@@ -1392,31 +1392,31 @@
     </x:row>
     <x:row r="29" ht="58.5" customHeight="1">
       <x:c r="A29" s="14" t="str">
-        <x:v>Ruotsissa verotettiin 26 000 litraa nikotiininestettä vuonna 2024.</x:v>
+        <x:v>Ruotsin julkinen evidenssi yhdistää vuoden 2024 veroankkurin ja 36 virallista FHM-rekisterirakenteen lukua vuosilta 2018–2026; rekisteriluvut eivät ole myyntiä tai markkina-arvoa.</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>Taulukon 7.5 pyöristetty virallinen määrä. Se kattaa nikotiinillisen sähkösavukenesteen, ei sisällä laitteita tai nikotiinitonta nestettä eikä ole vähittäismarkkina-arvo.</x:v>
+        <x:v>Vuonna 2024 verotettiin 26 000 litraa nikotiininestettä ja valmisteverotulo oli pyöristetysti 80 000 000 SEK. Viranomaisen toimittamassa ja 24.7.2026 tarkistetussa työkirjassa on 9 vuosilabelia × 4 rakennemittaria: raportoivat toimijat sekä ilmoitetut, aktiiviset ja markkinoilta poistetut tuotteet. Julkinen FHM-sivu dokumentoi ilmoitusjärjestelmän, ei siinä julkaistua numeerista sarjaa.</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf</x:v>
+        <x:v>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf ; https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/ ; site/data/market-values.json</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
-        <x:v>Hallituksen laskentaperusteessa ilmoitettu määrä.</x:v>
+        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 34 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>Verotettu nikotiinineste ei kata koko sähkötupakkamarkkinaa.</x:v>
+        <x:v>Rakenneluvuista ei päätellä myyntiarvoa, myyntimäärää tai markkinaosuutta. Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja vuosivirtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva eikä sitä vuositasoiteta.</x:v>
       </x:c>
       <x:c r="H29" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
-        <x:v>Tarvitaan toteutunut vähittäismyynti ja laitedata.</x:v>
+        <x:v>Tarvitaan toteutunut kuluttajamyynti EUR-määräisenä, laitekappaleet ja ml-määrät sekä julkisesti uudelleenkäytettävä numeerinen FHM-sarja.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="58.5" customHeight="1">
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde5cadb1e5ca49e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R043c67e4b017479f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2179,7 +2179,7 @@
   <x:sheetData>
     <x:row r="1" ht="25.5" customHeight="1">
       <x:c r="A1" s="20" t="str">
-        <x:v>Pixan · julkisen evidenssipaketin yhteenveto</x:v>
+        <x:v>Pixan · evidenssipaketin yhteenveto</x:v>
       </x:c>
       <x:c r="B1" s="20"/>
       <x:c r="C1" s="20"/>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.24-21</x:v>
+        <x:v>2026.07.24-22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R616976a2123e4324"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99089116fb25439f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3744,16 +3744,16 @@
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
       <x:c r="A75" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>Public Health Agency of Sweden</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3761,7 +3761,7 @@
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
       <x:c r="A76" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
         <x:v>Federal Trade Commission</x:v>
@@ -3770,7 +3770,7 @@
         <x:v>official_report</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3778,16 +3778,16 @@
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
       <x:c r="A77" s="14" t="str">
-        <x:v>UN-MEMBER-STATES</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -3795,7 +3795,7 @@
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
       <x:c r="A78" s="14" t="str">
-        <x:v>UN-NON-MEMBER-STATES</x:v>
+        <x:v>UN-MEMBER-STATES</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
         <x:v>United Nations</x:v>
@@ -3804,33 +3804,50 @@
         <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+      </x:c>
+      <x:c r="E78" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="31.5" customHeight="1">
+      <x:c r="A79" s="14" t="str">
+        <x:v>UN-NON-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
         <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
       </x:c>
-      <x:c r="E78" s="14" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="31.5" customHeight="1">
-      <x:c r="A79" s="15" t="str">
+      <x:c r="E79" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="31.5" customHeight="1">
+      <x:c r="A80" s="15" t="str">
         <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
       </x:c>
-      <x:c r="B79" s="15" t="str">
+      <x:c r="B80" s="15" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C79" s="15" t="str">
+      <x:c r="C80" s="15" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D79" s="15" t="str">
+      <x:c r="D80" s="15" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
       </x:c>
-      <x:c r="E79" s="15" t="str">
+      <x:c r="E80" s="15" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R447ef1127c5547fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31b637f922964536"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5876,7 +5893,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa167a56e4ba4443"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f3619f67cc4484"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rac01b668fec14551"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R9457bcb3dba74471"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R085be5525a8548b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rfad7af1819c84cc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Ra630f39d2e0c4b16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rd54783d54eec463f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R61f3502a2c664544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="Rbb559e97de874841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R8dfea550760847f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R9611b639b9a74420"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E82" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -1160,60 +1160,60 @@
     </x:row>
     <x:row r="21" ht="58.5" customHeight="1">
       <x:c r="A21" s="14" t="str">
-        <x:v>Kanadan Statistics Canada -sarja sisältää seitsemän koko vuoden kuluttajavähittäismyyntiestimaattia 2019–2025; vuoden 2024 arvo on 1 219 160 000 CAD.</x:v>
+        <x:v>Kanadan virallinen vuoden 2024 kuluttajavähittäismyynnin piste-estimaatti on 1 219 160 000 CAD eli 822 583 715,21 EUR; donor-testi läpäisee 7/10 ehtoa.</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Vuosisumma on neljän RCS-vuosineljänneksen summa NAPCS 5619122 -tuoteryhmälle. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusarvo on 1 160 753 796,78 CAD.</x:v>
+        <x:v>Neljän kvartaalin summa on 1 219 160 000 CAD; 12 kuukauden samaan kyselyyn perustuva summa on 1 219 161 000 CAD. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusten nettoarvo on 1 160 753 796,78 CAD.</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_RCS_2019_2025_RETAIL_SALES.md</x:v>
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>1 219 160 000 − 1 160 753 796,78 = 58 406 203,22 CAD; RCS / Health Canada = 1,0503175 eli +5,03 %.</x:v>
+        <x:v>Kuukausi − kvartaali = 1 000 CAD (0,000082 %). Retail − toimitukset = 58 406 203,22 CAD; retail / toimitukset − 1 = 5,031748 %. ECB 2024: 1 219 160 000 / 1,482110546875 = 822 583 715,21 EUR.</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
-        <x:v>Kaikilla vuoden 2024 neljänneksillä on E-laatuvaroitus. Sähkötupakkakohtaista kanavapeittoa ei ole määrällistetty eikä valmisteveroperustaa vahvistettu.</x:v>
+        <x:v>D8 läpäisee: CAD sekä GST/HST-, provinssi- ja valmisteverojen poissulku on lähteistetty. Kuukausireitti on saman kyselyn QA, ei D10; retail- ja toimitusreitit eivät muodosta markkinahaarukkaa.</x:v>
       </x:c>
       <x:c r="H21" s="14" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
-        <x:v>Retail–toimitus-silta ei vielä selitä katetta, varastoa, palautuksia, ajoitusta, tuoterajausta eikä verokäsittelyä; Kanada ei ole hyväksytty donor.</x:v>
+        <x:v>D5:n NAICS 459993/459999 -peitto, D7:n vuositason virheraja ja D10:n retail–toimitus-silta ovat avoimia; Kanada ei ole hyväksytty donor.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="58.5" customHeight="1">
       <x:c r="A22" s="14" t="str">
-        <x:v>Kanadan vuoden 2024 raportoidut toimitukset sisälsivät 1 251 843 litraa nestettä.</x:v>
+        <x:v>Health Canadan neljä vuoden 2024 tuoteryhmää summautuvat 1 160 753 796,78 CAD:n nettotoimitusarvoon, 118 901 910 yksikköön ja 1 251 843 litraan.</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Höyrystettävää ainetta sisältävien tuoteryhmien ilmoitettu määrä. Se on fyysinen määrä, ei vähittäismarkkina-arvo.</x:v>
+        <x:v>Arvo-osuudet ovat: laite tai osa ilman ainetta 2,602 %, aineen sisältävä laite 48,154 %, aineen sisältävä osa 27,252 % ja höyrystettävä aine 21,992 %. Kyse on toimituksista tukku- tai vähittäismyyjille, ei kuluttajaostoista.</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>https://health-infobase.canada.ca/substance-use/vaping/sales/</x:v>
+        <x:v>https://health-infobase.canada.ca/substance-use/vaping/sales/ ; https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html ; source/CANADA_2024_DONOR_CLOSURE_PACK.md</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
-        <x:v>Raportoitujen nestettä sisältävien tuoteryhmien summa.</x:v>
+        <x:v>30 207 822,87 + 558 947 200,26 + 316 329 158,83 + 255 269 614,82 = 1 160 753 796,78 CAD; osuudet lasketaan tästä summasta.</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>Fyysinen määrä, ei markkina-arvo.</x:v>
+        <x:v>Nettomyynti on myynti vähennettynä palautuksilla ja arvot ilmoitetaan ilman veroja ja maksuja. Nestettä sisältävä laite tai osa yhdistää laite- ja neste-arvoa.</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I22" s="14" t="str">
-        <x:v>Tarvitaan tuotemixin, keskihinnan ja vähittäiskanavan tiedot.</x:v>
+        <x:v>Toimitusosuuksia ei saa soveltaa retail-arvoon laite–neste-jaoksi eikä eri tapahtumatasoja summata.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58.5" customHeight="1">
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R043c67e4b017479f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3010dbca9ab845cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.24-22</x:v>
+        <x:v>2026.07.25-24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2224,7 +2224,7 @@
         <x:v>Päivitetty</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99089116fb25439f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ac6108403ba42c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3382,7 +3382,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
@@ -3399,7 +3399,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
@@ -3416,7 +3416,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
@@ -3433,7 +3433,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
@@ -3450,7 +3450,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
@@ -3467,7 +3467,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
@@ -3484,7 +3484,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
@@ -3501,7 +3501,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
@@ -3518,7 +3518,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
@@ -3535,7 +3535,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
@@ -3552,7 +3552,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
@@ -3569,7 +3569,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
@@ -3586,7 +3586,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
@@ -3603,7 +3603,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
@@ -3620,7 +3620,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
@@ -3637,7 +3637,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
@@ -3654,7 +3654,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
@@ -3671,7 +3671,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
@@ -3688,7 +3688,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
@@ -3705,7 +3705,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
@@ -3722,63 +3722,63 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
       <x:c r="A74" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
-        <x:v>ecb.europa.eu</x:v>
+        <x:v>laws-lois.justice.gc.ca</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
       <x:c r="A75" s="14" t="str">
-        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
+        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
-        <x:v>Public Health Agency of Sweden</x:v>
+        <x:v>ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
       <x:c r="A76" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>Public Health Agency of Sweden</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
       <x:c r="A77" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
         <x:v>Federal Trade Commission</x:v>
@@ -3787,32 +3787,32 @@
         <x:v>official_report</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
       <x:c r="A78" s="14" t="str">
-        <x:v>UN-MEMBER-STATES</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
       <x:c r="A79" s="14" t="str">
-        <x:v>UN-NON-MEMBER-STATES</x:v>
+        <x:v>UN-MEMBER-STATES</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
         <x:v>United Nations</x:v>
@@ -3821,33 +3821,67 @@
         <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+      </x:c>
+      <x:c r="E79" s="14" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="31.5" customHeight="1">
+      <x:c r="A80" s="14" t="str">
+        <x:v>UN-NON-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B80" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C80" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D80" s="14" t="str">
         <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
       </x:c>
-      <x:c r="E79" s="14" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="31.5" customHeight="1">
-      <x:c r="A80" s="15" t="str">
+      <x:c r="E80" s="14" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="31.5" customHeight="1">
+      <x:c r="A81" s="14" t="str">
         <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
       </x:c>
-      <x:c r="B80" s="15" t="str">
+      <x:c r="B81" s="14" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C80" s="15" t="str">
+      <x:c r="C81" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D80" s="15" t="str">
+      <x:c r="D81" s="14" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
       </x:c>
-      <x:c r="E80" s="15" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="E81" s="14" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="31.5" customHeight="1">
+      <x:c r="A82" s="15" t="str">
+        <x:v>REGISTER-REFERENCE-D61AFC87FA19</x:v>
+      </x:c>
+      <x:c r="B82" s="15" t="str">
+        <x:v>www150.statcan.gc.ca</x:v>
+      </x:c>
+      <x:c r="C82" s="15" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D82" s="15" t="str">
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
+      </x:c>
+      <x:c r="E82" s="15" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31b637f922964536"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23ee6bfad0f3490f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5893,7 +5927,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f3619f67cc4484"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R932b199935b04dcb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rd54783d54eec463f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R61f3502a2c664544"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="Rbb559e97de874841"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R8dfea550760847f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R9611b639b9a74420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R94b51e8d202a4396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R043eb794fa7c4449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R74f3a9ac605843d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R7c96e93e183d4063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rf8c4514a95574c1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E82" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E84" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -870,7 +870,7 @@
     </x:row>
     <x:row r="11" ht="58.5" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>Julkinen markkina-aineisto sisältää 79 havaintoa 21 lähteestä; 70 virallista havaintoa jakautuvat 34 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
+        <x:v>Julkinen markkina-aineisto sisältää 79 havaintoa 23 lähteestä; 70 virallista havaintoa jakautuvat 34 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>Markkinakoko</x:v>
@@ -882,7 +882,7 @@
         <x:v>site/data/market-values.json (julkisen sivuston koneellisesti luettava lähdetiedosto)</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
         <x:v>79 = 43 aiempaa havaintoa + 36 FHM-rakennelukua; 70 virallista = 34 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
@@ -911,7 +911,7 @@
         <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
         <x:v>Ehdokas tulee donor-lukuun vain, kun D1–D10 läpäisevät tarkistuksen; hylätty tai avoin ehto pitää sen luvun ulkopuolella.</x:v>
@@ -984,38 +984,38 @@
         <x:v>Raakasumma ei ole puhdistettu kansallinen markkina-arvo. Yleisvähittäiskauppa, puuttuvat ilmoitukset ja GST-käsittely ovat avoimia.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="58.5" customHeight="1">
+    <x:row r="15" ht="93" customHeight="1">
       <x:c r="A15" s="14" t="str">
-        <x:v>Varovainen tekstiluokitus tunnistaa Uuden-Seelannin vuoden 2024 sähkötupakkatuoterivien raakasummaksi 274 180 410,21 NZD.</x:v>
+        <x:v>Uuden-Seelannin vuoden 2024 AIS/AVP-erikoisvähittäiskaupan tunnistettu sähkötupakkasumma on 274 180 410,21 NZD; donor-testi läpäisee 7/10 ehtoa, mutta maa ei ole hyväksytty donor.</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>Viereisiksi ilmoitusvelvollisiksi tuotteiksi tunnistettiin 2 137 085,24 NZD ja ratkaisemattomaksi tuotetyypiksi 4 367 017,37 NZD. Sähkötupakkarivien toistorivien poistamisen herkkyys on 258 327 110,88 NZD, mutta se ei ole korjattu estimaatti.</x:v>
+        <x:v>Kulutustarvikkeet ovat 189 402 451,96 NZD, laitteet/hardware 84 709 409,85 NZD ja sekajärjestelmät 68 548,40 NZD. Viereiset ilmoitusvelvolliset tuotteet 2 137 085,24 NZD ja ratkaisemattomat tuotetyypit 4 367 017,37 NZD määrällistetään erikseen ja rajataan pois. Havaittu arvo tulee vain AIS/AVP-työkirjoista; Notifier- ja RPS-arvoa ei lisätä.</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_ANNUAL_RETURNS_RECONCILIATION.md</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return ; https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf ; source/NZ_2024_DONOR_CLOSURE_PACK.md ; source/NZ_2024_WORKBOOK_MANIFEST.json ; source/NZ_2024_PRODUCT_SCOPE_AUDIT.json ; scripts/analyze_nz_2024_returns.py</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="str">
-        <x:v>Konservatiivinen Product type -tekstiluokitus virallisten XLSX-tiedostojen tuoteriveille; luokittelu- ja toistoriviherkkyys raportoidaan erikseen.</x:v>
+        <x:v>2026-07-26</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="str">
+        <x:v>189 402 451,96 + 84 709 409,85 + 68 548,40 = 274 180 410,21 NZD. Viereiset ja ratkaisemattomat luokat käsitellään ennen vaping-summaa ja jätetään siitä pois. Kaikkien 29 tiedoston URL:t, koot ja SHA-256-tiivisteet validoidaan ennen aggregointia.</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>Tuotetyyppikentän virheet ja ratkaisemattomat rivit estävät kattavan sähkötupakkamarkkinan tulkinnan.</x:v>
+        <x:v>Deterministinen tuoterajaus on julkinen. Yleisvähittäiskaupan havaittu arvo puuttuu, GST-perusta on tuntematon, täsmälleen toistuvien rivien herkkyys ei ole korjattu estimaatti eikä riippumatonta täsmäytystä ole.</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>Hanki viranomaisen tuotekoodisanasto, toistorivien semantiikka, täydellinen kanavapeitto ja GST-perusta. Luku ei kelpaa luovuttajaksi.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="93" customHeight="1">
+        <x:v>D5 hylätään puuttuvan kansallisen kanavapeiton vuoksi; D8:n GST-perusta ja D10:n riippumaton täsmäytys ovat avoimia. Donor-portti pysyy 0/3:ssa.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="58.5" customHeight="1">
       <x:c r="A16" s="14" t="str">
-        <x:v>Uuden-Seelannin vuoden 2024 tunnistetun sähkötupakkavähittäismyynnin tuettu herkkyysväli on 533 662 383,68–731 175 792,50 NZD ja perusskenaario 641 811 687,89 NZD.</x:v>
+        <x:v>Uuden-Seelannin erillinen vuoden 2024 RPS-vähittäisherkkyys on tuettu malli: 533 662 383,68–731 175 792,50 NZD ja perusskenaario 641 811 687,89 NZD.</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
         <x:v>Markkinakoko</x:v>
@@ -1024,12 +1024,12 @@
         <x:v>Matalan, perus- ja korkean skenaarion yhdistetyt arvot ovat 533 662 383,68 / 641 811 687,89 / 731 175 792,50 NZD. Malli yhdistää erikoisvähittäiskaupan ankkurin yleisvähittäiskaupan määrä- ja hintamalliin.</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_RPS_RETAIL_VALUE_SENSITIVITY.md</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_RPS_RETAIL_VALUE_SENSITIVITY.md ; source/NZ_2024_DONOR_CLOSURE_PACK.md</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="str">
         <x:v>Matala (täsmällisten rivien deduplikointi): 258 327 110,88 + 275 335 272,80 = 533 662 383,68 NZD. Perus (raportoidut/raakrivit): 274 180 410,21 + 367 631 277,68 = 641 811 687,89 NZD. Korkea (raportoidut/raakrivit): 274 180 410,21 + 456 995 382,29 = 731 175 792,50 NZD.</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
@@ -1056,7 +1056,7 @@
         <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2023 ; source/NZ_2023_ANNUAL_RETURNS_FAIL_CLOSED.md</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
         <x:v>Kuusi virallista tiedostoa on eheystiivistetty; kaikki uusi laskenta palauttaa tilan not_computed.</x:v>
@@ -1114,7 +1114,7 @@
         <x:v>site/data/evidence-lanes.json ; site/data/donor-cockpit.json ; site/data/country-scenarios.json</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
         <x:v>Fail-closed-portit: puuttuva tai virheellinen syöte tuottaa tilan not_computed eikä nollaa.</x:v>
@@ -2100,7 +2100,7 @@
         <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
         <x:v>Kova portti: jokaisen donorin on läpäistävä D1–D10, ja lisäksi tarvitaan vähintään kolme yhteensopivaa donoria sekä molemmat peittoportit.</x:v>
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3010dbca9ab845cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd40710b4dcac4178"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.25-24</x:v>
+        <x:v>2026.07.26-25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2224,7 +2224,7 @@
         <x:v>Päivitetty</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ac6108403ba42c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R918c954bd0fc438b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3382,7 +3382,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
@@ -3399,7 +3399,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
@@ -3416,7 +3416,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
@@ -3433,7 +3433,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
@@ -3450,7 +3450,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
@@ -3467,7 +3467,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
@@ -3484,7 +3484,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
@@ -3501,7 +3501,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
@@ -3518,7 +3518,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
@@ -3535,7 +3535,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
@@ -3552,7 +3552,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
@@ -3569,7 +3569,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
@@ -3586,7 +3586,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
@@ -3603,7 +3603,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
@@ -3620,7 +3620,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
@@ -3637,7 +3637,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
@@ -3654,7 +3654,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
@@ -3671,7 +3671,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
@@ -3688,7 +3688,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
@@ -3705,7 +3705,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
@@ -3722,7 +3722,7 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
@@ -3739,7 +3739,7 @@
         <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
@@ -3756,7 +3756,7 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
@@ -3773,7 +3773,7 @@
         <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
@@ -3790,7 +3790,7 @@
         <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
@@ -3807,81 +3807,115 @@
         <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
       <x:c r="A79" s="14" t="str">
-        <x:v>UN-MEMBER-STATES</x:v>
+        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="31.5" customHeight="1">
       <x:c r="A80" s="14" t="str">
-        <x:v>UN-NON-MEMBER-STATES</x:v>
+        <x:v>REGISTER-REFERENCE-B5944DDC2320</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+        <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="31.5" customHeight="1">
       <x:c r="A81" s="14" t="str">
+        <x:v>UN-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B81" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+      </x:c>
+      <x:c r="E81" s="14" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="31.5" customHeight="1">
+      <x:c r="A82" s="14" t="str">
+        <x:v>UN-NON-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="31.5" customHeight="1">
+      <x:c r="A83" s="14" t="str">
         <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
       </x:c>
-      <x:c r="B81" s="14" t="str">
+      <x:c r="B83" s="14" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C81" s="14" t="str">
+      <x:c r="C83" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D81" s="14" t="str">
+      <x:c r="D83" s="14" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
       </x:c>
-      <x:c r="E81" s="14" t="str">
-        <x:v>2026-07-25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="31.5" customHeight="1">
-      <x:c r="A82" s="15" t="str">
+      <x:c r="E83" s="14" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="31.5" customHeight="1">
+      <x:c r="A84" s="15" t="str">
         <x:v>REGISTER-REFERENCE-D61AFC87FA19</x:v>
       </x:c>
-      <x:c r="B82" s="15" t="str">
+      <x:c r="B84" s="15" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C82" s="15" t="str">
+      <x:c r="C84" s="15" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D82" s="15" t="str">
+      <x:c r="D84" s="15" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
       </x:c>
-      <x:c r="E82" s="15" t="str">
-        <x:v>2026-07-25</x:v>
+      <x:c r="E84" s="15" t="str">
+        <x:v>2026-07-26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23ee6bfad0f3490f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R745500ba234f466b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5927,7 +5961,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R932b199935b04dcb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb347ebf2efa3451a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R94b51e8d202a4396"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R043eb794fa7c4449"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R74f3a9ac605843d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R7c96e93e183d4063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rf8c4514a95574c1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R09229dd2942b4e44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Rd2a0226c76854e1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R5d99bd19801d44aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R361eaa306a444f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R5d9d891f981c4282"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -882,7 +882,7 @@
         <x:v>site/data/market-values.json (julkisen sivuston koneellisesti luettava lähdetiedosto)</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
         <x:v>79 = 43 aiempaa havaintoa + 36 FHM-rakennelukua; 70 virallista = 34 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
@@ -911,7 +911,7 @@
         <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
         <x:v>Ehdokas tulee donor-lukuun vain, kun D1–D10 läpäisevät tarkistuksen; hylätty tai avoin ehto pitää sen luvun ulkopuolella.</x:v>
@@ -995,10 +995,10 @@
         <x:v>Kulutustarvikkeet ovat 189 402 451,96 NZD, laitteet/hardware 84 709 409,85 NZD ja sekajärjestelmät 68 548,40 NZD. Viereiset ilmoitusvelvolliset tuotteet 2 137 085,24 NZD ja ratkaisemattomat tuotetyypit 4 367 017,37 NZD määrällistetään erikseen ja rajataan pois. Havaittu arvo tulee vain AIS/AVP-työkirjoista; Notifier- ja RPS-arvoa ei lisätä.</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return ; https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf ; source/NZ_2024_DONOR_CLOSURE_PACK.md ; source/NZ_2024_WORKBOOK_MANIFEST.json ; source/NZ_2024_PRODUCT_SCOPE_AUDIT.json ; scripts/analyze_nz_2024_returns.py</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return ; https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf ; source/NZ_2024_DONOR_CLOSURE_PACK.md ; source/NZ_2024_D8_D10_OFFICIAL_SOURCE_AUDIT.md ; source/NZ_2024_WORKBOOK_MANIFEST.json ; source/NZ_2024_PRODUCT_SCOPE_AUDIT.json ; scripts/analyze_nz_2024_returns.py</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F15" s="17" t="str">
         <x:v>189 402 451,96 + 84 709 409,85 + 68 548,40 = 274 180 410,21 NZD. Viereiset ja ratkaisemattomat luokat käsitellään ennen vaping-summaa ja jätetään siitä pois. Kaikkien 29 tiedoston URL:t, koot ja SHA-256-tiivisteet validoidaan ennen aggregointia.</x:v>
@@ -1111,10 +1111,10 @@
         <x:v>Viisi ehdokasta on arvioitu samoilla 10 D1–D10-kriteerillä; yksikään ei ole hyväksytty. Lisäksi alue- ja sääntelytyyppien peittoporttien on läpäistävä tarkistus.</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>site/data/evidence-lanes.json ; site/data/donor-cockpit.json ; site/data/country-scenarios.json</x:v>
+        <x:v>site/data/evidence-lanes.json ; site/data/donor-cockpit.json ; site/data/third-donor-screen.json ; site/data/country-scenarios.json</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
         <x:v>Fail-closed-portit: puuttuva tai virheellinen syöte tuottaa tilan not_computed eikä nollaa.</x:v>
@@ -1169,10 +1169,10 @@
         <x:v>Neljän kvartaalin summa on 1 219 160 000 CAD; 12 kuukauden samaan kyselyyn perustuva summa on 1 219 161 000 CAD. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusten nettoarvo on 1 160 753 796,78 CAD.</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md</x:v>
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md ; source/CANADA_2024_D5_D7_D10_OFFICIAL_SOURCE_AUDIT.md</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
         <x:v>Kuukausi − kvartaali = 1 000 CAD (0,000082 %). Retail − toimitukset = 58 406 203,22 CAD; retail / toimitukset − 1 = 5,031748 %. ECB 2024: 1 219 160 000 / 1,482110546875 = 822 583 715,21 EUR.</x:v>
@@ -2100,7 +2100,7 @@
         <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
         <x:v>Kova portti: jokaisen donorin on läpäistävä D1–D10, ja lisäksi tarvitaan vähintään kolme yhteensopivaa donoria sekä molemmat peittoportit.</x:v>
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd40710b4dcac4178"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ad937c029db4b47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.26-25</x:v>
+        <x:v>2026.07.27-26</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2224,7 +2224,7 @@
         <x:v>Päivitetty</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R918c954bd0fc438b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5faf1eaec6eb40ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3382,7 +3382,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
@@ -3399,7 +3399,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
@@ -3416,7 +3416,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
@@ -3433,7 +3433,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
@@ -3450,7 +3450,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
@@ -3467,7 +3467,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
@@ -3484,7 +3484,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
@@ -3501,7 +3501,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
@@ -3518,7 +3518,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
@@ -3535,7 +3535,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
@@ -3552,7 +3552,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
@@ -3569,7 +3569,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
@@ -3586,7 +3586,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
@@ -3603,7 +3603,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
@@ -3620,7 +3620,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
@@ -3637,7 +3637,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
@@ -3654,7 +3654,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
@@ -3671,7 +3671,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
@@ -3688,7 +3688,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
@@ -3705,7 +3705,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
@@ -3722,7 +3722,7 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
@@ -3739,7 +3739,7 @@
         <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
@@ -3756,7 +3756,7 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
@@ -3773,7 +3773,7 @@
         <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
@@ -3790,7 +3790,7 @@
         <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
@@ -3807,7 +3807,7 @@
         <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
@@ -3824,7 +3824,7 @@
         <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="31.5" customHeight="1">
@@ -3841,7 +3841,7 @@
         <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="31.5" customHeight="1">
@@ -3858,7 +3858,7 @@
         <x:v>https://www.un.org/en/about-us/member-states</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="31.5" customHeight="1">
@@ -3875,7 +3875,7 @@
         <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="31.5" customHeight="1">
@@ -3892,7 +3892,7 @@
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="31.5" customHeight="1">
@@ -3909,13 +3909,13 @@
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
       </x:c>
       <x:c r="E84" s="15" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R745500ba234f466b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bf29edcf0f74dd0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5961,7 +5961,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb347ebf2efa3451a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4d50b41a7d44b43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R09229dd2942b4e44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Rd2a0226c76854e1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R5d99bd19801d44aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R361eaa306a444f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R5d9d891f981c4282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rf227ef55e4eb4d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Red7099d6089f4d34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R1ab675fa2cdb4207"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R4d2f1aef1e3240c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Re4f78ebfffb54c2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E84" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E89" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -841,36 +841,36 @@
     </x:row>
     <x:row r="10" ht="58.5" customHeight="1">
       <x:c r="A10" s="14" t="str">
-        <x:v>Julkinen atlas sisältää muuttumattoman 195 maan tutkimusuniversumin.</x:v>
+        <x:v>Julkinen avoin maapohja sisältää 578 havaittua World Bank -lukua; siinä on 0 sähkötupakkavähittäismyyntihavaintoa.</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
         <x:v>Markkinan rajaus</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>countryCount = 195; universe = UN193+VA+PS.</x:v>
+        <x:v>Väestö ja ikäryhmä 15–64 vuotta kattavat kumpikin 194/195 maata. BKT asukasta kohti kattaa 190/195 maata, ja kaikille 190 havainnolle on laskettu saman lähdevuoden EKP-kurssilla EUR-vasta-arvo. WHO- ja UN Comtrade -reitit ovat 195/195 jonossa ja puuttuvina, eivät nollina; vähittäismyyntiin kelpaavia havaintoja on 0.</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states ; https://www.un.org/en/about-us/non-member-states</x:v>
+        <x:v>site/data/global-base-layer.json ; site/data/global-base-layer.csv ; https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures ; https://www.un.org/en/about-us/member-states ; https://www.un.org/en/about-us/non-member-states</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>193 YK:n jäsenvaltiota + Pyhä istuin + Palestiinan valtio.</x:v>
+        <x:v>Kustakin World Bank -sarjasta valitaan uusin ei-tyhjä havainto vuosilta 2020–2024 ja alkuperäinen lähdevuosi säilytetään. USD/asukas jaetaan vain saman lähdevuoden EKP-kurssilla.</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>Universumi on tutkimusrunko, ei todistettu markkinapeitto.</x:v>
+        <x:v>Väestö, BKT, käyttäjäprevalenssi ja kauppavirrat ovat tausta- tai proxymittareita, eivät sähkötupakkamyynnin arvoja.</x:v>
       </x:c>
       <x:c r="H10" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I10" s="14" t="str">
-        <x:v>Ei puutetta universumin määrittelyssä; evidenssipeitto on erillinen asia.</x:v>
+        <x:v>Maakohtaiset vuosittaiset laite- ja e-nestemyyntiarvot, WHO-reitin numeerinen poiminta ja UN Comtrade -luokituksen validointi puuttuvat.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="58.5" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>Julkinen markkina-aineisto sisältää 79 havaintoa 23 lähteestä; 70 virallista havaintoa jakautuvat 34 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
+        <x:v>Julkinen markkina-aineisto sisältää 84 havaintoa 24 lähteestä; 75 virallista havaintoa jakautuvat 39 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>Markkinakoko</x:v>
@@ -885,7 +885,7 @@
         <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>79 = 43 aiempaa havaintoa + 36 FHM-rakennelukua; 70 virallista = 34 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
+        <x:v>84 = 48 markkina- ja mallihavaintoa + 36 FHM-rakennelukua; 75 virallista = 39 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
         <x:v>Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja kalenterivuoden virtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva, ei valmis vuosijakso. Virallinen lähde ei tee eri mittareista yhteismitallisia.</x:v>
@@ -1334,60 +1334,60 @@
     </x:row>
     <x:row r="27" ht="58.5" customHeight="1">
       <x:c r="A27" s="14" t="str">
-        <x:v>Puolassa raportoitu sähkötupakkanesteiden määrä oli 805 441 litraa vuonna 2023.</x:v>
+        <x:v>Puolan virallinen sähkötupakkanesteiden virta oli 1 451 529 litraa vuonna 2020, 277 265 litraa vuonna 2021, 416 088 litraa vuonna 2022 ja 805 441 litraa vuonna 2023.</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Virallisessa parlamenttivastauksessa ilmoitettu nestemäärä. Se on fyysinen määrä, ei sisällä laitteiden arvoa eikä ole havaittu vähittäismarkkina-arvo.</x:v>
+        <x:v>Ministeriön parlamenttivastauksen taulukko yhdistää ZEFIR2/AIS-järjestelmiin kirjatut kotimaan myynnit, EU-sisäiset hankinnat ja tuonnin. Sarja on fyysinen e-nestevirta, ei kuluttajamyynti tai havaittu vähittäismarkkina-arvo.</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
         <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDDEJZ5/i07255-o1.pdf</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
-        <x:v>2023</x:v>
+        <x:v>2020–2023</x:v>
       </x:c>
       <x:c r="F27" s="14" t="str">
-        <x:v>Parlamentaariseen vastaukseen raportoitu määrä.</x:v>
+        <x:v>Neljän virallisen vuosihavainnon suora toisto; eri vuosia ei summata markkina-arvoksi.</x:v>
       </x:c>
       <x:c r="G27" s="14" t="str">
-        <x:v>Mittarin kattavuus on luettava alkuperäislähteen rajauksin.</x:v>
+        <x:v>Julkaistu taulukko ei erittele kotimaan myyntiä, EU-sisäisiä hankintoja ja tuontia eikä sisällä laitteiden arvoa.</x:v>
       </x:c>
       <x:c r="H27" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I27" s="14" t="str">
-        <x:v>Tarvitaan uudempi vuosisarja ja vähittäisarvo.</x:v>
+        <x:v>Tarvitaan kuluttajavähittäisarvo, kanavapeitto, veroperusta ja riippumaton täsmäytys.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="58.5" customHeight="1">
       <x:c r="A28" s="14" t="str">
-        <x:v>Puolan vuoden 2025 ilmoitettu e-nestevalmisteveron määrä oli 993,1 milj. PLN.</x:v>
+        <x:v>Puolan vuoden 2025 verosilta antaa 4 382 500 johdettua verollista sähkötupakkalaitetta ja 62 500 johdettua verollista osasarjaa.</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>Virallisessa parlamenttivastauksessa ilmoitettu veromäärä. Se ei ole myyntituloa eikä vähittäismarkkina-arvoa, ja se pidetään erillään laitteiden ja osasarjojen veromääristä.</x:v>
+        <x:v>Virallinen parlamenttivastaus raportoi 993,1 milj. PLN e-nesteistä, 175,3 milj. PLN laitteista ja 2,5 milj. PLN osasarjoista. Laitteiden ja osasarjojen vero oli 40 PLN yksiköltä 1.7.2025 alkaen.</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf</x:v>
+        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf ; https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
-        <x:v>Parlamentaariseen vastaukseen raportoitu veromäärä.</x:v>
+        <x:v>175 300 000 / 40 = 4 382 500 verollista laitetta; 2 500 000 / 40 = 62 500 verollista osasarjaa.</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>Veromäärä ei ole vähittäismyynti.</x:v>
+        <x:v>Johdettu veropohja kattaa vain 1.7.2025 alkaen verotetut laitteet ja osasarjat. Se ei osoita kuluttajahintaa, vähittäismyyntiä, verottomia määriä tai varastosiirtymiä.</x:v>
       </x:c>
       <x:c r="H28" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
-        <x:v>Tarvitaan toteuman lopullisuus ja veropohjan täsmäytys.</x:v>
+        <x:v>Tarvitaan veron kuukausijakauma, lopullisuus, vähittäishinnat, kanavapeitto ja riippumaton täsmäytys.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58.5" customHeight="1">
@@ -1407,7 +1407,7 @@
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
-        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 34 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
+        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 39 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
         <x:v>Rakenneluvuista ei päätellä myyntiarvoa, myyntimäärää tai markkinaosuutta. Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja vuosivirtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva eikä sitä vuositasoiteta.</x:v>
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ad937c029db4b47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R331454a2a0f645fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.27-26</x:v>
+        <x:v>2026.07.27-27</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2257,7 +2257,7 @@
       </x:c>
       <x:c r="B11" s="13" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$54,A11)</x:f>
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20.25" customHeight="1">
@@ -2266,7 +2266,7 @@
       </x:c>
       <x:c r="B12" s="14" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$54,A12)</x:f>
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20.25" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5faf1eaec6eb40ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9793b05d44504549"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3693,7 +3693,7 @@
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
       <x:c r="A72" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
+        <x:v>REGISTER-REFERENCE-59446D8EB279</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3702,7 +3702,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3710,16 +3710,16 @@
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
       <x:c r="A73" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
+        <x:v>REGISTER-REFERENCE-BFB2E2E1B4A3</x:v>
       </x:c>
       <x:c r="B73" s="14" t="str">
-        <x:v>data.ecb.europa.eu</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3727,16 +3727,16 @@
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
       <x:c r="A74" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
+        <x:v>REGISTER-REFERENCE-D26C27B033B0</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
-        <x:v>laws-lois.justice.gc.ca</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3744,16 +3744,16 @@
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
       <x:c r="A75" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
-        <x:v>ecb.europa.eu</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3761,16 +3761,16 @@
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
       <x:c r="A76" s="14" t="str">
-        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
+        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
-        <x:v>Public Health Agency of Sweden</x:v>
+        <x:v>data.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3778,16 +3778,16 @@
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
       <x:c r="A77" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>REGISTER-REFERENCE-2DA87527D51F</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>datahelpdesk.worldbank.org</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3795,16 +3795,16 @@
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
       <x:c r="A78" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>laws-lois.justice.gc.ca</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3812,16 +3812,16 @@
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
       <x:c r="A79" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
+        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3829,16 +3829,16 @@
     </x:row>
     <x:row r="80" ht="31.5" customHeight="1">
       <x:c r="A80" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-B5944DDC2320</x:v>
+        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>Public Health Agency of Sweden</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>register_reference</x:v>
+        <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
+        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3846,16 +3846,16 @@
     </x:row>
     <x:row r="81" ht="31.5" customHeight="1">
       <x:c r="A81" s="14" t="str">
-        <x:v>UN-MEMBER-STATES</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3863,16 +3863,16 @@
     </x:row>
     <x:row r="82" ht="31.5" customHeight="1">
       <x:c r="A82" s="14" t="str">
-        <x:v>UN-NON-MEMBER-STATES</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
         <x:v>2026-07-27</x:v>
@@ -3880,42 +3880,127 @@
     </x:row>
     <x:row r="83" ht="31.5" customHeight="1">
       <x:c r="A83" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
+        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
-        <x:v>www150.statcan.gc.ca</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="31.5" customHeight="1">
-      <x:c r="A84" s="15" t="str">
+      <x:c r="A84" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-B5944DDC2320</x:v>
+      </x:c>
+      <x:c r="B84" s="14" t="str">
+        <x:v>health.govt.nz</x:v>
+      </x:c>
+      <x:c r="C84" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D84" s="14" t="str">
+        <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
+      </x:c>
+      <x:c r="E84" s="14" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="31.5" customHeight="1">
+      <x:c r="A85" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
+      </x:c>
+      <x:c r="B85" s="14" t="str">
+        <x:v>podatki.gov.pl</x:v>
+      </x:c>
+      <x:c r="C85" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D85" s="14" t="str">
+        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+      </x:c>
+      <x:c r="E85" s="14" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="31.5" customHeight="1">
+      <x:c r="A86" s="14" t="str">
+        <x:v>UN-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B86" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C86" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D86" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+      </x:c>
+      <x:c r="E86" s="14" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="31.5" customHeight="1">
+      <x:c r="A87" s="14" t="str">
+        <x:v>UN-NON-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B87" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C87" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D87" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+      </x:c>
+      <x:c r="E87" s="14" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="31.5" customHeight="1">
+      <x:c r="A88" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
+      </x:c>
+      <x:c r="B88" s="14" t="str">
+        <x:v>www150.statcan.gc.ca</x:v>
+      </x:c>
+      <x:c r="C88" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D88" s="14" t="str">
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
+      </x:c>
+      <x:c r="E88" s="14" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="31.5" customHeight="1">
+      <x:c r="A89" s="15" t="str">
         <x:v>REGISTER-REFERENCE-D61AFC87FA19</x:v>
       </x:c>
-      <x:c r="B84" s="15" t="str">
+      <x:c r="B89" s="15" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C84" s="15" t="str">
+      <x:c r="C89" s="15" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D84" s="15" t="str">
+      <x:c r="D89" s="15" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
       </x:c>
-      <x:c r="E84" s="15" t="str">
+      <x:c r="E89" s="15" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bf29edcf0f74dd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3287ed1b48543e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5961,7 +6046,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4d50b41a7d44b43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc2008d76cb04add"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rf227ef55e4eb4d56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Red7099d6089f4d34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R1ab675fa2cdb4207"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R4d2f1aef1e3240c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Re4f78ebfffb54c2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R65497c5dbccb424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R97cf25e895254b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R04f8a97717d24067"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rbc7b9bd43cc4479c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R3865d9494f544601"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R331454a2a0f645fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R217c5de96fbc4b80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.27-27</x:v>
+        <x:v>2026.07.27-28</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9793b05d44504549"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf6af0b251994cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4000,7 +4000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3287ed1b48543e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc98cf2da507a420e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6046,7 +6046,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc2008d76cb04add"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6152c8429f244dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R65497c5dbccb424f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R97cf25e895254b63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R04f8a97717d24067"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rbc7b9bd43cc4479c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R3865d9494f544601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R41208254da1c4697"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R1ae4ad48ab204573"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R4ac9bd8281944227"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R923762d66c384e18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rb63db5a9999f4133"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R217c5de96fbc4b80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bfc21523a6e4166"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.27-28</x:v>
+        <x:v>2026.07.27-29</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf6af0b251994cdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1779380b7ad44386"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4000,7 +4000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc98cf2da507a420e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd12cfe5a0475478b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6046,7 +6046,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6152c8429f244dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a955ea1f6e425b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R41208254da1c4697"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R1ae4ad48ab204573"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R4ac9bd8281944227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R923762d66c384e18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rb63db5a9999f4133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rcc08e05a5f22443f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R9fb6fafcfcdd4727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R670b4f1c130e44d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R47a4088282a44271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R2bcd95653aa94bca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bfc21523a6e4166"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd43488d06c34cc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1779380b7ad44386"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R732723de12dc4702"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4000,7 +4000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd12cfe5a0475478b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reba89781e37b49a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6046,7 +6046,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a955ea1f6e425b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9f4daa69a84468c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R65497c5dbccb424f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R97cf25e895254b63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R04f8a97717d24067"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rbc7b9bd43cc4479c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R3865d9494f544601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rcc08e05a5f22443f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R9fb6fafcfcdd4727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R670b4f1c130e44d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R47a4088282a44271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R2bcd95653aa94bca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2158,7 +2158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R217c5de96fbc4b80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd43488d06c34cc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2216,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.27-28</x:v>
+        <x:v>2026.07.27-29</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2468,7 +2468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf6af0b251994cdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R732723de12dc4702"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4000,7 +4000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc98cf2da507a420e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reba89781e37b49a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6046,7 +6046,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6152c8429f244dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9f4daa69a84468c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rcc08e05a5f22443f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R9fb6fafcfcdd4727"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R670b4f1c130e44d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R47a4088282a44271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R2bcd95653aa94bca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R4943de0902264aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R8c121ca5014f442f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R7284d4de90954458"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R7017d93aed7f414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R0be63e4b8e0c44fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -308,8 +308,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EvidenceRegisterFI" displayName="EvidenceRegisterFI" ref="A1:I54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EvidenceRegisterFI" displayName="EvidenceRegisterFI" ref="A1:I55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I55"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Väite"/>
     <x:tableColumn id="2" name="Dia/osio"/>
@@ -870,448 +870,448 @@
     </x:row>
     <x:row r="11" ht="58.5" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>Julkinen markkina-aineisto sisältää 84 havaintoa 24 lähteestä; 75 virallista havaintoa jakautuvat 39 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
+        <x:v>195 maan menetelmäkontrolli erottaa 23 tarkistettua maasuunnitelmaa, 5 tarkistettua lähdepolkua, 15 alueellista EU TPD -raportointimallia ja 152 maakohtaisesti rajaamatonta proxy-reittiä.</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinan rajaus</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>Markkinamittarit kattavat Kanadan, Saksan, Suomen, Uuden-Seelannin, Puolan, Ruotsin ja Yhdysvallat. FHM-luvut kuvaavat vuosien 2018–2026 raportoivia toimijoita sekä ilmoitettuja, aktiivisia ja markkinoilta poistettuja tuotteita; ne eivät ole myyntiä tai markkina-arvoa.</x:v>
+        <x:v>Jokaisella maalla on näkyvä menetelmäluokka, seuraava evidenssitoimi ja lähdeperusta. Luokitus ei ole myyntihavainto: kaikilla 195 maalla eligibleForGlobalRollup=false ja donorAccepted=false.</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>site/data/market-values.json (julkisen sivuston koneellisesti luettava lähdetiedosto)</x:v>
+        <x:v>site/data/global-base-layer.json ; source/country-method-route-config.json ; source/COUNTRY_METHOD_ROUTE_MAP.md</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>84 = 48 markkina- ja mallihavaintoa + 36 FHM-rakennelukua; 75 virallista = 39 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
+        <x:v>195 = 23 reviewed_method_plan + 5 reviewed_source_lead + 15 regional_tpd_pattern_only + 152 proxy_only_unscoped.</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja kalenterivuoden virtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva, ei valmis vuosijakso. Virallinen lähde ei tee eri mittareista yhteismitallisia.</x:v>
+        <x:v>Vain 23 maalla on tarkistettu maakohtainen menetelmäsuunnitelma. Viisi lähdepolkua ja 15 alueellista TPD-mallia eivät osoita kansallista myyntisarjaa; 152 reittiä vaatii maakohtaisen rajauksen.</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I11" s="14" t="str">
-        <x:v>Lisämaista tarvitaan yhteismitalliset vuotuiset laite- ja nestemäisen kuluttajavähittäisarvon sarjat.</x:v>
+        <x:v>Yksikään menetelmäluokka ei korvaa vuosittaista laite- ja e-nestemyynnin arvoa, veroperustaa, kanavapeittoa tai D1–D10-hyväksyntää.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="58.5" customHeight="1">
       <x:c r="A12" s="14" t="str">
-        <x:v>Hyväksyttyjä virallisia koko vuoden kansallisia kuluttajavähittäisarvon luovuttajamarkkinoita on nolla.</x:v>
+        <x:v>Julkinen markkina-aineisto sisältää 84 havaintoa 24 lähteestä; 75 virallista havaintoa jakautuvat 39 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>comparableFullYearMarketValueDonors = 0. Viisi ehdokasta on julkaistu samaa kymmenen ehdon protokollaa vasten.</x:v>
+        <x:v>Markkinamittarit kattavat Kanadan, Saksan, Suomen, Uuden-Seelannin, Puolan, Ruotsin ja Yhdysvallat. FHM-luvut kuvaavat vuosien 2018–2026 raportoivia toimijoita sekä ilmoitettuja, aktiivisia ja markkinoilta poistettuja tuotteita; ne eivät ole myyntiä tai markkina-arvoa.</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
+        <x:v>site/data/market-values.json (julkisen sivuston koneellisesti luettava lähdetiedosto)</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>Ehdokas tulee donor-lukuun vain, kun D1–D10 läpäisevät tarkistuksen; hylätty tai avoin ehto pitää sen luvun ulkopuolella.</x:v>
+        <x:v>84 = 48 markkina- ja mallihavaintoa + 36 FHM-rakennelukua; 75 virallista = 39 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>Virallisia alarajoja, institutionaalisia vertailuarvoja, toimitusarvoja, veroja, fyysisiä määriä ja malleja ei nimetä täydelliseksi kuluttajavähittäisarvoksi.</x:v>
+        <x:v>Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja kalenterivuoden virtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva, ei valmis vuosijakso. Virallinen lähde ei tee eri mittareista yhteismitallisia.</x:v>
       </x:c>
       <x:c r="H12" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I12" s="14" t="str">
-        <x:v>Tarvitaan vähintään kolme hyväksyttyä donoria sekä alue- ja sääntelytyyppien peitto.</x:v>
+        <x:v>Lisämaista tarvitaan yhteismitalliset vuotuiset laite- ja nestemäisen kuluttajavähittäisarvon sarjat.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58.5" customHeight="1">
       <x:c r="A13" s="14" t="str">
-        <x:v>Uuden-Seelannin vuoden 2024 erikoistuneiden sähkötupakkakauppiaiden myynniksi ilmoitettiin vähintään 280 milj. NZD.</x:v>
+        <x:v>Hyväksyttyjä virallisia koko vuoden kansallisia kuluttajavähittäisarvon luovuttajamarkkinoita on nolla.</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>Terveysministeriö julkaisee virallisen kuluttajavähittäismyynnin alarajan, joka perustuu vain puutteellisiin erikoistuneiden sähkötupakkakauppiaiden myynteihin. Yleisvähittäiskauppa puuttuu, viereisiä ilmoitusvelvollisia tuotteita sisältyy eikä ministeriö suosittele aineistoa perusteelliseen tutkimukseen.</x:v>
+        <x:v>comparableFullYearMarketValueDonors = 0. Viisi ehdokasta on julkaistu samaa kymmenen ehdon protokollaa vasten.</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024</x:v>
+        <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>Virallista vähintään-otsikkolukua käytetään suoraan; ei ekstrapolointia eikä muiden palautustyyppien yhteenlaskua.</x:v>
+        <x:v>Ehdokas tulee donor-lukuun vain, kun D1–D10 läpäisevät tarkistuksen; hylätty tai avoin ehto pitää sen luvun ulkopuolella.</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>Luku on alaraja, ei koko maan sähkötupakkamarkkinan arvo.</x:v>
+        <x:v>Virallisia alarajoja, institutionaalisia vertailuarvoja, toimitusarvoja, veroja, fyysisiä määriä ja malleja ei nimetä täydelliseksi kuluttajavähittäisarvoksi.</x:v>
       </x:c>
       <x:c r="H13" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I13" s="14" t="str">
-        <x:v>Hanki täydellinen valtakunnallinen vain sähkötupakkatuotteita koskeva vähittäiskaupan koonti, GST-perusta ja riippumaton täsmäytys.</x:v>
+        <x:v>Tarvitaan vähintään kolme hyväksyttyä donoria sekä alue- ja sääntelytyyppien peitto.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="58.5" customHeight="1">
       <x:c r="A14" s="14" t="str">
-        <x:v>Uuden-Seelannin 29 virallisen vuoden 2024 XLSX-tiedoston 612 765 numeerisen Total sales -solun raakasumma on 280 684 512,81 NZD.</x:v>
+        <x:v>Uuden-Seelannin vuoden 2024 erikoistuneiden sähkötupakkakauppiaiden myynniksi ilmoitettiin vähintään 280 milj. NZD.</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
         <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
+        <x:v>Terveysministeriö julkaisee virallisen kuluttajavähittäismyynnin alarajan, joka perustuu vain puutteellisiin erikoistuneiden sähkötupakkakauppiaiden myynteihin. Yleisvähittäiskauppa puuttuu, viereisiä ilmoitusvelvollisia tuotteita sisältyy eikä ministeriö suosittele aineistoa perusteelliseen tutkimukseen.</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>Virallista vähintään-otsikkolukua käytetään suoraan; ei ekstrapolointia eikä muiden palautustyyppien yhteenlaskua.</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>Luku on alaraja, ei koko maan sähkötupakkamarkkinan arvo.</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str">
+        <x:v>Vahvistettu</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>Hanki täydellinen valtakunnallinen vain sähkötupakkatuotteita koskeva vähittäiskaupan koonti, GST-perusta ja riippumaton täsmäytys.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="58.5" customHeight="1">
+      <x:c r="A15" s="14" t="str">
+        <x:v>Uuden-Seelannin 29 virallisen vuoden 2024 XLSX-tiedoston 612 765 numeerisen Total sales -solun raakasumma on 280 684 512,81 NZD.</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>Markkinan koko</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
         <x:v>Raakasumma täsmää ministeriön vähintään 280 milj. NZD otsikkolukuun. Aineistossa on 95 144 täsmälleen toistuvaa riviallekirjoitusta; niiden ensimmäisen esiintymän jälkeinen poistaminen antaisi 264 561 055,05 NZD, mutta toistojen merkitystä ei ole vahvistettu.</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="str">
+      <x:c r="D15" s="14" t="str">
         <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_ANNUAL_RETURNS_RECONCILIATION.md</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="str">
+      <x:c r="E15" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="str">
+      <x:c r="F15" s="14" t="str">
         <x:v>Kaikkien 29 virallisen XLSX-tiedoston numeeristen Total sales -solujen suora summa; ei deduplikointia, puhdistusta tai ekstrapolointia.</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="str">
+      <x:c r="G15" s="14" t="str">
         <x:v>Toistuvat rivit säilytetään raakasummassa, koska niiden liiketoiminnallista merkitystä ei tunneta.</x:v>
-      </x:c>
-      <x:c r="H14" s="14" t="str">
-        <x:v>Tuettu</x:v>
-      </x:c>
-      <x:c r="I14" s="14" t="str">
-        <x:v>Raakasumma ei ole puhdistettu kansallinen markkina-arvo. Yleisvähittäiskauppa, puuttuvat ilmoitukset ja GST-käsittely ovat avoimia.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="93" customHeight="1">
-      <x:c r="A15" s="14" t="str">
-        <x:v>Uuden-Seelannin vuoden 2024 AIS/AVP-erikoisvähittäiskaupan tunnistettu sähkötupakkasumma on 274 180 410,21 NZD; donor-testi läpäisee 7/10 ehtoa, mutta maa ei ole hyväksytty donor.</x:v>
-      </x:c>
-      <x:c r="B15" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="str">
-        <x:v>Kulutustarvikkeet ovat 189 402 451,96 NZD, laitteet/hardware 84 709 409,85 NZD ja sekajärjestelmät 68 548,40 NZD. Viereiset ilmoitusvelvolliset tuotteet 2 137 085,24 NZD ja ratkaisemattomat tuotetyypit 4 367 017,37 NZD määrällistetään erikseen ja rajataan pois. Havaittu arvo tulee vain AIS/AVP-työkirjoista; Notifier- ja RPS-arvoa ei lisätä.</x:v>
-      </x:c>
-      <x:c r="D15" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return ; https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf ; source/NZ_2024_DONOR_CLOSURE_PACK.md ; source/NZ_2024_D8_D10_OFFICIAL_SOURCE_AUDIT.md ; source/NZ_2024_WORKBOOK_MANIFEST.json ; source/NZ_2024_PRODUCT_SCOPE_AUDIT.json ; scripts/analyze_nz_2024_returns.py</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="str">
-        <x:v>189 402 451,96 + 84 709 409,85 + 68 548,40 = 274 180 410,21 NZD. Viereiset ja ratkaisemattomat luokat käsitellään ennen vaping-summaa ja jätetään siitä pois. Kaikkien 29 tiedoston URL:t, koot ja SHA-256-tiivisteet validoidaan ennen aggregointia.</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="str">
-        <x:v>Deterministinen tuoterajaus on julkinen. Yleisvähittäiskaupan havaittu arvo puuttuu, GST-perusta on tuntematon, täsmälleen toistuvien rivien herkkyys ei ole korjattu estimaatti eikä riippumatonta täsmäytystä ole.</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>D5 hylätään puuttuvan kansallisen kanavapeiton vuoksi; D8:n GST-perusta ja D10:n riippumaton täsmäytys ovat avoimia. Donor-portti pysyy 0/3:ssa.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="58.5" customHeight="1">
+        <x:v>Raakasumma ei ole puhdistettu kansallinen markkina-arvo. Yleisvähittäiskauppa, puuttuvat ilmoitukset ja GST-käsittely ovat avoimia.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="93" customHeight="1">
       <x:c r="A16" s="14" t="str">
-        <x:v>Uuden-Seelannin erillinen vuoden 2024 RPS-vähittäisherkkyys on tuettu malli: 533 662 383,68–731 175 792,50 NZD ja perusskenaario 641 811 687,89 NZD.</x:v>
+        <x:v>Uuden-Seelannin vuoden 2024 AIS/AVP-erikoisvähittäiskaupan tunnistettu sähkötupakkasumma on 274 180 410,21 NZD; donor-testi läpäisee 7/10 ehtoa, mutta maa ei ole hyväksytty donor.</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>Matalan, perus- ja korkean skenaarion yhdistetyt arvot ovat 533 662 383,68 / 641 811 687,89 / 731 175 792,50 NZD. Malli yhdistää erikoisvähittäiskaupan ankkurin yleisvähittäiskaupan määrä- ja hintamalliin.</x:v>
+        <x:v>Kulutustarvikkeet ovat 189 402 451,96 NZD, laitteet/hardware 84 709 409,85 NZD ja sekajärjestelmät 68 548,40 NZD. Viereiset ilmoitusvelvolliset tuotteet 2 137 085,24 NZD ja ratkaisemattomat tuotetyypit 4 367 017,37 NZD määrällistetään erikseen ja rajataan pois. Havaittu arvo tulee vain AIS/AVP-työkirjoista; Notifier- ja RPS-arvoa ei lisätä.</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_RPS_RETAIL_VALUE_SENSITIVITY.md ; source/NZ_2024_DONOR_CLOSURE_PACK.md</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return ; https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf ; source/NZ_2024_DONOR_CLOSURE_PACK.md ; source/NZ_2024_D8_D10_OFFICIAL_SOURCE_AUDIT.md ; source/NZ_2024_WORKBOOK_MANIFEST.json ; source/NZ_2024_PRODUCT_SCOPE_AUDIT.json ; scripts/analyze_nz_2024_returns.py</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>2026-07-26</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="str">
-        <x:v>Matala (täsmällisten rivien deduplikointi): 258 327 110,88 + 275 335 272,80 = 533 662 383,68 NZD. Perus (raportoidut/raakrivit): 274 180 410,21 + 367 631 277,68 = 641 811 687,89 NZD. Korkea (raportoidut/raakrivit): 274 180 410,21 + 456 995 382,29 = 731 175 792,50 NZD.</x:v>
+        <x:v>2026-07-27</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="str">
+        <x:v>189 402 451,96 + 84 709 409,85 + 68 548,40 = 274 180 410,21 NZD. Viereiset ja ratkaisemattomat luokat käsitellään ennen vaping-summaa ja jätetään siitä pois. Kaikkien 29 tiedoston URL:t, koot ja SHA-256-tiivisteet validoidaan ennen aggregointia.</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>GST-käsittely, palautusten täydellisyys ja riippumaton täsmäytys ovat avoimia; ilmoittajien toimitusketjutason arvot on jätetty pois.</x:v>
+        <x:v>Deterministinen tuoterajaus on julkinen. Yleisvähittäiskaupan havaittu arvo puuttuu, GST-perusta on tuntematon, täsmälleen toistuvien rivien herkkyys ei ole korjattu estimaatti eikä riippumatonta täsmäytystä ole.</x:v>
       </x:c>
       <x:c r="H16" s="14" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I16" s="14" t="str">
-        <x:v>Ei havaittu kansallinen arvo eikä hyväksytty donor. Tarvitaan viranomaisen scope- ja GST-vahvistus sekä riippumaton toisto.</x:v>
+        <x:v>D5 hylätään puuttuvan kansallisen kanavapeiton vuoksi; D8:n GST-perusta ja D10:n riippumaton täsmäytys ovat avoimia. Donor-portti pysyy 0/3:ssa.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58.5" customHeight="1">
       <x:c r="A17" s="14" t="str">
-        <x:v>Vuoden 2023 kuuden virallisen työkirjan uusi numeerinen rekonstruktio on jätetty tarkoituksella laskematta.</x:v>
+        <x:v>Uuden-Seelannin erillinen vuoden 2024 RPS-vähittäisherkkyys on tuettu malli: 533 662 383,68–731 175 792,50 NZD ja perusskenaario 641 811 687,89 NZD.</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>Ministeriön julkaisema koonti on vähintään 374 milj. NZD ja 2 570 ilmoitusta. Se sisältää kaikki ilmoitettavat tuotteet, myös heated tobacco -tuotteet, ja ministeriö varoittaa laadusta.</x:v>
+        <x:v>Matalan, perus- ja korkean skenaarion yhdistetyt arvot ovat 533 662 383,68 / 641 811 687,89 / 731 175 792,50 NZD. Malli yhdistää erikoisvähittäiskaupan ankkurin yleisvähittäiskaupan määrä- ja hintamalliin.</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2023 ; source/NZ_2023_ANNUAL_RETURNS_FAIL_CLOSED.md</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_RPS_RETAIL_VALUE_SENSITIVITY.md ; source/NZ_2024_DONOR_CLOSURE_PACK.md</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
         <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>Kuusi virallista tiedostoa on eheystiivistetty; kaikki uusi laskenta palauttaa tilan not_computed.</x:v>
+        <x:v>Matala (täsmällisten rivien deduplikointi): 258 327 110,88 + 275 335 272,80 = 533 662 383,68 NZD. Perus (raportoidut/raakrivit): 274 180 410,21 + 367 631 277,68 = 641 811 687,89 NZD. Korkea (raportoidut/raakrivit): 274 180 410,21 + 456 995 382,29 = 731 175 792,50 NZD.</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>Tuoterajaus, määräkentät, duplikaatit, toimitusketjutaso, veroperusta ja riippumaton täsmäytys ovat ratkaisematta.</x:v>
+        <x:v>GST-käsittely, palautusten täydellisyys ja riippumaton täsmäytys ovat avoimia; ilmoittajien toimitusketjutason arvot on jätetty pois.</x:v>
       </x:c>
       <x:c r="H17" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I17" s="14" t="str">
-        <x:v>Vuoden 2023 uusi vaping-only-arvo puuttuu, eikä 374 milj. NZD:tä saa nimetä puhtaaksi sähkötupakkamarkkinaksi.</x:v>
+        <x:v>Ei havaittu kansallinen arvo eikä hyväksytty donor. Tarvitaan viranomaisen scope- ja GST-vahvistus sekä riippumaton toisto.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="58.5" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>FTC:n virallisista taulukoista johdettu suljettujen järjestelmien ja kertakäyttötuotteiden raportoitu myynti oli 2 763 284 338 USD vuonna 2021.</x:v>
+        <x:v>Vuoden 2023 kuuden virallisen työkirjan uusi numeerinen rekonstruktio on jätetty tarkoituksella laskematta.</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>Seitsemän vuoden 2015–2021 sarja on laskettu summaamalla vuosittain cartridge-system- ja disposable-rivit. Vuoden 2020 korjattu taulukko kattaa viisi aiempaa raportoijaa sekä kolme neljästä uudesta; vuosi 2021 kattaa kaikki yhdeksän vastaanottajaa.</x:v>
+        <x:v>Ministeriön julkaisema koonti on vähintään 374 milj. NZD ja 2 570 ilmoitusta. Se sisältää kaikki ilmoitettavat tuotteet, myös heated tobacco -tuotteet, ja ministeriö varoittaa laadusta.</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018 ; https://www.ftc.gov/reports/e-cigarette-report-2021 ; source/US_FTC_2015_2021_REPORTED_SALES.md</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2023 ; source/NZ_2023_ANNUAL_RETURNS_FAIL_CLOSED.md</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>2021</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>FTC-taulukoiden cartridge systems + disposable e-cigarettes -myynnin vuosittainen summa.</x:v>
+        <x:v>Kuusi virallista tiedostoa on eheystiivistetty; kaikki uusi laskenta palauttaa tilan not_computed.</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
-        <x:v>Raportoijajoukko muuttuu, open-system-tuotteet puuttuvat, taso on valmistajaraportointi ja veroperustaa ei ilmoiteta.</x:v>
+        <x:v>Tuoterajaus, määräkentät, duplikaatit, toimitusketjutaso, veroperusta ja riippumaton täsmäytys ovat ratkaisematta.</x:v>
       </x:c>
       <x:c r="H18" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I18" s="14" t="str">
-        <x:v>Ei täydellinen kansallinen kuluttajavähittäisarvo eikä hyväksytty donor; tarvitaan avoin POS- tai kuluttajamyyntisarja ja veroperusta.</x:v>
+        <x:v>Vuoden 2023 uusi vaping-only-arvo puuttuu, eikä 374 milj. NZD:tä saa nimetä puhtaaksi sähkötupakkamarkkinaksi.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="58.5" customHeight="1">
       <x:c r="A19" s="14" t="str">
-        <x:v>Julkinen sivusto erottaa kolme evidenssikaistaa ja estää maailman kokonaisarvon, kun hyväksytty donor-portti on 0/3.</x:v>
+        <x:v>FTC:n virallisista taulukoista johdettu suljettujen järjestelmien ja kertakäyttötuotteiden raportoitu myynti oli 2 763 284 338 USD vuonna 2021.</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>Viisi ehdokasta on arvioitu samoilla 10 D1–D10-kriteerillä; yksikään ei ole hyväksytty. Lisäksi alue- ja sääntelytyyppien peittoporttien on läpäistävä tarkistus.</x:v>
+        <x:v>Seitsemän vuoden 2015–2021 sarja on laskettu summaamalla vuosittain cartridge-system- ja disposable-rivit. Vuoden 2020 korjattu taulukko kattaa viisi aiempaa raportoijaa sekä kolme neljästä uudesta; vuosi 2021 kattaa kaikki yhdeksän vastaanottajaa.</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>site/data/evidence-lanes.json ; site/data/donor-cockpit.json ; site/data/third-donor-screen.json ; site/data/country-scenarios.json</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018 ; https://www.ftc.gov/reports/e-cigarette-report-2021 ; source/US_FTC_2015_2021_REPORTED_SALES.md</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>Fail-closed-portit: puuttuva tai virheellinen syöte tuottaa tilan not_computed eikä nollaa.</x:v>
+        <x:v>FTC-taulukoiden cartridge systems + disposable e-cigarettes -myynnin vuosittainen summa.</x:v>
       </x:c>
       <x:c r="G19" s="14" t="str">
-        <x:v>Vain tarkistetut julkiset koontitiedot ja menetelmät ovat julkisella kaistalla; lisensoitu ja yksityinen aineisto eivät siirry repositorioon.</x:v>
+        <x:v>Raportoijajoukko muuttuu, open-system-tuotteet puuttuvat, taso on valmistajaraportointi ja veroperustaa ei ilmoiteta.</x:v>
       </x:c>
       <x:c r="H19" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I19" s="14" t="str">
-        <x:v>Maailmanarvo pysyy laskematta, kunnes vähintään kolme donoria sekä molemmat peittoportit hyväksytään.</x:v>
+        <x:v>Ei täydellinen kansallinen kuluttajavähittäisarvo eikä hyväksytty donor; tarvitaan avoin POS- tai kuluttajamyyntisarja ja veroperusta.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="58.5" customHeight="1">
       <x:c r="A20" s="14" t="str">
-        <x:v>Euroopan komissio julkaisee vuoden 2023 EU:n sähkötupakkamarkkinan 4,99 mrd euron vertailuarvon.</x:v>
+        <x:v>Julkinen sivusto erottaa kolme evidenssikaistaa ja estää maailman kokonaisarvon, kun hyväksytty donor-portti on 0/3.</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>SWD(2026) 111:n fyysisen PDF:n sivun 25 alaviite 83 nimeää seuraavien sivujen taulukoiden lähteeksi Euromonitor International Tobacco 2025 -aineiston; fyysisen sivun 27 taulukko 4 raportoi 4,99 mrd euroa. SWD(2025) 560:n fyysinen sivu 161 kuvaa lähes 5 mrd euron koonnin, joka sisältää laitteet ja nesteet, myös nikotiinittomat; sivu 162 ilmoittaa Kyproksen, Luxemburgin ja Maltan tiedot puuttuviksi.</x:v>
+        <x:v>Viisi ehdokasta on arvioitu samoilla 10 D1–D10-kriteerillä; yksikään ei ole hyväksytty. Lisäksi alue- ja sääntelytyyppien peittoporttien on läpäistävä tarkistus.</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2025%3A0560%3AFIN ; https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2026%3A111%3AFIN</x:v>
+        <x:v>site/data/evidence-lanes.json ; site/data/donor-cockpit.json ; site/data/third-donor-screen.json ; site/data/country-scenarios.json</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
-        <x:v>2023</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
-        <x:v>Kahden Euroopan komission valmisteluasiakirjan taulukko-, sivu- ja lähdeviitteiden ristiinvertailu; lukuja ei summata.</x:v>
+        <x:v>Fail-closed-portit: puuttuva tai virheellinen syöte tuottaa tilan not_computed eikä nollaa.</x:v>
       </x:c>
       <x:c r="G20" s="14" t="str">
-        <x:v>Komissio julkaisee vertailuarvon, mutta sen pohjana on kaupallinen Euromonitor-aineisto. Täysi menetelmä, veroperusta ja uudelleenkäytettävä maadata eivät ole julkisia, ja kolmesta EU-maasta ei ole tietoa.</x:v>
+        <x:v>Vain tarkistetut julkiset koontitiedot ja menetelmät ovat julkisella kaistalla; lisensoitu ja yksityinen aineisto eivät siirry repositorioon.</x:v>
       </x:c>
       <x:c r="H20" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I20" s="14" t="str">
-        <x:v>Hanki lisensoitu maataulukko ja menetelmä, tapahtumamääritelmä, kanavapeitto, veroperusta sekä riippumaton täsmäytys; täydennä Kypros, Luxemburg ja Malta.</x:v>
+        <x:v>Maailmanarvo pysyy laskematta, kunnes vähintään kolme donoria sekä molemmat peittoportit hyväksytään.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="58.5" customHeight="1">
       <x:c r="A21" s="14" t="str">
-        <x:v>Kanadan virallinen vuoden 2024 kuluttajavähittäismyynnin piste-estimaatti on 1 219 160 000 CAD eli 822 583 715,21 EUR; donor-testi läpäisee 7/10 ehtoa.</x:v>
+        <x:v>Euroopan komissio julkaisee vuoden 2023 EU:n sähkötupakkamarkkinan 4,99 mrd euron vertailuarvon.</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Neljän kvartaalin summa on 1 219 160 000 CAD; 12 kuukauden samaan kyselyyn perustuva summa on 1 219 161 000 CAD. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusten nettoarvo on 1 160 753 796,78 CAD.</x:v>
+        <x:v>SWD(2026) 111:n fyysisen PDF:n sivun 25 alaviite 83 nimeää seuraavien sivujen taulukoiden lähteeksi Euromonitor International Tobacco 2025 -aineiston; fyysisen sivun 27 taulukko 4 raportoi 4,99 mrd euroa. SWD(2025) 560:n fyysinen sivu 161 kuvaa lähes 5 mrd euron koonnin, joka sisältää laitteet ja nesteet, myös nikotiinittomat; sivu 162 ilmoittaa Kyproksen, Luxemburgin ja Maltan tiedot puuttuviksi.</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md ; source/CANADA_2024_D5_D7_D10_OFFICIAL_SOURCE_AUDIT.md</x:v>
+        <x:v>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2025%3A0560%3AFIN ; https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2026%3A111%3AFIN</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>Kuukausi − kvartaali = 1 000 CAD (0,000082 %). Retail − toimitukset = 58 406 203,22 CAD; retail / toimitukset − 1 = 5,031748 %. ECB 2024: 1 219 160 000 / 1,482110546875 = 822 583 715,21 EUR.</x:v>
+        <x:v>Kahden Euroopan komission valmisteluasiakirjan taulukko-, sivu- ja lähdeviitteiden ristiinvertailu; lukuja ei summata.</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
-        <x:v>D8 läpäisee: CAD sekä GST/HST-, provinssi- ja valmisteverojen poissulku on lähteistetty. Kuukausireitti on saman kyselyn QA, ei D10; retail- ja toimitusreitit eivät muodosta markkinahaarukkaa.</x:v>
+        <x:v>Komissio julkaisee vertailuarvon, mutta sen pohjana on kaupallinen Euromonitor-aineisto. Täysi menetelmä, veroperusta ja uudelleenkäytettävä maadata eivät ole julkisia, ja kolmesta EU-maasta ei ole tietoa.</x:v>
       </x:c>
       <x:c r="H21" s="14" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
-        <x:v>D5:n NAICS 459993/459999 -peitto, D7:n vuositason virheraja ja D10:n retail–toimitus-silta ovat avoimia; Kanada ei ole hyväksytty donor.</x:v>
+        <x:v>Hanki lisensoitu maataulukko ja menetelmä, tapahtumamääritelmä, kanavapeitto, veroperusta sekä riippumaton täsmäytys; täydennä Kypros, Luxemburg ja Malta.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="58.5" customHeight="1">
       <x:c r="A22" s="14" t="str">
-        <x:v>Health Canadan neljä vuoden 2024 tuoteryhmää summautuvat 1 160 753 796,78 CAD:n nettotoimitusarvoon, 118 901 910 yksikköön ja 1 251 843 litraan.</x:v>
+        <x:v>Kanadan virallinen vuoden 2024 kuluttajavähittäismyynnin piste-estimaatti on 1 219 160 000 CAD eli 822 583 715,21 EUR; donor-testi läpäisee 7/10 ehtoa.</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Arvo-osuudet ovat: laite tai osa ilman ainetta 2,602 %, aineen sisältävä laite 48,154 %, aineen sisältävä osa 27,252 % ja höyrystettävä aine 21,992 %. Kyse on toimituksista tukku- tai vähittäismyyjille, ei kuluttajaostoista.</x:v>
+        <x:v>Neljän kvartaalin summa on 1 219 160 000 CAD; 12 kuukauden samaan kyselyyn perustuva summa on 1 219 161 000 CAD. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusten nettoarvo on 1 160 753 796,78 CAD.</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>https://health-infobase.canada.ca/substance-use/vaping/sales/ ; https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html ; source/CANADA_2024_DONOR_CLOSURE_PACK.md</x:v>
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md ; source/CANADA_2024_D5_D7_D10_OFFICIAL_SOURCE_AUDIT.md</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
-        <x:v>30 207 822,87 + 558 947 200,26 + 316 329 158,83 + 255 269 614,82 = 1 160 753 796,78 CAD; osuudet lasketaan tästä summasta.</x:v>
+        <x:v>Kuukausi − kvartaali = 1 000 CAD (0,000082 %). Retail − toimitukset = 58 406 203,22 CAD; retail / toimitukset − 1 = 5,031748 %. ECB 2024: 1 219 160 000 / 1,482110546875 = 822 583 715,21 EUR.</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>Nettomyynti on myynti vähennettynä palautuksilla ja arvot ilmoitetaan ilman veroja ja maksuja. Nestettä sisältävä laite tai osa yhdistää laite- ja neste-arvoa.</x:v>
+        <x:v>D8 läpäisee: CAD sekä GST/HST-, provinssi- ja valmisteverojen poissulku on lähteistetty. Kuukausireitti on saman kyselyn QA, ei D10; retail- ja toimitusreitit eivät muodosta markkinahaarukkaa.</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I22" s="14" t="str">
-        <x:v>Toimitusosuuksia ei saa soveltaa retail-arvoon laite–neste-jaoksi eikä eri tapahtumatasoja summata.</x:v>
+        <x:v>D5:n NAICS 459993/459999 -peitto, D7:n vuositason virheraja ja D10:n retail–toimitus-silta ovat avoimia; Kanada ei ole hyväksytty donor.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58.5" customHeight="1">
       <x:c r="A23" s="14" t="str">
-        <x:v>Saksan verotettu nestemäärä kasvoi 1.241 milj. l:sta 1.518 milj. l:aan vuosina 2023–2025.</x:v>
+        <x:v>Health Canadan neljä vuoden 2024 tuoteryhmää summautuvat 1 160 753 796,78 CAD:n nettotoimitusarvoon, 118 901 910 yksikköön ja 1 251 843 litraan.</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>2023 ja 2024 lopullisia; 2025 alustava.</x:v>
+        <x:v>Arvo-osuudet ovat: laite tai osa ilman ainetta 2,602 %, aineen sisältävä laite 48,154 %, aineen sisältävä osa 27,252 % ja höyrystettävä aine 21,992 %. Kyse on toimituksista tukku- tai vähittäismyyjille, ei kuluttajaostoista.</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</x:v>
+        <x:v>https://health-infobase.canada.ca/substance-use/vaping/sales/ ; https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html ; source/CANADA_2024_DONOR_CLOSURE_PACK.md</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
-        <x:v>2023–2025</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
-        <x:v>Destatis-taulukon nettomäärät, ei ekstrapolointia.</x:v>
+        <x:v>30 207 822,87 + 558 947 200,26 + 316 329 158,83 + 255 269 614,82 = 1 160 753 796,78 CAD; osuudet lasketaan tästä summasta.</x:v>
       </x:c>
       <x:c r="G23" s="14" t="str">
-        <x:v>Mittaa verotettua nestettä, ei laitteita tai laitonta myyntiä.</x:v>
+        <x:v>Nettomyynti on myynti vähennettynä palautuksilla ja arvot ilmoitetaan ilman veroja ja maksuja. Nestettä sisältävä laite tai osa yhdistää laite- ja neste-arvoa.</x:v>
       </x:c>
       <x:c r="H23" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>Vuoden 2025 lopullinen luku ja vähittäismyyntitiedot puuttuvat.</x:v>
+        <x:v>Toimitusosuuksia ei saa soveltaa retail-arvoon laite–neste-jaoksi eikä eri tapahtumatasoja summata.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="58.5" customHeight="1">
       <x:c r="A24" s="14" t="str">
-        <x:v>Saksan tupakankorvikkeiden valmisteverotulot olivat 404 milj. euroa vuonna 2025 (alustava).</x:v>
+        <x:v>Saksan verotettu nestemäärä kasvoi 1.241 milj. l:sta 1.518 milj. l:aan vuosina 2023–2025.</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
         <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Alustavat viralliset kassaperusteiset valmisteverotulot. Verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</x:v>
+        <x:v>2023 ja 2024 lopullisia; 2025 alustava.</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
         <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
-        <x:v>2025</x:v>
+        <x:v>2023–2025</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>Virallinen kassaperusteinen verohavainto.</x:v>
+        <x:v>Destatis-taulukon nettomäärät, ei ekstrapolointia.</x:v>
       </x:c>
       <x:c r="G24" s="14" t="str">
-        <x:v>Verotulo ei ole myyntitulo tai vähittäismarkkina-arvo.</x:v>
+        <x:v>Mittaa verotettua nestettä, ei laitteita tai laitonta myyntiä.</x:v>
       </x:c>
       <x:c r="H24" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I24" s="14" t="str">
-        <x:v>Tarvitaan lopullinen 2025 tilasto ja tuoteryhmäkohtainen veropohja.</x:v>
+        <x:v>Vuoden 2025 lopullinen luku ja vähittäismyyntitiedot puuttuvat.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="58.5" customHeight="1">
       <x:c r="A25" s="14" t="str">
-        <x:v>Suomessa verotettiin 11 801,062 litraa nikotiininestettä vuonna 2025.</x:v>
+        <x:v>Saksan tupakankorvikkeiden valmisteverotulot olivat 404 milj. euroa vuonna 2025 (alustava).</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
         <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Virallinen koko vuoden nikotiinillisen sähkösavukenesteen määrä. Nikotiinittoman nesteen koko vuoden arvo on salattu; fyysinen määrä ei sisällä laitteita eikä ole vähittäismarkkina-arvo.</x:v>
+        <x:v>Alustavat viralliset kassaperusteiset valmisteverotulot. Verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</x:v>
+        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>Verohallinnon PXWeb-havainto.</x:v>
+        <x:v>Virallinen kassaperusteinen verohavainto.</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>Verotettu nikotiinineste ei kata koko sähkötupakkamarkkinaa.</x:v>
+        <x:v>Verotulo ei ole myyntitulo tai vähittäismarkkina-arvo.</x:v>
       </x:c>
       <x:c r="H25" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
-        <x:v>Laitteet, nikotiinittomat tuotteet, veroton ja laiton kauppa puuttuvat.</x:v>
+        <x:v>Tarvitaan lopullinen 2025 tilasto ja tuoteryhmäkohtainen veropohja.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58.5" customHeight="1">
       <x:c r="A26" s="14" t="str">
-        <x:v>Suomen nikotiininesteiden valmisteverotulot olivat 3 540 319 euroa vuonna 2025.</x:v>
+        <x:v>Suomessa verotettiin 11 801,062 litraa nikotiininestettä vuonna 2025.</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
         <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>Viralliset koko vuoden nikotiinillisen sähkösavukenesteen valmisteverotulot. Nikotiinittoman nesteen koko vuoden arvo on salattu; verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</x:v>
+        <x:v>Virallinen koko vuoden nikotiinillisen sähkösavukenesteen määrä. Nikotiinittoman nesteen koko vuoden arvo on salattu; fyysinen määrä ei sisällä laitteita eikä ole vähittäismarkkina-arvo.</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
         <x:v>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</x:v>
@@ -1323,227 +1323,227 @@
         <x:v>Verohallinnon PXWeb-havainto.</x:v>
       </x:c>
       <x:c r="G26" s="14" t="str">
-        <x:v>Verotulo ei ole kuluttajamyynti.</x:v>
+        <x:v>Verotettu nikotiinineste ei kata koko sähkötupakkamarkkinaa.</x:v>
       </x:c>
       <x:c r="H26" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I26" s="14" t="str">
-        <x:v>Tarvitaan vähittäismyynti- ja hintadata.</x:v>
+        <x:v>Laitteet, nikotiinittomat tuotteet, veroton ja laiton kauppa puuttuvat.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="58.5" customHeight="1">
       <x:c r="A27" s="14" t="str">
-        <x:v>Puolan virallinen sähkötupakkanesteiden virta oli 1 451 529 litraa vuonna 2020, 277 265 litraa vuonna 2021, 416 088 litraa vuonna 2022 ja 805 441 litraa vuonna 2023.</x:v>
+        <x:v>Suomen nikotiininesteiden valmisteverotulot olivat 3 540 319 euroa vuonna 2025.</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Ministeriön parlamenttivastauksen taulukko yhdistää ZEFIR2/AIS-järjestelmiin kirjatut kotimaan myynnit, EU-sisäiset hankinnat ja tuonnin. Sarja on fyysinen e-nestevirta, ei kuluttajamyynti tai havaittu vähittäismarkkina-arvo.</x:v>
+        <x:v>Viralliset koko vuoden nikotiinillisen sähkösavukenesteen valmisteverotulot. Nikotiinittoman nesteen koko vuoden arvo on salattu; verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDDEJZ5/i07255-o1.pdf</x:v>
+        <x:v>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
-        <x:v>2020–2023</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F27" s="14" t="str">
-        <x:v>Neljän virallisen vuosihavainnon suora toisto; eri vuosia ei summata markkina-arvoksi.</x:v>
+        <x:v>Verohallinnon PXWeb-havainto.</x:v>
       </x:c>
       <x:c r="G27" s="14" t="str">
-        <x:v>Julkaistu taulukko ei erittele kotimaan myyntiä, EU-sisäisiä hankintoja ja tuontia eikä sisällä laitteiden arvoa.</x:v>
+        <x:v>Verotulo ei ole kuluttajamyynti.</x:v>
       </x:c>
       <x:c r="H27" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I27" s="14" t="str">
-        <x:v>Tarvitaan kuluttajavähittäisarvo, kanavapeitto, veroperusta ja riippumaton täsmäytys.</x:v>
+        <x:v>Tarvitaan vähittäismyynti- ja hintadata.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="58.5" customHeight="1">
       <x:c r="A28" s="14" t="str">
-        <x:v>Puolan vuoden 2025 verosilta antaa 4 382 500 johdettua verollista sähkötupakkalaitetta ja 62 500 johdettua verollista osasarjaa.</x:v>
+        <x:v>Puolan virallinen sähkötupakkanesteiden virta oli 1 451 529 litraa vuonna 2020, 277 265 litraa vuonna 2021, 416 088 litraa vuonna 2022 ja 805 441 litraa vuonna 2023.</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>Virallinen parlamenttivastaus raportoi 993,1 milj. PLN e-nesteistä, 175,3 milj. PLN laitteista ja 2,5 milj. PLN osasarjoista. Laitteiden ja osasarjojen vero oli 40 PLN yksiköltä 1.7.2025 alkaen.</x:v>
+        <x:v>Ministeriön parlamenttivastauksen taulukko yhdistää ZEFIR2/AIS-järjestelmiin kirjatut kotimaan myynnit, EU-sisäiset hankinnat ja tuonnin. Sarja on fyysinen e-nestevirta, ei kuluttajamyynti tai havaittu vähittäismarkkina-arvo.</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf ; https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDDEJZ5/i07255-o1.pdf</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
-        <x:v>2025</x:v>
+        <x:v>2020–2023</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
-        <x:v>175 300 000 / 40 = 4 382 500 verollista laitetta; 2 500 000 / 40 = 62 500 verollista osasarjaa.</x:v>
+        <x:v>Neljän virallisen vuosihavainnon suora toisto; eri vuosia ei summata markkina-arvoksi.</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>Johdettu veropohja kattaa vain 1.7.2025 alkaen verotetut laitteet ja osasarjat. Se ei osoita kuluttajahintaa, vähittäismyyntiä, verottomia määriä tai varastosiirtymiä.</x:v>
+        <x:v>Julkaistu taulukko ei erittele kotimaan myyntiä, EU-sisäisiä hankintoja ja tuontia eikä sisällä laitteiden arvoa.</x:v>
       </x:c>
       <x:c r="H28" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
-        <x:v>Tarvitaan veron kuukausijakauma, lopullisuus, vähittäishinnat, kanavapeitto ja riippumaton täsmäytys.</x:v>
+        <x:v>Tarvitaan kuluttajavähittäisarvo, kanavapeitto, veroperusta ja riippumaton täsmäytys.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58.5" customHeight="1">
       <x:c r="A29" s="14" t="str">
-        <x:v>Ruotsin julkinen evidenssi yhdistää vuoden 2024 veroankkurin ja 36 virallista FHM-rekisterirakenteen lukua vuosilta 2018–2026; rekisteriluvut eivät ole myyntiä tai markkina-arvoa.</x:v>
+        <x:v>Puolan vuoden 2025 verosilta antaa 4 382 500 johdettua verollista sähkötupakkalaitetta ja 62 500 johdettua verollista osasarjaa.</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>Vuonna 2024 verotettiin 26 000 litraa nikotiininestettä ja valmisteverotulo oli pyöristetysti 80 000 000 SEK. Viranomaisen toimittamassa ja 24.7.2026 tarkistetussa työkirjassa on 9 vuosilabelia × 4 rakennemittaria: raportoivat toimijat sekä ilmoitetut, aktiiviset ja markkinoilta poistetut tuotteet. Julkinen FHM-sivu dokumentoi ilmoitusjärjestelmän, ei siinä julkaistua numeerista sarjaa.</x:v>
+        <x:v>Virallinen parlamenttivastaus raportoi 993,1 milj. PLN e-nesteistä, 175,3 milj. PLN laitteista ja 2,5 milj. PLN osasarjoista. Laitteiden ja osasarjojen vero oli 40 PLN yksiköltä 1.7.2025 alkaen.</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf ; https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/ ; site/data/market-values.json</x:v>
+        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf ; https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
-        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 39 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
+        <x:v>175 300 000 / 40 = 4 382 500 verollista laitetta; 2 500 000 / 40 = 62 500 verollista osasarjaa.</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>Rakenneluvuista ei päätellä myyntiarvoa, myyntimäärää tai markkinaosuutta. Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja vuosivirtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva eikä sitä vuositasoiteta.</x:v>
+        <x:v>Johdettu veropohja kattaa vain 1.7.2025 alkaen verotetut laitteet ja osasarjat. Se ei osoita kuluttajahintaa, vähittäismyyntiä, verottomia määriä tai varastosiirtymiä.</x:v>
       </x:c>
       <x:c r="H29" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
-        <x:v>Tarvitaan toteutunut kuluttajamyynti EUR-määräisenä, laitekappaleet ja ml-määrät sekä julkisesti uudelleenkäytettävä numeerinen FHM-sarja.</x:v>
+        <x:v>Tarvitaan veron kuukausijakauma, lopullisuus, vähittäishinnat, kanavapeitto ja riippumaton täsmäytys.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="58.5" customHeight="1">
       <x:c r="A30" s="14" t="str">
-        <x:v>Kolme kaupallista vuoden 2025 globaaliarviota muodostavat 26,0–46,32 mrd USD haarukan.</x:v>
+        <x:v>Ruotsin julkinen evidenssi yhdistää vuoden 2024 veroankkurin ja 36 virallista FHM-rekisterirakenteen lukua vuosilta 2018–2026; rekisteriluvut eivät ole myyntiä tai markkina-arvoa.</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>IMARC 26,0; Grand View Research 45,7; Fortune Business Insights 46,32 mrd USD.</x:v>
+        <x:v>Vuonna 2024 verotettiin 26 000 litraa nikotiininestettä ja valmisteverotulo oli pyöristetysti 80 000 000 SEK. Viranomaisen toimittamassa ja 24.7.2026 tarkistetussa työkirjassa on 9 vuosilabelia × 4 rakennemittaria: raportoivat toimijat sekä ilmoitetut, aktiiviset ja markkinoilta poistetut tuotteet. Julkinen FHM-sivu dokumentoi ilmoitusjärjestelmän, ei siinä julkaistua numeerista sarjaa.</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
-        <x:v>https://www.imarcgroup.com/e-cigarette-market ; https://www.grandviewresearch.com/industry-analysis/e-cigarette-vaping-market ; https://www.fortunebusinessinsights.com/e-cigarette-and-vaping-market-114882</x:v>
+        <x:v>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf ; https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/ ; site/data/market-values.json</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
-        <x:v>2025</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F30" s="14" t="str">
-        <x:v>Minimi 26000000000, maksimi 46320000000; arvioita verrataan, ei summata.</x:v>
+        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 39 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>Tuoterajaukset ja menetelmät eivät välttämättä ole yhteismitallisia.</x:v>
+        <x:v>Rakenneluvuista ei päätellä myyntiarvoa, myyntimäärää tai markkinaosuutta. Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja vuosivirtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva eikä sitä vuositasoiteta.</x:v>
       </x:c>
       <x:c r="H30" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I30" s="14" t="str">
-        <x:v>Hanki raporttien täydet metodit ja harmonisoi tuoterajaus.</x:v>
+        <x:v>Tarvitaan toteutunut kuluttajamyynti EUR-määräisenä, laitekappaleet ja ml-määrät sekä julkisesti uudelleenkäytettävä numeerinen FHM-sarja.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="58.5" customHeight="1">
       <x:c r="A31" s="14" t="str">
-        <x:v>Saksan vuoden 2025 verotetun nesteen vähittäismyyntivastaavuuden mallihaitari on 667,92–1 654,62 milj. euroa.</x:v>
+        <x:v>Kolme kaupallista vuoden 2025 globaaliarviota muodostavat 26,0–46,32 mrd USD haarukan.</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>Taloudellinen malli</x:v>
+        <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>Ei havaittua myyntiä. Laskelma kertoo vuoden 2025 alustavan verotetun nestemäärän kolmella yksittäisellä saksalaisen verkkokaupan vuoden 2026 hinnalla. Vuosiero, yhden kaupan hintakori, tuotejakauma ja pois rajatut tuoteryhmät tekevät luottamustasosta matalan.</x:v>
+        <x:v>IMARC 26,0; Grand View Research 45,7; Fortune Business Insights 46,32 mrd USD.</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003 ; https://www.intaste.de/pfefferminz-liquid-germanflavours-liquid ; https://www.intaste.de/anstand-liquid-samurai-liquid ; https://www.intaste.de/tobacco-vanilla-nikotinsalz-revoltage-liquid</x:v>
+        <x:v>https://www.imarcgroup.com/e-cigarette-market ; https://www.grandviewresearch.com/industry-analysis/e-cigarette-vaping-market ; https://www.fortunebusinessinsights.com/e-cigarette-and-vaping-market-114882</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
-        <x:v>2025 määrä / 2026 hinnat</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F31" s="14" t="str">
-        <x:v>volume_litres * 1000 * retail_price_eur_per_ml</x:v>
+        <x:v>Minimi 26000000000, maksimi 46320000000; arvioita verrataan, ei summata.</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>Kolme yksittäistä verkkokauppahintaa; syötevuodet 2025 ja 2026; vain verotettu neste.</x:v>
+        <x:v>Tuoterajaukset ja menetelmät eivät välttämättä ole yhteismitallisia.</x:v>
       </x:c>
       <x:c r="H31" s="14" t="str">
-        <x:v>Oletus</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I31" s="14" t="str">
-        <x:v>Tarvitaan edustava hintakori, tuotemix ja kanavamarginaalit sekä mallivuoden 2025 hinnat.</x:v>
+        <x:v>Hanki raporttien täydet metodit ja harmonisoi tuoterajaus.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="58.5" customHeight="1">
       <x:c r="A32" s="14" t="str">
-        <x:v>Atlas ei ole vielä lainanantajavalmis markkina-arvio.</x:v>
+        <x:v>Saksan vuoden 2025 verotetun nesteen vähittäismyyntivastaavuuden mallihaitari on 667,92–1 654,62 milj. euroa.</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Taloudellinen malli</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>research_dataset_not_valuation: Useimmista maista puuttuu virallinen vuosittainen laite- ja nestemyynti Markkinaevidenssiä ei ole vielä sidottu maakohtaiseen patenttistatukseen ja claim charteihin Aineisto ei sisällä riippumatonta IVS-arvonmääritystä eikä realisoitunutta lisenssi- tai vahingonkorvauskassavirtaa</x:v>
+        <x:v>Ei havaittua myyntiä. Laskelma kertoo vuoden 2025 alustavan verotetun nestemäärän kolmella yksittäisellä saksalaisen verkkokaupan vuoden 2026 hinnalla. Vuosiero, yhden kaupan hintakori, tuotejakauma ja pois rajatut tuoteryhmät tekevät luottamustasosta matalan.</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
-        <x:v>site/data/atlas.json (readiness)</x:v>
+        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003 ; https://www.intaste.de/pfefferminz-liquid-germanflavours-liquid ; https://www.intaste.de/anstand-liquid-samurai-liquid ; https://www.intaste.de/tobacco-vanilla-nikotinsalz-revoltage-liquid</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2025 määrä / 2026 hinnat</x:v>
       </x:c>
       <x:c r="F32" s="14" t="str">
-        <x:v>Julkisen datasetin oma readiness-luokitus.</x:v>
+        <x:v>volume_litres * 1000 * retail_price_eur_per_ml</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>Markkinadata ja IP-arvo pidetään erillään.</x:v>
+        <x:v>Kolme yksittäistä verkkokauppahintaa; syötevuodet 2025 ja 2026; vain verotettu neste.</x:v>
       </x:c>
       <x:c r="H32" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Oletus</x:v>
       </x:c>
       <x:c r="I32" s="14" t="str">
-        <x:v>Täytä blocker-lista ennen vakuusarvo- tai yritysarvopäätelmää.</x:v>
+        <x:v>Tarvitaan edustava hintakori, tuotemix ja kanavamarginaalit sekä mallivuoden 2025 hinnat.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="58.5" customHeight="1">
       <x:c r="A33" s="14" t="str">
-        <x:v>Julkinen aineisto ei sisällä riippumatonta IVS-arvonmääritystä.</x:v>
+        <x:v>Atlas ei ole vielä lainanantajavalmis markkina-arvio.</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>Taloudellinen malli</x:v>
+        <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>Readiness-blocker ilmoittaa riippumattoman arvonmäärityksen puuttuvan.</x:v>
+        <x:v>research_dataset_not_valuation: Useimmista maista puuttuu virallinen vuosittainen laite- ja nestemyynti Markkinaevidenssiä ei ole vielä sidottu maakohtaiseen patenttistatukseen ja claim charteihin Aineisto ei sisällä riippumatonta IVS-arvonmääritystä eikä realisoitunutta lisenssi- tai vahingonkorvauskassavirtaa</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>site/data/atlas.json (readiness.blockers)</x:v>
+        <x:v>site/data/atlas.json (readiness)</x:v>
       </x:c>
       <x:c r="E33" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F33" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>Julkisen datasetin oma readiness-luokitus.</x:v>
       </x:c>
       <x:c r="G33" s="14" t="str">
-        <x:v>Ei oletuksia.</x:v>
+        <x:v>Markkinadata ja IP-arvo pidetään erillään.</x:v>
       </x:c>
       <x:c r="H33" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I33" s="14" t="str">
-        <x:v>Tilaa riippumaton IP- ja tarvittaessa yritysarvonmääritys skenaarioineen.</x:v>
+        <x:v>Täytä blocker-lista ennen vakuusarvo- tai yritysarvopäätelmää.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="58.5" customHeight="1">
       <x:c r="A34" s="14" t="str">
-        <x:v>Julkinen aineisto ei osoita toteutunutta lisenssi- tai vahingonkorvauskassavirtaa.</x:v>
+        <x:v>Julkinen aineisto ei sisällä riippumatonta IVS-arvonmääritystä.</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>Kaupallistamismalli</x:v>
+        <x:v>Taloudellinen malli</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>Readiness-blocker ilmoittaa realisoituneen kassavirran puuttuvan.</x:v>
+        <x:v>Readiness-blocker ilmoittaa riippumattoman arvonmäärityksen puuttuvan.</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
         <x:v>site/data/atlas.json (readiness.blockers)</x:v>
@@ -1561,366 +1561,366 @@
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I34" s="14" t="str">
-        <x:v>Lisää allekirjoitetut sopimukset, laskut, maksutositteet ja saamisten täsmäytys.</x:v>
+        <x:v>Tilaa riippumaton IP- ja tarvittaessa yritysarvonmääritys skenaarioineen.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="58.5" customHeight="1">
       <x:c r="A35" s="14" t="str">
-        <x:v>Julkinen aineisto ei vahvista testituloksia tai riippumatonta teknistä validointia.</x:v>
+        <x:v>Julkinen aineisto ei osoita toteutunutta lisenssi- tai vahingonkorvauskassavirtaa.</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
-        <x:v>Tekninen erottautuminen</x:v>
+        <x:v>Kaupallistamismalli</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>Patenttiselitys kuvaa ratkaisun; erillistä testirekisteriä ei ole julkisessa datassa.</x:v>
+        <x:v>Readiness-blocker ilmoittaa realisoituneen kassavirran puuttuvan.</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>site/data/patent-history.json</x:v>
+        <x:v>site/data/atlas.json (readiness.blockers)</x:v>
       </x:c>
       <x:c r="E35" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F35" s="14" t="str">
-        <x:v>Aineiston puute suhteessa tekniseen suorituskykyväitteeseen.</x:v>
+        <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G35" s="14" t="str">
-        <x:v>Patenttijulkaisu ei ole tuotetestiraportti.</x:v>
+        <x:v>Ei oletuksia.</x:v>
       </x:c>
       <x:c r="H35" s="14" t="str">
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I35" s="14" t="str">
-        <x:v>Hanki testiprotokolla, riippumaton laboratorio, tulokset ja raakadata.</x:v>
+        <x:v>Lisää allekirjoitetut sopimukset, laskut, maksutositteet ja saamisten täsmäytys.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="58.5" customHeight="1">
       <x:c r="A36" s="14" t="str">
-        <x:v>Julkinen aineisto ei vahvista piloteja tai nimettyä asiakasnäyttöä.</x:v>
+        <x:v>Julkinen aineisto ei vahvista testituloksia tai riippumatonta teknistä validointia.</x:v>
       </x:c>
       <x:c r="B36" s="14" t="str">
-        <x:v>Validointi</x:v>
+        <x:v>Tekninen erottautuminen</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>Julkisessa evidenssirekisterissä ei ole pilotti- tai asiakasvalidointia.</x:v>
+        <x:v>Patenttiselitys kuvaa ratkaisun; erillistä testirekisteriä ei ole julkisessa datassa.</x:v>
       </x:c>
       <x:c r="D36" s="14" t="str">
-        <x:v>site/data/evidence.csv</x:v>
+        <x:v>site/data/patent-history.json</x:v>
       </x:c>
       <x:c r="E36" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>Aineiston puute suhteessa tekniseen suorituskykyväitteeseen.</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>Ei päätellä asiakkaiden olemassaoloa tai puuttumista yhtiötasolla.</x:v>
+        <x:v>Patenttijulkaisu ei ole tuotetestiraportti.</x:v>
       </x:c>
       <x:c r="H36" s="14" t="str">
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I36" s="14" t="str">
-        <x:v>Lisää allekirjoitetut pilotit, toimitusnäyttö, asiakasreferenssit ja käyttödata.</x:v>
+        <x:v>Hanki testiprotokolla, riippumaton laboratorio, tulokset ja raakadata.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="58.5" customHeight="1">
       <x:c r="A37" s="14" t="str">
-        <x:v>Julkinen aineisto ei vahvista nykyistä maakohtaista omistusta, vuosimaksuja ja rasitteettomuutta koko perheessä.</x:v>
+        <x:v>Julkinen aineisto ei vahvista piloteja tai nimettyä asiakasnäyttöä.</x:v>
       </x:c>
       <x:c r="B37" s="14" t="str">
-        <x:v>IP-status</x:v>
+        <x:v>Validointi</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>Perhejulkaisut eivät yksin osoita kansallista post-grant-tilaa.</x:v>
+        <x:v>Julkisessa evidenssirekisterissä ei ole pilotti- tai asiakasvalidointia.</x:v>
       </x:c>
       <x:c r="D37" s="14" t="str">
-        <x:v>https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=family ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=legal ; https://www.epo.org/en/applying/european/validation</x:v>
+        <x:v>site/data/evidence.csv</x:v>
       </x:c>
       <x:c r="E37" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F37" s="14" t="str">
-        <x:v>Diligence-rajaus.</x:v>
+        <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G37" s="14" t="str">
-        <x:v>Neljä kansallista rekisterijurisdiktiota ei kata koko perhettä.</x:v>
+        <x:v>Ei päätellä asiakkaiden olemassaoloa tai puuttumista yhtiötasolla.</x:v>
       </x:c>
       <x:c r="H37" s="14" t="str">
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I37" s="14" t="str">
-        <x:v>Laadi asiamiehen allekirjoittama maamatriisi ja liitä tuoreet rekisteriotteet sekä maksukuitit.</x:v>
+        <x:v>Lisää allekirjoitetut pilotit, toimitusnäyttö, asiakasreferenssit ja käyttödata.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="58.5" customHeight="1">
       <x:c r="A38" s="14" t="str">
-        <x:v>Julkinen aineisto ei sisällä maakohtaisia tuote–vaatimusvertailuja.</x:v>
+        <x:v>Julkinen aineisto ei vahvista nykyistä maakohtaista omistusta, vuosimaksuja ja rasitteettomuutta koko perheessä.</x:v>
       </x:c>
       <x:c r="B38" s="14" t="str">
-        <x:v>Tekninen erottautuminen</x:v>
+        <x:v>IP-status</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
-        <x:v>Patenttihistorian guardrail edellyttää counsel-reviewed claim chartia.</x:v>
+        <x:v>Perhejulkaisut eivät yksin osoita kansallista post-grant-tilaa.</x:v>
       </x:c>
       <x:c r="D38" s="14" t="str">
-        <x:v>https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB2/document.pdf ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</x:v>
+        <x:v>https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=family ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=legal ; https://www.epo.org/en/applying/european/validation</x:v>
       </x:c>
       <x:c r="E38" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F38" s="14" t="str">
-        <x:v>Vaatimuspiirteiden tuotekohtainen kartoitus puuttuu.</x:v>
+        <x:v>Diligence-rajaus.</x:v>
       </x:c>
       <x:c r="G38" s="14" t="str">
-        <x:v>Samankaltaisuus ei ole loukkaus.</x:v>
+        <x:v>Neljä kansallista rekisterijurisdiktiota ei kata koko perhettä.</x:v>
       </x:c>
       <x:c r="H38" s="14" t="str">
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I38" s="14" t="str">
-        <x:v>Hanki tuotteet, säilytä hallussapitoketju, tee teardown ja asiamiehen tarkastama claim chart.</x:v>
+        <x:v>Laadi asiamiehen allekirjoittama maamatriisi ja liitä tuoreet rekisteriotteet sekä maksukuitit.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="58.5" customHeight="1">
       <x:c r="A39" s="14" t="str">
-        <x:v>Markkinan kokonaisarvo ei ole automaattisesti rojaltipohja.</x:v>
+        <x:v>Julkinen aineisto ei sisällä maakohtaisia tuote–vaatimusvertailuja.</x:v>
       </x:c>
       <x:c r="B39" s="14" t="str">
-        <x:v>Taloudellinen malli</x:v>
+        <x:v>Tekninen erottautuminen</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>Patenttihistorian kaupallistamisrajaus erottaa markkinan, kohdistettavan myynnin ja kassavirran.</x:v>
+        <x:v>Patenttihistorian guardrail edellyttää counsel-reviewed claim chartia.</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
-        <x:v>https://www.wipo.int/en/web/business/ip-valuation</x:v>
+        <x:v>https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB2/document.pdf ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</x:v>
       </x:c>
       <x:c r="E39" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F39" s="14" t="str">
-        <x:v>Arvonmäärityksen perusrajaus.</x:v>
+        <x:v>Vaatimuspiirteiden tuotekohtainen kartoitus puuttuu.</x:v>
       </x:c>
       <x:c r="G39" s="14" t="str">
-        <x:v>Rojaltipohja vaatii patentin maantieteellisen, ajallisen ja tuotekohtaisen osuvuuden.</x:v>
+        <x:v>Samankaltaisuus ei ole loukkaus.</x:v>
       </x:c>
       <x:c r="H39" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I39" s="14" t="str">
-        <x:v>Tarvitaan addressable/in-scope/claim-mapped sales -silta.</x:v>
+        <x:v>Hanki tuotteet, säilytä hallussapitoketju, tee teardown ja asiamiehen tarkastama claim chart.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="58.5" customHeight="1">
       <x:c r="A40" s="14" t="str">
-        <x:v>Patenttiarvo, yritysarvo, osakearvo ja vakuusarvo ovat eri mittareita.</x:v>
+        <x:v>Markkinan kokonaisarvo ei ole automaattisesti rojaltipohja.</x:v>
       </x:c>
       <x:c r="B40" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Taloudellinen malli</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
-        <x:v>WIPO:n IP-arvonmääritys- ja rahoituskehys sekä aineiston oma guardrail.</x:v>
+        <x:v>Patenttihistorian kaupallistamisrajaus erottaa markkinan, kohdistettavan myynnin ja kassavirran.</x:v>
       </x:c>
       <x:c r="D40" s="14" t="str">
-        <x:v>https://www.wipo.int/en/web/business/ip-valuation ; https://www.wipo.int/en/web/ip-financing</x:v>
+        <x:v>https://www.wipo.int/en/web/business/ip-valuation</x:v>
       </x:c>
       <x:c r="E40" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F40" s="14" t="str">
-        <x:v>Arvokäsitteiden erottelu.</x:v>
+        <x:v>Arvonmäärityksen perusrajaus.</x:v>
       </x:c>
       <x:c r="G40" s="14" t="str">
-        <x:v>Ei oletuksia.</x:v>
+        <x:v>Rojaltipohja vaatii patentin maantieteellisen, ajallisen ja tuotekohtaisen osuvuuden.</x:v>
       </x:c>
       <x:c r="H40" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I40" s="14" t="str">
-        <x:v>Rahoitusrakenne ja vakuusarvo vaativat erillisen oikeudellisen ja taloudellisen analyysin.</x:v>
+        <x:v>Tarvitaan addressable/in-scope/claim-mapped sales -silta.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="58.5" customHeight="1">
       <x:c r="A41" s="14" t="str">
-        <x:v>Asiantuntijavetoinen rajattu lisensointi- tai sovintopilotti on mahdollinen kaupallistamishypoteesi.</x:v>
+        <x:v>Patenttiarvo, yritysarvo, osakearvo ja vakuusarvo ovat eri mittareita.</x:v>
       </x:c>
       <x:c r="B41" s="14" t="str">
-        <x:v>Kaupallistamismalli</x:v>
+        <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
-        <x:v>Patenttihistorian vaiheistus suosittelee kovia portteja, claim chartia ja auditoitavaa yhteydenottoa.</x:v>
+        <x:v>WIPO:n IP-arvonmääritys- ja rahoituskehys sekä aineiston oma guardrail.</x:v>
       </x:c>
       <x:c r="D41" s="14" t="str">
-        <x:v>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/business/settle-ip-disputes ; https://www.epo.org/en/searching-for-patents/business/ipscore</x:v>
+        <x:v>https://www.wipo.int/en/web/business/ip-valuation ; https://www.wipo.int/en/web/ip-financing</x:v>
       </x:c>
       <x:c r="E41" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F41" s="14" t="str">
-        <x:v>Hypoteesi, ei toteutunut kaupallinen näyttö.</x:v>
+        <x:v>Arvokäsitteiden erottelu.</x:v>
       </x:c>
       <x:c r="G41" s="14" t="str">
-        <x:v>Kohdemaat ja vastapuolet valitaan vasta oikeus- ja evidenssiporttien jälkeen.</x:v>
+        <x:v>Ei oletuksia.</x:v>
       </x:c>
       <x:c r="H41" s="14" t="str">
-        <x:v>Oletus</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I41" s="14" t="str">
-        <x:v>Hyväksytä pilottimalli johdolla ja patenttiasiantuntijalla; dokumentoi kustannus, vasteet ja termit.</x:v>
+        <x:v>Rahoitusrakenne ja vakuusarvo vaativat erillisen oikeudellisen ja taloudellisen analyysin.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="58.5" customHeight="1">
       <x:c r="A42" s="14" t="str">
-        <x:v>Patenttivakuudellinen rahoitus on arvioitava vain vahvistettujen oikeuksien ja kassavirtojen pohjalta.</x:v>
+        <x:v>Asiantuntijavetoinen rajattu lisensointi- tai sovintopilotti on mahdollinen kaupallistamishypoteesi.</x:v>
       </x:c>
       <x:c r="B42" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Kaupallistamismalli</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
-        <x:v>WIPO IP Finance ja patenttihistorian vaihe 5.</x:v>
+        <x:v>Patenttihistorian vaiheistus suosittelee kovia portteja, claim chartia ja auditoitavaa yhteydenottoa.</x:v>
       </x:c>
       <x:c r="D42" s="14" t="str">
-        <x:v>https://www.wipo.int/en/web/ip-financing ; https://www.wipo.int/en/web/business/ip-valuation</x:v>
+        <x:v>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/business/settle-ip-disputes ; https://www.epo.org/en/searching-for-patents/business/ipscore</x:v>
       </x:c>
       <x:c r="E42" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F42" s="14" t="str">
-        <x:v>Rahoitusperiaate.</x:v>
+        <x:v>Hypoteesi, ei toteutunut kaupallinen näyttö.</x:v>
       </x:c>
       <x:c r="G42" s="14" t="str">
-        <x:v>Ei näyttöä olemassa olevasta vakuusarvosta.</x:v>
+        <x:v>Kohdemaat ja vastapuolet valitaan vasta oikeus- ja evidenssiporttien jälkeen.</x:v>
       </x:c>
       <x:c r="H42" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Oletus</x:v>
       </x:c>
       <x:c r="I42" s="14" t="str">
-        <x:v>Tarvitaan riippumaton arvonmääritys, oikeuksien due diligence, toteutuneet tai sopimuspohjaiset kassavirrat ja downside-analyysi.</x:v>
+        <x:v>Hyväksytä pilottimalli johdolla ja patenttiasiantuntijalla; dokumentoi kustannus, vasteet ja termit.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="58.5" customHeight="1">
       <x:c r="A43" s="14" t="str">
-        <x:v>Australian oikeuden seuraava uusiminen on vahvistettava välittömästi.</x:v>
+        <x:v>Patenttivakuudellinen rahoitus on arvioitava vain vahvistettujen oikeuksien ja kassavirtojen pohjalta.</x:v>
       </x:c>
       <x:c r="B43" s="14" t="str">
-        <x:v>Riskit</x:v>
+        <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
-        <x:v>IP Australian API näyttää GRANTED-tilan, viimeisen uusimismaksun 18.7.2025 ja in-force date -päivän 14.8.2026.</x:v>
+        <x:v>WIPO IP Finance ja patenttihistorian vaihe 5.</x:v>
       </x:c>
       <x:c r="D43" s="14" t="str">
-        <x:v>https://production.api.ipaustralia.gov.au/public/ipright-search-api/v1/patents/2014307829</x:v>
+        <x:v>https://www.wipo.int/en/web/ip-financing ; https://www.wipo.int/en/web/business/ip-valuation</x:v>
       </x:c>
       <x:c r="E43" s="14" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F43" s="14" t="str">
-        <x:v>Virallisen API-tiedon diligence-hälytys.</x:v>
+        <x:v>Rahoitusperiaate.</x:v>
       </x:c>
       <x:c r="G43" s="14" t="str">
-        <x:v>API:n in-force-through-päivä ei ole tässä lakisääteinen eräpäiväväite.</x:v>
+        <x:v>Ei näyttöä olemassa olevasta vakuusarvosta.</x:v>
       </x:c>
       <x:c r="H43" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I43" s="14" t="str">
-        <x:v>Patenttihallinto ja Australian asiamies: vahvistakaa lakisääteinen maksupäivä, summa, maksuvaltuus ja suoritettu maksu; arkistoikaa kuitti ja tuore rekisteriote.</x:v>
+        <x:v>Tarvitaan riippumaton arvonmääritys, oikeuksien due diligence, toteutuneet tai sopimuspohjaiset kassavirrat ja downside-analyysi.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="58.5" customHeight="1">
       <x:c r="A44" s="14" t="str">
-        <x:v>Suomen 14. vuosimaksun eräpäiväksi on rekisteröity 31.8.2026.</x:v>
+        <x:v>Australian oikeuden seuraava uusiminen on vahvistettava välittömästi.</x:v>
       </x:c>
       <x:c r="B44" s="14" t="str">
         <x:v>Riskit</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
-        <x:v>PRH kirjaa 14. vuoden 670 euron maksun eräpäiväksi 31.8.2026 ja myöhäisen maksukauden päättymispäiväksi 28.2.2027.</x:v>
+        <x:v>IP Australian API näyttää GRANTED-tilan, viimeisen uusimismaksun 18.7.2025 ja in-force date -päivän 14.8.2026.</x:v>
       </x:c>
       <x:c r="D44" s="14" t="str">
-        <x:v>https://patenttitietopalvelu.prh.fi/en/patent/20135829</x:v>
+        <x:v>https://production.api.ipaustralia.gov.au/public/ipright-search-api/v1/patents/2014307829</x:v>
       </x:c>
       <x:c r="E44" s="14" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="F44" s="14" t="str">
-        <x:v>PRH:n rekisterihavainto.</x:v>
+        <x:v>Virallisen API-tiedon diligence-hälytys.</x:v>
       </x:c>
       <x:c r="G44" s="14" t="str">
-        <x:v>Tavoite on maksaa normaalina eräpäivänä.</x:v>
+        <x:v>API:n in-force-through-päivä ei ole tässä lakisääteinen eräpäiväväite.</x:v>
       </x:c>
       <x:c r="H44" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I44" s="14" t="str">
-        <x:v>Patenttihallinto: maksakaa ennen normaalia eräpäivää ja säilyttäkää maksukuitti sekä päivitetty PRH-ote.</x:v>
+        <x:v>Patenttihallinto ja Australian asiamies: vahvistakaa lakisääteinen maksupäivä, summa, maksuvaltuus ja suoritettu maksu; arkistoikaa kuitti ja tuore rekisteriote.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="58.5" customHeight="1">
       <x:c r="A45" s="14" t="str">
-        <x:v>Yhdysvaltain 7,5 vuoden ylläpitomaksun tila on vahvistettava.</x:v>
+        <x:v>Suomen 14. vuosimaksun eräpäiväksi on rekisteröity 31.8.2026.</x:v>
       </x:c>
       <x:c r="B45" s="14" t="str">
         <x:v>Riskit</x:v>
       </x:c>
       <x:c r="C45" s="14" t="str">
-        <x:v>USPTO:n ylläpitomaksureitti näyttää normaalimaksuikkunan päättyvän 4.12.2026; maksutilaa ei vahvistettu riippumattomasti tässä julkaisussa.</x:v>
+        <x:v>PRH kirjaa 14. vuoden 670 euron maksun eräpäiväksi 31.8.2026 ja myöhäisen maksukauden päättymispäiväksi 28.2.2027.</x:v>
       </x:c>
       <x:c r="D45" s="14" t="str">
-        <x:v>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923 ; https://patentcenter.uspto.gov/applications/14911851 ; https://assignment.uspto.gov/patent/index.html#/patent/search/resultFilter?searchInput=10306923</x:v>
+        <x:v>https://patenttitietopalvelu.prh.fi/en/patent/20135829</x:v>
       </x:c>
       <x:c r="E45" s="14" t="str">
-        <x:v>2026-12-04</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="F45" s="14" t="str">
-        <x:v>Virallisen maksuikkunan tarkistus.</x:v>
+        <x:v>PRH:n rekisterihavainto.</x:v>
       </x:c>
       <x:c r="G45" s="14" t="str">
-        <x:v>Julkaisu ei väitä, että maksu on tai ei ole suoritettu.</x:v>
+        <x:v>Tavoite on maksaa normaalina eräpäivänä.</x:v>
       </x:c>
       <x:c r="H45" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I45" s="14" t="str">
-        <x:v>Yhdysvaltain patenttiasiamies: vahvistakaa entity status, summa ja maksu sekä arkistoikaa virallinen kuitti ja tuoreet ylläpito- ja siirtotiedot.</x:v>
+        <x:v>Patenttihallinto: maksakaa ennen normaalia eräpäivää ja säilyttäkää maksukuitti sekä päivitetty PRH-ote.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="58.5" customHeight="1">
       <x:c r="A46" s="14" t="str">
-        <x:v>Julkinen aineisto ei sisällä auditoituja historiallisia tilinpäätöksiä tai kassavirtaennustetta.</x:v>
+        <x:v>Yhdysvaltain 7,5 vuoden ylläpitomaksun tila on vahvistettava.</x:v>
       </x:c>
       <x:c r="B46" s="14" t="str">
-        <x:v>Taloudellinen malli</x:v>
+        <x:v>Riskit</x:v>
       </x:c>
       <x:c r="C46" s="14" t="str">
-        <x:v>Markkina- ja patenttiaineisto ei ole yhtiön talousaineisto.</x:v>
+        <x:v>USPTO:n ylläpitomaksureitti näyttää normaalimaksuikkunan päättyvän 4.12.2026; maksutilaa ei vahvistettu riippumattomasti tässä julkaisussa.</x:v>
       </x:c>
       <x:c r="D46" s="14" t="str">
-        <x:v>Julkisen paketin rajaus</x:v>
+        <x:v>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923 ; https://patentcenter.uspto.gov/applications/14911851 ; https://assignment.uspto.gov/patent/index.html#/patent/search/resultFilter?searchInput=10306923</x:v>
       </x:c>
       <x:c r="E46" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-12-04</x:v>
       </x:c>
       <x:c r="F46" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>Virallisen maksuikkunan tarkistus.</x:v>
       </x:c>
       <x:c r="G46" s="14" t="str">
-        <x:v>Yhtiön taloudellisesta tilanteesta ei tehdä päätelmää.</x:v>
+        <x:v>Julkaisu ei väitä, että maksu on tai ei ole suoritettu.</x:v>
       </x:c>
       <x:c r="H46" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I46" s="14" t="str">
-        <x:v>Lisää 3–5 vuoden tilinpäätökset, tuore pääkirja, budjetti, kassavirta, velat ja verovelkatodistus.</x:v>
+        <x:v>Yhdysvaltain patenttiasiamies: vahvistakaa entity status, summa ja maksu sekä arkistoikaa virallinen kuitti ja tuoreet ylläpito- ja siirtotiedot.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="58.5" customHeight="1">
       <x:c r="A47" s="14" t="str">
-        <x:v>Julkinen aineisto ei yksilöi rahoitustarvetta, käyttötarkoitusta tai takaisinmaksulähdettä.</x:v>
+        <x:v>Julkinen aineisto ei sisällä auditoituja historiallisia tilinpäätöksiä tai kassavirtaennustetta.</x:v>
       </x:c>
       <x:c r="B47" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Taloudellinen malli</x:v>
       </x:c>
       <x:c r="C47" s="14" t="str">
-        <x:v>Rahoitusparametreja ei ole markkina- tai patenttidatassa.</x:v>
+        <x:v>Markkina- ja patenttiaineisto ei ole yhtiön talousaineisto.</x:v>
       </x:c>
       <x:c r="D47" s="14" t="str">
         <x:v>Julkisen paketin rajaus</x:v>
@@ -1932,24 +1932,24 @@
         <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G47" s="14" t="str">
-        <x:v>Ei oleteta lainamäärää, maturiteettia tai vakuusrakennetta.</x:v>
+        <x:v>Yhtiön taloudellisesta tilanteesta ei tehdä päätelmää.</x:v>
       </x:c>
       <x:c r="H47" s="14" t="str">
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I47" s="14" t="str">
-        <x:v>Määritä lainamäärä, käyttötarkoitus, maturiteetti, lyhennysprofiili, takaisinmaksu ja kovenantit.</x:v>
+        <x:v>Lisää 3–5 vuoden tilinpäätökset, tuore pääkirja, budjetti, kassavirta, velat ja verovelkatodistus.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="58.5" customHeight="1">
       <x:c r="A48" s="14" t="str">
-        <x:v>Julkinen aineisto ei osoita osakekantaa, cap tablea tai osakkeiden rasitteita.</x:v>
+        <x:v>Julkinen aineisto ei yksilöi rahoitustarvetta, käyttötarkoitusta tai takaisinmaksulähdettä.</x:v>
       </x:c>
       <x:c r="B48" s="14" t="str">
         <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>Julkinen paketti on rajattu markkina- ja patenttievidenssiin.</x:v>
+        <x:v>Rahoitusparametreja ei ole markkina- tai patenttidatassa.</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
         <x:v>Julkisen paketin rajaus</x:v>
@@ -1961,27 +1961,27 @@
         <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G48" s="14" t="str">
-        <x:v>Ei oleteta omistusosuuksia tai vakuuskelpoisuutta.</x:v>
+        <x:v>Ei oleteta lainamäärää, maturiteettia tai vakuusrakennetta.</x:v>
       </x:c>
       <x:c r="H48" s="14" t="str">
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I48" s="14" t="str">
-        <x:v>Toimita varmennettu osakasluettelo, yhtiöjärjestys, päätökset, panttaus- ja rasiteselvitys suljettuun datahuoneeseen.</x:v>
+        <x:v>Määritä lainamäärä, käyttötarkoitus, maturiteetti, lyhennysprofiili, takaisinmaksu ja kovenantit.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="58.5" customHeight="1">
       <x:c r="A49" s="14" t="str">
-        <x:v>Julkinen aineisto ei sisällä vertailukelpoista kilpailija- ja vaihtoehtoanalyysiä.</x:v>
+        <x:v>Julkinen aineisto ei osoita osakekantaa, cap tablea tai osakkeiden rasitteita.</x:v>
       </x:c>
       <x:c r="B49" s="14" t="str">
-        <x:v>Kilpailu</x:v>
+        <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>Patenttiselitys ja oikeustapaukset eivät yksin muodosta markkinakilpailukarttaa.</x:v>
+        <x:v>Julkinen paketti on rajattu markkina- ja patenttievidenssiin.</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
-        <x:v>site/data/patent-history.json</x:v>
+        <x:v>Julkisen paketin rajaus</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
         <x:v>2026-07-24</x:v>
@@ -1990,175 +1990,204 @@
         <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G49" s="14" t="str">
-        <x:v>Kilpailu on erotettava patenttien päällekkäisyydestä ja ei-patentoiduista vaihtoehdoista.</x:v>
+        <x:v>Ei oleteta omistusosuuksia tai vakuuskelpoisuutta.</x:v>
       </x:c>
       <x:c r="H49" s="14" t="str">
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I49" s="14" t="str">
-        <x:v>Laadi tuotteet, valmistajat, vaihtoehtoiset teknologiat, patenttiperheet, hinnat ja claim-map-status kattava vertailu.</x:v>
+        <x:v>Toimita varmennettu osakasluettelo, yhtiöjärjestys, päätökset, panttaus- ja rasiteselvitys suljettuun datahuoneeseen.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="58.5" customHeight="1">
       <x:c r="A50" s="14" t="str">
-        <x:v>Asiakassegmentit voidaan alustavasti jäsentää valmistajiin, teknologiatoimittajiin ja IP-rahoittajiin.</x:v>
+        <x:v>Julkinen aineisto ei sisällä vertailukelpoista kilpailija- ja vaihtoehtoanalyysiä.</x:v>
       </x:c>
       <x:c r="B50" s="14" t="str">
-        <x:v>Asiakkaat</x:v>
+        <x:v>Kilpailu</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>Patenttihistorian kaupallistamisreitit sisältävät lisensoinnin, luovutuksen ja IP-rahoituksen.</x:v>
+        <x:v>Patenttiselitys ja oikeustapaukset eivät yksin muodosta markkinakilpailukarttaa.</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/ip-financing</x:v>
+        <x:v>site/data/patent-history.json</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
-        <x:v>Segmentointihypoteesi kaupallistamisreiteistä.</x:v>
+        <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G50" s="14" t="str">
-        <x:v>Ei todennettua ostoaikomusta tai asiakaskantaa.</x:v>
+        <x:v>Kilpailu on erotettava patenttien päällekkäisyydestä ja ei-patentoiduista vaihtoehdoista.</x:v>
       </x:c>
       <x:c r="H50" s="14" t="str">
-        <x:v>Oletus</x:v>
+        <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I50" s="14" t="str">
-        <x:v>Validoi 10–15 strukturoitua ostaja- ja rahoittajahaastattelua sekä dokumentoi päätöskriteerit.</x:v>
+        <x:v>Laadi tuotteet, valmistajat, vaihtoehtoiset teknologiat, patenttiperheet, hinnat ja claim-map-status kattava vertailu.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="58.5" customHeight="1">
       <x:c r="A51" s="14" t="str">
-        <x:v>Saksan ratkaisut voivat toimia evidenssiankkurina, mutta eivät maailmanlaajuisena loukkausratkaisuna.</x:v>
+        <x:v>Asiakassegmentit voidaan alustavasti jäsentää valmistajiin, teknologiatoimittajiin ja IP-rahoittajiin.</x:v>
       </x:c>
       <x:c r="B51" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Asiakkaat</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>Ratkaisut ovat kansallisia, tuote-, osapuoli- ja ajanjaksokohtaisia.</x:v>
+        <x:v>Patenttihistorian kaupallistamisreitit sisältävät lisensoinnin, luovutuksen ja IP-rahoituksen.</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
-        <x:v>https://www.rechtsprechung-im-internet.de/jportal/?quelle=jlink&amp;docid=JURE269032275&amp;psml=bsjrsprod.psml ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</x:v>
+        <x:v>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/ip-financing</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F51" s="14" t="str">
-        <x:v>Oikeudellisen vaikutuksen alueellinen rajaus.</x:v>
+        <x:v>Segmentointihypoteesi kaupallistamisreiteistä.</x:v>
       </x:c>
       <x:c r="G51" s="14" t="str">
-        <x:v>Muiden maiden tulokset riippuvat paikallisista oikeuksista ja tuotteista.</x:v>
+        <x:v>Ei todennettua ostoaikomusta tai asiakaskantaa.</x:v>
       </x:c>
       <x:c r="H51" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Oletus</x:v>
       </x:c>
       <x:c r="I51" s="14" t="str">
-        <x:v>Laadi maakohtaiset oikeus- ja claim chart -paketit ennen yhteydenottoja.</x:v>
+        <x:v>Validoi 10–15 strukturoitua ostaja- ja rahoittajahaastattelua sekä dokumentoi päätöskriteerit.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="58.5" customHeight="1">
       <x:c r="A52" s="14" t="str">
-        <x:v>Aineiston A-luokan maita on viisi, mutta 158 maata on D-luokassa.</x:v>
+        <x:v>Saksan ratkaisut voivat toimia evidenssiankkurina, mutta eivät maailmanlaajuisena loukkausratkaisuna.</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>Luokat: A 5, B 13, C 19, D 158.</x:v>
+        <x:v>Ratkaisut ovat kansallisia, tuote-, osapuoli- ja ajanjaksokohtaisia.</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>site/data/atlas.json (summary.gradeCounts)</x:v>
+        <x:v>https://www.rechtsprechung-im-internet.de/jportal/?quelle=jlink&amp;docid=JURE269032275&amp;psml=bsjrsprod.psml ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F52" s="14" t="str">
-        <x:v>Maakohtaisten evidenssiluokkien laskenta.</x:v>
+        <x:v>Oikeudellisen vaikutuksen alueellinen rajaus.</x:v>
       </x:c>
       <x:c r="G52" s="14" t="str">
-        <x:v>Luokka mittaa evidenssikypsyyttä, ei markkinan houkuttelevuutta.</x:v>
+        <x:v>Muiden maiden tulokset riippuvat paikallisista oikeuksista ja tuotteista.</x:v>
       </x:c>
       <x:c r="H52" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I52" s="14" t="str">
-        <x:v>Priorisoi D-maiden tietopyynnöt talouskoon, patenttistatuksen ja sääntelyn mukaan.</x:v>
+        <x:v>Laadi maakohtaiset oikeus- ja claim chart -paketit ennen yhteydenottoja.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="58.5" customHeight="1">
       <x:c r="A53" s="14" t="str">
-        <x:v>Maailmanlaajuista atlasestimaattia ei ole hyväksytty julkaistavaksi.</x:v>
+        <x:v>Aineiston A-luokan maita on viisi, mutta 158 maata on D-luokassa.</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>Nolla hyväksyttyä donoria alittaa kolmen vähimmäisrajan. Uuden-Seelannin, EU:n, Kanadan, Saksan ja Yhdysvaltain 5 julkaistulla ehdokkaalla on jokaisella vähintään yksi hylätty tai avoin D1–D10-ehto; myös alue- ja sääntelytyyppien peittoportit puuttuvat.</x:v>
+        <x:v>Luokat: A 5, B 13, C 19, D 158.</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
+        <x:v>site/data/atlas.json (summary.gradeCounts)</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
-        <x:v>Kova portti: jokaisen donorin on läpäistävä D1–D10, ja lisäksi tarvitaan vähintään kolme yhteensopivaa donoria sekä molemmat peittoportit.</x:v>
+        <x:v>Maakohtaisten evidenssiluokkien laskenta.</x:v>
       </x:c>
       <x:c r="G53" s="14" t="str">
-        <x:v>Viralliset alarajat ja ulkoiset vertailuarvot säilyvät ristiintarkistuksina, mutta niitä ei lasketa hyväksytyiksi donoreiksi.</x:v>
+        <x:v>Luokka mittaa evidenssikypsyyttä, ei markkinan houkuttelevuutta.</x:v>
       </x:c>
       <x:c r="H53" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I53" s="14" t="str">
+        <x:v>Priorisoi D-maiden tietopyynnöt talouskoon, patenttistatuksen ja sääntelyn mukaan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="58.5" customHeight="1">
+      <x:c r="A54" s="14" t="str">
+        <x:v>Maailmanlaajuista atlasestimaattia ei ole hyväksytty julkaistavaksi.</x:v>
+      </x:c>
+      <x:c r="B54" s="14" t="str">
+        <x:v>Markkinakoko</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="str">
+        <x:v>Nolla hyväksyttyä donoria alittaa kolmen vähimmäisrajan. Uuden-Seelannin, EU:n, Kanadan, Saksan ja Yhdysvaltain 5 julkaistulla ehdokkaalla on jokaisella vähintään yksi hylätty tai avoin D1–D10-ehto; myös alue- ja sääntelytyyppien peittoportit puuttuvat.</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="str">
+        <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="str">
+        <x:v>Kova portti: jokaisen donorin on läpäistävä D1–D10, ja lisäksi tarvitaan vähintään kolme yhteensopivaa donoria sekä molemmat peittoportit.</x:v>
+      </x:c>
+      <x:c r="G54" s="14" t="str">
+        <x:v>Viralliset alarajat ja ulkoiset vertailuarvot säilyvät ristiintarkistuksina, mutta niitä ei lasketa hyväksytyiksi donoreiksi.</x:v>
+      </x:c>
+      <x:c r="H54" s="14" t="str">
+        <x:v>Vahvistettu</x:v>
+      </x:c>
+      <x:c r="I54" s="14" t="str">
         <x:v>Älä julkaise yhtä maailmanarvoa ennen menetelmäporttien läpäisyä.</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="58.5" customHeight="1">
-      <x:c r="A54" s="15" t="str">
+    <x:row r="55" ht="58.5" customHeight="1">
+      <x:c r="A55" s="15" t="str">
         <x:v>Korkean luottamuksen rahoituspaketti vaatii suljetun datahuoneen julkisen paketin rinnalle.</x:v>
       </x:c>
-      <x:c r="B54" s="15" t="str">
+      <x:c r="B55" s="15" t="str">
         <x:v>Seuraavat vaiheet</x:v>
       </x:c>
-      <x:c r="C54" s="15" t="str">
+      <x:c r="C55" s="15" t="str">
         <x:v>Julkinen paketti osoittaa lähteet ja puutteet mutta ei sisällä luottamuksellista talous-, sopimus- tai omistusaineistoa.</x:v>
       </x:c>
-      <x:c r="D54" s="15" t="str">
+      <x:c r="D55" s="15" t="str">
         <x:v>Julkisen paketin rajaus</x:v>
       </x:c>
-      <x:c r="E54" s="15" t="str">
+      <x:c r="E55" s="15" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
-      <x:c r="F54" s="15" t="str">
+      <x:c r="F55" s="15" t="str">
         <x:v>Diligence-arkkitehtuurin suositus.</x:v>
       </x:c>
-      <x:c r="G54" s="15" t="str">
+      <x:c r="G55" s="15" t="str">
         <x:v>Pääsy rajataan ja lokitetaan.</x:v>
       </x:c>
-      <x:c r="H54" s="15" t="str">
+      <x:c r="H55" s="15" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
-      <x:c r="I54" s="15" t="str">
+      <x:c r="I55" s="15" t="str">
         <x:v>Perusta indeksoitu datahuone: Corporate, IP, Legal, Commercial, Finance, Valuation, Security.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="H2:H54">
+  <x:conditionalFormatting sqref="H2:H55">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Vahvistettu"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Tuettu"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Oletus"/>
     <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Puuttuu"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H2:H54">
+    <x:dataValidation type="list" sqref="H2:H55">
       <x:formula1>"Vahvistettu,Tuettu,Oletus,Puuttuu"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd43488d06c34cc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4da1ccdb515a4d7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2216,7 +2245,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.27-29</x:v>
+        <x:v>2026.07.27-30</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2240,8 +2269,8 @@
         <x:v>Evidenssirivejä</x:v>
       </x:c>
       <x:c r="B8" s="15" t="n">
-        <x:f>COUNTA('Evidence Register'!$A$2:$A$54)</x:f>
-        <x:v>53</x:v>
+        <x:f>COUNTA('Evidence Register'!$A$2:$A$55)</x:f>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20.25" customHeight="1"/>
@@ -2256,8 +2285,8 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="B11" s="13" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$54,A11)</x:f>
-        <x:v>28</x:v>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$55,A11)</x:f>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20.25" customHeight="1">
@@ -2265,7 +2294,7 @@
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="B12" s="14" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$54,A12)</x:f>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$55,A12)</x:f>
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2274,7 +2303,7 @@
         <x:v>Oletus</x:v>
       </x:c>
       <x:c r="B13" s="14" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$54,A13)</x:f>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$55,A13)</x:f>
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -2283,7 +2312,7 @@
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$54,A14)</x:f>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$55,A14)</x:f>
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -2468,7 +2497,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R732723de12dc4702"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78bac05ebb424231"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4000,7 +4029,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reba89781e37b49a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a167b487b74d5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6046,7 +6075,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9f4daa69a84468c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re74002499e814d93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R4943de0902264aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R8c121ca5014f442f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R7284d4de90954458"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R7017d93aed7f414d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R0be63e4b8e0c44fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rcf03bba813f54433"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R36f3f7cdaedc40d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R508b9317fe8e46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R5c071efc6b73419a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R954e1c60c2bc4d7d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -308,8 +308,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EvidenceRegisterFI" displayName="EvidenceRegisterFI" ref="A1:I55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I55"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EvidenceRegisterFI" displayName="EvidenceRegisterFI" ref="A1:I61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I61"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Väite"/>
     <x:tableColumn id="2" name="Dia/osio"/>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E89" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E90" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -870,7 +870,7 @@
     </x:row>
     <x:row r="11" ht="58.5" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>195 maan menetelmäkontrolli erottaa 23 tarkistettua maasuunnitelmaa, 5 tarkistettua lähdepolkua, 15 alueellista EU TPD -raportointimallia ja 152 maakohtaisesti rajaamatonta proxy-reittiä.</x:v>
+        <x:v>195 maan menetelmäkontrolli erottaa 28 tarkistettua maasuunnitelmaa, 0 tarkistettua lähdepolkua, 15 alueellista EU TPD -raportointimallia ja 152 maakohtaisesti rajaamatonta proxy-reittiä.</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>Markkinan rajaus</x:v>
@@ -879,16 +879,16 @@
         <x:v>Jokaisella maalla on näkyvä menetelmäluokka, seuraava evidenssitoimi ja lähdeperusta. Luokitus ei ole myyntihavainto: kaikilla 195 maalla eligibleForGlobalRollup=false ja donorAccepted=false.</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>site/data/global-base-layer.json ; source/country-method-route-config.json ; source/COUNTRY_METHOD_ROUTE_MAP.md</x:v>
+        <x:v>site/data/global-base-layer.json ; source/country-method-route-config.json ; source/COUNTRY_METHOD_ROUTE_MAP.md ; source/FIVE_COUNTRY_METHOD_SPRINT_2026-07-27.md</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>195 = 23 reviewed_method_plan + 5 reviewed_source_lead + 15 regional_tpd_pattern_only + 152 proxy_only_unscoped.</x:v>
+        <x:v>195 = 28 reviewed_method_plan + 0 reviewed_source_lead + 15 regional_tpd_pattern_only + 152 proxy_only_unscoped.</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>Vain 23 maalla on tarkistettu maakohtainen menetelmäsuunnitelma. Viisi lähdepolkua ja 15 alueellista TPD-mallia eivät osoita kansallista myyntisarjaa; 152 reittiä vaatii maakohtaisen rajauksen.</x:v>
+        <x:v>Vain 28 maalla on tarkistettu maakohtainen menetelmäsuunnitelma. Viisi tässä sprintissä tarkistettua lähdepolkua siirrettiin maasuunnitelmiksi vasta, kun virallinen haltija, kentät, kaava ja rajoitteet oli dokumentoitu. Luokitus ei osoita kansallista myyntisarjaa; 152 reittiä vaatii maakohtaisen rajauksen.</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str">
         <x:v>Vahvistettu</x:v>
@@ -899,1295 +899,1469 @@
     </x:row>
     <x:row r="12" ht="58.5" customHeight="1">
       <x:c r="A12" s="14" t="str">
-        <x:v>Julkinen markkina-aineisto sisältää 84 havaintoa 24 lähteestä; 75 virallista havaintoa jakautuvat 39 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
+        <x:v>Itävallalla on tarkistettu vuosittaiseen lakisääteiseen myyntiraportointiin ja sähkönestevalmisteveroon perustuva menetelmäsuunnitelma; vähittäismarkkina-arvoa ei ole laskettu.</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinakoko / Itävalta</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>Markkinamittarit kattavat Kanadan, Saksan, Suomen, Uuden-Seelannin, Puolan, Ruotsin ja Yhdysvallat. FHM-luvut kuvaavat vuosien 2018–2026 raportoivia toimijoita sekä ilmoitettuja, aktiivisia ja markkinoilta poistettuja tuotteita; ne eivät ole myyntiä tai markkina-arvoa.</x:v>
+        <x:v>Virallinen reitti edellyttää edellisen vuoden vuosivolyymien raportointia ja vahvistaa sähkönestevalmisteveron alkavan 2026-04-01 tasolla EUR 200 litralta.</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>site/data/market-values.json (julkisen sivuston koneellisesti luettava lähdetiedosto)</x:v>
+        <x:v>source/FIVE_COUNTRY_METHOD_SPRINT_2026-07-27.md (Austria)</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>84 = 48 markkina- ja mallihavaintoa + 36 FHM-rakennelukua; 75 virallista = 39 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
+        <x:v>Verolliset litrat = sähkönestekohtainen nettovero / sovellettava EUR 200 litralta 2026-04-01 alkavalla jaksolla.</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja kalenterivuoden virtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva, ei valmis vuosijakso. Virallinen lähde ei tee eri mittareista yhteismitallisia.</x:v>
+        <x:v>Sekajaksot erotellaan; vuosiraportointi ja veroinversio ovat vaihtoehtoisia sovitusreittejä, eivät yhteenlaskettavia.</x:v>
       </x:c>
       <x:c r="H12" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I12" s="14" t="str">
-        <x:v>Lisämaista tarvitaan yhteismitalliset vuotuiset laite- ja nestemäisen kuluttajavähittäisarvon sarjat.</x:v>
+        <x:v>Kansallista vuosikoostetta, hintasarjaa, kattavuutta ja vähittäismyynnin sovitusta ei ole saatu; retailValueStatus on not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58.5" customHeight="1">
       <x:c r="A13" s="14" t="str">
-        <x:v>Hyväksyttyjä virallisia koko vuoden kansallisia kuluttajavähittäisarvon luovuttajamarkkinoita on nolla.</x:v>
+        <x:v>Belgian virallinen osavuosiveroluku tuottaa vain pyöristetyn 9 kuukauden verovolyymi-indikaattorin; se ei ole koko vuoden myynti eikä vähittäismarkkina-arvo.</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinakoko / Belgia</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>comparableFullYearMarketValueDonors = 0. Viisi ehdokasta on julkaistu samaa kymmenen ehdon protokollaa vasten.</x:v>
+        <x:v>Virallinen arviolta EUR 12 500 000 ja verokanta EUR 0,15 per ml vastaavat arviolta 83 333 333 ml eli 83 333 litraa.</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
+        <x:v>source/FIVE_COUNTRY_METHOD_SPRINT_2026-07-27.md (Belgium)</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>Ehdokas tulee donor-lukuun vain, kun D1–D10 läpäisevät tarkistuksen; hylätty tai avoin ehto pitää sen luvun ulkopuolella.</x:v>
+        <x:v>EUR 12 500 000 / EUR 0,15 per ml = arviolta 83 333 333 ml ≈ 83 333 litraa.</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>Virallisia alarajoja, institutionaalisia vertailuarvoja, toimitusarvoja, veroja, fyysisiä määriä ja malleja ei nimetä täydelliseksi kuluttajavähittäisarvoksi.</x:v>
+        <x:v>Luku koskee 9 kuukauden jaksoa; varastointi, rajakauppa ja maksujen ajoitus voivat vääristää tulkintaa.</x:v>
       </x:c>
       <x:c r="H13" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I13" s="14" t="str">
-        <x:v>Tarvitaan vähintään kolme hyväksyttyä donoria sekä alue- ja sääntelytyyppien peitto.</x:v>
+        <x:v>Nettoveronalaisia luovutuksia, koko vuotta, kuluttajamyyntiä, hintaa ja kanavakattavuutta ei ole vahvistettu; 9 kuukauden indikaattoria ei hyväksytä donoriksi.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="58.5" customHeight="1">
       <x:c r="A14" s="14" t="str">
-        <x:v>Uuden-Seelannin vuoden 2024 erikoistuneiden sähkötupakkakauppiaiden myynniksi ilmoitettiin vähintään 280 milj. NZD.</x:v>
+        <x:v>Sveitsillä on 2024-10-01 alkanut kahden verokannan menetelmäreitti; vähittäismarkkina-arvoa ei ole laskettu.</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko / Sveitsi</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>Terveysministeriö julkaisee virallisen kuluttajavähittäismyynnin alarajan, joka perustuu vain puutteellisiin erikoistuneiden sähkötupakkakauppiaiden myynteihin. Yleisvähittäiskauppa puuttuu, viereisiä ilmoitusvelvollisia tuotteita sisältyy eikä ministeriö suosittele aineistoa perusteelliseen tutkimukseen.</x:v>
+        <x:v>Virallinen reitti erottaa kertakäyttötuotteiden CHF 1,00 per ml ja uudelleenkäytettävien nikotiinituotteiden CHF 0,20 per ml; ensimmäinen jakso on 2024-10-01–2024-12-31.</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024</x:v>
+        <x:v>source/FIVE_COUNTRY_METHOD_SPRINT_2026-07-27.md (Switzerland)</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>Virallista vähintään-otsikkolukua käytetään suoraan; ei ekstrapolointia eikä muiden palautustyyppien yhteenlaskua.</x:v>
+        <x:v>Kertakäyttötuotteiden verollinen ml = luokan nettovero / CHF 1,00; uudelleenkäytettävien nikotiinituotteiden verollinen ml = luokan nettovero / CHF 0,20; litrat = ml / 1 000.</x:v>
       </x:c>
       <x:c r="G14" s="14" t="str">
-        <x:v>Luku on alaraja, ei koko maan sähkötupakkamarkkinan arvo.</x:v>
+        <x:v>Veroluokat on toimitettava erillään eikä yhdistetylle verolle ole yksikäsitteistä volyymiratkaisua.</x:v>
       </x:c>
       <x:c r="H14" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I14" s="14" t="str">
-        <x:v>Hanki täydellinen valtakunnallinen vain sähkötupakkatuotteita koskeva vähittäiskaupan koonti, GST-perusta ja riippumaton täsmäytys.</x:v>
+        <x:v>Luokkakohtaiset nettoverot tai millilitrat, oikaisut, nikotiinittomat täyttönesteet, hinnat ja kuluttajamyynti puuttuvat; retailValueStatus on not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="58.5" customHeight="1">
       <x:c r="A15" s="14" t="str">
-        <x:v>Uuden-Seelannin 29 virallisen vuoden 2024 XLSX-tiedoston 612 765 numeerisen Total sales -solun raakasumma on 280 684 512,81 NZD.</x:v>
+        <x:v>Luxemburgilla on 2024-10-01 alkanut valmistevero- ja veromerkkimenetelmä; vähittäismarkkina-arvoa ei ole laskettu.</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko / Luxemburg</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>Raakasumma täsmää ministeriön vähintään 280 milj. NZD otsikkolukuun. Aineistossa on 95 144 täsmälleen toistuvaa riviallekirjoitusta; niiden ensimmäisen esiintymän jälkeinen poistaminen antaisi 264 561 055,05 NZD, mutta toistojen merkitystä ei ole vahvistettu.</x:v>
+        <x:v>Virallinen verokanta on EUR 0,12 per ml 2024-10-01 alkaen, ja veromerkit sisältävät nestetilavuuden sekä pakollisen kuluttajahinnan.</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_ANNUAL_RETURNS_RECONCILIATION.md</x:v>
+        <x:v>source/FIVE_COUNTRY_METHOD_SPRINT_2026-07-27.md (Luxembourg)</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>Kaikkien 29 virallisen XLSX-tiedoston numeeristen Total sales -solujen suora summa; ei deduplikointia, puhdistusta tai ekstrapolointia.</x:v>
+        <x:v>Verolliset litrat = sähkönestekohtainen nettovero / EUR 120 litralta; merkitty kuluttajahintainen arvo = summa(merkitty pakkausmäärä × pakollinen merkitty hinta).</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>Toistuvat rivit säilytetään raakasummassa, koska niiden liiketoiminnallista merkitystä ei tunneta.</x:v>
+        <x:v>Volyymi- ja veromerkkilaskelmia ei lasketa yhteen; ulkomaan B2B-toimitukset, hävitykset, palautukset ja oikaisut erotellaan.</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>Raakasumma ei ole puhdistettu kansallinen markkina-arvo. Yleisvähittäiskauppa, puuttuvat ilmoitukset ja GST-käsittely ovat avoimia.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="93" customHeight="1">
+        <x:v>Kansallinen kooste, veromerkkien määrä- ja hintakentät, kuluttajamyynti ja kauden lopullisuus puuttuvat; retailValueStatus on not_computed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="58.5" customHeight="1">
       <x:c r="A16" s="14" t="str">
-        <x:v>Uuden-Seelannin vuoden 2024 AIS/AVP-erikoisvähittäiskaupan tunnistettu sähkötupakkasumma on 274 180 410,21 NZD; donor-testi läpäisee 7/10 ehtoa, mutta maa ei ole hyväksytty donor.</x:v>
+        <x:v>Norjalla ei ole nykyistä Article 20(7) -vuosimyyntireittiä; vuoden 2026 NOK 5,38 per ml oleva lakisääteinen verokanta ei ole käytännössä voimassa eikä osoita markkina-arvoa.</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinakoko / Norja</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>Kulutustarvikkeet ovat 189 402 451,96 NZD, laitteet/hardware 84 709 409,85 NZD ja sekajärjestelmät 68 548,40 NZD. Viereiset ilmoitusvelvolliset tuotteet 2 137 085,24 NZD ja ratkaisemattomat tuotetyypit 4 367 017,37 NZD määrällistetään erikseen ja rajataan pois. Havaittu arvo tulee vain AIS/AVP-työkirjoista; Notifier- ja RPS-arvoa ei lisätä.</x:v>
+        <x:v>Virallinen ohje kieltää nikotiinituotteiden kaupallisen tuonnin ja myynnin, eikä uutta TPD-reittiä sovelleta; SSB:n ulkomaankauppatiedot ovat vain tulliproxy.</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return ; https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf ; source/NZ_2024_DONOR_CLOSURE_PACK.md ; source/NZ_2024_D8_D10_OFFICIAL_SOURCE_AUDIT.md ; source/NZ_2024_WORKBOOK_MANIFEST.json ; source/NZ_2024_PRODUCT_SCOPE_AUDIT.json ; scripts/analyze_nz_2024_returns.py</x:v>
+        <x:v>source/FIVE_COUNTRY_METHOD_SPRINT_2026-07-27.md (Norway)</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
-      <x:c r="F16" s="17" t="str">
-        <x:v>189 402 451,96 + 84 709 409,85 + 68 548,40 = 274 180 410,21 NZD. Viereiset ja ratkaisemattomat luokat käsitellään ennen vaping-summaa ja jätetään siitä pois. Kaikkien 29 tiedoston URL:t, koot ja SHA-256-tiivisteet validoidaan ennen aggregointia.</x:v>
+      <x:c r="F16" s="14" t="str">
+        <x:v>Veroinversio sallitaan vain, jos käytännössä voimassa olevat luokkakohtaiset nettotulot saadaan; tulliproxy ei muutu kansalliseksi kuluttajamyynniksi.</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>Deterministinen tuoterajaus on julkinen. Yleisvähittäiskaupan havaittu arvo puuttuu, GST-perusta on tuntematon, täsmälleen toistuvien rivien herkkyys ei ole korjattu estimaatti eikä riippumatonta täsmäytystä ole.</x:v>
+        <x:v>Kielto, lakisääteinen verokanta tai puuttuva tietue ei osoita markkinan puuttumista.</x:v>
       </x:c>
       <x:c r="H16" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I16" s="14" t="str">
-        <x:v>D5 hylätään puuttuvan kansallisen kanavapeiton vuoksi; D8:n GST-perusta ja D10:n riippumaton täsmäytys ovat avoimia. Donor-portti pysyy 0/3:ssa.</x:v>
+        <x:v>Nikotiinittomien tuotteiden kuluttajamyynti, millilitrat, hinnat, kotimainen tuotanto, varastot, jälleenvienti ja laittomat kanavat puuttuvat; retailValueStatus on not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58.5" customHeight="1">
       <x:c r="A17" s="14" t="str">
-        <x:v>Uuden-Seelannin erillinen vuoden 2024 RPS-vähittäisherkkyys on tuettu malli: 533 662 383,68–731 175 792,50 NZD ja perusskenaario 641 811 687,89 NZD.</x:v>
+        <x:v>Italian ADM:n PLI-tuotteiden kulutusverotuotto oli 55 910 871,89 EUR vuonna 2023 ja 84 309 841,41 EUR vuonna 2024; kyse ei ole vähittäismarkkina-arvosta.</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinakoko / Italia</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>Matalan, perus- ja korkean skenaarion yhdistetyt arvot ovat 533 662 383,68 / 641 811 687,89 / 731 175 792,50 NZD. Malli yhdistää erikoisvähittäiskaupan ankkurin yleisvähittäiskaupan määrä- ja hintamalliin.</x:v>
+        <x:v>ADM:n Libro Blu 2024 -raportin taulukko III.9 näyttää 50,79 prosentin verotuottomuutoksen. Vuonna 2024 verotus laajeni myös PLI-tuotteisiin tarkoitettuihin aromeihin ja verotukseen kohdistui muutoksia, joten prosenttia ei tulkita myynti- tai volyymikasvuksi.</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_RPS_RETAIL_VALUE_SENSITIVITY.md ; source/NZ_2024_DONOR_CLOSURE_PACK.md</x:v>
+        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43 ; source/ITALY_ADM_RESPONSE_BOUNDARY_2026-07-24.md</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>Matala (täsmällisten rivien deduplikointi): 258 327 110,88 + 275 335 272,80 = 533 662 383,68 NZD. Perus (raportoidut/raakrivit): 274 180 410,21 + 367 631 277,68 = 641 811 687,89 NZD. Korkea (raportoidut/raakrivit): 274 180 410,21 + 456 995 382,29 = 731 175 792,50 NZD.</x:v>
+        <x:v>Suora taulukkotoisto: 55 910 871,89 EUR vuonna 2023; 84 309 841,41 EUR vuonna 2024; ilmoitettu muutos 50,79 prosenttia.</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>GST-käsittely, palautusten täydellisyys ja riippumaton täsmäytys ovat avoimia; ilmoittajien toimitusketjutason arvot on jätetty pois.</x:v>
+        <x:v>Verotuotto on fiskaalinen mittari. Sitä ei käännetä litroiksi tai vähittäisarvoksi ilman erillisiä verokantoja, luokkia, oikaisuja ja samaa rajausta.</x:v>
       </x:c>
       <x:c r="H17" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I17" s="14" t="str">
-        <x:v>Ei havaittu kansallinen arvo eikä hyväksytty donor. Tarvitaan viranomaisen scope- ja GST-vahvistus sekä riippumaton toisto.</x:v>
+        <x:v>Nikotiini- ja nikotiiniton jako, litrat, laitteet, kuluttajahinta, palautukset, maksujen ajoitus ja rajaukseltaan vertailukelpoinen sarja puuttuvat; Italia ei ole donor.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="58.5" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>Vuoden 2023 kuuden virallisen työkirjan uusi numeerinen rekonstruktio on jätetty tarkoituksella laskematta.</x:v>
+        <x:v>Julkinen markkina-aineisto sisältää 84 havaintoa 24 lähteestä; 75 virallista havaintoa jakautuvat 39 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>Ministeriön julkaisema koonti on vähintään 374 milj. NZD ja 2 570 ilmoitusta. Se sisältää kaikki ilmoitettavat tuotteet, myös heated tobacco -tuotteet, ja ministeriö varoittaa laadusta.</x:v>
+        <x:v>Markkinamittarit kattavat Kanadan, Saksan, Suomen, Uuden-Seelannin, Puolan, Ruotsin ja Yhdysvallat. FHM-luvut kuvaavat vuosien 2018–2026 raportoivia toimijoita sekä ilmoitettuja, aktiivisia ja markkinoilta poistettuja tuotteita; ne eivät ole myyntiä tai markkina-arvoa.</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2023 ; source/NZ_2023_ANNUAL_RETURNS_FAIL_CLOSED.md</x:v>
+        <x:v>site/data/market-values.json (julkisen sivuston koneellisesti luettava lähdetiedosto)</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>Kuusi virallista tiedostoa on eheystiivistetty; kaikki uusi laskenta palauttaa tilan not_computed.</x:v>
+        <x:v>84 = 48 markkina- ja mallihavaintoa + 36 FHM-rakennelukua; 75 virallista = 39 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
-        <x:v>Tuoterajaus, määräkentät, duplikaatit, toimitusketjutaso, veroperusta ja riippumaton täsmäytys ovat ratkaisematta.</x:v>
+        <x:v>Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja kalenterivuoden virtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva, ei valmis vuosijakso. Virallinen lähde ei tee eri mittareista yhteismitallisia.</x:v>
       </x:c>
       <x:c r="H18" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I18" s="14" t="str">
-        <x:v>Vuoden 2023 uusi vaping-only-arvo puuttuu, eikä 374 milj. NZD:tä saa nimetä puhtaaksi sähkötupakkamarkkinaksi.</x:v>
+        <x:v>Lisämaista tarvitaan yhteismitalliset vuotuiset laite- ja nestemäisen kuluttajavähittäisarvon sarjat.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="58.5" customHeight="1">
       <x:c r="A19" s="14" t="str">
-        <x:v>FTC:n virallisista taulukoista johdettu suljettujen järjestelmien ja kertakäyttötuotteiden raportoitu myynti oli 2 763 284 338 USD vuonna 2021.</x:v>
+        <x:v>Hyväksyttyjä virallisia koko vuoden kansallisia kuluttajavähittäisarvon luovuttajamarkkinoita on nolla.</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>Seitsemän vuoden 2015–2021 sarja on laskettu summaamalla vuosittain cartridge-system- ja disposable-rivit. Vuoden 2020 korjattu taulukko kattaa viisi aiempaa raportoijaa sekä kolme neljästä uudesta; vuosi 2021 kattaa kaikki yhdeksän vastaanottajaa.</x:v>
+        <x:v>comparableFullYearMarketValueDonors = 0. Viisi ehdokasta on julkaistu samaa kymmenen ehdon protokollaa vasten.</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018 ; https://www.ftc.gov/reports/e-cigarette-report-2021 ; source/US_FTC_2015_2021_REPORTED_SALES.md</x:v>
+        <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>2021</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>FTC-taulukoiden cartridge systems + disposable e-cigarettes -myynnin vuosittainen summa.</x:v>
+        <x:v>Ehdokas tulee donor-lukuun vain, kun D1–D10 läpäisevät tarkistuksen; hylätty tai avoin ehto pitää sen luvun ulkopuolella.</x:v>
       </x:c>
       <x:c r="G19" s="14" t="str">
-        <x:v>Raportoijajoukko muuttuu, open-system-tuotteet puuttuvat, taso on valmistajaraportointi ja veroperustaa ei ilmoiteta.</x:v>
+        <x:v>Virallisia alarajoja, institutionaalisia vertailuarvoja, toimitusarvoja, veroja, fyysisiä määriä ja malleja ei nimetä täydelliseksi kuluttajavähittäisarvoksi.</x:v>
       </x:c>
       <x:c r="H19" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I19" s="14" t="str">
-        <x:v>Ei täydellinen kansallinen kuluttajavähittäisarvo eikä hyväksytty donor; tarvitaan avoin POS- tai kuluttajamyyntisarja ja veroperusta.</x:v>
+        <x:v>Tarvitaan vähintään kolme hyväksyttyä donoria sekä alue- ja sääntelytyyppien peitto.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="58.5" customHeight="1">
       <x:c r="A20" s="14" t="str">
-        <x:v>Julkinen sivusto erottaa kolme evidenssikaistaa ja estää maailman kokonaisarvon, kun hyväksytty donor-portti on 0/3.</x:v>
+        <x:v>Uuden-Seelannin vuoden 2024 erikoistuneiden sähkötupakkakauppiaiden myynniksi ilmoitettiin vähintään 280 milj. NZD.</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>Viisi ehdokasta on arvioitu samoilla 10 D1–D10-kriteerillä; yksikään ei ole hyväksytty. Lisäksi alue- ja sääntelytyyppien peittoporttien on läpäistävä tarkistus.</x:v>
+        <x:v>Terveysministeriö julkaisee virallisen kuluttajavähittäismyynnin alarajan, joka perustuu vain puutteellisiin erikoistuneiden sähkötupakkakauppiaiden myynteihin. Yleisvähittäiskauppa puuttuu, viereisiä ilmoitusvelvollisia tuotteita sisältyy eikä ministeriö suosittele aineistoa perusteelliseen tutkimukseen.</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>site/data/evidence-lanes.json ; site/data/donor-cockpit.json ; site/data/third-donor-screen.json ; site/data/country-scenarios.json</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
-        <x:v>Fail-closed-portit: puuttuva tai virheellinen syöte tuottaa tilan not_computed eikä nollaa.</x:v>
+        <x:v>Virallista vähintään-otsikkolukua käytetään suoraan; ei ekstrapolointia eikä muiden palautustyyppien yhteenlaskua.</x:v>
       </x:c>
       <x:c r="G20" s="14" t="str">
-        <x:v>Vain tarkistetut julkiset koontitiedot ja menetelmät ovat julkisella kaistalla; lisensoitu ja yksityinen aineisto eivät siirry repositorioon.</x:v>
+        <x:v>Luku on alaraja, ei koko maan sähkötupakkamarkkinan arvo.</x:v>
       </x:c>
       <x:c r="H20" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I20" s="14" t="str">
-        <x:v>Maailmanarvo pysyy laskematta, kunnes vähintään kolme donoria sekä molemmat peittoportit hyväksytään.</x:v>
+        <x:v>Hanki täydellinen valtakunnallinen vain sähkötupakkatuotteita koskeva vähittäiskaupan koonti, GST-perusta ja riippumaton täsmäytys.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="58.5" customHeight="1">
       <x:c r="A21" s="14" t="str">
-        <x:v>Euroopan komissio julkaisee vuoden 2023 EU:n sähkötupakkamarkkinan 4,99 mrd euron vertailuarvon.</x:v>
+        <x:v>Uuden-Seelannin 29 virallisen vuoden 2024 XLSX-tiedoston 612 765 numeerisen Total sales -solun raakasumma on 280 684 512,81 NZD.</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
         <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>SWD(2026) 111:n fyysisen PDF:n sivun 25 alaviite 83 nimeää seuraavien sivujen taulukoiden lähteeksi Euromonitor International Tobacco 2025 -aineiston; fyysisen sivun 27 taulukko 4 raportoi 4,99 mrd euroa. SWD(2025) 560:n fyysinen sivu 161 kuvaa lähes 5 mrd euron koonnin, joka sisältää laitteet ja nesteet, myös nikotiinittomat; sivu 162 ilmoittaa Kyproksen, Luxemburgin ja Maltan tiedot puuttuviksi.</x:v>
+        <x:v>Raakasumma täsmää ministeriön vähintään 280 milj. NZD otsikkolukuun. Aineistossa on 95 144 täsmälleen toistuvaa riviallekirjoitusta; niiden ensimmäisen esiintymän jälkeinen poistaminen antaisi 264 561 055,05 NZD, mutta toistojen merkitystä ei ole vahvistettu.</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2025%3A0560%3AFIN ; https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2026%3A111%3AFIN</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_ANNUAL_RETURNS_RECONCILIATION.md</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>2023</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>Kahden Euroopan komission valmisteluasiakirjan taulukko-, sivu- ja lähdeviitteiden ristiinvertailu; lukuja ei summata.</x:v>
+        <x:v>Kaikkien 29 virallisen XLSX-tiedoston numeeristen Total sales -solujen suora summa; ei deduplikointia, puhdistusta tai ekstrapolointia.</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
-        <x:v>Komissio julkaisee vertailuarvon, mutta sen pohjana on kaupallinen Euromonitor-aineisto. Täysi menetelmä, veroperusta ja uudelleenkäytettävä maadata eivät ole julkisia, ja kolmesta EU-maasta ei ole tietoa.</x:v>
+        <x:v>Toistuvat rivit säilytetään raakasummassa, koska niiden liiketoiminnallista merkitystä ei tunneta.</x:v>
       </x:c>
       <x:c r="H21" s="14" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
-        <x:v>Hanki lisensoitu maataulukko ja menetelmä, tapahtumamääritelmä, kanavapeitto, veroperusta sekä riippumaton täsmäytys; täydennä Kypros, Luxemburg ja Malta.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="58.5" customHeight="1">
+        <x:v>Raakasumma ei ole puhdistettu kansallinen markkina-arvo. Yleisvähittäiskauppa, puuttuvat ilmoitukset ja GST-käsittely ovat avoimia.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="93" customHeight="1">
       <x:c r="A22" s="14" t="str">
-        <x:v>Kanadan virallinen vuoden 2024 kuluttajavähittäismyynnin piste-estimaatti on 1 219 160 000 CAD eli 822 583 715,21 EUR; donor-testi läpäisee 7/10 ehtoa.</x:v>
+        <x:v>Uuden-Seelannin vuoden 2024 AIS/AVP-erikoisvähittäiskaupan tunnistettu sähkötupakkasumma on 274 180 410,21 NZD; donor-testi läpäisee 7/10 ehtoa, mutta maa ei ole hyväksytty donor.</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Neljän kvartaalin summa on 1 219 160 000 CAD; 12 kuukauden samaan kyselyyn perustuva summa on 1 219 161 000 CAD. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusten nettoarvo on 1 160 753 796,78 CAD.</x:v>
+        <x:v>Kulutustarvikkeet ovat 189 402 451,96 NZD, laitteet/hardware 84 709 409,85 NZD ja sekajärjestelmät 68 548,40 NZD. Viereiset ilmoitusvelvolliset tuotteet 2 137 085,24 NZD ja ratkaisemattomat tuotetyypit 4 367 017,37 NZD määrällistetään erikseen ja rajataan pois. Havaittu arvo tulee vain AIS/AVP-työkirjoista; Notifier- ja RPS-arvoa ei lisätä.</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md ; source/CANADA_2024_D5_D7_D10_OFFICIAL_SOURCE_AUDIT.md</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return ; https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf ; source/NZ_2024_DONOR_CLOSURE_PACK.md ; source/NZ_2024_D8_D10_OFFICIAL_SOURCE_AUDIT.md ; source/NZ_2024_WORKBOOK_MANIFEST.json ; source/NZ_2024_PRODUCT_SCOPE_AUDIT.json ; scripts/analyze_nz_2024_returns.py</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="str">
-        <x:v>Kuukausi − kvartaali = 1 000 CAD (0,000082 %). Retail − toimitukset = 58 406 203,22 CAD; retail / toimitukset − 1 = 5,031748 %. ECB 2024: 1 219 160 000 / 1,482110546875 = 822 583 715,21 EUR.</x:v>
+      <x:c r="F22" s="17" t="str">
+        <x:v>189 402 451,96 + 84 709 409,85 + 68 548,40 = 274 180 410,21 NZD. Viereiset ja ratkaisemattomat luokat käsitellään ennen vaping-summaa ja jätetään siitä pois. Kaikkien 29 tiedoston URL:t, koot ja SHA-256-tiivisteet validoidaan ennen aggregointia.</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>D8 läpäisee: CAD sekä GST/HST-, provinssi- ja valmisteverojen poissulku on lähteistetty. Kuukausireitti on saman kyselyn QA, ei D10; retail- ja toimitusreitit eivät muodosta markkinahaarukkaa.</x:v>
+        <x:v>Deterministinen tuoterajaus on julkinen. Yleisvähittäiskaupan havaittu arvo puuttuu, GST-perusta on tuntematon, täsmälleen toistuvien rivien herkkyys ei ole korjattu estimaatti eikä riippumatonta täsmäytystä ole.</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I22" s="14" t="str">
-        <x:v>D5:n NAICS 459993/459999 -peitto, D7:n vuositason virheraja ja D10:n retail–toimitus-silta ovat avoimia; Kanada ei ole hyväksytty donor.</x:v>
+        <x:v>D5 hylätään puuttuvan kansallisen kanavapeiton vuoksi; D8:n GST-perusta ja D10:n riippumaton täsmäytys ovat avoimia. Donor-portti pysyy 0/3:ssa.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58.5" customHeight="1">
       <x:c r="A23" s="14" t="str">
-        <x:v>Health Canadan neljä vuoden 2024 tuoteryhmää summautuvat 1 160 753 796,78 CAD:n nettotoimitusarvoon, 118 901 910 yksikköön ja 1 251 843 litraan.</x:v>
+        <x:v>Uuden-Seelannin erillinen vuoden 2024 RPS-vähittäisherkkyys on tuettu malli: 533 662 383,68–731 175 792,50 NZD ja perusskenaario 641 811 687,89 NZD.</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>Arvo-osuudet ovat: laite tai osa ilman ainetta 2,602 %, aineen sisältävä laite 48,154 %, aineen sisältävä osa 27,252 % ja höyrystettävä aine 21,992 %. Kyse on toimituksista tukku- tai vähittäismyyjille, ei kuluttajaostoista.</x:v>
+        <x:v>Matalan, perus- ja korkean skenaarion yhdistetyt arvot ovat 533 662 383,68 / 641 811 687,89 / 731 175 792,50 NZD. Malli yhdistää erikoisvähittäiskaupan ankkurin yleisvähittäiskaupan määrä- ja hintamalliin.</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>https://health-infobase.canada.ca/substance-use/vaping/sales/ ; https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html ; source/CANADA_2024_DONOR_CLOSURE_PACK.md</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_RPS_RETAIL_VALUE_SENSITIVITY.md ; source/NZ_2024_DONOR_CLOSURE_PACK.md</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
-        <x:v>30 207 822,87 + 558 947 200,26 + 316 329 158,83 + 255 269 614,82 = 1 160 753 796,78 CAD; osuudet lasketaan tästä summasta.</x:v>
+        <x:v>Matala (täsmällisten rivien deduplikointi): 258 327 110,88 + 275 335 272,80 = 533 662 383,68 NZD. Perus (raportoidut/raakrivit): 274 180 410,21 + 367 631 277,68 = 641 811 687,89 NZD. Korkea (raportoidut/raakrivit): 274 180 410,21 + 456 995 382,29 = 731 175 792,50 NZD.</x:v>
       </x:c>
       <x:c r="G23" s="14" t="str">
-        <x:v>Nettomyynti on myynti vähennettynä palautuksilla ja arvot ilmoitetaan ilman veroja ja maksuja. Nestettä sisältävä laite tai osa yhdistää laite- ja neste-arvoa.</x:v>
+        <x:v>GST-käsittely, palautusten täydellisyys ja riippumaton täsmäytys ovat avoimia; ilmoittajien toimitusketjutason arvot on jätetty pois.</x:v>
       </x:c>
       <x:c r="H23" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>Toimitusosuuksia ei saa soveltaa retail-arvoon laite–neste-jaoksi eikä eri tapahtumatasoja summata.</x:v>
+        <x:v>Ei havaittu kansallinen arvo eikä hyväksytty donor. Tarvitaan viranomaisen scope- ja GST-vahvistus sekä riippumaton toisto.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="58.5" customHeight="1">
       <x:c r="A24" s="14" t="str">
-        <x:v>Saksan verotettu nestemäärä kasvoi 1.241 milj. l:sta 1.518 milj. l:aan vuosina 2023–2025.</x:v>
+        <x:v>Vuoden 2023 kuuden virallisen työkirjan uusi numeerinen rekonstruktio on jätetty tarkoituksella laskematta.</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>2023 ja 2024 lopullisia; 2025 alustava.</x:v>
+        <x:v>Ministeriön julkaisema koonti on vähintään 374 milj. NZD ja 2 570 ilmoitusta. Se sisältää kaikki ilmoitettavat tuotteet, myös heated tobacco -tuotteet, ja ministeriö varoittaa laadusta.</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2023 ; source/NZ_2023_ANNUAL_RETURNS_FAIL_CLOSED.md</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
-        <x:v>2023–2025</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>Destatis-taulukon nettomäärät, ei ekstrapolointia.</x:v>
+        <x:v>Kuusi virallista tiedostoa on eheystiivistetty; kaikki uusi laskenta palauttaa tilan not_computed.</x:v>
       </x:c>
       <x:c r="G24" s="14" t="str">
-        <x:v>Mittaa verotettua nestettä, ei laitteita tai laitonta myyntiä.</x:v>
+        <x:v>Tuoterajaus, määräkentät, duplikaatit, toimitusketjutaso, veroperusta ja riippumaton täsmäytys ovat ratkaisematta.</x:v>
       </x:c>
       <x:c r="H24" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I24" s="14" t="str">
-        <x:v>Vuoden 2025 lopullinen luku ja vähittäismyyntitiedot puuttuvat.</x:v>
+        <x:v>Vuoden 2023 uusi vaping-only-arvo puuttuu, eikä 374 milj. NZD:tä saa nimetä puhtaaksi sähkötupakkamarkkinaksi.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="58.5" customHeight="1">
       <x:c r="A25" s="14" t="str">
-        <x:v>Saksan tupakankorvikkeiden valmisteverotulot olivat 404 milj. euroa vuonna 2025 (alustava).</x:v>
+        <x:v>FTC:n virallisista taulukoista johdettu suljettujen järjestelmien ja kertakäyttötuotteiden raportoitu myynti oli 2 763 284 338 USD vuonna 2021.</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Alustavat viralliset kassaperusteiset valmisteverotulot. Verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</x:v>
+        <x:v>Seitsemän vuoden 2015–2021 sarja on laskettu summaamalla vuosittain cartridge-system- ja disposable-rivit. Vuoden 2020 korjattu taulukko kattaa viisi aiempaa raportoijaa sekä kolme neljästä uudesta; vuosi 2021 kattaa kaikki yhdeksän vastaanottajaa.</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018 ; https://www.ftc.gov/reports/e-cigarette-report-2021 ; source/US_FTC_2015_2021_REPORTED_SALES.md</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
-        <x:v>2025</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>Virallinen kassaperusteinen verohavainto.</x:v>
+        <x:v>FTC-taulukoiden cartridge systems + disposable e-cigarettes -myynnin vuosittainen summa.</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>Verotulo ei ole myyntitulo tai vähittäismarkkina-arvo.</x:v>
+        <x:v>Raportoijajoukko muuttuu, open-system-tuotteet puuttuvat, taso on valmistajaraportointi ja veroperustaa ei ilmoiteta.</x:v>
       </x:c>
       <x:c r="H25" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
-        <x:v>Tarvitaan lopullinen 2025 tilasto ja tuoteryhmäkohtainen veropohja.</x:v>
+        <x:v>Ei täydellinen kansallinen kuluttajavähittäisarvo eikä hyväksytty donor; tarvitaan avoin POS- tai kuluttajamyyntisarja ja veroperusta.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58.5" customHeight="1">
       <x:c r="A26" s="14" t="str">
-        <x:v>Suomessa verotettiin 11 801,062 litraa nikotiininestettä vuonna 2025.</x:v>
+        <x:v>Julkinen sivusto erottaa kolme evidenssikaistaa ja estää maailman kokonaisarvon, kun hyväksytty donor-portti on 0/3.</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>Virallinen koko vuoden nikotiinillisen sähkösavukenesteen määrä. Nikotiinittoman nesteen koko vuoden arvo on salattu; fyysinen määrä ei sisällä laitteita eikä ole vähittäismarkkina-arvo.</x:v>
+        <x:v>Viisi ehdokasta on arvioitu samoilla 10 D1–D10-kriteerillä; yksikään ei ole hyväksytty. Lisäksi alue- ja sääntelytyyppien peittoporttien on läpäistävä tarkistus.</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</x:v>
+        <x:v>site/data/evidence-lanes.json ; site/data/donor-cockpit.json ; site/data/third-donor-screen.json ; site/data/country-scenarios.json</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
-        <x:v>2025</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
-        <x:v>Verohallinnon PXWeb-havainto.</x:v>
+        <x:v>Fail-closed-portit: puuttuva tai virheellinen syöte tuottaa tilan not_computed eikä nollaa.</x:v>
       </x:c>
       <x:c r="G26" s="14" t="str">
-        <x:v>Verotettu nikotiinineste ei kata koko sähkötupakkamarkkinaa.</x:v>
+        <x:v>Vain tarkistetut julkiset koontitiedot ja menetelmät ovat julkisella kaistalla; lisensoitu ja yksityinen aineisto eivät siirry repositorioon.</x:v>
       </x:c>
       <x:c r="H26" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I26" s="14" t="str">
-        <x:v>Laitteet, nikotiinittomat tuotteet, veroton ja laiton kauppa puuttuvat.</x:v>
+        <x:v>Maailmanarvo pysyy laskematta, kunnes vähintään kolme donoria sekä molemmat peittoportit hyväksytään.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="58.5" customHeight="1">
       <x:c r="A27" s="14" t="str">
-        <x:v>Suomen nikotiininesteiden valmisteverotulot olivat 3 540 319 euroa vuonna 2025.</x:v>
+        <x:v>Euroopan komissio julkaisee vuoden 2023 EU:n sähkötupakkamarkkinan 4,99 mrd euron vertailuarvon.</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
         <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Viralliset koko vuoden nikotiinillisen sähkösavukenesteen valmisteverotulot. Nikotiinittoman nesteen koko vuoden arvo on salattu; verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</x:v>
+        <x:v>SWD(2026) 111:n fyysisen PDF:n sivun 25 alaviite 83 nimeää seuraavien sivujen taulukoiden lähteeksi Euromonitor International Tobacco 2025 -aineiston; fyysisen sivun 27 taulukko 4 raportoi 4,99 mrd euroa. SWD(2025) 560:n fyysinen sivu 161 kuvaa lähes 5 mrd euron koonnin, joka sisältää laitteet ja nesteet, myös nikotiinittomat; sivu 162 ilmoittaa Kyproksen, Luxemburgin ja Maltan tiedot puuttuviksi.</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</x:v>
+        <x:v>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2025%3A0560%3AFIN ; https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=SWD%3A2026%3A111%3AFIN</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
-        <x:v>2025</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="F27" s="14" t="str">
-        <x:v>Verohallinnon PXWeb-havainto.</x:v>
+        <x:v>Kahden Euroopan komission valmisteluasiakirjan taulukko-, sivu- ja lähdeviitteiden ristiinvertailu; lukuja ei summata.</x:v>
       </x:c>
       <x:c r="G27" s="14" t="str">
-        <x:v>Verotulo ei ole kuluttajamyynti.</x:v>
+        <x:v>Komissio julkaisee vertailuarvon, mutta sen pohjana on kaupallinen Euromonitor-aineisto. Täysi menetelmä, veroperusta ja uudelleenkäytettävä maadata eivät ole julkisia, ja kolmesta EU-maasta ei ole tietoa.</x:v>
       </x:c>
       <x:c r="H27" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I27" s="14" t="str">
-        <x:v>Tarvitaan vähittäismyynti- ja hintadata.</x:v>
+        <x:v>Hanki lisensoitu maataulukko ja menetelmä, tapahtumamääritelmä, kanavapeitto, veroperusta sekä riippumaton täsmäytys; täydennä Kypros, Luxemburg ja Malta.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="58.5" customHeight="1">
       <x:c r="A28" s="14" t="str">
-        <x:v>Puolan virallinen sähkötupakkanesteiden virta oli 1 451 529 litraa vuonna 2020, 277 265 litraa vuonna 2021, 416 088 litraa vuonna 2022 ja 805 441 litraa vuonna 2023.</x:v>
+        <x:v>Kanadan virallinen vuoden 2024 kuluttajavähittäismyynnin piste-estimaatti on 1 219 160 000 CAD eli 822 583 715,21 EUR; donor-testi läpäisee 7/10 ehtoa.</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>Ministeriön parlamenttivastauksen taulukko yhdistää ZEFIR2/AIS-järjestelmiin kirjatut kotimaan myynnit, EU-sisäiset hankinnat ja tuonnin. Sarja on fyysinen e-nestevirta, ei kuluttajamyynti tai havaittu vähittäismarkkina-arvo.</x:v>
+        <x:v>Neljän kvartaalin summa on 1 219 160 000 CAD; 12 kuukauden samaan kyselyyn perustuva summa on 1 219 161 000 CAD. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusten nettoarvo on 1 160 753 796,78 CAD.</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDDEJZ5/i07255-o1.pdf</x:v>
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md ; source/CANADA_2024_D5_D7_D10_OFFICIAL_SOURCE_AUDIT.md</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
-        <x:v>2020–2023</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
-        <x:v>Neljän virallisen vuosihavainnon suora toisto; eri vuosia ei summata markkina-arvoksi.</x:v>
+        <x:v>Kuukausi − kvartaali = 1 000 CAD (0,000082 %). Retail − toimitukset = 58 406 203,22 CAD; retail / toimitukset − 1 = 5,031748 %. ECB 2024: 1 219 160 000 / 1,482110546875 = 822 583 715,21 EUR.</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>Julkaistu taulukko ei erittele kotimaan myyntiä, EU-sisäisiä hankintoja ja tuontia eikä sisällä laitteiden arvoa.</x:v>
+        <x:v>D8 läpäisee: CAD sekä GST/HST-, provinssi- ja valmisteverojen poissulku on lähteistetty. Kuukausireitti on saman kyselyn QA, ei D10; retail- ja toimitusreitit eivät muodosta markkinahaarukkaa.</x:v>
       </x:c>
       <x:c r="H28" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
-        <x:v>Tarvitaan kuluttajavähittäisarvo, kanavapeitto, veroperusta ja riippumaton täsmäytys.</x:v>
+        <x:v>D5:n NAICS 459993/459999 -peitto, D7:n vuositason virheraja ja D10:n retail–toimitus-silta ovat avoimia; Kanada ei ole hyväksytty donor.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58.5" customHeight="1">
       <x:c r="A29" s="14" t="str">
-        <x:v>Puolan vuoden 2025 verosilta antaa 4 382 500 johdettua verollista sähkötupakkalaitetta ja 62 500 johdettua verollista osasarjaa.</x:v>
+        <x:v>Health Canadan neljä vuoden 2024 tuoteryhmää summautuvat 1 160 753 796,78 CAD:n nettotoimitusarvoon, 118 901 910 yksikköön ja 1 251 843 litraan.</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>Virallinen parlamenttivastaus raportoi 993,1 milj. PLN e-nesteistä, 175,3 milj. PLN laitteista ja 2,5 milj. PLN osasarjoista. Laitteiden ja osasarjojen vero oli 40 PLN yksiköltä 1.7.2025 alkaen.</x:v>
+        <x:v>Arvo-osuudet ovat: laite tai osa ilman ainetta 2,602 %, aineen sisältävä laite 48,154 %, aineen sisältävä osa 27,252 % ja höyrystettävä aine 21,992 %. Kyse on toimituksista tukku- tai vähittäismyyjille, ei kuluttajaostoista.</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf ; https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+        <x:v>https://health-infobase.canada.ca/substance-use/vaping/sales/ ; https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html ; source/CANADA_2024_DONOR_CLOSURE_PACK.md</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
-        <x:v>2025</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
-        <x:v>175 300 000 / 40 = 4 382 500 verollista laitetta; 2 500 000 / 40 = 62 500 verollista osasarjaa.</x:v>
+        <x:v>30 207 822,87 + 558 947 200,26 + 316 329 158,83 + 255 269 614,82 = 1 160 753 796,78 CAD; osuudet lasketaan tästä summasta.</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>Johdettu veropohja kattaa vain 1.7.2025 alkaen verotetut laitteet ja osasarjat. Se ei osoita kuluttajahintaa, vähittäismyyntiä, verottomia määriä tai varastosiirtymiä.</x:v>
+        <x:v>Nettomyynti on myynti vähennettynä palautuksilla ja arvot ilmoitetaan ilman veroja ja maksuja. Nestettä sisältävä laite tai osa yhdistää laite- ja neste-arvoa.</x:v>
       </x:c>
       <x:c r="H29" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
-        <x:v>Tarvitaan veron kuukausijakauma, lopullisuus, vähittäishinnat, kanavapeitto ja riippumaton täsmäytys.</x:v>
+        <x:v>Toimitusosuuksia ei saa soveltaa retail-arvoon laite–neste-jaoksi eikä eri tapahtumatasoja summata.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="58.5" customHeight="1">
       <x:c r="A30" s="14" t="str">
-        <x:v>Ruotsin julkinen evidenssi yhdistää vuoden 2024 veroankkurin ja 36 virallista FHM-rekisterirakenteen lukua vuosilta 2018–2026; rekisteriluvut eivät ole myyntiä tai markkina-arvoa.</x:v>
+        <x:v>Saksan verotettu nestemäärä kasvoi 1.241 milj. l:sta 1.518 milj. l:aan vuosina 2023–2025.</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>Vuonna 2024 verotettiin 26 000 litraa nikotiininestettä ja valmisteverotulo oli pyöristetysti 80 000 000 SEK. Viranomaisen toimittamassa ja 24.7.2026 tarkistetussa työkirjassa on 9 vuosilabelia × 4 rakennemittaria: raportoivat toimijat sekä ilmoitetut, aktiiviset ja markkinoilta poistetut tuotteet. Julkinen FHM-sivu dokumentoi ilmoitusjärjestelmän, ei siinä julkaistua numeerista sarjaa.</x:v>
+        <x:v>2023 ja 2024 lopullisia; 2025 alustava.</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
-        <x:v>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf ; https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/ ; site/data/market-values.json</x:v>
+        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2023–2025</x:v>
       </x:c>
       <x:c r="F30" s="14" t="str">
-        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 39 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
+        <x:v>Destatis-taulukon nettomäärät, ei ekstrapolointia.</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>Rakenneluvuista ei päätellä myyntiarvoa, myyntimäärää tai markkinaosuutta. Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja vuosivirtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva eikä sitä vuositasoiteta.</x:v>
+        <x:v>Mittaa verotettua nestettä, ei laitteita tai laitonta myyntiä.</x:v>
       </x:c>
       <x:c r="H30" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I30" s="14" t="str">
-        <x:v>Tarvitaan toteutunut kuluttajamyynti EUR-määräisenä, laitekappaleet ja ml-määrät sekä julkisesti uudelleenkäytettävä numeerinen FHM-sarja.</x:v>
+        <x:v>Vuoden 2025 lopullinen luku ja vähittäismyyntitiedot puuttuvat.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="58.5" customHeight="1">
       <x:c r="A31" s="14" t="str">
-        <x:v>Kolme kaupallista vuoden 2025 globaaliarviota muodostavat 26,0–46,32 mrd USD haarukan.</x:v>
+        <x:v>Saksan tupakankorvikkeiden valmisteverotulot olivat 404 milj. euroa vuonna 2025 (alustava).</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
         <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>IMARC 26,0; Grand View Research 45,7; Fortune Business Insights 46,32 mrd USD.</x:v>
+        <x:v>Alustavat viralliset kassaperusteiset valmisteverotulot. Verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>https://www.imarcgroup.com/e-cigarette-market ; https://www.grandviewresearch.com/industry-analysis/e-cigarette-vaping-market ; https://www.fortunebusinessinsights.com/e-cigarette-and-vaping-market-114882</x:v>
+        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F31" s="14" t="str">
-        <x:v>Minimi 26000000000, maksimi 46320000000; arvioita verrataan, ei summata.</x:v>
+        <x:v>Virallinen kassaperusteinen verohavainto.</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>Tuoterajaukset ja menetelmät eivät välttämättä ole yhteismitallisia.</x:v>
+        <x:v>Verotulo ei ole myyntitulo tai vähittäismarkkina-arvo.</x:v>
       </x:c>
       <x:c r="H31" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I31" s="14" t="str">
-        <x:v>Hanki raporttien täydet metodit ja harmonisoi tuoterajaus.</x:v>
+        <x:v>Tarvitaan lopullinen 2025 tilasto ja tuoteryhmäkohtainen veropohja.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="58.5" customHeight="1">
       <x:c r="A32" s="14" t="str">
-        <x:v>Saksan vuoden 2025 verotetun nesteen vähittäismyyntivastaavuuden mallihaitari on 667,92–1 654,62 milj. euroa.</x:v>
+        <x:v>Suomessa verotettiin 11 801,062 litraa nikotiininestettä vuonna 2025.</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>Taloudellinen malli</x:v>
+        <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>Ei havaittua myyntiä. Laskelma kertoo vuoden 2025 alustavan verotetun nestemäärän kolmella yksittäisellä saksalaisen verkkokaupan vuoden 2026 hinnalla. Vuosiero, yhden kaupan hintakori, tuotejakauma ja pois rajatut tuoteryhmät tekevät luottamustasosta matalan.</x:v>
+        <x:v>Virallinen koko vuoden nikotiinillisen sähkösavukenesteen määrä. Nikotiinittoman nesteen koko vuoden arvo on salattu; fyysinen määrä ei sisällä laitteita eikä ole vähittäismarkkina-arvo.</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
-        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003 ; https://www.intaste.de/pfefferminz-liquid-germanflavours-liquid ; https://www.intaste.de/anstand-liquid-samurai-liquid ; https://www.intaste.de/tobacco-vanilla-nikotinsalz-revoltage-liquid</x:v>
+        <x:v>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
-        <x:v>2025 määrä / 2026 hinnat</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F32" s="14" t="str">
-        <x:v>volume_litres * 1000 * retail_price_eur_per_ml</x:v>
+        <x:v>Verohallinnon PXWeb-havainto.</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>Kolme yksittäistä verkkokauppahintaa; syötevuodet 2025 ja 2026; vain verotettu neste.</x:v>
+        <x:v>Verotettu nikotiinineste ei kata koko sähkötupakkamarkkinaa.</x:v>
       </x:c>
       <x:c r="H32" s="14" t="str">
-        <x:v>Oletus</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I32" s="14" t="str">
-        <x:v>Tarvitaan edustava hintakori, tuotemix ja kanavamarginaalit sekä mallivuoden 2025 hinnat.</x:v>
+        <x:v>Laitteet, nikotiinittomat tuotteet, veroton ja laiton kauppa puuttuvat.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="58.5" customHeight="1">
       <x:c r="A33" s="14" t="str">
-        <x:v>Atlas ei ole vielä lainanantajavalmis markkina-arvio.</x:v>
+        <x:v>Suomen nikotiininesteiden valmisteverotulot olivat 3 540 319 euroa vuonna 2025.</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>research_dataset_not_valuation: Useimmista maista puuttuu virallinen vuosittainen laite- ja nestemyynti Markkinaevidenssiä ei ole vielä sidottu maakohtaiseen patenttistatukseen ja claim charteihin Aineisto ei sisällä riippumatonta IVS-arvonmääritystä eikä realisoitunutta lisenssi- tai vahingonkorvauskassavirtaa</x:v>
+        <x:v>Viralliset koko vuoden nikotiinillisen sähkösavukenesteen valmisteverotulot. Nikotiinittoman nesteen koko vuoden arvo on salattu; verotulo ei ole myyntituloa eikä vähittäismarkkina-arvoa.</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>site/data/atlas.json (readiness)</x:v>
+        <x:v>https://vero2.stat.fi/PXWeb/api/v1/en/Vero/Valmistevero/vvt_010.px</x:v>
       </x:c>
       <x:c r="E33" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F33" s="14" t="str">
-        <x:v>Julkisen datasetin oma readiness-luokitus.</x:v>
+        <x:v>Verohallinnon PXWeb-havainto.</x:v>
       </x:c>
       <x:c r="G33" s="14" t="str">
-        <x:v>Markkinadata ja IP-arvo pidetään erillään.</x:v>
+        <x:v>Verotulo ei ole kuluttajamyynti.</x:v>
       </x:c>
       <x:c r="H33" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I33" s="14" t="str">
-        <x:v>Täytä blocker-lista ennen vakuusarvo- tai yritysarvopäätelmää.</x:v>
+        <x:v>Tarvitaan vähittäismyynti- ja hintadata.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="58.5" customHeight="1">
       <x:c r="A34" s="14" t="str">
-        <x:v>Julkinen aineisto ei sisällä riippumatonta IVS-arvonmääritystä.</x:v>
+        <x:v>Puolan virallinen sähkötupakkanesteiden virta oli 1 451 529 litraa vuonna 2020, 277 265 litraa vuonna 2021, 416 088 litraa vuonna 2022 ja 805 441 litraa vuonna 2023.</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>Taloudellinen malli</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>Readiness-blocker ilmoittaa riippumattoman arvonmäärityksen puuttuvan.</x:v>
+        <x:v>Ministeriön parlamenttivastauksen taulukko yhdistää ZEFIR2/AIS-järjestelmiin kirjatut kotimaan myynnit, EU-sisäiset hankinnat ja tuonnin. Sarja on fyysinen e-nestevirta, ei kuluttajamyynti tai havaittu vähittäismarkkina-arvo.</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
-        <x:v>site/data/atlas.json (readiness.blockers)</x:v>
+        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDDEJZ5/i07255-o1.pdf</x:v>
       </x:c>
       <x:c r="E34" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2020–2023</x:v>
       </x:c>
       <x:c r="F34" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>Neljän virallisen vuosihavainnon suora toisto; eri vuosia ei summata markkina-arvoksi.</x:v>
       </x:c>
       <x:c r="G34" s="14" t="str">
-        <x:v>Ei oletuksia.</x:v>
+        <x:v>Julkaistu taulukko ei erittele kotimaan myyntiä, EU-sisäisiä hankintoja ja tuontia eikä sisällä laitteiden arvoa.</x:v>
       </x:c>
       <x:c r="H34" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I34" s="14" t="str">
-        <x:v>Tilaa riippumaton IP- ja tarvittaessa yritysarvonmääritys skenaarioineen.</x:v>
+        <x:v>Tarvitaan kuluttajavähittäisarvo, kanavapeitto, veroperusta ja riippumaton täsmäytys.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="58.5" customHeight="1">
       <x:c r="A35" s="14" t="str">
-        <x:v>Julkinen aineisto ei osoita toteutunutta lisenssi- tai vahingonkorvauskassavirtaa.</x:v>
+        <x:v>Puolan vuoden 2025 verosilta antaa 4 382 500 johdettua verollista sähkötupakkalaitetta ja 62 500 johdettua verollista osasarjaa.</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
-        <x:v>Kaupallistamismalli</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>Readiness-blocker ilmoittaa realisoituneen kassavirran puuttuvan.</x:v>
+        <x:v>Virallinen parlamenttivastaus raportoi 993,1 milj. PLN e-nesteistä, 175,3 milj. PLN laitteista ja 2,5 milj. PLN osasarjoista. Laitteiden ja osasarjojen vero oli 40 PLN yksiköltä 1.7.2025 alkaen.</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>site/data/atlas.json (readiness.blockers)</x:v>
+        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf ; https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
       </x:c>
       <x:c r="E35" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F35" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>175 300 000 / 40 = 4 382 500 verollista laitetta; 2 500 000 / 40 = 62 500 verollista osasarjaa.</x:v>
       </x:c>
       <x:c r="G35" s="14" t="str">
-        <x:v>Ei oletuksia.</x:v>
+        <x:v>Johdettu veropohja kattaa vain 1.7.2025 alkaen verotetut laitteet ja osasarjat. Se ei osoita kuluttajahintaa, vähittäismyyntiä, verottomia määriä tai varastosiirtymiä.</x:v>
       </x:c>
       <x:c r="H35" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I35" s="14" t="str">
-        <x:v>Lisää allekirjoitetut sopimukset, laskut, maksutositteet ja saamisten täsmäytys.</x:v>
+        <x:v>Tarvitaan veron kuukausijakauma, lopullisuus, vähittäishinnat, kanavapeitto ja riippumaton täsmäytys.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="58.5" customHeight="1">
       <x:c r="A36" s="14" t="str">
-        <x:v>Julkinen aineisto ei vahvista testituloksia tai riippumatonta teknistä validointia.</x:v>
+        <x:v>Ruotsin julkinen evidenssi yhdistää vuoden 2024 veroankkurin ja 36 virallista FHM-rekisterirakenteen lukua vuosilta 2018–2026; rekisteriluvut eivät ole myyntiä tai markkina-arvoa.</x:v>
       </x:c>
       <x:c r="B36" s="14" t="str">
-        <x:v>Tekninen erottautuminen</x:v>
+        <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>Patenttiselitys kuvaa ratkaisun; erillistä testirekisteriä ei ole julkisessa datassa.</x:v>
+        <x:v>Vuonna 2024 verotettiin 26 000 litraa nikotiininestettä ja valmisteverotulo oli pyöristetysti 80 000 000 SEK. Viranomaisen toimittamassa ja 24.7.2026 tarkistetussa työkirjassa on 9 vuosilabelia × 4 rakennemittaria: raportoivat toimijat sekä ilmoitetut, aktiiviset ja markkinoilta poistetut tuotteet. Julkinen FHM-sivu dokumentoi ilmoitusjärjestelmän, ei siinä julkaistua numeerista sarjaa.</x:v>
       </x:c>
       <x:c r="D36" s="14" t="str">
-        <x:v>site/data/patent-history.json</x:v>
+        <x:v>https://www.regeringen.se/contentassets/1ed01e00001b42e5ad8d47433db63ece/berakningskonventioner_2026.pdf ; https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/ ; site/data/market-values.json</x:v>
       </x:c>
       <x:c r="E36" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
-        <x:v>Aineiston puute suhteessa tekniseen suorituskykyväitteeseen.</x:v>
+        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 39 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>Patenttijulkaisu ei ole tuotetestiraportti.</x:v>
+        <x:v>Rakenneluvuista ei päätellä myyntiarvoa, myyntimäärää tai markkinaosuutta. Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja vuosivirtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva eikä sitä vuositasoiteta.</x:v>
       </x:c>
       <x:c r="H36" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I36" s="14" t="str">
-        <x:v>Hanki testiprotokolla, riippumaton laboratorio, tulokset ja raakadata.</x:v>
+        <x:v>Tarvitaan toteutunut kuluttajamyynti EUR-määräisenä, laitekappaleet ja ml-määrät sekä julkisesti uudelleenkäytettävä numeerinen FHM-sarja.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="58.5" customHeight="1">
       <x:c r="A37" s="14" t="str">
-        <x:v>Julkinen aineisto ei vahvista piloteja tai nimettyä asiakasnäyttöä.</x:v>
+        <x:v>Kolme kaupallista vuoden 2025 globaaliarviota muodostavat 26,0–46,32 mrd USD haarukan.</x:v>
       </x:c>
       <x:c r="B37" s="14" t="str">
-        <x:v>Validointi</x:v>
+        <x:v>Markkinan koko</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>Julkisessa evidenssirekisterissä ei ole pilotti- tai asiakasvalidointia.</x:v>
+        <x:v>IMARC 26,0; Grand View Research 45,7; Fortune Business Insights 46,32 mrd USD.</x:v>
       </x:c>
       <x:c r="D37" s="14" t="str">
-        <x:v>site/data/evidence.csv</x:v>
+        <x:v>https://www.imarcgroup.com/e-cigarette-market ; https://www.grandviewresearch.com/industry-analysis/e-cigarette-vaping-market ; https://www.fortunebusinessinsights.com/e-cigarette-and-vaping-market-114882</x:v>
       </x:c>
       <x:c r="E37" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F37" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>Minimi 26000000000, maksimi 46320000000; arvioita verrataan, ei summata.</x:v>
       </x:c>
       <x:c r="G37" s="14" t="str">
-        <x:v>Ei päätellä asiakkaiden olemassaoloa tai puuttumista yhtiötasolla.</x:v>
+        <x:v>Tuoterajaukset ja menetelmät eivät välttämättä ole yhteismitallisia.</x:v>
       </x:c>
       <x:c r="H37" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I37" s="14" t="str">
-        <x:v>Lisää allekirjoitetut pilotit, toimitusnäyttö, asiakasreferenssit ja käyttödata.</x:v>
+        <x:v>Hanki raporttien täydet metodit ja harmonisoi tuoterajaus.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="58.5" customHeight="1">
       <x:c r="A38" s="14" t="str">
-        <x:v>Julkinen aineisto ei vahvista nykyistä maakohtaista omistusta, vuosimaksuja ja rasitteettomuutta koko perheessä.</x:v>
+        <x:v>Saksan vuoden 2025 verotetun nesteen vähittäismyyntivastaavuuden mallihaitari on 667,92–1 654,62 milj. euroa.</x:v>
       </x:c>
       <x:c r="B38" s="14" t="str">
-        <x:v>IP-status</x:v>
+        <x:v>Taloudellinen malli</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
-        <x:v>Perhejulkaisut eivät yksin osoita kansallista post-grant-tilaa.</x:v>
+        <x:v>Ei havaittua myyntiä. Laskelma kertoo vuoden 2025 alustavan verotetun nestemäärän kolmella yksittäisellä saksalaisen verkkokaupan vuoden 2026 hinnalla. Vuosiero, yhden kaupan hintakori, tuotejakauma ja pois rajatut tuoteryhmät tekevät luottamustasosta matalan.</x:v>
       </x:c>
       <x:c r="D38" s="14" t="str">
-        <x:v>https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=family ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=legal ; https://www.epo.org/en/applying/european/validation</x:v>
+        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003 ; https://www.intaste.de/pfefferminz-liquid-germanflavours-liquid ; https://www.intaste.de/anstand-liquid-samurai-liquid ; https://www.intaste.de/tobacco-vanilla-nikotinsalz-revoltage-liquid</x:v>
       </x:c>
       <x:c r="E38" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2025 määrä / 2026 hinnat</x:v>
       </x:c>
       <x:c r="F38" s="14" t="str">
-        <x:v>Diligence-rajaus.</x:v>
+        <x:v>volume_litres * 1000 * retail_price_eur_per_ml</x:v>
       </x:c>
       <x:c r="G38" s="14" t="str">
-        <x:v>Neljä kansallista rekisterijurisdiktiota ei kata koko perhettä.</x:v>
+        <x:v>Kolme yksittäistä verkkokauppahintaa; syötevuodet 2025 ja 2026; vain verotettu neste.</x:v>
       </x:c>
       <x:c r="H38" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Oletus</x:v>
       </x:c>
       <x:c r="I38" s="14" t="str">
-        <x:v>Laadi asiamiehen allekirjoittama maamatriisi ja liitä tuoreet rekisteriotteet sekä maksukuitit.</x:v>
+        <x:v>Tarvitaan edustava hintakori, tuotemix ja kanavamarginaalit sekä mallivuoden 2025 hinnat.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="58.5" customHeight="1">
       <x:c r="A39" s="14" t="str">
-        <x:v>Julkinen aineisto ei sisällä maakohtaisia tuote–vaatimusvertailuja.</x:v>
+        <x:v>Atlas ei ole vielä lainanantajavalmis markkina-arvio.</x:v>
       </x:c>
       <x:c r="B39" s="14" t="str">
-        <x:v>Tekninen erottautuminen</x:v>
+        <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>Patenttihistorian guardrail edellyttää counsel-reviewed claim chartia.</x:v>
+        <x:v>research_dataset_not_valuation: Useimmista maista puuttuu virallinen vuosittainen laite- ja nestemyynti Markkinaevidenssiä ei ole vielä sidottu maakohtaiseen patenttistatukseen ja claim charteihin Aineisto ei sisällä riippumatonta IVS-arvonmääritystä eikä realisoitunutta lisenssi- tai vahingonkorvauskassavirtaa</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
-        <x:v>https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB2/document.pdf ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</x:v>
+        <x:v>site/data/atlas.json (readiness)</x:v>
       </x:c>
       <x:c r="E39" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F39" s="14" t="str">
-        <x:v>Vaatimuspiirteiden tuotekohtainen kartoitus puuttuu.</x:v>
+        <x:v>Julkisen datasetin oma readiness-luokitus.</x:v>
       </x:c>
       <x:c r="G39" s="14" t="str">
-        <x:v>Samankaltaisuus ei ole loukkaus.</x:v>
+        <x:v>Markkinadata ja IP-arvo pidetään erillään.</x:v>
       </x:c>
       <x:c r="H39" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I39" s="14" t="str">
-        <x:v>Hanki tuotteet, säilytä hallussapitoketju, tee teardown ja asiamiehen tarkastama claim chart.</x:v>
+        <x:v>Täytä blocker-lista ennen vakuusarvo- tai yritysarvopäätelmää.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="58.5" customHeight="1">
       <x:c r="A40" s="14" t="str">
-        <x:v>Markkinan kokonaisarvo ei ole automaattisesti rojaltipohja.</x:v>
+        <x:v>Julkinen aineisto ei sisällä riippumatonta IVS-arvonmääritystä.</x:v>
       </x:c>
       <x:c r="B40" s="14" t="str">
         <x:v>Taloudellinen malli</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
-        <x:v>Patenttihistorian kaupallistamisrajaus erottaa markkinan, kohdistettavan myynnin ja kassavirran.</x:v>
+        <x:v>Readiness-blocker ilmoittaa riippumattoman arvonmäärityksen puuttuvan.</x:v>
       </x:c>
       <x:c r="D40" s="14" t="str">
-        <x:v>https://www.wipo.int/en/web/business/ip-valuation</x:v>
+        <x:v>site/data/atlas.json (readiness.blockers)</x:v>
       </x:c>
       <x:c r="E40" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F40" s="14" t="str">
-        <x:v>Arvonmäärityksen perusrajaus.</x:v>
+        <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G40" s="14" t="str">
-        <x:v>Rojaltipohja vaatii patentin maantieteellisen, ajallisen ja tuotekohtaisen osuvuuden.</x:v>
+        <x:v>Ei oletuksia.</x:v>
       </x:c>
       <x:c r="H40" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I40" s="14" t="str">
-        <x:v>Tarvitaan addressable/in-scope/claim-mapped sales -silta.</x:v>
+        <x:v>Tilaa riippumaton IP- ja tarvittaessa yritysarvonmääritys skenaarioineen.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="58.5" customHeight="1">
       <x:c r="A41" s="14" t="str">
-        <x:v>Patenttiarvo, yritysarvo, osakearvo ja vakuusarvo ovat eri mittareita.</x:v>
+        <x:v>Julkinen aineisto ei osoita toteutunutta lisenssi- tai vahingonkorvauskassavirtaa.</x:v>
       </x:c>
       <x:c r="B41" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Kaupallistamismalli</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
-        <x:v>WIPO:n IP-arvonmääritys- ja rahoituskehys sekä aineiston oma guardrail.</x:v>
+        <x:v>Readiness-blocker ilmoittaa realisoituneen kassavirran puuttuvan.</x:v>
       </x:c>
       <x:c r="D41" s="14" t="str">
-        <x:v>https://www.wipo.int/en/web/business/ip-valuation ; https://www.wipo.int/en/web/ip-financing</x:v>
+        <x:v>site/data/atlas.json (readiness.blockers)</x:v>
       </x:c>
       <x:c r="E41" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F41" s="14" t="str">
-        <x:v>Arvokäsitteiden erottelu.</x:v>
+        <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G41" s="14" t="str">
         <x:v>Ei oletuksia.</x:v>
       </x:c>
       <x:c r="H41" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I41" s="14" t="str">
-        <x:v>Rahoitusrakenne ja vakuusarvo vaativat erillisen oikeudellisen ja taloudellisen analyysin.</x:v>
+        <x:v>Lisää allekirjoitetut sopimukset, laskut, maksutositteet ja saamisten täsmäytys.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="58.5" customHeight="1">
       <x:c r="A42" s="14" t="str">
-        <x:v>Asiantuntijavetoinen rajattu lisensointi- tai sovintopilotti on mahdollinen kaupallistamishypoteesi.</x:v>
+        <x:v>Julkinen aineisto ei vahvista testituloksia tai riippumatonta teknistä validointia.</x:v>
       </x:c>
       <x:c r="B42" s="14" t="str">
-        <x:v>Kaupallistamismalli</x:v>
+        <x:v>Tekninen erottautuminen</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
-        <x:v>Patenttihistorian vaiheistus suosittelee kovia portteja, claim chartia ja auditoitavaa yhteydenottoa.</x:v>
+        <x:v>Patenttiselitys kuvaa ratkaisun; erillistä testirekisteriä ei ole julkisessa datassa.</x:v>
       </x:c>
       <x:c r="D42" s="14" t="str">
-        <x:v>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/business/settle-ip-disputes ; https://www.epo.org/en/searching-for-patents/business/ipscore</x:v>
+        <x:v>site/data/patent-history.json</x:v>
       </x:c>
       <x:c r="E42" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F42" s="14" t="str">
-        <x:v>Hypoteesi, ei toteutunut kaupallinen näyttö.</x:v>
+        <x:v>Aineiston puute suhteessa tekniseen suorituskykyväitteeseen.</x:v>
       </x:c>
       <x:c r="G42" s="14" t="str">
-        <x:v>Kohdemaat ja vastapuolet valitaan vasta oikeus- ja evidenssiporttien jälkeen.</x:v>
+        <x:v>Patenttijulkaisu ei ole tuotetestiraportti.</x:v>
       </x:c>
       <x:c r="H42" s="14" t="str">
-        <x:v>Oletus</x:v>
+        <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I42" s="14" t="str">
-        <x:v>Hyväksytä pilottimalli johdolla ja patenttiasiantuntijalla; dokumentoi kustannus, vasteet ja termit.</x:v>
+        <x:v>Hanki testiprotokolla, riippumaton laboratorio, tulokset ja raakadata.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="58.5" customHeight="1">
       <x:c r="A43" s="14" t="str">
-        <x:v>Patenttivakuudellinen rahoitus on arvioitava vain vahvistettujen oikeuksien ja kassavirtojen pohjalta.</x:v>
+        <x:v>Julkinen aineisto ei vahvista piloteja tai nimettyä asiakasnäyttöä.</x:v>
       </x:c>
       <x:c r="B43" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Validointi</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
-        <x:v>WIPO IP Finance ja patenttihistorian vaihe 5.</x:v>
+        <x:v>Julkisessa evidenssirekisterissä ei ole pilotti- tai asiakasvalidointia.</x:v>
       </x:c>
       <x:c r="D43" s="14" t="str">
-        <x:v>https://www.wipo.int/en/web/ip-financing ; https://www.wipo.int/en/web/business/ip-valuation</x:v>
+        <x:v>site/data/evidence.csv</x:v>
       </x:c>
       <x:c r="E43" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F43" s="14" t="str">
-        <x:v>Rahoitusperiaate.</x:v>
+        <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G43" s="14" t="str">
-        <x:v>Ei näyttöä olemassa olevasta vakuusarvosta.</x:v>
+        <x:v>Ei päätellä asiakkaiden olemassaoloa tai puuttumista yhtiötasolla.</x:v>
       </x:c>
       <x:c r="H43" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I43" s="14" t="str">
-        <x:v>Tarvitaan riippumaton arvonmääritys, oikeuksien due diligence, toteutuneet tai sopimuspohjaiset kassavirrat ja downside-analyysi.</x:v>
+        <x:v>Lisää allekirjoitetut pilotit, toimitusnäyttö, asiakasreferenssit ja käyttödata.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="58.5" customHeight="1">
       <x:c r="A44" s="14" t="str">
-        <x:v>Australian oikeuden seuraava uusiminen on vahvistettava välittömästi.</x:v>
+        <x:v>Julkinen aineisto ei vahvista nykyistä maakohtaista omistusta, vuosimaksuja ja rasitteettomuutta koko perheessä.</x:v>
       </x:c>
       <x:c r="B44" s="14" t="str">
-        <x:v>Riskit</x:v>
+        <x:v>IP-status</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
-        <x:v>IP Australian API näyttää GRANTED-tilan, viimeisen uusimismaksun 18.7.2025 ja in-force date -päivän 14.8.2026.</x:v>
+        <x:v>Perhejulkaisut eivät yksin osoita kansallista post-grant-tilaa.</x:v>
       </x:c>
       <x:c r="D44" s="14" t="str">
-        <x:v>https://production.api.ipaustralia.gov.au/public/ipright-search-api/v1/patents/2014307829</x:v>
+        <x:v>https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=family ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=legal ; https://www.epo.org/en/applying/european/validation</x:v>
       </x:c>
       <x:c r="E44" s="14" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F44" s="14" t="str">
-        <x:v>Virallisen API-tiedon diligence-hälytys.</x:v>
+        <x:v>Diligence-rajaus.</x:v>
       </x:c>
       <x:c r="G44" s="14" t="str">
-        <x:v>API:n in-force-through-päivä ei ole tässä lakisääteinen eräpäiväväite.</x:v>
+        <x:v>Neljä kansallista rekisterijurisdiktiota ei kata koko perhettä.</x:v>
       </x:c>
       <x:c r="H44" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I44" s="14" t="str">
-        <x:v>Patenttihallinto ja Australian asiamies: vahvistakaa lakisääteinen maksupäivä, summa, maksuvaltuus ja suoritettu maksu; arkistoikaa kuitti ja tuore rekisteriote.</x:v>
+        <x:v>Laadi asiamiehen allekirjoittama maamatriisi ja liitä tuoreet rekisteriotteet sekä maksukuitit.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="58.5" customHeight="1">
       <x:c r="A45" s="14" t="str">
-        <x:v>Suomen 14. vuosimaksun eräpäiväksi on rekisteröity 31.8.2026.</x:v>
+        <x:v>Julkinen aineisto ei sisällä maakohtaisia tuote–vaatimusvertailuja.</x:v>
       </x:c>
       <x:c r="B45" s="14" t="str">
-        <x:v>Riskit</x:v>
+        <x:v>Tekninen erottautuminen</x:v>
       </x:c>
       <x:c r="C45" s="14" t="str">
-        <x:v>PRH kirjaa 14. vuoden 670 euron maksun eräpäiväksi 31.8.2026 ja myöhäisen maksukauden päättymispäiväksi 28.2.2027.</x:v>
+        <x:v>Patenttihistorian guardrail edellyttää counsel-reviewed claim chartia.</x:v>
       </x:c>
       <x:c r="D45" s="14" t="str">
-        <x:v>https://patenttitietopalvelu.prh.fi/en/patent/20135829</x:v>
+        <x:v>https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB2/document.pdf ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</x:v>
       </x:c>
       <x:c r="E45" s="14" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F45" s="14" t="str">
-        <x:v>PRH:n rekisterihavainto.</x:v>
+        <x:v>Vaatimuspiirteiden tuotekohtainen kartoitus puuttuu.</x:v>
       </x:c>
       <x:c r="G45" s="14" t="str">
-        <x:v>Tavoite on maksaa normaalina eräpäivänä.</x:v>
+        <x:v>Samankaltaisuus ei ole loukkaus.</x:v>
       </x:c>
       <x:c r="H45" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I45" s="14" t="str">
-        <x:v>Patenttihallinto: maksakaa ennen normaalia eräpäivää ja säilyttäkää maksukuitti sekä päivitetty PRH-ote.</x:v>
+        <x:v>Hanki tuotteet, säilytä hallussapitoketju, tee teardown ja asiamiehen tarkastama claim chart.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="58.5" customHeight="1">
       <x:c r="A46" s="14" t="str">
-        <x:v>Yhdysvaltain 7,5 vuoden ylläpitomaksun tila on vahvistettava.</x:v>
+        <x:v>Markkinan kokonaisarvo ei ole automaattisesti rojaltipohja.</x:v>
       </x:c>
       <x:c r="B46" s="14" t="str">
-        <x:v>Riskit</x:v>
+        <x:v>Taloudellinen malli</x:v>
       </x:c>
       <x:c r="C46" s="14" t="str">
-        <x:v>USPTO:n ylläpitomaksureitti näyttää normaalimaksuikkunan päättyvän 4.12.2026; maksutilaa ei vahvistettu riippumattomasti tässä julkaisussa.</x:v>
+        <x:v>Patenttihistorian kaupallistamisrajaus erottaa markkinan, kohdistettavan myynnin ja kassavirran.</x:v>
       </x:c>
       <x:c r="D46" s="14" t="str">
-        <x:v>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923 ; https://patentcenter.uspto.gov/applications/14911851 ; https://assignment.uspto.gov/patent/index.html#/patent/search/resultFilter?searchInput=10306923</x:v>
+        <x:v>https://www.wipo.int/en/web/business/ip-valuation</x:v>
       </x:c>
       <x:c r="E46" s="14" t="str">
-        <x:v>2026-12-04</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F46" s="14" t="str">
-        <x:v>Virallisen maksuikkunan tarkistus.</x:v>
+        <x:v>Arvonmäärityksen perusrajaus.</x:v>
       </x:c>
       <x:c r="G46" s="14" t="str">
-        <x:v>Julkaisu ei väitä, että maksu on tai ei ole suoritettu.</x:v>
+        <x:v>Rojaltipohja vaatii patentin maantieteellisen, ajallisen ja tuotekohtaisen osuvuuden.</x:v>
       </x:c>
       <x:c r="H46" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I46" s="14" t="str">
-        <x:v>Yhdysvaltain patenttiasiamies: vahvistakaa entity status, summa ja maksu sekä arkistoikaa virallinen kuitti ja tuoreet ylläpito- ja siirtotiedot.</x:v>
+        <x:v>Tarvitaan addressable/in-scope/claim-mapped sales -silta.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="58.5" customHeight="1">
       <x:c r="A47" s="14" t="str">
-        <x:v>Julkinen aineisto ei sisällä auditoituja historiallisia tilinpäätöksiä tai kassavirtaennustetta.</x:v>
+        <x:v>Patenttiarvo, yritysarvo, osakearvo ja vakuusarvo ovat eri mittareita.</x:v>
       </x:c>
       <x:c r="B47" s="14" t="str">
-        <x:v>Taloudellinen malli</x:v>
+        <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C47" s="14" t="str">
-        <x:v>Markkina- ja patenttiaineisto ei ole yhtiön talousaineisto.</x:v>
+        <x:v>WIPO:n IP-arvonmääritys- ja rahoituskehys sekä aineiston oma guardrail.</x:v>
       </x:c>
       <x:c r="D47" s="14" t="str">
-        <x:v>Julkisen paketin rajaus</x:v>
+        <x:v>https://www.wipo.int/en/web/business/ip-valuation ; https://www.wipo.int/en/web/ip-financing</x:v>
       </x:c>
       <x:c r="E47" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F47" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>Arvokäsitteiden erottelu.</x:v>
       </x:c>
       <x:c r="G47" s="14" t="str">
-        <x:v>Yhtiön taloudellisesta tilanteesta ei tehdä päätelmää.</x:v>
+        <x:v>Ei oletuksia.</x:v>
       </x:c>
       <x:c r="H47" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I47" s="14" t="str">
-        <x:v>Lisää 3–5 vuoden tilinpäätökset, tuore pääkirja, budjetti, kassavirta, velat ja verovelkatodistus.</x:v>
+        <x:v>Rahoitusrakenne ja vakuusarvo vaativat erillisen oikeudellisen ja taloudellisen analyysin.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="58.5" customHeight="1">
       <x:c r="A48" s="14" t="str">
-        <x:v>Julkinen aineisto ei yksilöi rahoitustarvetta, käyttötarkoitusta tai takaisinmaksulähdettä.</x:v>
+        <x:v>Asiantuntijavetoinen rajattu lisensointi- tai sovintopilotti on mahdollinen kaupallistamishypoteesi.</x:v>
       </x:c>
       <x:c r="B48" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Kaupallistamismalli</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>Rahoitusparametreja ei ole markkina- tai patenttidatassa.</x:v>
+        <x:v>Patenttihistorian vaiheistus suosittelee kovia portteja, claim chartia ja auditoitavaa yhteydenottoa.</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
-        <x:v>Julkisen paketin rajaus</x:v>
+        <x:v>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/business/settle-ip-disputes ; https://www.epo.org/en/searching-for-patents/business/ipscore</x:v>
       </x:c>
       <x:c r="E48" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F48" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>Hypoteesi, ei toteutunut kaupallinen näyttö.</x:v>
       </x:c>
       <x:c r="G48" s="14" t="str">
-        <x:v>Ei oleteta lainamäärää, maturiteettia tai vakuusrakennetta.</x:v>
+        <x:v>Kohdemaat ja vastapuolet valitaan vasta oikeus- ja evidenssiporttien jälkeen.</x:v>
       </x:c>
       <x:c r="H48" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Oletus</x:v>
       </x:c>
       <x:c r="I48" s="14" t="str">
-        <x:v>Määritä lainamäärä, käyttötarkoitus, maturiteetti, lyhennysprofiili, takaisinmaksu ja kovenantit.</x:v>
+        <x:v>Hyväksytä pilottimalli johdolla ja patenttiasiantuntijalla; dokumentoi kustannus, vasteet ja termit.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="58.5" customHeight="1">
       <x:c r="A49" s="14" t="str">
-        <x:v>Julkinen aineisto ei osoita osakekantaa, cap tablea tai osakkeiden rasitteita.</x:v>
+        <x:v>Patenttivakuudellinen rahoitus on arvioitava vain vahvistettujen oikeuksien ja kassavirtojen pohjalta.</x:v>
       </x:c>
       <x:c r="B49" s="14" t="str">
         <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>Julkinen paketti on rajattu markkina- ja patenttievidenssiin.</x:v>
+        <x:v>WIPO IP Finance ja patenttihistorian vaihe 5.</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
-        <x:v>Julkisen paketin rajaus</x:v>
+        <x:v>https://www.wipo.int/en/web/ip-financing ; https://www.wipo.int/en/web/business/ip-valuation</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F49" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>Rahoitusperiaate.</x:v>
       </x:c>
       <x:c r="G49" s="14" t="str">
-        <x:v>Ei oleteta omistusosuuksia tai vakuuskelpoisuutta.</x:v>
+        <x:v>Ei näyttöä olemassa olevasta vakuusarvosta.</x:v>
       </x:c>
       <x:c r="H49" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I49" s="14" t="str">
-        <x:v>Toimita varmennettu osakasluettelo, yhtiöjärjestys, päätökset, panttaus- ja rasiteselvitys suljettuun datahuoneeseen.</x:v>
+        <x:v>Tarvitaan riippumaton arvonmääritys, oikeuksien due diligence, toteutuneet tai sopimuspohjaiset kassavirrat ja downside-analyysi.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="58.5" customHeight="1">
       <x:c r="A50" s="14" t="str">
-        <x:v>Julkinen aineisto ei sisällä vertailukelpoista kilpailija- ja vaihtoehtoanalyysiä.</x:v>
+        <x:v>Australian oikeuden seuraava uusiminen on vahvistettava välittömästi.</x:v>
       </x:c>
       <x:c r="B50" s="14" t="str">
-        <x:v>Kilpailu</x:v>
+        <x:v>Riskit</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>Patenttiselitys ja oikeustapaukset eivät yksin muodosta markkinakilpailukarttaa.</x:v>
+        <x:v>IP Australian API näyttää GRANTED-tilan, viimeisen uusimismaksun 18.7.2025 ja in-force date -päivän 14.8.2026.</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>site/data/patent-history.json</x:v>
+        <x:v>https://production.api.ipaustralia.gov.au/public/ipright-search-api/v1/patents/2014307829</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
-        <x:v>Aineiston puute.</x:v>
+        <x:v>Virallisen API-tiedon diligence-hälytys.</x:v>
       </x:c>
       <x:c r="G50" s="14" t="str">
-        <x:v>Kilpailu on erotettava patenttien päällekkäisyydestä ja ei-patentoiduista vaihtoehdoista.</x:v>
+        <x:v>API:n in-force-through-päivä ei ole tässä lakisääteinen eräpäiväväite.</x:v>
       </x:c>
       <x:c r="H50" s="14" t="str">
-        <x:v>Puuttuu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I50" s="14" t="str">
-        <x:v>Laadi tuotteet, valmistajat, vaihtoehtoiset teknologiat, patenttiperheet, hinnat ja claim-map-status kattava vertailu.</x:v>
+        <x:v>Patenttihallinto ja Australian asiamies: vahvistakaa lakisääteinen maksupäivä, summa, maksuvaltuus ja suoritettu maksu; arkistoikaa kuitti ja tuore rekisteriote.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="58.5" customHeight="1">
       <x:c r="A51" s="14" t="str">
-        <x:v>Asiakassegmentit voidaan alustavasti jäsentää valmistajiin, teknologiatoimittajiin ja IP-rahoittajiin.</x:v>
+        <x:v>Suomen 14. vuosimaksun eräpäiväksi on rekisteröity 31.8.2026.</x:v>
       </x:c>
       <x:c r="B51" s="14" t="str">
-        <x:v>Asiakkaat</x:v>
+        <x:v>Riskit</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>Patenttihistorian kaupallistamisreitit sisältävät lisensoinnin, luovutuksen ja IP-rahoituksen.</x:v>
+        <x:v>PRH kirjaa 14. vuoden 670 euron maksun eräpäiväksi 31.8.2026 ja myöhäisen maksukauden päättymispäiväksi 28.2.2027.</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
-        <x:v>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/ip-financing</x:v>
+        <x:v>https://patenttitietopalvelu.prh.fi/en/patent/20135829</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="F51" s="14" t="str">
-        <x:v>Segmentointihypoteesi kaupallistamisreiteistä.</x:v>
+        <x:v>PRH:n rekisterihavainto.</x:v>
       </x:c>
       <x:c r="G51" s="14" t="str">
-        <x:v>Ei todennettua ostoaikomusta tai asiakaskantaa.</x:v>
+        <x:v>Tavoite on maksaa normaalina eräpäivänä.</x:v>
       </x:c>
       <x:c r="H51" s="14" t="str">
-        <x:v>Oletus</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I51" s="14" t="str">
-        <x:v>Validoi 10–15 strukturoitua ostaja- ja rahoittajahaastattelua sekä dokumentoi päätöskriteerit.</x:v>
+        <x:v>Patenttihallinto: maksakaa ennen normaalia eräpäivää ja säilyttäkää maksukuitti sekä päivitetty PRH-ote.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="58.5" customHeight="1">
       <x:c r="A52" s="14" t="str">
-        <x:v>Saksan ratkaisut voivat toimia evidenssiankkurina, mutta eivät maailmanlaajuisena loukkausratkaisuna.</x:v>
+        <x:v>Yhdysvaltain 7,5 vuoden ylläpitomaksun tila on vahvistettava.</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
-        <x:v>Rahoitusteesi</x:v>
+        <x:v>Riskit</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>Ratkaisut ovat kansallisia, tuote-, osapuoli- ja ajanjaksokohtaisia.</x:v>
+        <x:v>USPTO:n ylläpitomaksureitti näyttää normaalimaksuikkunan päättyvän 4.12.2026; maksutilaa ei vahvistettu riippumattomasti tässä julkaisussa.</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>https://www.rechtsprechung-im-internet.de/jportal/?quelle=jlink&amp;docid=JURE269032275&amp;psml=bsjrsprod.psml ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</x:v>
+        <x:v>https://fees.uspto.gov/MaintenanceFees/fees/details?patentNumber=10306923 ; https://patentcenter.uspto.gov/applications/14911851 ; https://assignment.uspto.gov/patent/index.html#/patent/search/resultFilter?searchInput=10306923</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-12-04</x:v>
       </x:c>
       <x:c r="F52" s="14" t="str">
-        <x:v>Oikeudellisen vaikutuksen alueellinen rajaus.</x:v>
+        <x:v>Virallisen maksuikkunan tarkistus.</x:v>
       </x:c>
       <x:c r="G52" s="14" t="str">
-        <x:v>Muiden maiden tulokset riippuvat paikallisista oikeuksista ja tuotteista.</x:v>
+        <x:v>Julkaisu ei väitä, että maksu on tai ei ole suoritettu.</x:v>
       </x:c>
       <x:c r="H52" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I52" s="14" t="str">
-        <x:v>Laadi maakohtaiset oikeus- ja claim chart -paketit ennen yhteydenottoja.</x:v>
+        <x:v>Yhdysvaltain patenttiasiamies: vahvistakaa entity status, summa ja maksu sekä arkistoikaa virallinen kuitti ja tuoreet ylläpito- ja siirtotiedot.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="58.5" customHeight="1">
       <x:c r="A53" s="14" t="str">
-        <x:v>Aineiston A-luokan maita on viisi, mutta 158 maata on D-luokassa.</x:v>
+        <x:v>Julkinen aineisto ei sisällä auditoituja historiallisia tilinpäätöksiä tai kassavirtaennustetta.</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
-        <x:v>Markkinan koko</x:v>
+        <x:v>Taloudellinen malli</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>Luokat: A 5, B 13, C 19, D 158.</x:v>
+        <x:v>Markkina- ja patenttiaineisto ei ole yhtiön talousaineisto.</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>site/data/atlas.json (summary.gradeCounts)</x:v>
+        <x:v>Julkisen paketin rajaus</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
-        <x:v>Maakohtaisten evidenssiluokkien laskenta.</x:v>
+        <x:v>Aineiston puute.</x:v>
       </x:c>
       <x:c r="G53" s="14" t="str">
-        <x:v>Luokka mittaa evidenssikypsyyttä, ei markkinan houkuttelevuutta.</x:v>
+        <x:v>Yhtiön taloudellisesta tilanteesta ei tehdä päätelmää.</x:v>
       </x:c>
       <x:c r="H53" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I53" s="14" t="str">
-        <x:v>Priorisoi D-maiden tietopyynnöt talouskoon, patenttistatuksen ja sääntelyn mukaan.</x:v>
+        <x:v>Lisää 3–5 vuoden tilinpäätökset, tuore pääkirja, budjetti, kassavirta, velat ja verovelkatodistus.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="58.5" customHeight="1">
       <x:c r="A54" s="14" t="str">
+        <x:v>Julkinen aineisto ei yksilöi rahoitustarvetta, käyttötarkoitusta tai takaisinmaksulähdettä.</x:v>
+      </x:c>
+      <x:c r="B54" s="14" t="str">
+        <x:v>Rahoitusteesi</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="str">
+        <x:v>Rahoitusparametreja ei ole markkina- tai patenttidatassa.</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="str">
+        <x:v>Julkisen paketin rajaus</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="str">
+        <x:v>Aineiston puute.</x:v>
+      </x:c>
+      <x:c r="G54" s="14" t="str">
+        <x:v>Ei oleteta lainamäärää, maturiteettia tai vakuusrakennetta.</x:v>
+      </x:c>
+      <x:c r="H54" s="14" t="str">
+        <x:v>Puuttuu</x:v>
+      </x:c>
+      <x:c r="I54" s="14" t="str">
+        <x:v>Määritä lainamäärä, käyttötarkoitus, maturiteetti, lyhennysprofiili, takaisinmaksu ja kovenantit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="58.5" customHeight="1">
+      <x:c r="A55" s="14" t="str">
+        <x:v>Julkinen aineisto ei osoita osakekantaa, cap tablea tai osakkeiden rasitteita.</x:v>
+      </x:c>
+      <x:c r="B55" s="14" t="str">
+        <x:v>Rahoitusteesi</x:v>
+      </x:c>
+      <x:c r="C55" s="14" t="str">
+        <x:v>Julkinen paketti on rajattu markkina- ja patenttievidenssiin.</x:v>
+      </x:c>
+      <x:c r="D55" s="14" t="str">
+        <x:v>Julkisen paketin rajaus</x:v>
+      </x:c>
+      <x:c r="E55" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="str">
+        <x:v>Aineiston puute.</x:v>
+      </x:c>
+      <x:c r="G55" s="14" t="str">
+        <x:v>Ei oleteta omistusosuuksia tai vakuuskelpoisuutta.</x:v>
+      </x:c>
+      <x:c r="H55" s="14" t="str">
+        <x:v>Puuttuu</x:v>
+      </x:c>
+      <x:c r="I55" s="14" t="str">
+        <x:v>Toimita varmennettu osakasluettelo, yhtiöjärjestys, päätökset, panttaus- ja rasiteselvitys suljettuun datahuoneeseen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="58.5" customHeight="1">
+      <x:c r="A56" s="14" t="str">
+        <x:v>Julkinen aineisto ei sisällä vertailukelpoista kilpailija- ja vaihtoehtoanalyysiä.</x:v>
+      </x:c>
+      <x:c r="B56" s="14" t="str">
+        <x:v>Kilpailu</x:v>
+      </x:c>
+      <x:c r="C56" s="14" t="str">
+        <x:v>Patenttiselitys ja oikeustapaukset eivät yksin muodosta markkinakilpailukarttaa.</x:v>
+      </x:c>
+      <x:c r="D56" s="14" t="str">
+        <x:v>site/data/patent-history.json</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="str">
+        <x:v>Aineiston puute.</x:v>
+      </x:c>
+      <x:c r="G56" s="14" t="str">
+        <x:v>Kilpailu on erotettava patenttien päällekkäisyydestä ja ei-patentoiduista vaihtoehdoista.</x:v>
+      </x:c>
+      <x:c r="H56" s="14" t="str">
+        <x:v>Puuttuu</x:v>
+      </x:c>
+      <x:c r="I56" s="14" t="str">
+        <x:v>Laadi tuotteet, valmistajat, vaihtoehtoiset teknologiat, patenttiperheet, hinnat ja claim-map-status kattava vertailu.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="58.5" customHeight="1">
+      <x:c r="A57" s="14" t="str">
+        <x:v>Asiakassegmentit voidaan alustavasti jäsentää valmistajiin, teknologiatoimittajiin ja IP-rahoittajiin.</x:v>
+      </x:c>
+      <x:c r="B57" s="14" t="str">
+        <x:v>Asiakkaat</x:v>
+      </x:c>
+      <x:c r="C57" s="14" t="str">
+        <x:v>Patenttihistorian kaupallistamisreitit sisältävät lisensoinnin, luovutuksen ja IP-rahoituksen.</x:v>
+      </x:c>
+      <x:c r="D57" s="14" t="str">
+        <x:v>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/ip-financing</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="str">
+        <x:v>Segmentointihypoteesi kaupallistamisreiteistä.</x:v>
+      </x:c>
+      <x:c r="G57" s="14" t="str">
+        <x:v>Ei todennettua ostoaikomusta tai asiakaskantaa.</x:v>
+      </x:c>
+      <x:c r="H57" s="14" t="str">
+        <x:v>Oletus</x:v>
+      </x:c>
+      <x:c r="I57" s="14" t="str">
+        <x:v>Validoi 10–15 strukturoitua ostaja- ja rahoittajahaastattelua sekä dokumentoi päätöskriteerit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="58.5" customHeight="1">
+      <x:c r="A58" s="14" t="str">
+        <x:v>Saksan ratkaisut voivat toimia evidenssiankkurina, mutta eivät maailmanlaajuisena loukkausratkaisuna.</x:v>
+      </x:c>
+      <x:c r="B58" s="14" t="str">
+        <x:v>Rahoitusteesi</x:v>
+      </x:c>
+      <x:c r="C58" s="14" t="str">
+        <x:v>Ratkaisut ovat kansallisia, tuote-, osapuoli- ja ajanjaksokohtaisia.</x:v>
+      </x:c>
+      <x:c r="D58" s="14" t="str">
+        <x:v>https://www.rechtsprechung-im-internet.de/jportal/?quelle=jlink&amp;docid=JURE269032275&amp;psml=bsjrsprod.psml ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="str">
+        <x:v>Oikeudellisen vaikutuksen alueellinen rajaus.</x:v>
+      </x:c>
+      <x:c r="G58" s="14" t="str">
+        <x:v>Muiden maiden tulokset riippuvat paikallisista oikeuksista ja tuotteista.</x:v>
+      </x:c>
+      <x:c r="H58" s="14" t="str">
+        <x:v>Vahvistettu</x:v>
+      </x:c>
+      <x:c r="I58" s="14" t="str">
+        <x:v>Laadi maakohtaiset oikeus- ja claim chart -paketit ennen yhteydenottoja.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="58.5" customHeight="1">
+      <x:c r="A59" s="14" t="str">
+        <x:v>Aineiston A-luokan maita on viisi, mutta 158 maata on D-luokassa.</x:v>
+      </x:c>
+      <x:c r="B59" s="14" t="str">
+        <x:v>Markkinan koko</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="str">
+        <x:v>Luokat: A 5, B 13, C 19, D 158.</x:v>
+      </x:c>
+      <x:c r="D59" s="14" t="str">
+        <x:v>site/data/atlas.json (summary.gradeCounts)</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="str">
+        <x:v>Maakohtaisten evidenssiluokkien laskenta.</x:v>
+      </x:c>
+      <x:c r="G59" s="14" t="str">
+        <x:v>Luokka mittaa evidenssikypsyyttä, ei markkinan houkuttelevuutta.</x:v>
+      </x:c>
+      <x:c r="H59" s="14" t="str">
+        <x:v>Vahvistettu</x:v>
+      </x:c>
+      <x:c r="I59" s="14" t="str">
+        <x:v>Priorisoi D-maiden tietopyynnöt talouskoon, patenttistatuksen ja sääntelyn mukaan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="58.5" customHeight="1">
+      <x:c r="A60" s="14" t="str">
         <x:v>Maailmanlaajuista atlasestimaattia ei ole hyväksytty julkaistavaksi.</x:v>
       </x:c>
-      <x:c r="B54" s="14" t="str">
+      <x:c r="B60" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
-      <x:c r="C54" s="14" t="str">
+      <x:c r="C60" s="14" t="str">
         <x:v>Nolla hyväksyttyä donoria alittaa kolmen vähimmäisrajan. Uuden-Seelannin, EU:n, Kanadan, Saksan ja Yhdysvaltain 5 julkaistulla ehdokkaalla on jokaisella vähintään yksi hylätty tai avoin D1–D10-ehto; myös alue- ja sääntelytyyppien peittoportit puuttuvat.</x:v>
       </x:c>
-      <x:c r="D54" s="14" t="str">
+      <x:c r="D60" s="14" t="str">
         <x:v>site/data/market-values.json (modelReadiness, donorProtocol ja donorCandidates)</x:v>
       </x:c>
-      <x:c r="E54" s="14" t="str">
+      <x:c r="E60" s="14" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
-      <x:c r="F54" s="14" t="str">
+      <x:c r="F60" s="14" t="str">
         <x:v>Kova portti: jokaisen donorin on läpäistävä D1–D10, ja lisäksi tarvitaan vähintään kolme yhteensopivaa donoria sekä molemmat peittoportit.</x:v>
       </x:c>
-      <x:c r="G54" s="14" t="str">
+      <x:c r="G60" s="14" t="str">
         <x:v>Viralliset alarajat ja ulkoiset vertailuarvot säilyvät ristiintarkistuksina, mutta niitä ei lasketa hyväksytyiksi donoreiksi.</x:v>
       </x:c>
-      <x:c r="H54" s="14" t="str">
+      <x:c r="H60" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
-      <x:c r="I54" s="14" t="str">
+      <x:c r="I60" s="14" t="str">
         <x:v>Älä julkaise yhtä maailmanarvoa ennen menetelmäporttien läpäisyä.</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="58.5" customHeight="1">
-      <x:c r="A55" s="15" t="str">
+    <x:row r="61" ht="58.5" customHeight="1">
+      <x:c r="A61" s="15" t="str">
         <x:v>Korkean luottamuksen rahoituspaketti vaatii suljetun datahuoneen julkisen paketin rinnalle.</x:v>
       </x:c>
-      <x:c r="B55" s="15" t="str">
+      <x:c r="B61" s="15" t="str">
         <x:v>Seuraavat vaiheet</x:v>
       </x:c>
-      <x:c r="C55" s="15" t="str">
+      <x:c r="C61" s="15" t="str">
         <x:v>Julkinen paketti osoittaa lähteet ja puutteet mutta ei sisällä luottamuksellista talous-, sopimus- tai omistusaineistoa.</x:v>
       </x:c>
-      <x:c r="D55" s="15" t="str">
+      <x:c r="D61" s="15" t="str">
         <x:v>Julkisen paketin rajaus</x:v>
       </x:c>
-      <x:c r="E55" s="15" t="str">
+      <x:c r="E61" s="15" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
-      <x:c r="F55" s="15" t="str">
+      <x:c r="F61" s="15" t="str">
         <x:v>Diligence-arkkitehtuurin suositus.</x:v>
       </x:c>
-      <x:c r="G55" s="15" t="str">
+      <x:c r="G61" s="15" t="str">
         <x:v>Pääsy rajataan ja lokitetaan.</x:v>
       </x:c>
-      <x:c r="H55" s="15" t="str">
+      <x:c r="H61" s="15" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
-      <x:c r="I55" s="15" t="str">
+      <x:c r="I61" s="15" t="str">
         <x:v>Perusta indeksoitu datahuone: Corporate, IP, Legal, Commercial, Finance, Valuation, Security.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="H2:H55">
+  <x:conditionalFormatting sqref="H2:H61">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Vahvistettu"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Tuettu"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Oletus"/>
     <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Puuttuu"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H2:H55">
+    <x:dataValidation type="list" sqref="H2:H61">
       <x:formula1>"Vahvistettu,Tuettu,Oletus,Puuttuu"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4da1ccdb515a4d7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc5ba70b38d54615"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2245,7 +2419,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.27-30</x:v>
+        <x:v>2026.07.28-32</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2253,7 +2427,7 @@
         <x:v>Päivitetty</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -2269,8 +2443,8 @@
         <x:v>Evidenssirivejä</x:v>
       </x:c>
       <x:c r="B8" s="15" t="n">
-        <x:f>COUNTA('Evidence Register'!$A$2:$A$55)</x:f>
-        <x:v>54</x:v>
+        <x:f>COUNTA('Evidence Register'!$A$2:$A$61)</x:f>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20.25" customHeight="1"/>
@@ -2285,8 +2459,8 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="B11" s="13" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$55,A11)</x:f>
-        <x:v>29</x:v>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A11)</x:f>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20.25" customHeight="1">
@@ -2294,8 +2468,8 @@
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="B12" s="14" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$55,A12)</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A12)</x:f>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20.25" customHeight="1">
@@ -2303,7 +2477,7 @@
         <x:v>Oletus</x:v>
       </x:c>
       <x:c r="B13" s="14" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$55,A13)</x:f>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A13)</x:f>
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -2312,7 +2486,7 @@
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$55,A14)</x:f>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A14)</x:f>
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -2497,7 +2671,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78bac05ebb424231"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96a6f48c1c674caf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3411,7 +3585,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
@@ -3428,7 +3602,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
@@ -3445,7 +3619,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
@@ -3462,7 +3636,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
@@ -3479,7 +3653,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
@@ -3496,7 +3670,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
@@ -3513,7 +3687,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
@@ -3530,7 +3704,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
@@ -3547,7 +3721,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
@@ -3564,7 +3738,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
@@ -3581,7 +3755,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
@@ -3598,7 +3772,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
@@ -3615,7 +3789,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
@@ -3632,7 +3806,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
@@ -3649,7 +3823,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
@@ -3666,7 +3840,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
@@ -3683,7 +3857,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
@@ -3700,7 +3874,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
@@ -3717,7 +3891,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
@@ -3734,7 +3908,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
@@ -3751,7 +3925,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
@@ -3768,7 +3942,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
@@ -3785,7 +3959,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
@@ -3802,7 +3976,7 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
@@ -3819,7 +3993,7 @@
         <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
@@ -3836,63 +4010,63 @@
         <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
       <x:c r="A79" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
-        <x:v>ecb.europa.eu</x:v>
+        <x:v>adm.gov.it</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="31.5" customHeight="1">
       <x:c r="A80" s="14" t="str">
-        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
+        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
-        <x:v>Public Health Agency of Sweden</x:v>
+        <x:v>ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="31.5" customHeight="1">
       <x:c r="A81" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>Public Health Agency of Sweden</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="31.5" customHeight="1">
       <x:c r="A82" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
         <x:v>Federal Trade Commission</x:v>
@@ -3901,32 +4075,32 @@
         <x:v>official_report</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="31.5" customHeight="1">
       <x:c r="A83" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>register_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="31.5" customHeight="1">
       <x:c r="A84" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-B5944DDC2320</x:v>
+        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
         <x:v>health.govt.nz</x:v>
@@ -3935,49 +4109,49 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="31.5" customHeight="1">
       <x:c r="A85" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
+        <x:v>REGISTER-REFERENCE-B5944DDC2320</x:v>
       </x:c>
       <x:c r="B85" s="14" t="str">
-        <x:v>podatki.gov.pl</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+        <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="31.5" customHeight="1">
       <x:c r="A86" s="14" t="str">
-        <x:v>UN-MEMBER-STATES</x:v>
+        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
       </x:c>
       <x:c r="B86" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>podatki.gov.pl</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="31.5" customHeight="1">
       <x:c r="A87" s="14" t="str">
-        <x:v>UN-NON-MEMBER-STATES</x:v>
+        <x:v>UN-MEMBER-STATES</x:v>
       </x:c>
       <x:c r="B87" s="14" t="str">
         <x:v>United Nations</x:v>
@@ -3986,50 +4160,67 @@
         <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+        <x:v>https://www.un.org/en/about-us/member-states</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="31.5" customHeight="1">
       <x:c r="A88" s="14" t="str">
+        <x:v>UN-NON-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B88" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C88" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D88" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+      </x:c>
+      <x:c r="E88" s="14" t="str">
+        <x:v>2026-07-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="31.5" customHeight="1">
+      <x:c r="A89" s="14" t="str">
         <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
       </x:c>
-      <x:c r="B88" s="14" t="str">
+      <x:c r="B89" s="14" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C88" s="14" t="str">
+      <x:c r="C89" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D88" s="14" t="str">
+      <x:c r="D89" s="14" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
       </x:c>
-      <x:c r="E88" s="14" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="31.5" customHeight="1">
-      <x:c r="A89" s="15" t="str">
+      <x:c r="E89" s="14" t="str">
+        <x:v>2026-07-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="31.5" customHeight="1">
+      <x:c r="A90" s="15" t="str">
         <x:v>REGISTER-REFERENCE-D61AFC87FA19</x:v>
       </x:c>
-      <x:c r="B89" s="15" t="str">
+      <x:c r="B90" s="15" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C89" s="15" t="str">
+      <x:c r="C90" s="15" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D89" s="15" t="str">
+      <x:c r="D90" s="15" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
       </x:c>
-      <x:c r="E89" s="15" t="str">
-        <x:v>2026-07-27</x:v>
+      <x:c r="E90" s="15" t="str">
+        <x:v>2026-07-28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a167b487b74d5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03b0445a8cc04dd9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6075,7 +6266,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re74002499e814d93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8c6d5ff06414cb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rcf03bba813f54433"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R36f3f7cdaedc40d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R508b9317fe8e46c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R5c071efc6b73419a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R954e1c60c2bc4d7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R308764d6f9164aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R6e3b7b278a51445f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="Raf87b8ff1d014f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rf88a7093b3f9490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R69eb39db36ae470d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E90" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E91" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -986,31 +986,31 @@
     </x:row>
     <x:row r="15" ht="58.5" customHeight="1">
       <x:c r="A15" s="14" t="str">
-        <x:v>Luxemburgilla on 2024-10-01 alkanut valmistevero- ja veromerkkimenetelmä; vähittäismarkkina-arvoa ei ole laskettu.</x:v>
+        <x:v>Luxemburgilla on 2024-10-01 alkanut valmistevero- ja veromerkkimenetelmä, mutta virallinen vastaus vahvistaa, ettei pyydettyjä kulutukseen luovutettuja määriä, verotuottoa tai kategoriatilastoja ole saatavilla; vähittäismarkkina-arvoa ei ole laskettu.</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
         <x:v>Markkinakoko / Luxemburg</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>Virallinen verokanta on EUR 0,12 per ml 2024-10-01 alkaen, ja veromerkit sisältävät nestetilavuuden sekä pakollisen kuluttajahinnan.</x:v>
+        <x:v>Viranomainen ei toimittanut volyymi- tai verotuottosarjaa eikä erottele pyydettyjä tuotekategorioita. Se osoitti virallisen rekisteröityjen vähittäishintojen listan, joka on vain hinta- ja veromerkkireferenssi.</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>source/FIVE_COUNTRY_METHOD_SPRINT_2026-07-27.md (Luxembourg)</x:v>
+        <x:v>https://douanes.public.lu/dam-assets/fr/accises/signes-fiscaux/2024/s48/bareme-e-liquide-s48.pdf ; source/FIVE_COUNTRY_METHOD_SPRINT_2026-07-27.md (Luxembourg)</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>Verolliset litrat = sähkönestekohtainen nettovero / EUR 120 litralta; merkitty kuluttajahintainen arvo = summa(merkitty pakkausmäärä × pakollinen merkitty hinta).</x:v>
+        <x:v>Ei laskentaa: hintalistaa ei kerrota vahvistamattomalla pakkausmäärällä eikä verokantaa käännetä volyymiksi ilman nettoverotuottoa.</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>Volyymi- ja veromerkkilaskelmia ei lasketa yhteen; ulkomaan B2B-toimitukset, hävitykset, palautukset ja oikaisut erotellaan.</x:v>
+        <x:v>Puuttuvaa viranomaiskoostetta ei käsitellä nollana. Hintalista ei osoita myyntiä, volyymia, kulutukseen luovutusta tai kuluttajakysyntää.</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str">
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>Kansallinen kooste, veromerkkien määrä- ja hintakentät, kuluttajamyynti ja kauden lopullisuus puuttuvat; retailValueStatus on not_computed.</x:v>
+        <x:v>Vuosittaiset veronalaiset millilitrat, verotuotto, veromerkkien pakkausmäärät, laitemäärät, sell-through ja kauden lopullisuus puuttuvat; retailValueStatus on not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58.5" customHeight="1">
@@ -2361,7 +2361,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc5ba70b38d54615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b1feabc56774ba1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2419,7 +2419,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.28-32</x:v>
+        <x:v>2026.07.29-35</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2427,7 +2427,7 @@
         <x:v>Päivitetty</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -2671,7 +2671,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96a6f48c1c674caf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4e9547659564401"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3585,7 +3585,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
@@ -3602,7 +3602,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
@@ -3619,7 +3619,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
@@ -3636,7 +3636,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
@@ -3653,7 +3653,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
@@ -3670,7 +3670,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
@@ -3687,7 +3687,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
@@ -3704,7 +3704,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
@@ -3721,7 +3721,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
@@ -3738,7 +3738,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
@@ -3755,7 +3755,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
@@ -3772,7 +3772,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
@@ -3789,7 +3789,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
@@ -3806,7 +3806,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
@@ -3823,7 +3823,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
@@ -3840,7 +3840,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
@@ -3857,7 +3857,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
@@ -3874,7 +3874,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
@@ -3891,7 +3891,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
@@ -3908,7 +3908,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
@@ -3925,7 +3925,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
@@ -3942,7 +3942,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
@@ -3959,7 +3959,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
@@ -3976,7 +3976,7 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
@@ -3993,97 +3993,97 @@
         <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
       <x:c r="A78" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
+        <x:v>REGISTER-REFERENCE-1208D3C8F46C</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
-        <x:v>laws-lois.justice.gc.ca</x:v>
+        <x:v>douanes.public.lu</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
+        <x:v>https://douanes.public.lu/dam-assets/fr/accises/signes-fiscaux/2024/s48/bareme-e-liquide-s48.pdf</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
       <x:c r="A79" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
+        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
-        <x:v>adm.gov.it</x:v>
+        <x:v>laws-lois.justice.gc.ca</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
+        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="31.5" customHeight="1">
       <x:c r="A80" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
-        <x:v>ecb.europa.eu</x:v>
+        <x:v>adm.gov.it</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="31.5" customHeight="1">
       <x:c r="A81" s="14" t="str">
-        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
+        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
-        <x:v>Public Health Agency of Sweden</x:v>
+        <x:v>ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="31.5" customHeight="1">
       <x:c r="A82" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>Public Health Agency of Sweden</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="31.5" customHeight="1">
       <x:c r="A83" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
         <x:v>Federal Trade Commission</x:v>
@@ -4092,32 +4092,32 @@
         <x:v>official_report</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="31.5" customHeight="1">
       <x:c r="A84" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>register_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="31.5" customHeight="1">
       <x:c r="A85" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-B5944DDC2320</x:v>
+        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
       </x:c>
       <x:c r="B85" s="14" t="str">
         <x:v>health.govt.nz</x:v>
@@ -4126,49 +4126,49 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="31.5" customHeight="1">
       <x:c r="A86" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
+        <x:v>REGISTER-REFERENCE-B5944DDC2320</x:v>
       </x:c>
       <x:c r="B86" s="14" t="str">
-        <x:v>podatki.gov.pl</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+        <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="31.5" customHeight="1">
       <x:c r="A87" s="14" t="str">
-        <x:v>UN-MEMBER-STATES</x:v>
+        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
       </x:c>
       <x:c r="B87" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>podatki.gov.pl</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="31.5" customHeight="1">
       <x:c r="A88" s="14" t="str">
-        <x:v>UN-NON-MEMBER-STATES</x:v>
+        <x:v>UN-MEMBER-STATES</x:v>
       </x:c>
       <x:c r="B88" s="14" t="str">
         <x:v>United Nations</x:v>
@@ -4177,50 +4177,67 @@
         <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+        <x:v>https://www.un.org/en/about-us/member-states</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="31.5" customHeight="1">
       <x:c r="A89" s="14" t="str">
+        <x:v>UN-NON-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B89" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C89" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D89" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+      </x:c>
+      <x:c r="E89" s="14" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="31.5" customHeight="1">
+      <x:c r="A90" s="14" t="str">
         <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
       </x:c>
-      <x:c r="B89" s="14" t="str">
+      <x:c r="B90" s="14" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C89" s="14" t="str">
+      <x:c r="C90" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D89" s="14" t="str">
+      <x:c r="D90" s="14" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
       </x:c>
-      <x:c r="E89" s="14" t="str">
-        <x:v>2026-07-28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="31.5" customHeight="1">
-      <x:c r="A90" s="15" t="str">
+      <x:c r="E90" s="14" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="31.5" customHeight="1">
+      <x:c r="A91" s="15" t="str">
         <x:v>REGISTER-REFERENCE-D61AFC87FA19</x:v>
       </x:c>
-      <x:c r="B90" s="15" t="str">
+      <x:c r="B91" s="15" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C90" s="15" t="str">
+      <x:c r="C91" s="15" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D90" s="15" t="str">
+      <x:c r="D91" s="15" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
       </x:c>
-      <x:c r="E90" s="15" t="str">
-        <x:v>2026-07-28</x:v>
+      <x:c r="E91" s="15" t="str">
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03b0445a8cc04dd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf5c0b2c4d3a4a65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6266,7 +6283,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8c6d5ff06414cb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68154232205c4637"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R308764d6f9164aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R6e3b7b278a51445f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="Raf87b8ff1d014f70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rf88a7093b3f9490b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R69eb39db36ae470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rac327ed464c740e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Rf870ac7f55204085"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="Rd85482d5e4b34512"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R45b58120c9744a8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Ra640caa341cf4d30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1372,16 +1372,16 @@
         <x:v>Neljän kvartaalin summa on 1 219 160 000 CAD; 12 kuukauden samaan kyselyyn perustuva summa on 1 219 161 000 CAD. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusten nettoarvo on 1 160 753 796,78 CAD.</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md ; source/CANADA_2024_D5_D7_D10_OFFICIAL_SOURCE_AUDIT.md</x:v>
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md ; source/CANADA_RCS_TAX_BASIS_CLARIFICATION_2026-07-29.md ; source/CANADA_2024_D5_D7_D10_OFFICIAL_SOURCE_AUDIT.md</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
         <x:v>Kuukausi − kvartaali = 1 000 CAD (0,000082 %). Retail − toimitukset = 58 406 203,22 CAD; retail / toimitukset − 1 = 5,031748 %. ECB 2024: 1 219 160 000 / 1,482110546875 = 822 583 715,21 EUR.</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>D8 läpäisee: CAD sekä GST/HST-, provinssi- ja valmisteverojen poissulku on lähteistetty. Kuukausireitti on saman kyselyn QA, ei D10; retail- ja toimitusreitit eivät muodosta markkinahaarukkaa.</x:v>
+        <x:v>D8 läpäisee: taulukolle 20-10-0071-01 on vahvistettu CAD, GST/HST/PST/QST-verojen poissulku sekä vähittäishintaan sisältyvien lisäverojen mukanaolo. Täsmälliset lisäverokomponentit sekä kuukausi- ja legacy-taulukoiden veroperusta odottavat täsmennystä. Kuukausireitti on saman kyselyn QA, ei D10; retail- ja toimitusreitit eivät muodosta markkinahaarukkaa.</x:v>
       </x:c>
       <x:c r="H28" s="14" t="str">
         <x:v>Tuettu</x:v>
@@ -2361,7 +2361,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b1feabc56774ba1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd84bea34981747a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2419,7 +2419,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.29-35</x:v>
+        <x:v>2026.07.30-36</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2427,7 +2427,7 @@
         <x:v>Päivitetty</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -2671,7 +2671,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4e9547659564401"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf51ebecdce724d47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3585,7 +3585,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
@@ -3602,7 +3602,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
@@ -3619,7 +3619,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
@@ -3636,7 +3636,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
@@ -3653,7 +3653,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
@@ -3670,7 +3670,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
@@ -3687,7 +3687,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
@@ -3704,7 +3704,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
@@ -3721,7 +3721,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
@@ -3738,7 +3738,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
@@ -3755,7 +3755,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
@@ -3772,7 +3772,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
@@ -3789,7 +3789,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
@@ -3806,7 +3806,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
@@ -3823,7 +3823,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
@@ -3840,7 +3840,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
@@ -3857,7 +3857,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
@@ -3874,7 +3874,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
@@ -3891,7 +3891,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
@@ -3908,7 +3908,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
@@ -3925,7 +3925,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
@@ -3942,7 +3942,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
@@ -3959,7 +3959,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
@@ -3976,7 +3976,7 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
@@ -3993,7 +3993,7 @@
         <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
@@ -4010,7 +4010,7 @@
         <x:v>https://douanes.public.lu/dam-assets/fr/accises/signes-fiscaux/2024/s48/bareme-e-liquide-s48.pdf</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
@@ -4027,7 +4027,7 @@
         <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="31.5" customHeight="1">
@@ -4044,7 +4044,7 @@
         <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="31.5" customHeight="1">
@@ -4061,7 +4061,7 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="31.5" customHeight="1">
@@ -4078,7 +4078,7 @@
         <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="31.5" customHeight="1">
@@ -4095,7 +4095,7 @@
         <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="31.5" customHeight="1">
@@ -4112,7 +4112,7 @@
         <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="31.5" customHeight="1">
@@ -4129,7 +4129,7 @@
         <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="31.5" customHeight="1">
@@ -4146,7 +4146,7 @@
         <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="31.5" customHeight="1">
@@ -4163,7 +4163,7 @@
         <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="31.5" customHeight="1">
@@ -4180,7 +4180,7 @@
         <x:v>https://www.un.org/en/about-us/member-states</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="31.5" customHeight="1">
@@ -4197,7 +4197,7 @@
         <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="31.5" customHeight="1">
@@ -4214,7 +4214,7 @@
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
       </x:c>
       <x:c r="E90" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="31.5" customHeight="1">
@@ -4231,13 +4231,13 @@
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
       </x:c>
       <x:c r="E91" s="15" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf5c0b2c4d3a4a65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd64bcc2c700048ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6283,7 +6283,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68154232205c4637"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80fd762408c0442a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rac327ed464c740e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="Rf870ac7f55204085"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="Rd85482d5e4b34512"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R45b58120c9744a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Ra640caa341cf4d30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R0bb0e68f3a54427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R785eac05bb9741f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R6eadfea0081643ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R07bb81100c634b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rbf0911e28c514390"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E91" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E93" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -1198,16 +1198,16 @@
         <x:v>Kulutustarvikkeet ovat 189 402 451,96 NZD, laitteet/hardware 84 709 409,85 NZD ja sekajärjestelmät 68 548,40 NZD. Viereiset ilmoitusvelvolliset tuotteet 2 137 085,24 NZD ja ratkaisemattomat tuotetyypit 4 367 017,37 NZD määrällistetään erikseen ja rajataan pois. Havaittu arvo tulee vain AIS/AVP-työkirjoista; Notifier- ja RPS-arvoa ei lisätä.</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return ; https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf ; source/NZ_2024_DONOR_CLOSURE_PACK.md ; source/NZ_2024_D8_D10_OFFICIAL_SOURCE_AUDIT.md ; source/NZ_2024_WORKBOOK_MANIFEST.json ; source/NZ_2024_PRODUCT_SCOPE_AUDIT.json ; scripts/analyze_nz_2024_returns.py</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return ; https://www.health.govt.nz/system/files/2025-11/notifiable-products-annual-sales-return-2025-user-guide.pdf ; source/NZ_2024_DONOR_CLOSURE_PACK.md ; source/NZ_2024_D8_D10_OFFICIAL_SOURCE_AUDIT.md ; source/NZ_DONOR_FOLLOWUP_PACK_2026-08-07.md ; source/NZ_2024_WORKBOOK_MANIFEST.json ; source/NZ_2024_PRODUCT_SCOPE_AUDIT.json ; scripts/analyze_nz_2024_returns.py</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
       <x:c r="F22" s="17" t="str">
         <x:v>189 402 451,96 + 84 709 409,85 + 68 548,40 = 274 180 410,21 NZD. Viereiset ja ratkaisemattomat luokat käsitellään ennen vaping-summaa ja jätetään siitä pois. Kaikkien 29 tiedoston URL:t, koot ja SHA-256-tiivisteet validoidaan ennen aggregointia.</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>Deterministinen tuoterajaus on julkinen. Yleisvähittäiskaupan havaittu arvo puuttuu, GST-perusta on tuntematon, täsmälleen toistuvien rivien herkkyys ei ole korjattu estimaatti eikä riippumatonta täsmäytystä ole.</x:v>
+        <x:v>Deterministinen tuoterajaus on julkinen. RPS kerää tuotelajeja ja määriä mutta ei havaittua retail-arvoa. GST-perusta on tuntematon. Stats NZ:n lopullinen 2024 HS10 -kontrolli on tullivaiheen herkkyys eikä riippumaton retail-täsmäytys.</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str">
         <x:v>Tuettu</x:v>
@@ -1372,22 +1372,22 @@
         <x:v>Neljän kvartaalin summa on 1 219 160 000 CAD; 12 kuukauden samaan kyselyyn perustuva summa on 1 219 161 000 CAD. Health Canadan vuoden 2024 valmistaja-/maahantuojatoimitusten nettoarvo on 1 160 753 796,78 CAD.</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md ; source/CANADA_RCS_TAX_BASIS_CLARIFICATION_2026-07-29.md ; source/CANADA_2024_D5_D7_D10_OFFICIAL_SOURCE_AUDIT.md</x:v>
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101 ; https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001 ; https://health-infobase.canada.ca/substance-use/vaping/sales/ ; source/CANADA_2024_DONOR_CLOSURE_PACK.md ; source/CANADA_RCS_TAX_BASIS_CLARIFICATION_2026-07-29.md ; source/CANADA_RCS_SCOPE_QUALITY_CLARIFICATION_2026-07-30.md ; source/CANADA_2024_D5_D7_D10_OFFICIAL_SOURCE_AUDIT.md</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
         <x:v>Kuukausi − kvartaali = 1 000 CAD (0,000082 %). Retail − toimitukset = 58 406 203,22 CAD; retail / toimitukset − 1 = 5,031748 %. ECB 2024: 1 219 160 000 / 1,482110546875 = 822 583 715,21 EUR.</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>D8 läpäisee: taulukolle 20-10-0071-01 on vahvistettu CAD, GST/HST/PST/QST-verojen poissulku sekä vähittäishintaan sisältyvien lisäverojen mukanaolo. Täsmälliset lisäverokomponentit sekä kuukausi- ja legacy-taulukoiden veroperusta odottavat täsmennystä. Kuukausireitti on saman kyselyn QA, ei D10; retail- ja toimitusreitit eivät muodosta markkinahaarukkaa.</x:v>
+        <x:v>D8 läpäisee: tarkistetuille kvartaali-, kuukausi- ja arkistotaulukoille on vahvistettu CAD, GST/HST/PST/QST-verojen poissulku sekä hintaan upotettujen lisäverojen mukanaolo. Lisäveroihin voivat kuulua liittovaltion, lisä- ja provinssien vaping-verot. Kuukausireitti on saman kyselyn QA, ei D10.</x:v>
       </x:c>
       <x:c r="H28" s="14" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
-        <x:v>D5:n NAICS 459993/459999 -peitto, D7:n vuositason virheraja ja D10:n retail–toimitus-silta ovat avoimia; Kanada ei ole hyväksytty donor.</x:v>
+        <x:v>D5 hylättiin, koska NAICS 459999 -erikoiskauppa jää vahvistetun kohdejoukon 441100–459993 ulkopuolelle. D7 hylättiin, koska täsmällisiä tuoteryhmätason laatu- ja vuositason epävarmuustietoja ei ole saatavilla. D10 on avoin; Kanada ei ole hyväksytty donor.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58.5" customHeight="1">
@@ -1566,31 +1566,31 @@
     </x:row>
     <x:row r="35" ht="58.5" customHeight="1">
       <x:c r="A35" s="14" t="str">
-        <x:v>Puolan vuoden 2025 verosilta antaa 4 382 500 johdettua verollista sähkötupakkalaitetta ja 62 500 johdettua verollista osasarjaa.</x:v>
+        <x:v>Puolan vuoden 2025 verosilta antaa 4 382 500 johdettua verollista laajan höyrystyslaiteryhmän yksikköä ja 62 500 johdettua verollista osasarjaa; luvut eivät ole sähkötupakkakohtaisia.</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>Virallinen parlamenttivastaus raportoi 993,1 milj. PLN e-nesteistä, 175,3 milj. PLN laitteista ja 2,5 milj. PLN osasarjoista. Laitteiden ja osasarjojen vero oli 40 PLN yksiköltä 1.7.2025 alkaen.</x:v>
+        <x:v>Virallinen parlamenttivastaus raportoi 993,1 milj. PLN e-nesteistä, 175,3 milj. PLN laajasta laiteryhmästä ja 2,5 milj. PLN osasarjoista. Lakisääteinen ryhmä sisältää uudelleentäytettävät sähkötupakat, kuumennettavan tupakan lämmittimet ja monitoimilaitteet. Vero oli 40 PLN yksiköltä 1.7.2025 alkaen.</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf ; https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+        <x:v>https://api.sejm.gov.pl/sejm/term10/interpellations/attachment/ATTDVKHSJ/i17526-o1.pdf ; https://www.podatki.gov.pl/akcyza/stawki-podatkowe/ ; https://www.podatki.gov.pl/akcyza/komunikaty-w-zakresie-podatku-akcyzowego ; https://api.sejm.gov.pl/eli/acts/DU/2025/698/text.pdf ; source/POLAND_D1_D10_PREASSESSMENT_2026-07-31.md</x:v>
       </x:c>
       <x:c r="E35" s="14" t="str">
-        <x:v>2025</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
       <x:c r="F35" s="14" t="str">
-        <x:v>175 300 000 / 40 = 4 382 500 verollista laitetta; 2 500 000 / 40 = 62 500 verollista osasarjaa.</x:v>
+        <x:v>175 300 000 / 40 = 4 382 500 laajan ryhmän verollista yksikköä; 2 500 000 / 40 = 62 500 verollista osasarjaa.</x:v>
       </x:c>
       <x:c r="G35" s="14" t="str">
-        <x:v>Johdettu veropohja kattaa vain 1.7.2025 alkaen verotetut laitteet ja osasarjat. Se ei osoita kuluttajahintaa, vähittäismyyntiä, verottomia määriä tai varastosiirtymiä.</x:v>
+        <x:v>Johdettu veropohja kattaa vain 1.7.2025 alkaen verotetut laitteet ja osasarjat. AKC-4/R vaatii laitetyypin erittelyn, mutta nykyinen julkinen koonti ei julkaise sitä. Luvut eivät osoita kuluttajahintaa, vähittäismyyntiä tai e-savukekohtaista määrää.</x:v>
       </x:c>
       <x:c r="H35" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I35" s="14" t="str">
-        <x:v>Tarvitaan veron kuukausijakauma, lopullisuus, vähittäishinnat, kanavapeitto ja riippumaton täsmäytys.</x:v>
+        <x:v>Tarvitaan AKC-4/R:n e-savuke–lämmitin–monitoimilaitejako, veron kuukausijakauma, vähittäishinnat, kanavapeitto ja riippumaton täsmäytys. Puolalle ei anneta donor-pistemäärää ilman maa–vuosi retail-arvoa.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="58.5" customHeight="1">
@@ -2361,7 +2361,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd84bea34981747a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R551342fd9c054791"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2419,7 +2419,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.30-36</x:v>
+        <x:v>2026.07.31-37</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2427,7 +2427,7 @@
         <x:v>Päivitetty</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -2460,7 +2460,7 @@
       </x:c>
       <x:c r="B11" s="13" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A11)</x:f>
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20.25" customHeight="1">
@@ -2469,7 +2469,7 @@
       </x:c>
       <x:c r="B12" s="14" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A12)</x:f>
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20.25" customHeight="1">
@@ -2671,7 +2671,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf51ebecdce724d47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e076316909d4d56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3573,24 +3573,24 @@
     </x:row>
     <x:row r="53" ht="31.5" customHeight="1">
       <x:c r="A53" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-BC2CDD0708D5</x:v>
+        <x:v>REGISTER-REFERENCE-067A847A44A9</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
-        <x:v>data-api.ecb.europa.eu</x:v>
+        <x:v>api.sejm.gov.pl</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
+        <x:v>https://api.sejm.gov.pl/eli/acts/DU/2025/698/text.pdf</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
       <x:c r="A54" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-7264539499F0</x:v>
+        <x:v>REGISTER-REFERENCE-BC2CDD0708D5</x:v>
       </x:c>
       <x:c r="B54" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3599,15 +3599,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
       <x:c r="A55" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-2580DD0733C9</x:v>
+        <x:v>REGISTER-REFERENCE-7264539499F0</x:v>
       </x:c>
       <x:c r="B55" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3616,15 +3616,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
       <x:c r="A56" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-38DD93023815</x:v>
+        <x:v>REGISTER-REFERENCE-2580DD0733C9</x:v>
       </x:c>
       <x:c r="B56" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3633,15 +3633,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D56" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
       <x:c r="A57" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-72D82058EA8A</x:v>
+        <x:v>REGISTER-REFERENCE-38DD93023815</x:v>
       </x:c>
       <x:c r="B57" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3650,15 +3650,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
       <x:c r="A58" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-E8408060156E</x:v>
+        <x:v>REGISTER-REFERENCE-72D82058EA8A</x:v>
       </x:c>
       <x:c r="B58" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3667,15 +3667,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D58" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
       <x:c r="A59" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-ACB549D404B8</x:v>
+        <x:v>REGISTER-REFERENCE-E8408060156E</x:v>
       </x:c>
       <x:c r="B59" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3684,15 +3684,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
       <x:c r="A60" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-2FB6E2117AD7</x:v>
+        <x:v>REGISTER-REFERENCE-ACB549D404B8</x:v>
       </x:c>
       <x:c r="B60" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3701,15 +3701,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D60" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
       <x:c r="A61" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-8FEBAD85B03E</x:v>
+        <x:v>REGISTER-REFERENCE-2FB6E2117AD7</x:v>
       </x:c>
       <x:c r="B61" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3718,15 +3718,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
       <x:c r="A62" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-37CBB91A050A</x:v>
+        <x:v>REGISTER-REFERENCE-8FEBAD85B03E</x:v>
       </x:c>
       <x:c r="B62" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3735,15 +3735,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
       <x:c r="A63" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-54AB30A87D3D</x:v>
+        <x:v>REGISTER-REFERENCE-37CBB91A050A</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3752,15 +3752,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
       <x:c r="A64" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-4B9D48C385C9</x:v>
+        <x:v>REGISTER-REFERENCE-54AB30A87D3D</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3769,15 +3769,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
       <x:c r="A65" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-97704C5CE7D4</x:v>
+        <x:v>REGISTER-REFERENCE-4B9D48C385C9</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3786,15 +3786,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
       <x:c r="A66" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-EF5511CEAE3C</x:v>
+        <x:v>REGISTER-REFERENCE-97704C5CE7D4</x:v>
       </x:c>
       <x:c r="B66" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3803,15 +3803,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
       <x:c r="A67" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-15452EF50F15</x:v>
+        <x:v>REGISTER-REFERENCE-EF5511CEAE3C</x:v>
       </x:c>
       <x:c r="B67" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3820,15 +3820,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
       <x:c r="A68" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-9C7C0F0FD33F</x:v>
+        <x:v>REGISTER-REFERENCE-15452EF50F15</x:v>
       </x:c>
       <x:c r="B68" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3837,15 +3837,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
       <x:c r="A69" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-82A9C0A0E9C4</x:v>
+        <x:v>REGISTER-REFERENCE-9C7C0F0FD33F</x:v>
       </x:c>
       <x:c r="B69" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3854,15 +3854,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
       <x:c r="A70" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-25E2E410922F</x:v>
+        <x:v>REGISTER-REFERENCE-82A9C0A0E9C4</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3871,15 +3871,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
       <x:c r="A71" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-74211110370B</x:v>
+        <x:v>REGISTER-REFERENCE-25E2E410922F</x:v>
       </x:c>
       <x:c r="B71" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3888,15 +3888,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
       <x:c r="A72" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-59446D8EB279</x:v>
+        <x:v>REGISTER-REFERENCE-74211110370B</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3905,15 +3905,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
       <x:c r="A73" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-BFB2E2E1B4A3</x:v>
+        <x:v>REGISTER-REFERENCE-59446D8EB279</x:v>
       </x:c>
       <x:c r="B73" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3922,15 +3922,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
       <x:c r="A74" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-D26C27B033B0</x:v>
+        <x:v>REGISTER-REFERENCE-BFB2E2E1B4A3</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3939,15 +3939,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
       <x:c r="A75" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
+        <x:v>REGISTER-REFERENCE-D26C27B033B0</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3956,151 +3956,151 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
       <x:c r="A76" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
+        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
-        <x:v>data.ecb.europa.eu</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
       <x:c r="A77" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-2DA87527D51F</x:v>
+        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
-        <x:v>datahelpdesk.worldbank.org</x:v>
+        <x:v>data.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
       <x:c r="A78" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-1208D3C8F46C</x:v>
+        <x:v>REGISTER-REFERENCE-2DA87527D51F</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
-        <x:v>douanes.public.lu</x:v>
+        <x:v>datahelpdesk.worldbank.org</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>https://douanes.public.lu/dam-assets/fr/accises/signes-fiscaux/2024/s48/bareme-e-liquide-s48.pdf</x:v>
+        <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
       <x:c r="A79" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
+        <x:v>REGISTER-REFERENCE-1208D3C8F46C</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
-        <x:v>laws-lois.justice.gc.ca</x:v>
+        <x:v>douanes.public.lu</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
+        <x:v>https://douanes.public.lu/dam-assets/fr/accises/signes-fiscaux/2024/s48/bareme-e-liquide-s48.pdf</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="31.5" customHeight="1">
       <x:c r="A80" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
+        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
-        <x:v>adm.gov.it</x:v>
+        <x:v>laws-lois.justice.gc.ca</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
+        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="31.5" customHeight="1">
       <x:c r="A81" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
-        <x:v>ecb.europa.eu</x:v>
+        <x:v>adm.gov.it</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="31.5" customHeight="1">
       <x:c r="A82" s="14" t="str">
-        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
+        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
-        <x:v>Public Health Agency of Sweden</x:v>
+        <x:v>ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="31.5" customHeight="1">
       <x:c r="A83" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>Public Health Agency of Sweden</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="31.5" customHeight="1">
       <x:c r="A84" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
         <x:v>Federal Trade Commission</x:v>
@@ -4109,32 +4109,32 @@
         <x:v>official_report</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="31.5" customHeight="1">
       <x:c r="A85" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
       </x:c>
       <x:c r="B85" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>register_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="31.5" customHeight="1">
       <x:c r="A86" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-B5944DDC2320</x:v>
+        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
       </x:c>
       <x:c r="B86" s="14" t="str">
         <x:v>health.govt.nz</x:v>
@@ -4143,101 +4143,135 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>https://www.health.govt.nz/system/files/2024-12/2024-annual-returns-user-guide.pdf</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="31.5" customHeight="1">
       <x:c r="A87" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
+        <x:v>REGISTER-REFERENCE-1766C84ECA96</x:v>
       </x:c>
       <x:c r="B87" s="14" t="str">
-        <x:v>podatki.gov.pl</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+        <x:v>https://www.health.govt.nz/system/files/2025-11/notifiable-products-annual-sales-return-2025-user-guide.pdf</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="31.5" customHeight="1">
       <x:c r="A88" s="14" t="str">
-        <x:v>UN-MEMBER-STATES</x:v>
+        <x:v>REGISTER-REFERENCE-529570B0D6C7</x:v>
       </x:c>
       <x:c r="B88" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>podatki.gov.pl</x:v>
       </x:c>
       <x:c r="C88" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+        <x:v>https://www.podatki.gov.pl/akcyza/komunikaty-w-zakresie-podatku-akcyzowego</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="31.5" customHeight="1">
       <x:c r="A89" s="14" t="str">
-        <x:v>UN-NON-MEMBER-STATES</x:v>
+        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
       </x:c>
       <x:c r="B89" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>podatki.gov.pl</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="31.5" customHeight="1">
       <x:c r="A90" s="14" t="str">
+        <x:v>UN-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B90" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C90" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D90" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+      </x:c>
+      <x:c r="E90" s="14" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="31.5" customHeight="1">
+      <x:c r="A91" s="14" t="str">
+        <x:v>UN-NON-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B91" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C91" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D91" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+      </x:c>
+      <x:c r="E91" s="14" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="31.5" customHeight="1">
+      <x:c r="A92" s="14" t="str">
         <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
       </x:c>
-      <x:c r="B90" s="14" t="str">
+      <x:c r="B92" s="14" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C90" s="14" t="str">
+      <x:c r="C92" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D90" s="14" t="str">
+      <x:c r="D92" s="14" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
       </x:c>
-      <x:c r="E90" s="14" t="str">
-        <x:v>2026-07-30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" ht="31.5" customHeight="1">
-      <x:c r="A91" s="15" t="str">
+      <x:c r="E92" s="14" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="31.5" customHeight="1">
+      <x:c r="A93" s="15" t="str">
         <x:v>REGISTER-REFERENCE-D61AFC87FA19</x:v>
       </x:c>
-      <x:c r="B91" s="15" t="str">
+      <x:c r="B93" s="15" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C91" s="15" t="str">
+      <x:c r="C93" s="15" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D91" s="15" t="str">
+      <x:c r="D93" s="15" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
       </x:c>
-      <x:c r="E91" s="15" t="str">
-        <x:v>2026-07-30</x:v>
+      <x:c r="E93" s="15" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd64bcc2c700048ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31d734131d4a4db4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5169,7 +5203,7 @@
         <x:v>PL-2025-VAPING-DEVICE-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>vaping_device_excise_amount</x:v>
+        <x:v>vaporisation_device_broad_group_excise_amount</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
         <x:v>Poland</x:v>
@@ -5214,7 +5248,7 @@
         <x:v>PL-2025-VAPING-COMPONENT-SETS-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>vaping_component_sets_excise_amount</x:v>
+        <x:v>vaporisation_device_component_sets_broad_group_excise_amount</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
         <x:v>Poland</x:v>
@@ -6283,7 +6317,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80fd762408c0442a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6ce77f0000c4cd3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R0bb0e68f3a54427e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R785eac05bb9741f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R6eadfea0081643ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R07bb81100c634b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rbf0911e28c514390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R3153ea57e86f465d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R6164b0abc4714e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="Re23596c1224a4611"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rdbeee81d39a445a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rd710870d042f465b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E93" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E102" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EurEquivalentsFI" displayName="EurEquivalentsFI" ref="A1:N45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EurEquivalentsFI" displayName="EurEquivalentsFI" ref="A1:N76" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Tietuetyyppi"/>
     <x:tableColumn id="2" name="Tunniste"/>
@@ -1073,7 +1073,7 @@
     </x:row>
     <x:row r="18" ht="58.5" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>Julkinen markkina-aineisto sisältää 84 havaintoa 24 lähteestä; 75 virallista havaintoa jakautuvat 39 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
+        <x:v>Julkinen markkina-aineisto sisältää 156 havaintoa 47 lähteestä; 134 virallista havaintoa jakautuvat 98 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
         <x:v>Markkinakoko</x:v>
@@ -1088,7 +1088,7 @@
         <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>84 = 48 markkina- ja mallihavaintoa + 36 FHM-rakennelukua; 75 virallista = 39 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
+        <x:v>156 = 120 markkina- ja mallihavaintoa + 36 FHM-rakennelukua; 134 virallista = 98 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
         <x:v>Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja kalenterivuoden virtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva, ei valmis vuosijakso. Virallinen lähde ei tee eri mittareista yhteismitallisia.</x:v>
@@ -1218,89 +1218,89 @@
     </x:row>
     <x:row r="23" ht="58.5" customHeight="1">
       <x:c r="A23" s="14" t="str">
-        <x:v>Uuden-Seelannin erillinen vuoden 2024 RPS-vähittäisherkkyys on tuettu malli: 533 662 383,68–731 175 792,50 NZD ja perusskenaario 641 811 687,89 NZD.</x:v>
+        <x:v>Stats NZ:n valittu vuoden 2024 HS10-kontrolli tuottaa 183 370 681 ja 197 070 322 NZD:n nettorajaproxyt; ne eivät ole vähittäismarkkina-arvoja.</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>Matalan, perus- ja korkean skenaarion yhdistetyt arvot ovat 533 662 383,68 / 641 811 687,89 / 731 175 792,50 NZD. Malli yhdistää erikoisvähittäiskaupan ankkurin yleisvähittäiskaupan määrä- ja hintamalliin.</x:v>
+        <x:v>Valitut tuonnit ovat 189 640 890 NZD tullausarvona ja 203 340 531 NZD CIF-arvona. Valitut viennit ovat 6 270 209 NZD FOB-arvona. Kontrolli käyttää lukittua vuoden 2024 tuotekoodisääntöä.</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2024 ; source/NZ_2024_RPS_RETAIL_VALUE_SENSITIVITY.md ; source/NZ_2024_DONOR_CLOSURE_PACK.md</x:v>
+        <x:v>https://www.stats.govt.nz/large-datasets/csv-files-for-download/overseas-merchandise-trade-datasets/ ; https://www3.stats.govt.nz/HS10_by_Country/2024_Imports_HS10.zip ; https://www3.stats.govt.nz/HS10_by_Country/2024_Exports_HS10.zip ; source/NZ_CA_DE_DONOR_CONTROL_SPRINT_2026-08-02.md</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
-        <x:v>Matala (täsmällisten rivien deduplikointi): 258 327 110,88 + 275 335 272,80 = 533 662 383,68 NZD. Perus (raportoidut/raakrivit): 274 180 410,21 + 367 631 277,68 = 641 811 687,89 NZD. Korkea (raportoidut/raakrivit): 274 180 410,21 + 456 995 382,29 = 731 175 792,50 NZD.</x:v>
+        <x:v>189 640 890 − 6 270 209 = 183 370 681 NZD; 203 340 531 − 6 270 209 = 197 070 322 NZD. Ehdokas / proxyt = 1,495224911 ja 1,391282094.</x:v>
       </x:c>
       <x:c r="G23" s="14" t="str">
-        <x:v>GST-käsittely, palautusten täydellisyys ja riippumaton täsmäytys ovat avoimia; ilmoittajien toimitusketjutason arvot on jätetty pois.</x:v>
+        <x:v>Rajavaihe, tuoterajaus, kotimainen tuotanto, varastot, jälleenvienti, katteet, kanavat, GST ja kuluttajamyynti eivät täsmää vähittäisrajaan.</x:v>
       </x:c>
       <x:c r="H23" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>Ei havaittu kansallinen arvo eikä hyväksytty donor. Tarvitaan viranomaisen scope- ja GST-vahvistus sekä riippumaton toisto.</x:v>
+        <x:v>Suhteet eivät ole kate, korotuskerroin, validointiväli tai markkinahaarukka. D10 pysyy avoinna ja NZ pysyy 7/10 EI HYVÄKSYTTY.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="58.5" customHeight="1">
       <x:c r="A24" s="14" t="str">
-        <x:v>Vuoden 2023 kuuden virallisen työkirjan uusi numeerinen rekonstruktio on jätetty tarkoituksella laskematta.</x:v>
+        <x:v>FTC:n virallisista taulukoista johdettu suljettujen järjestelmien ja kertakäyttötuotteiden raportoitu myynti oli 2 763 284 338 USD vuonna 2021.</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Ministeriön julkaisema koonti on vähintään 374 milj. NZD ja 2 570 ilmoitusta. Se sisältää kaikki ilmoitettavat tuotteet, myös heated tobacco -tuotteet, ja ministeriö varoittaa laadusta.</x:v>
+        <x:v>Seitsemän vuoden 2015–2021 sarja on laskettu summaamalla vuosittain cartridge-system- ja disposable-rivit. Vuoden 2020 korjattu taulukko kattaa viisi aiempaa raportoijaa sekä kolme neljästä uudesta; vuosi 2021 kattaa kaikki yhdeksän vastaanottajaa.</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return/annual-returns-2023 ; source/NZ_2023_ANNUAL_RETURNS_FAIL_CLOSED.md</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018 ; https://www.ftc.gov/reports/e-cigarette-report-2021 ; source/US_FTC_2015_2021_REPORTED_SALES.md</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>Kuusi virallista tiedostoa on eheystiivistetty; kaikki uusi laskenta palauttaa tilan not_computed.</x:v>
+        <x:v>FTC-taulukoiden cartridge systems + disposable e-cigarettes -myynnin vuosittainen summa.</x:v>
       </x:c>
       <x:c r="G24" s="14" t="str">
-        <x:v>Tuoterajaus, määräkentät, duplikaatit, toimitusketjutaso, veroperusta ja riippumaton täsmäytys ovat ratkaisematta.</x:v>
+        <x:v>Raportoijajoukko muuttuu, open-system-tuotteet puuttuvat, taso on valmistajaraportointi ja veroperustaa ei ilmoiteta.</x:v>
       </x:c>
       <x:c r="H24" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I24" s="14" t="str">
-        <x:v>Vuoden 2023 uusi vaping-only-arvo puuttuu, eikä 374 milj. NZD:tä saa nimetä puhtaaksi sähkötupakkamarkkinaksi.</x:v>
+        <x:v>Ei täydellinen kansallinen kuluttajavähittäisarvo eikä hyväksytty donor; tarvitaan avoin POS- tai kuluttajamyyntisarja ja veroperusta.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="58.5" customHeight="1">
       <x:c r="A25" s="14" t="str">
-        <x:v>FTC:n virallisista taulukoista johdettu suljettujen järjestelmien ja kertakäyttötuotteiden raportoitu myynti oli 2 763 284 338 USD vuonna 2021.</x:v>
+        <x:v>Saksan tuleva toimittajatesti DE-BLIND-1.0.0 lukittiin ennen tulevan toimituksen pisteytystä; testi on EI PISTEYTETTY.</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>Markkinakoko</x:v>
+        <x:v>Markkinakoko / Saksa</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Seitsemän vuoden 2015–2021 sarja on laskettu summaamalla vuosittain cartridge-system- ja disposable-rivit. Vuoden 2020 korjattu taulukko kattaa viisi aiempaa raportoijaa sekä kolme neljästä uudesta; vuosi 2021 kattaa kaikki yhdeksän vastaanottajaa.</x:v>
+        <x:v>Viralliset lopulliset ankkurit ovat 1 241 000 litraa vuonna 2023 ja 1 284 000 litraa vuonna 2024 eli yhteensä 2 525 000 litraa. Ennalta rekisteröidyt rajat ovat 15 % vuodessa ja 10 % yhteensä.</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018 ; https://www.ftc.gov/reports/e-cigarette-report-2021 ; source/US_FTC_2015_2021_REPORTED_SALES.md</x:v>
+        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003/ ; source/NZ_CA_DE_DONOR_CONTROL_SPRINT_2026-08-02.md</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
-        <x:v>2021</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>FTC-taulukoiden cartridge systems + disposable e-cigarettes -myynnin vuosittainen summa.</x:v>
+        <x:v>Vuotuinen poikkeama = |toimittajan litrat / viralliset litrat − 1|; yhteispoikkeama = |toimittajan kahden vuoden summa / 2 525 000 − 1|.</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>Raportoijajoukko muuttuu, open-system-tuotteet puuttuvat, taso on valmistajaraportointi ja veroperustaa ei ilmoiteta.</x:v>
+        <x:v>Numeerinen osuma ei yksin osoita samaa tuotetta, yksikköä, veroperustaa, kanavaa tai tapahtumavaihetta. Rajoja ei soviteta yksityisiin arvoihin.</x:v>
       </x:c>
       <x:c r="H25" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
-        <x:v>Ei täydellinen kansallinen kuluttajavähittäisarvo eikä hyväksytty donor; tarvitaan avoin POS- tai kuluttajamyyntisarja ja veroperusta.</x:v>
+        <x:v>Testin läpäisy ei hyväksy Saksaa donoriksi eikä valtuuta ostoa, lisenssiä, maksua tai luovutusta. Saksan virallinen retail-arvo pysyy not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58.5" customHeight="1">
@@ -1317,7 +1317,7 @@
         <x:v>site/data/evidence-lanes.json ; site/data/donor-cockpit.json ; site/data/third-donor-screen.json ; site/data/country-scenarios.json</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
         <x:v>Fail-closed-portit: puuttuva tai virheellinen syöte tuottaa tilan not_computed eikä nollaa.</x:v>
@@ -1387,7 +1387,7 @@
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
-        <x:v>D5 hylättiin, koska NAICS 459999 -erikoiskauppa jää vahvistetun kohdejoukon 441100–459993 ulkopuolelle. D7 hylättiin, koska täsmällisiä tuoteryhmätason laatu- ja vuositason epävarmuustietoja ei ole saatavilla. D10 on avoin; Kanada ei ole hyväksytty donor.</x:v>
+        <x:v>D5 hylättiin, koska NAICS 459999 -erikoiskauppa jää vahvistetun kohdejoukon 441100–459993 ulkopuolelle; kehikkoon kuuluva verkkomyynti ei kata pois rajattuja erikois-, ulkomaisia suora- tai rajakauppakanavia. D7 hylättiin, koska täsmälliset NAPCS 5619122 -vastaus-, imputointi-, CV-, keskivirhe-, luottamusväli- ja kovarianssimittarit puuttuvat. D10 on avoin; Kanada ei ole hyväksytty donor.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58.5" customHeight="1">
@@ -1610,7 +1610,7 @@
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
-        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 39 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
+        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 98 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
         <x:v>Rakenneluvuista ei päätellä myyntiarvoa, myyntimäärää tai markkinaosuutta. Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja vuosivirtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva eikä sitä vuositasoiteta.</x:v>
@@ -2361,7 +2361,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R551342fd9c054791"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb7c46ce2af94a95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2419,7 +2419,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.07.31-37</x:v>
+        <x:v>2026.08.02-41</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2427,7 +2427,7 @@
         <x:v>Päivitetty</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -2460,7 +2460,7 @@
       </x:c>
       <x:c r="B11" s="13" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A11)</x:f>
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20.25" customHeight="1">
@@ -2469,7 +2469,7 @@
       </x:c>
       <x:c r="B12" s="14" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A12)</x:f>
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20.25" customHeight="1">
@@ -2671,7 +2671,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e076316909d4d56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redea25e6cf804d42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3585,7 +3585,7 @@
         <x:v>https://api.sejm.gov.pl/eli/acts/DU/2025/698/text.pdf</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
@@ -3602,7 +3602,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
@@ -3619,7 +3619,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
@@ -3636,7 +3636,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
@@ -3653,7 +3653,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
@@ -3670,7 +3670,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
@@ -3687,7 +3687,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
@@ -3704,7 +3704,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
@@ -3721,7 +3721,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
@@ -3738,7 +3738,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
@@ -3755,12 +3755,12 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
       <x:c r="A64" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-54AB30A87D3D</x:v>
+        <x:v>REGISTER-REFERENCE-BCE59F2D3F9D</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3769,15 +3769,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
       <x:c r="A65" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-4B9D48C385C9</x:v>
+        <x:v>REGISTER-REFERENCE-2267B190A073</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3786,15 +3786,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
       <x:c r="A66" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-97704C5CE7D4</x:v>
+        <x:v>REGISTER-REFERENCE-957871D9CB33</x:v>
       </x:c>
       <x:c r="B66" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3803,15 +3803,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
       <x:c r="A67" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-EF5511CEAE3C</x:v>
+        <x:v>REGISTER-REFERENCE-5C7194247112</x:v>
       </x:c>
       <x:c r="B67" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3820,15 +3820,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
       <x:c r="A68" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-15452EF50F15</x:v>
+        <x:v>REGISTER-REFERENCE-75BF634166B2</x:v>
       </x:c>
       <x:c r="B68" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3837,15 +3837,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
       <x:c r="A69" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-9C7C0F0FD33F</x:v>
+        <x:v>REGISTER-REFERENCE-54AB30A87D3D</x:v>
       </x:c>
       <x:c r="B69" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3854,15 +3854,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
       <x:c r="A70" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-82A9C0A0E9C4</x:v>
+        <x:v>REGISTER-REFERENCE-4B9D48C385C9</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3871,15 +3871,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
       <x:c r="A71" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-25E2E410922F</x:v>
+        <x:v>REGISTER-REFERENCE-97704C5CE7D4</x:v>
       </x:c>
       <x:c r="B71" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3888,15 +3888,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
       <x:c r="A72" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-74211110370B</x:v>
+        <x:v>REGISTER-REFERENCE-EF5511CEAE3C</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3905,15 +3905,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
       <x:c r="A73" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-59446D8EB279</x:v>
+        <x:v>REGISTER-REFERENCE-15452EF50F15</x:v>
       </x:c>
       <x:c r="B73" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3922,15 +3922,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
       <x:c r="A74" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-BFB2E2E1B4A3</x:v>
+        <x:v>REGISTER-REFERENCE-9C7C0F0FD33F</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3939,15 +3939,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
       <x:c r="A75" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-D26C27B033B0</x:v>
+        <x:v>REGISTER-REFERENCE-82A9C0A0E9C4</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3956,15 +3956,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
       <x:c r="A76" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
+        <x:v>REGISTER-REFERENCE-25E2E410922F</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3973,305 +3973,458 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
       <x:c r="A77" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
+        <x:v>REGISTER-REFERENCE-74211110370B</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
-        <x:v>data.ecb.europa.eu</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
       <x:c r="A78" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-2DA87527D51F</x:v>
+        <x:v>REGISTER-REFERENCE-59446D8EB279</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
-        <x:v>datahelpdesk.worldbank.org</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
       <x:c r="A79" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-1208D3C8F46C</x:v>
+        <x:v>REGISTER-REFERENCE-BFB2E2E1B4A3</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
-        <x:v>douanes.public.lu</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>https://douanes.public.lu/dam-assets/fr/accises/signes-fiscaux/2024/s48/bareme-e-liquide-s48.pdf</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="31.5" customHeight="1">
       <x:c r="A80" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
+        <x:v>REGISTER-REFERENCE-D26C27B033B0</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
-        <x:v>laws-lois.justice.gc.ca</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="31.5" customHeight="1">
       <x:c r="A81" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
+        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
-        <x:v>adm.gov.it</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="31.5" customHeight="1">
       <x:c r="A82" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
-        <x:v>ecb.europa.eu</x:v>
+        <x:v>data.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="31.5" customHeight="1">
       <x:c r="A83" s="14" t="str">
-        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
+        <x:v>REGISTER-REFERENCE-2DA87527D51F</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
-        <x:v>Public Health Agency of Sweden</x:v>
+        <x:v>datahelpdesk.worldbank.org</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
+        <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="31.5" customHeight="1">
       <x:c r="A84" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>REGISTER-REFERENCE-1208D3C8F46C</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>douanes.public.lu</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://douanes.public.lu/dam-assets/fr/accises/signes-fiscaux/2024/s48/bareme-e-liquide-s48.pdf</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="31.5" customHeight="1">
       <x:c r="A85" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>REGISTER-REFERENCE-25E8C2FC0150</x:v>
       </x:c>
       <x:c r="B85" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>genesis.destatis.de</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003/</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="31.5" customHeight="1">
       <x:c r="A86" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
+        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
       </x:c>
       <x:c r="B86" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>laws-lois.justice.gc.ca</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
+        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="31.5" customHeight="1">
       <x:c r="A87" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-1766C84ECA96</x:v>
+        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
       </x:c>
       <x:c r="B87" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>adm.gov.it</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>https://www.health.govt.nz/system/files/2025-11/notifiable-products-annual-sales-return-2025-user-guide.pdf</x:v>
+        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="31.5" customHeight="1">
       <x:c r="A88" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-529570B0D6C7</x:v>
+        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
       </x:c>
       <x:c r="B88" s="14" t="str">
-        <x:v>podatki.gov.pl</x:v>
+        <x:v>ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C88" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>https://www.podatki.gov.pl/akcyza/komunikaty-w-zakresie-podatku-akcyzowego</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="31.5" customHeight="1">
       <x:c r="A89" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
+        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
       </x:c>
       <x:c r="B89" s="14" t="str">
-        <x:v>podatki.gov.pl</x:v>
+        <x:v>Public Health Agency of Sweden</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
-        <x:v>register_reference</x:v>
+        <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="31.5" customHeight="1">
       <x:c r="A90" s="14" t="str">
-        <x:v>UN-MEMBER-STATES</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
       </x:c>
       <x:c r="B90" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C90" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D90" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E90" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="31.5" customHeight="1">
       <x:c r="A91" s="14" t="str">
-        <x:v>UN-NON-MEMBER-STATES</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
       </x:c>
       <x:c r="B91" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="31.5" customHeight="1">
       <x:c r="A92" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
+        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
       </x:c>
       <x:c r="B92" s="14" t="str">
-        <x:v>www150.statcan.gc.ca</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C92" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D92" s="14" t="str">
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
+      </x:c>
+      <x:c r="E92" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="31.5" customHeight="1">
+      <x:c r="A93" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-1766C84ECA96</x:v>
+      </x:c>
+      <x:c r="B93" s="14" t="str">
+        <x:v>health.govt.nz</x:v>
+      </x:c>
+      <x:c r="C93" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D93" s="14" t="str">
+        <x:v>https://www.health.govt.nz/system/files/2025-11/notifiable-products-annual-sales-return-2025-user-guide.pdf</x:v>
+      </x:c>
+      <x:c r="E93" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="31.5" customHeight="1">
+      <x:c r="A94" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-529570B0D6C7</x:v>
+      </x:c>
+      <x:c r="B94" s="14" t="str">
+        <x:v>podatki.gov.pl</x:v>
+      </x:c>
+      <x:c r="C94" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D94" s="14" t="str">
+        <x:v>https://www.podatki.gov.pl/akcyza/komunikaty-w-zakresie-podatku-akcyzowego</x:v>
+      </x:c>
+      <x:c r="E94" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="31.5" customHeight="1">
+      <x:c r="A95" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
+      </x:c>
+      <x:c r="B95" s="14" t="str">
+        <x:v>podatki.gov.pl</x:v>
+      </x:c>
+      <x:c r="C95" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D95" s="14" t="str">
+        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+      </x:c>
+      <x:c r="E95" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="31.5" customHeight="1">
+      <x:c r="A96" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-645255DD4B34</x:v>
+      </x:c>
+      <x:c r="B96" s="14" t="str">
+        <x:v>stats.govt.nz</x:v>
+      </x:c>
+      <x:c r="C96" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D96" s="14" t="str">
+        <x:v>https://www.stats.govt.nz/large-datasets/csv-files-for-download/overseas-merchandise-trade-datasets/</x:v>
+      </x:c>
+      <x:c r="E96" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="31.5" customHeight="1">
+      <x:c r="A97" s="14" t="str">
+        <x:v>UN-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B97" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C97" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D97" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+      </x:c>
+      <x:c r="E97" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="31.5" customHeight="1">
+      <x:c r="A98" s="14" t="str">
+        <x:v>UN-NON-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B98" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C98" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D98" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+      </x:c>
+      <x:c r="E98" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="31.5" customHeight="1">
+      <x:c r="A99" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
+      </x:c>
+      <x:c r="B99" s="14" t="str">
+        <x:v>www150.statcan.gc.ca</x:v>
+      </x:c>
+      <x:c r="C99" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D99" s="14" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
       </x:c>
-      <x:c r="E92" s="14" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="31.5" customHeight="1">
-      <x:c r="A93" s="15" t="str">
+      <x:c r="E99" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="31.5" customHeight="1">
+      <x:c r="A100" s="14" t="str">
         <x:v>REGISTER-REFERENCE-D61AFC87FA19</x:v>
       </x:c>
-      <x:c r="B93" s="15" t="str">
+      <x:c r="B100" s="14" t="str">
         <x:v>www150.statcan.gc.ca</x:v>
       </x:c>
-      <x:c r="C93" s="15" t="str">
+      <x:c r="C100" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D93" s="15" t="str">
+      <x:c r="D100" s="14" t="str">
         <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
       </x:c>
-      <x:c r="E93" s="15" t="str">
-        <x:v>2026-07-31</x:v>
+      <x:c r="E100" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="31.5" customHeight="1">
+      <x:c r="A101" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-9479B1548E50</x:v>
+      </x:c>
+      <x:c r="B101" s="14" t="str">
+        <x:v>www3.stats.govt.nz</x:v>
+      </x:c>
+      <x:c r="C101" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D101" s="14" t="str">
+        <x:v>https://www3.stats.govt.nz/HS10_by_Country/2024_Exports_HS10.zip</x:v>
+      </x:c>
+      <x:c r="E101" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="31.5" customHeight="1">
+      <x:c r="A102" s="15" t="str">
+        <x:v>REGISTER-REFERENCE-94B1312153E9</x:v>
+      </x:c>
+      <x:c r="B102" s="15" t="str">
+        <x:v>www3.stats.govt.nz</x:v>
+      </x:c>
+      <x:c r="C102" s="15" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D102" s="15" t="str">
+        <x:v>https://www3.stats.govt.nz/HS10_by_Country/2024_Imports_HS10.zip</x:v>
+      </x:c>
+      <x:c r="E102" s="15" t="str">
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31d734131d4a4db4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6c4dc40110f477c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5110,22 +5263,22 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>FI-2025-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
+        <x:v>DE-2019-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>nicotine_e_liquid_excise_receipts</x:v>
+        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>Finland</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="E19" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G19" s="45" t="n">
-        <x:v>3540319</x:v>
+        <x:v>2247267035</x:v>
       </x:c>
       <x:c r="H19" s="45" t="str">
         <x:v>EUR</x:v>
@@ -5135,7 +5288,7 @@
       </x:c>
       <x:c r="J19" s="45" t="n">
         <x:f>G19</x:f>
-        <x:v>3540319</x:v>
+        <x:v>2247267035</x:v>
       </x:c>
       <x:c r="K19" s="14" t="str">
         <x:v>EUR-IDENTITY</x:v>
@@ -5155,44 +5308,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>PL-2025-E-LIQUID-EXCISE-AMOUNT</x:v>
+        <x:v>DE-2020-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>e_liquid_excise_amount</x:v>
+        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="E20" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G20" s="45" t="n">
-        <x:v>993100000</x:v>
+        <x:v>2444948000</x:v>
       </x:c>
       <x:c r="H20" s="45" t="str">
-        <x:v>PLN</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I20" s="45" t="n">
-        <x:v>4.2396576470588</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="45" t="n">
-        <x:f>G20/I20</x:f>
-        <x:v>234240611.54771507</x:v>
+        <x:f>G20</x:f>
+        <x:v>2444948000</x:v>
       </x:c>
       <x:c r="K20" s="14" t="str">
-        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L20" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M20" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N20" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="25.5" customHeight="1">
@@ -5200,44 +5353,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>PL-2025-VAPING-DEVICE-EXCISE-AMOUNT</x:v>
+        <x:v>DE-2021-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>vaporisation_device_broad_group_excise_amount</x:v>
+        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="E21" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G21" s="45" t="n">
-        <x:v>175300000</x:v>
+        <x:v>2325648577</x:v>
       </x:c>
       <x:c r="H21" s="45" t="str">
-        <x:v>PLN</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I21" s="45" t="n">
-        <x:v>4.2396576470588</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J21" s="45" t="n">
-        <x:f>G21/I21</x:f>
-        <x:v>41347678.183782555</x:v>
+        <x:f>G21</x:f>
+        <x:v>2325648577</x:v>
       </x:c>
       <x:c r="K21" s="14" t="str">
-        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L21" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M21" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N21" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="25.5" customHeight="1">
@@ -5245,44 +5398,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>PL-2025-VAPING-COMPONENT-SETS-EXCISE-AMOUNT</x:v>
+        <x:v>DE-2022-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>vaporisation_device_component_sets_broad_group_excise_amount</x:v>
+        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="E22" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G22" s="45" t="n">
-        <x:v>2500000</x:v>
+        <x:v>2510888578</x:v>
       </x:c>
       <x:c r="H22" s="45" t="str">
-        <x:v>PLN</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I22" s="45" t="n">
-        <x:v>4.2396576470588</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J22" s="45" t="n">
-        <x:f>G22/I22</x:f>
-        <x:v>589670.2536192606</x:v>
+        <x:f>G22</x:f>
+        <x:v>2510888578</x:v>
       </x:c>
       <x:c r="K22" s="14" t="str">
-        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L22" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M22" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="25.5" customHeight="1">
@@ -5290,44 +5443,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>SE-2024-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
+        <x:v>DE-2023-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>nicotine_e_liquid_excise_receipts</x:v>
+        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>Sweden</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="E23" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G23" s="45" t="n">
-        <x:v>80000000</x:v>
+        <x:v>2581608198</x:v>
       </x:c>
       <x:c r="H23" s="45" t="str">
-        <x:v>SEK</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I23" s="45" t="n">
-        <x:v>11.432519140625</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="45" t="n">
-        <x:f>G23/I23</x:f>
-        <x:v>6997582.861306848</x:v>
+        <x:f>G23</x:f>
+        <x:v>2581608198</x:v>
       </x:c>
       <x:c r="K23" s="14" t="str">
-        <x:v>ECB-EXR-A-SEK-EUR-SP00-A-2024</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L23" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M23" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="25.5" customHeight="1">
@@ -5335,44 +5488,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>GLOBAL-2025-IMARC-COMMERCIAL-ESTIMATE</x:v>
+        <x:v>DE-2024-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>commercial_market_estimate</x:v>
+        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>Global</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="E24" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>calendar_year_estimate</x:v>
+        <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G24" s="45" t="n">
-        <x:v>26000000000</x:v>
+        <x:v>2687776000</x:v>
       </x:c>
       <x:c r="H24" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I24" s="45" t="n">
-        <x:v>1.1299831372549</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J24" s="45" t="n">
-        <x:f>G24/I24</x:f>
-        <x:v>23009192918.721367</x:v>
+        <x:f>G24</x:f>
+        <x:v>2687776000</x:v>
       </x:c>
       <x:c r="K24" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L24" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M24" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="25.5" customHeight="1">
@@ -5380,44 +5533,44 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>GLOBAL-2025-GVR-COMMERCIAL-ESTIMATE</x:v>
+        <x:v>FI-2025-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>commercial_market_estimate</x:v>
+        <x:v>nicotine_e_liquid_excise_receipts</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>Global</x:v>
+        <x:v>Finland</x:v>
       </x:c>
       <x:c r="E25" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>calendar_year_estimate</x:v>
+        <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G25" s="45" t="n">
-        <x:v>45700000000</x:v>
+        <x:v>3540319</x:v>
       </x:c>
       <x:c r="H25" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I25" s="45" t="n">
-        <x:v>1.1299831372549</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J25" s="45" t="n">
-        <x:f>G25/I25</x:f>
-        <x:v>40443081399.44486</x:v>
+        <x:f>G25</x:f>
+        <x:v>3540319</x:v>
       </x:c>
       <x:c r="K25" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L25" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M25" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="25.5" customHeight="1">
@@ -5425,38 +5578,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>GLOBAL-2025-FORTUNE-COMMERCIAL-ESTIMATE</x:v>
+        <x:v>PL-2021-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>commercial_market_estimate</x:v>
+        <x:v>e_liquid_excise_receipts</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>Global</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E26" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
-        <x:v>calendar_year_estimate</x:v>
+        <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G26" s="45" t="n">
-        <x:v>46320000000</x:v>
+        <x:v>179500000</x:v>
       </x:c>
       <x:c r="H26" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I26" s="45" t="n">
-        <x:v>1.1299831372549</x:v>
+        <x:v>4.5651786821705</x:v>
       </x:c>
       <x:c r="J26" s="45" t="n">
         <x:f>G26/I26</x:f>
-        <x:v>40991762153.66052</x:v>
+        <x:v>39319381.01372568</x:v>
       </x:c>
       <x:c r="K26" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2021</x:v>
       </x:c>
       <x:c r="L26" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M26" s="14" t="str">
         <x:v>computed</x:v>
@@ -5470,38 +5623,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>US-2015-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2022-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>e_liquid_excise_receipts</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E27" s="14" t="n">
-        <x:v>2015</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="F27" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G27" s="45" t="n">
-        <x:v>304170046</x:v>
+        <x:v>229900000</x:v>
       </x:c>
       <x:c r="H27" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I27" s="45" t="n">
-        <x:v>1.109512890625</x:v>
+        <x:v>4.686106614786</x:v>
       </x:c>
       <x:c r="J27" s="45" t="n">
         <x:f>G27/I27</x:f>
-        <x:v>274147374.5552049</x:v>
+        <x:v>49059916.66399566</x:v>
       </x:c>
       <x:c r="K27" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2015</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2022</x:v>
       </x:c>
       <x:c r="L27" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M27" s="14" t="str">
         <x:v>computed</x:v>
@@ -5515,38 +5668,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>US-2016-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2023-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>e_liquid_excise_receipts</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E28" s="14" t="n">
-        <x:v>2016</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G28" s="45" t="n">
-        <x:v>485707484</x:v>
+        <x:v>443600000</x:v>
       </x:c>
       <x:c r="H28" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I28" s="45" t="n">
-        <x:v>1.1069031128405</x:v>
+        <x:v>4.5419658823529</x:v>
       </x:c>
       <x:c r="J28" s="45" t="n">
         <x:f>G28/I28</x:f>
-        <x:v>438798552.7961817</x:v>
+        <x:v>97666959.96628653</x:v>
       </x:c>
       <x:c r="K28" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2016</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2023</x:v>
       </x:c>
       <x:c r="L28" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M28" s="14" t="str">
         <x:v>computed</x:v>
@@ -5560,38 +5713,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>US-2017-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2024-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>e_liquid_excise_receipts</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E29" s="14" t="n">
-        <x:v>2017</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G29" s="45" t="n">
-        <x:v>779836399</x:v>
+        <x:v>561400000</x:v>
       </x:c>
       <x:c r="H29" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I29" s="45" t="n">
-        <x:v>1.1296811764706</x:v>
+        <x:v>4.305795703125</x:v>
       </x:c>
       <x:c r="J29" s="45" t="n">
         <x:f>G29/I29</x:f>
-        <x:v>690315475.943752</x:v>
+        <x:v>130382405.18298511</x:v>
       </x:c>
       <x:c r="K29" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2017</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L29" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M29" s="14" t="str">
         <x:v>computed</x:v>
@@ -5605,44 +5758,37 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>US-2018-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2015-UOKIK-E-CIGARETTE-MARKET-VALUE-ESTIMATE</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>institutional_market_value_benchmark</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E30" s="14" t="n">
-        <x:v>2018</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="F30" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>study_reference_period_may_2015</x:v>
       </x:c>
       <x:c r="G30" s="45" t="n">
-        <x:v>2043703005</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="H30" s="45" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I30" s="45" t="n">
-        <x:v>1.1809545098039</x:v>
-      </x:c>
-      <x:c r="J30" s="45" t="n">
-        <x:f>G30/I30</x:f>
-        <x:v>1730551844.3207107</x:v>
-      </x:c>
-      <x:c r="K30" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2018</x:v>
-      </x:c>
+        <x:v>PLN</x:v>
+      </x:c>
+      <x:c r="I30" s="45"/>
+      <x:c r="J30" s="45"/>
+      <x:c r="K30" s="14"/>
       <x:c r="L30" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="M30" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>not_computed</x:v>
       </x:c>
       <x:c r="N30" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>period_not_compatible_with_annual_average</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="25.5" customHeight="1">
@@ -5650,38 +5796,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>US-2019-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2025-E-LIQUID-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>e_liquid_excise_receipts</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E31" s="14" t="n">
-        <x:v>2019</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F31" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G31" s="45" t="n">
-        <x:v>2702608307</x:v>
+        <x:v>993100000</x:v>
       </x:c>
       <x:c r="H31" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I31" s="45" t="n">
-        <x:v>1.1194745098039</x:v>
+        <x:v>4.2396576470588</x:v>
       </x:c>
       <x:c r="J31" s="45" t="n">
         <x:f>G31/I31</x:f>
-        <x:v>2414175832.796246</x:v>
+        <x:v>234240611.54771507</x:v>
       </x:c>
       <x:c r="K31" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2019</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L31" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M31" s="14" t="str">
         <x:v>computed</x:v>
@@ -5695,38 +5841,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>US-2020-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2025-VAPING-DEVICE-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>vaporisation_device_broad_group_excise_amount</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E32" s="14" t="n">
-        <x:v>2020</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F32" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G32" s="45" t="n">
-        <x:v>2394423105</x:v>
+        <x:v>175300000</x:v>
       </x:c>
       <x:c r="H32" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I32" s="45" t="n">
-        <x:v>1.1421961089494</x:v>
+        <x:v>4.2396576470588</x:v>
       </x:c>
       <x:c r="J32" s="45" t="n">
         <x:f>G32/I32</x:f>
-        <x:v>2096332745.523365</x:v>
+        <x:v>41347678.183782555</x:v>
       </x:c>
       <x:c r="K32" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2020</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L32" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M32" s="14" t="str">
         <x:v>computed</x:v>
@@ -5740,38 +5886,38 @@
         <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>US-2021-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
+        <x:v>PL-2025-VAPING-COMPONENT-SETS-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>vaporisation_device_component_sets_broad_group_excise_amount</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Poland</x:v>
       </x:c>
       <x:c r="E33" s="14" t="n">
-        <x:v>2021</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F33" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G33" s="45" t="n">
-        <x:v>2763284338</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="H33" s="45" t="str">
-        <x:v>USD</x:v>
+        <x:v>PLN</x:v>
       </x:c>
       <x:c r="I33" s="45" t="n">
-        <x:v>1.1827403100775</x:v>
+        <x:v>4.2396576470588</x:v>
       </x:c>
       <x:c r="J33" s="45" t="n">
         <x:f>G33/I33</x:f>
-        <x:v>2336340711.866778</x:v>
+        <x:v>589670.2536192606</x:v>
       </x:c>
       <x:c r="K33" s="14" t="str">
-        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2021</x:v>
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L33" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M33" s="14" t="str">
         <x:v>computed</x:v>
@@ -5782,16 +5928,16 @@
     </x:row>
     <x:row r="34" ht="25.5" customHeight="1">
       <x:c r="A34" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>SE-2024-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>low.specialistRetailNzd</x:v>
+        <x:v>nicotine_e_liquid_excise_receipts</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Sweden</x:v>
       </x:c>
       <x:c r="E34" s="14" t="n">
         <x:v>2024</x:v>
@@ -5800,23 +5946,23 @@
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G34" s="45" t="n">
-        <x:v>258327110.88</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="H34" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>SEK</x:v>
       </x:c>
       <x:c r="I34" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>11.432519140625</x:v>
       </x:c>
       <x:c r="J34" s="45" t="n">
         <x:f>G34/I34</x:f>
-        <x:v>144474304.51375833</x:v>
+        <x:v>6997582.861306848</x:v>
       </x:c>
       <x:c r="K34" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-SEK-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L34" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M34" s="14" t="str">
         <x:v>computed</x:v>
@@ -5827,41 +5973,41 @@
     </x:row>
     <x:row r="35" ht="25.5" customHeight="1">
       <x:c r="A35" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>GLOBAL-2025-IMARC-COMMERCIAL-ESTIMATE</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>low.generalRetailRpsNzd</x:v>
+        <x:v>commercial_market_estimate</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Global</x:v>
       </x:c>
       <x:c r="E35" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F35" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>calendar_year_estimate</x:v>
       </x:c>
       <x:c r="G35" s="45" t="n">
-        <x:v>275335272.8</x:v>
+        <x:v>26000000000</x:v>
       </x:c>
       <x:c r="H35" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I35" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1299831372549</x:v>
       </x:c>
       <x:c r="J35" s="45" t="n">
         <x:f>G35/I35</x:f>
-        <x:v>153986439.55865824</x:v>
+        <x:v>23009192918.721367</x:v>
       </x:c>
       <x:c r="K35" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L35" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M35" s="14" t="str">
         <x:v>computed</x:v>
@@ -5872,41 +6018,41 @@
     </x:row>
     <x:row r="36" ht="25.5" customHeight="1">
       <x:c r="A36" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B36" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>GLOBAL-2025-GVR-COMMERCIAL-ESTIMATE</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>low.combinedNzd</x:v>
+        <x:v>commercial_market_estimate</x:v>
       </x:c>
       <x:c r="D36" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Global</x:v>
       </x:c>
       <x:c r="E36" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>calendar_year_estimate</x:v>
       </x:c>
       <x:c r="G36" s="45" t="n">
-        <x:v>533662383.68</x:v>
+        <x:v>45700000000</x:v>
       </x:c>
       <x:c r="H36" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I36" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1299831372549</x:v>
       </x:c>
       <x:c r="J36" s="45" t="n">
         <x:f>G36/I36</x:f>
-        <x:v>298460744.0724166</x:v>
+        <x:v>40443081399.44486</x:v>
       </x:c>
       <x:c r="K36" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L36" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M36" s="14" t="str">
         <x:v>computed</x:v>
@@ -5917,41 +6063,41 @@
     </x:row>
     <x:row r="37" ht="25.5" customHeight="1">
       <x:c r="A37" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B37" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>GLOBAL-2025-FORTUNE-COMMERCIAL-ESTIMATE</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>base.specialistRetailNzd</x:v>
+        <x:v>commercial_market_estimate</x:v>
       </x:c>
       <x:c r="D37" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Global</x:v>
       </x:c>
       <x:c r="E37" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F37" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>calendar_year_estimate</x:v>
       </x:c>
       <x:c r="G37" s="45" t="n">
-        <x:v>274180410.21</x:v>
+        <x:v>46320000000</x:v>
       </x:c>
       <x:c r="H37" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I37" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1299831372549</x:v>
       </x:c>
       <x:c r="J37" s="45" t="n">
         <x:f>G37/I37</x:f>
-        <x:v>153340560.89369413</x:v>
+        <x:v>40991762153.66052</x:v>
       </x:c>
       <x:c r="K37" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L37" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M37" s="14" t="str">
         <x:v>computed</x:v>
@@ -5962,41 +6108,41 @@
     </x:row>
     <x:row r="38" ht="25.5" customHeight="1">
       <x:c r="A38" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B38" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2015-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
-        <x:v>base.generalRetailRpsNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D38" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E38" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="F38" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G38" s="45" t="n">
-        <x:v>367631277.68</x:v>
+        <x:v>304170046</x:v>
       </x:c>
       <x:c r="H38" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I38" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.109512890625</x:v>
       </x:c>
       <x:c r="J38" s="45" t="n">
         <x:f>G38/I38</x:f>
-        <x:v>205604719.4558489</x:v>
+        <x:v>274147374.5552049</x:v>
       </x:c>
       <x:c r="K38" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2015</x:v>
       </x:c>
       <x:c r="L38" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M38" s="14" t="str">
         <x:v>computed</x:v>
@@ -6007,41 +6153,41 @@
     </x:row>
     <x:row r="39" ht="25.5" customHeight="1">
       <x:c r="A39" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B39" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2016-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>base.combinedNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E39" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="F39" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G39" s="45" t="n">
-        <x:v>641811687.89</x:v>
+        <x:v>485707484</x:v>
       </x:c>
       <x:c r="H39" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I39" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1069031128405</x:v>
       </x:c>
       <x:c r="J39" s="45" t="n">
         <x:f>G39/I39</x:f>
-        <x:v>358945280.34954304</x:v>
+        <x:v>438798552.7961817</x:v>
       </x:c>
       <x:c r="K39" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2016</x:v>
       </x:c>
       <x:c r="L39" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M39" s="14" t="str">
         <x:v>computed</x:v>
@@ -6052,41 +6198,41 @@
     </x:row>
     <x:row r="40" ht="25.5" customHeight="1">
       <x:c r="A40" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B40" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2017-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
-        <x:v>high.specialistRetailNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D40" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E40" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="F40" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G40" s="45" t="n">
-        <x:v>274180410.21</x:v>
+        <x:v>779836399</x:v>
       </x:c>
       <x:c r="H40" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I40" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1296811764706</x:v>
       </x:c>
       <x:c r="J40" s="45" t="n">
         <x:f>G40/I40</x:f>
-        <x:v>153340560.89369413</x:v>
+        <x:v>690315475.943752</x:v>
       </x:c>
       <x:c r="K40" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2017</x:v>
       </x:c>
       <x:c r="L40" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M40" s="14" t="str">
         <x:v>computed</x:v>
@@ -6097,41 +6243,41 @@
     </x:row>
     <x:row r="41" ht="25.5" customHeight="1">
       <x:c r="A41" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B41" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2018-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
-        <x:v>high.generalRetailRpsNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D41" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E41" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="F41" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G41" s="45" t="n">
-        <x:v>456995382.29</x:v>
+        <x:v>2043703005</x:v>
       </x:c>
       <x:c r="H41" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I41" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1809545098039</x:v>
       </x:c>
       <x:c r="J41" s="45" t="n">
         <x:f>G41/I41</x:f>
-        <x:v>255583278.88015154</x:v>
+        <x:v>1730551844.3207107</x:v>
       </x:c>
       <x:c r="K41" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2018</x:v>
       </x:c>
       <x:c r="L41" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M41" s="14" t="str">
         <x:v>computed</x:v>
@@ -6142,41 +6288,41 @@
     </x:row>
     <x:row r="42" ht="25.5" customHeight="1">
       <x:c r="A42" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B42" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>US-2019-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
-        <x:v>high.combinedNzd</x:v>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
       </x:c>
       <x:c r="D42" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="E42" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="F42" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G42" s="45" t="n">
-        <x:v>731175792.5</x:v>
+        <x:v>2702608307</x:v>
       </x:c>
       <x:c r="H42" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I42" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1.1194745098039</x:v>
       </x:c>
       <x:c r="J42" s="45" t="n">
         <x:f>G42/I42</x:f>
-        <x:v>408923839.7738457</x:v>
+        <x:v>2414175832.796246</x:v>
       </x:c>
       <x:c r="K42" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2019</x:v>
       </x:c>
       <x:c r="L42" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M42" s="14" t="str">
         <x:v>computed</x:v>
@@ -6187,137 +6333,1490 @@
     </x:row>
     <x:row r="43" ht="25.5" customHeight="1">
       <x:c r="A43" s="14" t="str">
-        <x:v>model</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B43" s="14" t="str">
-        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+        <x:v>US-2020-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
-        <x:v>low</x:v>
-      </x:c>
-      <x:c r="D43" s="14"/>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+      </x:c>
+      <x:c r="D43" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
       <x:c r="E43" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="F43" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G43" s="45" t="n">
-        <x:v>667920000</x:v>
+        <x:v>2394423105</x:v>
       </x:c>
       <x:c r="H43" s="45" t="str">
-        <x:v>EUR</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="I43" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>1.1421961089494</x:v>
       </x:c>
       <x:c r="J43" s="45" t="n">
-        <x:f>G43</x:f>
-        <x:v>667920000</x:v>
+        <x:f>G43/I43</x:f>
+        <x:v>2096332745.523365</x:v>
       </x:c>
       <x:c r="K43" s="14" t="str">
-        <x:v>EUR-IDENTITY</x:v>
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2020</x:v>
       </x:c>
       <x:c r="L43" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M43" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>computed</x:v>
       </x:c>
       <x:c r="N43" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="25.5" customHeight="1">
       <x:c r="A44" s="14" t="str">
-        <x:v>model</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B44" s="14" t="str">
-        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+        <x:v>US-2021-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
-        <x:v>central</x:v>
-      </x:c>
-      <x:c r="D44" s="14"/>
+        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+      </x:c>
+      <x:c r="D44" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
       <x:c r="E44" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="F44" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G44" s="45" t="n">
+        <x:v>2763284338</x:v>
+      </x:c>
+      <x:c r="H44" s="45" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I44" s="45" t="n">
+        <x:v>1.1827403100775</x:v>
+      </x:c>
+      <x:c r="J44" s="45" t="n">
+        <x:f>G44/I44</x:f>
+        <x:v>2336340711.866778</x:v>
+      </x:c>
+      <x:c r="K44" s="14" t="str">
+        <x:v>ECB-EXR-A-USD-EUR-SP00-A-2021</x:v>
+      </x:c>
+      <x:c r="L44" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M44" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N44" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="25.5" customHeight="1">
+      <x:c r="A45" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B45" s="14" t="str">
+        <x:v>NZ-2019-HES-E-CIGARETTES-AND-REFILLS-EXPENDITURE-NZD</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="str">
+        <x:v>household_expenditure_estimate</x:v>
+      </x:c>
+      <x:c r="D45" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="str">
+        <x:v>year_ended_june</x:v>
+      </x:c>
+      <x:c r="G45" s="45" t="n">
+        <x:v>42276000</x:v>
+      </x:c>
+      <x:c r="H45" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I45" s="45"/>
+      <x:c r="J45" s="45"/>
+      <x:c r="K45" s="14"/>
+      <x:c r="L45" s="14" t="str">
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+      </x:c>
+      <x:c r="M45" s="14" t="str">
+        <x:v>not_computed</x:v>
+      </x:c>
+      <x:c r="N45" s="14" t="str">
+        <x:v>period_not_compatible_with_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="25.5" customHeight="1">
+      <x:c r="A46" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B46" s="14" t="str">
+        <x:v>NZ-2019-HES-E-CIGARETTE-DEVICES-EXPENDITURE-NZD</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="str">
+        <x:v>household_expenditure_estimate</x:v>
+      </x:c>
+      <x:c r="D46" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="str">
+        <x:v>year_ended_june</x:v>
+      </x:c>
+      <x:c r="G46" s="45" t="n">
+        <x:v>18034000</x:v>
+      </x:c>
+      <x:c r="H46" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I46" s="45"/>
+      <x:c r="J46" s="45"/>
+      <x:c r="K46" s="14"/>
+      <x:c r="L46" s="14" t="str">
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+      </x:c>
+      <x:c r="M46" s="14" t="str">
+        <x:v>not_computed</x:v>
+      </x:c>
+      <x:c r="N46" s="14" t="str">
+        <x:v>period_not_compatible_with_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="25.5" customHeight="1">
+      <x:c r="A47" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B47" s="14" t="str">
+        <x:v>NZ-2019-HES-E-CIGARETTE-REFILLS-EXPENDITURE-NZD</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="str">
+        <x:v>household_expenditure_estimate</x:v>
+      </x:c>
+      <x:c r="D47" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="str">
+        <x:v>year_ended_june</x:v>
+      </x:c>
+      <x:c r="G47" s="45" t="n">
+        <x:v>24242000</x:v>
+      </x:c>
+      <x:c r="H47" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I47" s="45"/>
+      <x:c r="J47" s="45"/>
+      <x:c r="K47" s="14"/>
+      <x:c r="L47" s="14" t="str">
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+      </x:c>
+      <x:c r="M47" s="14" t="str">
+        <x:v>not_computed</x:v>
+      </x:c>
+      <x:c r="N47" s="14" t="str">
+        <x:v>period_not_compatible_with_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="25.5" customHeight="1">
+      <x:c r="A48" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B48" s="14" t="str">
+        <x:v>NZ-2023-HES-E-CIGARETTES-AND-REFILLS-EXPENDITURE-NZD</x:v>
+      </x:c>
+      <x:c r="C48" s="14" t="str">
+        <x:v>household_expenditure_estimate</x:v>
+      </x:c>
+      <x:c r="D48" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="str">
+        <x:v>year_ended_june</x:v>
+      </x:c>
+      <x:c r="G48" s="45" t="n">
+        <x:v>186980000</x:v>
+      </x:c>
+      <x:c r="H48" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I48" s="45"/>
+      <x:c r="J48" s="45"/>
+      <x:c r="K48" s="14"/>
+      <x:c r="L48" s="14" t="str">
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+      </x:c>
+      <x:c r="M48" s="14" t="str">
+        <x:v>not_computed</x:v>
+      </x:c>
+      <x:c r="N48" s="14" t="str">
+        <x:v>period_not_compatible_with_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="25.5" customHeight="1">
+      <x:c r="A49" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B49" s="14" t="str">
+        <x:v>NZ-2023-HES-E-CIGARETTE-DEVICES-EXPENDITURE-NZD</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="str">
+        <x:v>household_expenditure_estimate</x:v>
+      </x:c>
+      <x:c r="D49" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="str">
+        <x:v>year_ended_june</x:v>
+      </x:c>
+      <x:c r="G49" s="45" t="n">
+        <x:v>22488000</x:v>
+      </x:c>
+      <x:c r="H49" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I49" s="45"/>
+      <x:c r="J49" s="45"/>
+      <x:c r="K49" s="14"/>
+      <x:c r="L49" s="14" t="str">
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+      </x:c>
+      <x:c r="M49" s="14" t="str">
+        <x:v>not_computed</x:v>
+      </x:c>
+      <x:c r="N49" s="14" t="str">
+        <x:v>period_not_compatible_with_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="25.5" customHeight="1">
+      <x:c r="A50" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B50" s="14" t="str">
+        <x:v>NZ-2023-HES-E-CIGARETTE-REFILLS-EXPENDITURE-NZD</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="str">
+        <x:v>household_expenditure_estimate</x:v>
+      </x:c>
+      <x:c r="D50" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="str">
+        <x:v>year_ended_june</x:v>
+      </x:c>
+      <x:c r="G50" s="45" t="n">
+        <x:v>164492000</x:v>
+      </x:c>
+      <x:c r="H50" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I50" s="45"/>
+      <x:c r="J50" s="45"/>
+      <x:c r="K50" s="14"/>
+      <x:c r="L50" s="14" t="str">
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+      </x:c>
+      <x:c r="M50" s="14" t="str">
+        <x:v>not_computed</x:v>
+      </x:c>
+      <x:c r="N50" s="14" t="str">
+        <x:v>period_not_compatible_with_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="25.5" customHeight="1">
+      <x:c r="A51" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B51" s="14" t="str">
+        <x:v>CA-2021-HC-VAPING-MARKET-BENCHMARK</x:v>
+      </x:c>
+      <x:c r="C51" s="14" t="str">
+        <x:v>institutional_market_value_benchmark</x:v>
+      </x:c>
+      <x:c r="D51" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E51" s="14" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G51" s="45" t="n">
+        <x:v>2040000000</x:v>
+      </x:c>
+      <x:c r="H51" s="45" t="str">
+        <x:v>CAD</x:v>
+      </x:c>
+      <x:c r="I51" s="45" t="n">
+        <x:v>1.4825689922481</x:v>
+      </x:c>
+      <x:c r="J51" s="45" t="n">
+        <x:f>G51/I51</x:f>
+        <x:v>1375989927.3939602</x:v>
+      </x:c>
+      <x:c r="K51" s="14" t="str">
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2021</x:v>
+      </x:c>
+      <x:c r="L51" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M51" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N51" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="25.5" customHeight="1">
+      <x:c r="A52" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B52" s="14" t="str">
+        <x:v>CA-2021-HC-GAS-CONVENIENCE-VAPING-SALES-BENCHMARK</x:v>
+      </x:c>
+      <x:c r="C52" s="14" t="str">
+        <x:v>institutional_channel_value_benchmark</x:v>
+      </x:c>
+      <x:c r="D52" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G52" s="45" t="n">
+        <x:v>631000000</x:v>
+      </x:c>
+      <x:c r="H52" s="45" t="str">
+        <x:v>CAD</x:v>
+      </x:c>
+      <x:c r="I52" s="45" t="n">
+        <x:v>1.4825689922481</x:v>
+      </x:c>
+      <x:c r="J52" s="45" t="n">
+        <x:f>G52/I52</x:f>
+        <x:v>425612570.67921025</x:v>
+      </x:c>
+      <x:c r="K52" s="14" t="str">
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2021</x:v>
+      </x:c>
+      <x:c r="L52" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M52" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N52" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="25.5" customHeight="1">
+      <x:c r="A53" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B53" s="14" t="str">
+        <x:v>CA-2021-HC-ONLINE-VAPING-SALES-BENCHMARK</x:v>
+      </x:c>
+      <x:c r="C53" s="14" t="str">
+        <x:v>institutional_channel_value_benchmark</x:v>
+      </x:c>
+      <x:c r="D53" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E53" s="14" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G53" s="45" t="n">
+        <x:v>436000000</x:v>
+      </x:c>
+      <x:c r="H53" s="45" t="str">
+        <x:v>CAD</x:v>
+      </x:c>
+      <x:c r="I53" s="45" t="n">
+        <x:v>1.4825689922481</x:v>
+      </x:c>
+      <x:c r="J53" s="45" t="n">
+        <x:f>G53/I53</x:f>
+        <x:v>294084121.73714054</x:v>
+      </x:c>
+      <x:c r="K53" s="14" t="str">
+        <x:v>ECB-EXR-A-CAD-EUR-SP00-A-2021</x:v>
+      </x:c>
+      <x:c r="L53" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M53" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N53" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="25.5" customHeight="1">
+      <x:c r="A54" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B54" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-20595980-SOLD-PRODUCTION-EUR</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="str">
+        <x:v>prodcom_20595980_sold_production_value</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G54" s="45" t="n">
+        <x:v>39078000</x:v>
+      </x:c>
+      <x:c r="H54" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I54" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J54" s="45" t="n">
+        <x:f>G54</x:f>
+        <x:v>39078000</x:v>
+      </x:c>
+      <x:c r="K54" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L54" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M54" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N54" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="25.5" customHeight="1">
+      <x:c r="A55" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B55" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-20595980-IMPORTS-EUR</x:v>
+      </x:c>
+      <x:c r="C55" s="14" t="str">
+        <x:v>prodcom_20595980_import_value</x:v>
+      </x:c>
+      <x:c r="D55" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E55" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G55" s="45" t="n">
+        <x:v>400843037</x:v>
+      </x:c>
+      <x:c r="H55" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I55" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J55" s="45" t="n">
+        <x:f>G55</x:f>
+        <x:v>400843037</x:v>
+      </x:c>
+      <x:c r="K55" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L55" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M55" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N55" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="25.5" customHeight="1">
+      <x:c r="A56" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B56" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-20595980-EXPORTS-EUR</x:v>
+      </x:c>
+      <x:c r="C56" s="14" t="str">
+        <x:v>prodcom_20595980_export_value</x:v>
+      </x:c>
+      <x:c r="D56" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G56" s="45" t="n">
+        <x:v>120676188</x:v>
+      </x:c>
+      <x:c r="H56" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I56" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J56" s="45" t="n">
+        <x:f>G56</x:f>
+        <x:v>120676188</x:v>
+      </x:c>
+      <x:c r="K56" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L56" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M56" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N56" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="25.5" customHeight="1">
+      <x:c r="A57" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B57" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-27901152-SOLD-PRODUCTION-EUR</x:v>
+      </x:c>
+      <x:c r="C57" s="14" t="str">
+        <x:v>prodcom_27901152_sold_production_value</x:v>
+      </x:c>
+      <x:c r="D57" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G57" s="45" t="n">
+        <x:v>99890000</x:v>
+      </x:c>
+      <x:c r="H57" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I57" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J57" s="45" t="n">
+        <x:f>G57</x:f>
+        <x:v>99890000</x:v>
+      </x:c>
+      <x:c r="K57" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L57" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M57" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N57" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="25.5" customHeight="1">
+      <x:c r="A58" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B58" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-27901152-IMPORTS-EUR</x:v>
+      </x:c>
+      <x:c r="C58" s="14" t="str">
+        <x:v>prodcom_27901152_import_value</x:v>
+      </x:c>
+      <x:c r="D58" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G58" s="45" t="n">
+        <x:v>490580247</x:v>
+      </x:c>
+      <x:c r="H58" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I58" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J58" s="45" t="n">
+        <x:f>G58</x:f>
+        <x:v>490580247</x:v>
+      </x:c>
+      <x:c r="K58" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L58" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M58" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N58" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="25.5" customHeight="1">
+      <x:c r="A59" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B59" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-27901152-EXPORTS-EUR</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="str">
+        <x:v>prodcom_27901152_export_value</x:v>
+      </x:c>
+      <x:c r="D59" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G59" s="45" t="n">
+        <x:v>301380538</x:v>
+      </x:c>
+      <x:c r="H59" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I59" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J59" s="45" t="n">
+        <x:f>G59</x:f>
+        <x:v>301380538</x:v>
+      </x:c>
+      <x:c r="K59" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L59" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M59" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N59" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="25.5" customHeight="1">
+      <x:c r="A60" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B60" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-20595980-APPARENT-SUPPLY-EUR</x:v>
+      </x:c>
+      <x:c r="C60" s="14" t="str">
+        <x:v>prodcom_20595980_apparent_supply_value</x:v>
+      </x:c>
+      <x:c r="D60" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E60" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G60" s="45" t="n">
+        <x:v>319244849</x:v>
+      </x:c>
+      <x:c r="H60" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I60" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J60" s="45" t="n">
+        <x:f>G60</x:f>
+        <x:v>319244849</x:v>
+      </x:c>
+      <x:c r="K60" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L60" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M60" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N60" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="25.5" customHeight="1">
+      <x:c r="A61" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B61" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-27901152-APPARENT-SUPPLY-EUR</x:v>
+      </x:c>
+      <x:c r="C61" s="14" t="str">
+        <x:v>prodcom_27901152_apparent_supply_value</x:v>
+      </x:c>
+      <x:c r="D61" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E61" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G61" s="45" t="n">
+        <x:v>289089709</x:v>
+      </x:c>
+      <x:c r="H61" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I61" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J61" s="45" t="n">
+        <x:f>G61</x:f>
+        <x:v>289089709</x:v>
+      </x:c>
+      <x:c r="K61" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L61" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M61" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N61" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="25.5" customHeight="1">
+      <x:c r="A62" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B62" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-COMBINED-APPARENT-SUPPLY-EUR</x:v>
+      </x:c>
+      <x:c r="C62" s="14" t="str">
+        <x:v>combined_prodcom_apparent_supply_value</x:v>
+      </x:c>
+      <x:c r="D62" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E62" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G62" s="45" t="n">
+        <x:v>608334558</x:v>
+      </x:c>
+      <x:c r="H62" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I62" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J62" s="45" t="n">
+        <x:f>G62</x:f>
+        <x:v>608334558</x:v>
+      </x:c>
+      <x:c r="K62" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L62" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M62" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N62" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="25.5" customHeight="1">
+      <x:c r="A63" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B63" s="14" t="str">
+        <x:v>DE-2024-EUROSTAT-APPARENT-SUPPLY-EXCISE-VAT-BRIDGE-EUR</x:v>
+      </x:c>
+      <x:c r="C63" s="14" t="str">
+        <x:v>mechanical_apparent_supply_excise_vat_bridge</x:v>
+      </x:c>
+      <x:c r="D63" s="14" t="str">
+        <x:v>Germany</x:v>
+      </x:c>
+      <x:c r="E63" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F63" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G63" s="45" t="n">
+        <x:v>1040458124.02</x:v>
+      </x:c>
+      <x:c r="H63" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I63" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J63" s="45" t="n">
+        <x:f>G63</x:f>
+        <x:v>1040458124.02</x:v>
+      </x:c>
+      <x:c r="K63" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L63" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M63" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N63" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="25.5" customHeight="1">
+      <x:c r="A64" s="14" t="str">
+        <x:v>market_observation</x:v>
+      </x:c>
+      <x:c r="B64" s="14" t="str">
+        <x:v>PL-2023-CMR-DISPOSABLE-E-CIGARETTE-RETAIL-SALES-VALUE</x:v>
+      </x:c>
+      <x:c r="C64" s="14" t="str">
+        <x:v>commercial_disposable_e_cigarette_retail_sales_value</x:v>
+      </x:c>
+      <x:c r="D64" s="14" t="str">
+        <x:v>Poland</x:v>
+      </x:c>
+      <x:c r="E64" s="14" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G64" s="45" t="n">
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="H64" s="45" t="str">
+        <x:v>PLN</x:v>
+      </x:c>
+      <x:c r="I64" s="45" t="n">
+        <x:v>4.5419658823529</x:v>
+      </x:c>
+      <x:c r="J64" s="45" t="n">
+        <x:f>G64/I64</x:f>
+        <x:v>440337961.9760439</x:v>
+      </x:c>
+      <x:c r="K64" s="14" t="str">
+        <x:v>ECB-EXR-A-PLN-EUR-SP00-A-2023</x:v>
+      </x:c>
+      <x:c r="L64" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M64" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N64" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="25.5" customHeight="1">
+      <x:c r="A65" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B65" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C65" s="14" t="str">
+        <x:v>low.specialistRetailNzd</x:v>
+      </x:c>
+      <x:c r="D65" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E65" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G65" s="45" t="n">
+        <x:v>258327110.88</x:v>
+      </x:c>
+      <x:c r="H65" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I65" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J65" s="45" t="n">
+        <x:f>G65/I65</x:f>
+        <x:v>144474304.51375833</x:v>
+      </x:c>
+      <x:c r="K65" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L65" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M65" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N65" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="25.5" customHeight="1">
+      <x:c r="A66" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B66" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C66" s="14" t="str">
+        <x:v>low.generalRetailRpsNzd</x:v>
+      </x:c>
+      <x:c r="D66" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E66" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F66" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G66" s="45" t="n">
+        <x:v>275335272.8</x:v>
+      </x:c>
+      <x:c r="H66" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I66" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J66" s="45" t="n">
+        <x:f>G66/I66</x:f>
+        <x:v>153986439.55865824</x:v>
+      </x:c>
+      <x:c r="K66" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L66" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M66" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N66" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="25.5" customHeight="1">
+      <x:c r="A67" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B67" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C67" s="14" t="str">
+        <x:v>low.combinedNzd</x:v>
+      </x:c>
+      <x:c r="D67" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E67" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G67" s="45" t="n">
+        <x:v>533662383.68</x:v>
+      </x:c>
+      <x:c r="H67" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I67" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J67" s="45" t="n">
+        <x:f>G67/I67</x:f>
+        <x:v>298460744.0724166</x:v>
+      </x:c>
+      <x:c r="K67" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L67" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M67" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N67" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="25.5" customHeight="1">
+      <x:c r="A68" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B68" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C68" s="14" t="str">
+        <x:v>base.specialistRetailNzd</x:v>
+      </x:c>
+      <x:c r="D68" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E68" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F68" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G68" s="45" t="n">
+        <x:v>274180410.21</x:v>
+      </x:c>
+      <x:c r="H68" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I68" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J68" s="45" t="n">
+        <x:f>G68/I68</x:f>
+        <x:v>153340560.89369413</x:v>
+      </x:c>
+      <x:c r="K68" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L68" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M68" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N68" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="25.5" customHeight="1">
+      <x:c r="A69" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B69" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C69" s="14" t="str">
+        <x:v>base.generalRetailRpsNzd</x:v>
+      </x:c>
+      <x:c r="D69" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E69" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F69" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G69" s="45" t="n">
+        <x:v>367631277.68</x:v>
+      </x:c>
+      <x:c r="H69" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I69" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J69" s="45" t="n">
+        <x:f>G69/I69</x:f>
+        <x:v>205604719.4558489</x:v>
+      </x:c>
+      <x:c r="K69" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L69" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M69" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N69" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="25.5" customHeight="1">
+      <x:c r="A70" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B70" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C70" s="14" t="str">
+        <x:v>base.combinedNzd</x:v>
+      </x:c>
+      <x:c r="D70" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E70" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F70" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G70" s="45" t="n">
+        <x:v>641811687.89</x:v>
+      </x:c>
+      <x:c r="H70" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I70" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J70" s="45" t="n">
+        <x:f>G70/I70</x:f>
+        <x:v>358945280.34954304</x:v>
+      </x:c>
+      <x:c r="K70" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L70" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M70" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N70" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="25.5" customHeight="1">
+      <x:c r="A71" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B71" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C71" s="14" t="str">
+        <x:v>high.specialistRetailNzd</x:v>
+      </x:c>
+      <x:c r="D71" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E71" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F71" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G71" s="45" t="n">
+        <x:v>274180410.21</x:v>
+      </x:c>
+      <x:c r="H71" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I71" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J71" s="45" t="n">
+        <x:f>G71/I71</x:f>
+        <x:v>153340560.89369413</x:v>
+      </x:c>
+      <x:c r="K71" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L71" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M71" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N71" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="25.5" customHeight="1">
+      <x:c r="A72" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B72" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C72" s="14" t="str">
+        <x:v>high.generalRetailRpsNzd</x:v>
+      </x:c>
+      <x:c r="D72" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E72" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F72" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G72" s="45" t="n">
+        <x:v>456995382.29</x:v>
+      </x:c>
+      <x:c r="H72" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I72" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J72" s="45" t="n">
+        <x:f>G72/I72</x:f>
+        <x:v>255583278.88015154</x:v>
+      </x:c>
+      <x:c r="K72" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L72" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M72" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N72" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="25.5" customHeight="1">
+      <x:c r="A73" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B73" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C73" s="14" t="str">
+        <x:v>high.combinedNzd</x:v>
+      </x:c>
+      <x:c r="D73" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E73" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F73" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G73" s="45" t="n">
+        <x:v>731175792.5</x:v>
+      </x:c>
+      <x:c r="H73" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I73" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J73" s="45" t="n">
+        <x:f>G73/I73</x:f>
+        <x:v>408923839.7738457</x:v>
+      </x:c>
+      <x:c r="K73" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L73" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M73" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N73" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="25.5" customHeight="1">
+      <x:c r="A74" s="14" t="str">
+        <x:v>model</x:v>
+      </x:c>
+      <x:c r="B74" s="14" t="str">
+        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+      </x:c>
+      <x:c r="C74" s="14" t="str">
+        <x:v>low</x:v>
+      </x:c>
+      <x:c r="D74" s="14"/>
+      <x:c r="E74" s="14" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="F74" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G74" s="45" t="n">
+        <x:v>667920000</x:v>
+      </x:c>
+      <x:c r="H74" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I74" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J74" s="45" t="n">
+        <x:f>G74</x:f>
+        <x:v>667920000</x:v>
+      </x:c>
+      <x:c r="K74" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L74" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M74" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N74" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="25.5" customHeight="1">
+      <x:c r="A75" s="14" t="str">
+        <x:v>model</x:v>
+      </x:c>
+      <x:c r="B75" s="14" t="str">
+        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+      </x:c>
+      <x:c r="C75" s="14" t="str">
+        <x:v>central</x:v>
+      </x:c>
+      <x:c r="D75" s="14"/>
+      <x:c r="E75" s="14" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="F75" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G75" s="45" t="n">
         <x:v>1199220000</x:v>
       </x:c>
-      <x:c r="H44" s="45" t="str">
+      <x:c r="H75" s="45" t="str">
         <x:v>EUR</x:v>
       </x:c>
-      <x:c r="I44" s="45" t="n">
+      <x:c r="I75" s="45" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J44" s="45" t="n">
-        <x:f>G44</x:f>
+      <x:c r="J75" s="45" t="n">
+        <x:f>G75</x:f>
         <x:v>1199220000</x:v>
       </x:c>
-      <x:c r="K44" s="14" t="str">
+      <x:c r="K75" s="14" t="str">
         <x:v>EUR-IDENTITY</x:v>
       </x:c>
-      <x:c r="L44" s="14" t="str">
+      <x:c r="L75" s="14" t="str">
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
-      <x:c r="M44" s="14" t="str">
+      <x:c r="M75" s="14" t="str">
         <x:v>already_eur</x:v>
       </x:c>
-      <x:c r="N44" s="14" t="str">
+      <x:c r="N75" s="14" t="str">
         <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="25.5" customHeight="1">
-      <x:c r="A45" s="15" t="str">
+    <x:row r="76" ht="25.5" customHeight="1">
+      <x:c r="A76" s="15" t="str">
         <x:v>model</x:v>
       </x:c>
-      <x:c r="B45" s="15" t="str">
+      <x:c r="B76" s="15" t="str">
         <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
       </x:c>
-      <x:c r="C45" s="15" t="str">
+      <x:c r="C76" s="15" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="D45" s="15"/>
-      <x:c r="E45" s="15" t="n">
+      <x:c r="D76" s="15"/>
+      <x:c r="E76" s="15" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F45" s="15" t="str">
+      <x:c r="F76" s="15" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
-      <x:c r="G45" s="46" t="n">
+      <x:c r="G76" s="46" t="n">
         <x:v>1654620000</x:v>
       </x:c>
-      <x:c r="H45" s="46" t="str">
+      <x:c r="H76" s="46" t="str">
         <x:v>EUR</x:v>
       </x:c>
-      <x:c r="I45" s="46" t="n">
+      <x:c r="I76" s="46" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J45" s="46" t="n">
-        <x:f>G45</x:f>
+      <x:c r="J76" s="46" t="n">
+        <x:f>G76</x:f>
         <x:v>1654620000</x:v>
       </x:c>
-      <x:c r="K45" s="15" t="str">
+      <x:c r="K76" s="15" t="str">
         <x:v>EUR-IDENTITY</x:v>
       </x:c>
-      <x:c r="L45" s="15" t="str">
+      <x:c r="L76" s="15" t="str">
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
-      <x:c r="M45" s="15" t="str">
+      <x:c r="M76" s="15" t="str">
         <x:v>already_eur</x:v>
       </x:c>
-      <x:c r="N45" s="15" t="str">
+      <x:c r="N76" s="15" t="str">
         <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6ce77f0000c4cd3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7242543625e42ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="R3153ea57e86f465d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R6164b0abc4714e88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="Re23596c1224a4611"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rdbeee81d39a445a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rd710870d042f465b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rf78f0f343c03432d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R4d7d4fdac86c4c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R9874534607d14a0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R9471cf0fc7cf437b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rd7f57f1b00ba4d81"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E102" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourcesFI" displayName="SourcesFI" ref="A1:E106" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Lähdetunnus"/>
     <x:tableColumn id="2" name="Julkaisija"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EurEquivalentsFI" displayName="EurEquivalentsFI" ref="A1:N76" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EurEquivalentsFI" displayName="EurEquivalentsFI" ref="A1:N85" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Tietuetyyppi"/>
     <x:tableColumn id="2" name="Tunniste"/>
@@ -1073,22 +1073,22 @@
     </x:row>
     <x:row r="18" ht="58.5" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>Julkinen markkina-aineisto sisältää 156 havaintoa 47 lähteestä; 134 virallista havaintoa jakautuvat 98 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
+        <x:v>Julkinen markkina-aineisto sisältää 174 havaintoa 54 lähteestä; 152 virallista havaintoa jakautuvat 116 markkinamittariin ja 36 Ruotsin FHM-rekisterirakenteen lukuun.</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
         <x:v>Markkinakoko</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>Markkinamittarit kattavat Kanadan, Saksan, Suomen, Uuden-Seelannin, Puolan, Ruotsin ja Yhdysvallat. FHM-luvut kuvaavat vuosien 2018–2026 raportoivia toimijoita sekä ilmoitettuja, aktiivisia ja markkinoilta poistettuja tuotteita; ne eivät ole myyntiä tai markkina-arvoa.</x:v>
+        <x:v>Markkinamittarit kattavat Kanadan, Saksan, Espanjan, Suomen, Japanin, Uuden-Seelannin, Puolan, Ruotsin ja Yhdysvallat. FHM-luvut kuvaavat vuosien 2018–2026 raportoivia toimijoita sekä ilmoitettuja, aktiivisia ja markkinoilta poistettuja tuotteita; ne eivät ole myyntiä tai markkina-arvoa.</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
         <x:v>site/data/market-values.json (julkisen sivuston koneellisesti luettava lähdetiedosto)</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>156 = 120 markkina- ja mallihavaintoa + 36 FHM-rakennelukua; 134 virallista = 98 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
+        <x:v>174 = 138 markkina- ja mallihavaintoa + 36 FHM-rakennelukua; 152 virallista = 116 markkinamittaria + 36 rakennelukua. Luokat pidetään erillään eikä niitä summata markkinaksi.</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
         <x:v>Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja kalenterivuoden virtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva, ei valmis vuosijakso. Virallinen lähde ei tee eri mittareista yhteismitallisia.</x:v>
@@ -1276,31 +1276,31 @@
     </x:row>
     <x:row r="25" ht="58.5" customHeight="1">
       <x:c r="A25" s="14" t="str">
-        <x:v>Saksan tuleva toimittajatesti DE-BLIND-1.0.0 lukittiin ennen tulevan toimituksen pisteytystä; testi on EI PISTEYTETTY.</x:v>
+        <x:v>Saksan yksityinen DE-BLIND-1.0.0-audit läpäisi vuosien 2023 ja 2024 vuosirajat sekä yhdistetyn rajan; toimittaja-arvot ja tarkat poikkeamat pidetään salassa.</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
         <x:v>Markkinakoko / Saksa</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Viralliset lopulliset ankkurit ovat 1 241 000 litraa vuonna 2023 ja 1 284 000 litraa vuonna 2024 eli yhteensä 2 525 000 litraa. Ennalta rekisteröidyt rajat ovat 15 % vuodessa ja 10 % yhteensä.</x:v>
+        <x:v>Viralliset lopulliset ankkurit ja ennalta rekisteröidyt vuosittaiset sekä yhdistetty numeerinen raja olivat julkisesti lukittuja ennen lisensoidun otteen yksityistä tarkastusta. Kaikki kolme numeerista testiä läpäistiin.</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003/ ; source/NZ_CA_DE_DONOR_CONTROL_SPRINT_2026-08-02.md</x:v>
+        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003/ ; source/NZ_CA_DE_DONOR_CONTROL_SPRINT_2026-08-02.md ; source/GERMANY_VENDOR_AUDIT_BOUNDARY_2026-08-03.md</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
         <x:v>Vuotuinen poikkeama = |toimittajan litrat / viralliset litrat − 1|; yhteispoikkeama = |toimittajan kahden vuoden summa / 2 525 000 − 1|.</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>Numeerinen osuma ei yksin osoita samaa tuotetta, yksikköä, veroperustaa, kanavaa tai tapahtumavaihetta. Rajoja ei soviteta yksityisiin arvoihin.</x:v>
+        <x:v>Numeerinen osuma ei yksin osoita samaa tuotetta, veroperustaa, kanavaa, tapahtumavaihetta tai lähdelinjaa. Rajoja ei sovitettu yksityisiin arvoihin.</x:v>
       </x:c>
       <x:c r="H25" s="14" t="str">
-        <x:v>Vahvistettu</x:v>
+        <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
-        <x:v>Testin läpäisy ei hyväksy Saksaa donoriksi eikä valtuuta ostoa, lisenssiä, maksua tai luovutusta. Saksan virallinen retail-arvo pysyy not_computed.</x:v>
+        <x:v>Julkinen lukija ei voi toisintaa lisensoitujen toimittaja-arvojen vertailua. Saksa ei ole donor, Euromonitor on 1/6 ja EI PISTEYTETTY, laajempi paketti HOLD ja Saksan retail-arvo not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58.5" customHeight="1">
@@ -1610,7 +1610,7 @@
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
-        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 98 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
+        <x:v>36 = 9 vuotta (2018–2026) × 4 rekisterirakenteen mittaria. Veroankkuri, 116 markkinamittaria ja 36 rakennelukua pidetään erillään.</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
         <x:v>Rakenneluvuista ei päätellä myyntiarvoa, myyntimäärää tai markkinaosuutta. Vuosien 2018–2025 luvut ovat viranomaisen vuosilabeleita, eivät oletettuja vuosivirtoja tai vuoden lopun tilannekuvia. Vuosi 2026 on tarkistushetken tilannekuva eikä sitä vuositasoiteta.</x:v>
@@ -2361,7 +2361,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb7c46ce2af94a95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ed77eb7ae4f4515"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2419,7 +2419,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.08.02-41</x:v>
+        <x:v>2026.08.03-43</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2427,7 +2427,7 @@
         <x:v>Päivitetty</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -2460,7 +2460,7 @@
       </x:c>
       <x:c r="B11" s="13" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A11)</x:f>
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20.25" customHeight="1">
@@ -2469,7 +2469,7 @@
       </x:c>
       <x:c r="B12" s="14" t="n">
         <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A12)</x:f>
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20.25" customHeight="1">
@@ -2671,7 +2671,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redea25e6cf804d42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d812dee99214549"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3585,7 +3585,7 @@
         <x:v>https://api.sejm.gov.pl/eli/acts/DU/2025/698/text.pdf</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="31.5" customHeight="1">
@@ -3602,7 +3602,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="31.5" customHeight="1">
@@ -3619,7 +3619,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="31.5" customHeight="1">
@@ -3636,7 +3636,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="31.5" customHeight="1">
@@ -3653,7 +3653,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="31.5" customHeight="1">
@@ -3670,7 +3670,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="31.5" customHeight="1">
@@ -3687,7 +3687,7 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="31.5" customHeight="1">
@@ -3704,12 +3704,12 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="31.5" customHeight="1">
       <x:c r="A61" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-2FB6E2117AD7</x:v>
+        <x:v>REGISTER-REFERENCE-D5953C312D13</x:v>
       </x:c>
       <x:c r="B61" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3718,15 +3718,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="31.5" customHeight="1">
       <x:c r="A62" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-8FEBAD85B03E</x:v>
+        <x:v>REGISTER-REFERENCE-9C49B54585D6</x:v>
       </x:c>
       <x:c r="B62" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3735,15 +3735,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="31.5" customHeight="1">
       <x:c r="A63" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-37CBB91A050A</x:v>
+        <x:v>REGISTER-REFERENCE-E8955C1A58F7</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3752,15 +3752,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="31.5" customHeight="1">
       <x:c r="A64" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-BCE59F2D3F9D</x:v>
+        <x:v>REGISTER-REFERENCE-AB39FAE18104</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3769,15 +3769,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="31.5" customHeight="1">
       <x:c r="A65" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-2267B190A073</x:v>
+        <x:v>REGISTER-REFERENCE-2FB6E2117AD7</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3786,15 +3786,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="31.5" customHeight="1">
       <x:c r="A66" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-957871D9CB33</x:v>
+        <x:v>REGISTER-REFERENCE-8FEBAD85B03E</x:v>
       </x:c>
       <x:c r="B66" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3803,15 +3803,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="31.5" customHeight="1">
       <x:c r="A67" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-5C7194247112</x:v>
+        <x:v>REGISTER-REFERENCE-37CBB91A050A</x:v>
       </x:c>
       <x:c r="B67" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3820,15 +3820,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="31.5" customHeight="1">
       <x:c r="A68" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-75BF634166B2</x:v>
+        <x:v>REGISTER-REFERENCE-BCE59F2D3F9D</x:v>
       </x:c>
       <x:c r="B68" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3837,15 +3837,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="31.5" customHeight="1">
       <x:c r="A69" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-54AB30A87D3D</x:v>
+        <x:v>REGISTER-REFERENCE-2267B190A073</x:v>
       </x:c>
       <x:c r="B69" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3854,15 +3854,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="31.5" customHeight="1">
       <x:c r="A70" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-4B9D48C385C9</x:v>
+        <x:v>REGISTER-REFERENCE-957871D9CB33</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3871,15 +3871,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="31.5" customHeight="1">
       <x:c r="A71" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-97704C5CE7D4</x:v>
+        <x:v>REGISTER-REFERENCE-5C7194247112</x:v>
       </x:c>
       <x:c r="B71" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3888,15 +3888,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="31.5" customHeight="1">
       <x:c r="A72" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-EF5511CEAE3C</x:v>
+        <x:v>REGISTER-REFERENCE-75BF634166B2</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3905,15 +3905,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="31.5" customHeight="1">
       <x:c r="A73" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-15452EF50F15</x:v>
+        <x:v>REGISTER-REFERENCE-54AB30A87D3D</x:v>
       </x:c>
       <x:c r="B73" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3922,15 +3922,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="31.5" customHeight="1">
       <x:c r="A74" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-9C7C0F0FD33F</x:v>
+        <x:v>REGISTER-REFERENCE-4B9D48C385C9</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3939,15 +3939,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="31.5" customHeight="1">
       <x:c r="A75" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-82A9C0A0E9C4</x:v>
+        <x:v>REGISTER-REFERENCE-97704C5CE7D4</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3956,15 +3956,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="31.5" customHeight="1">
       <x:c r="A76" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-25E2E410922F</x:v>
+        <x:v>REGISTER-REFERENCE-EF5511CEAE3C</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3973,15 +3973,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="31.5" customHeight="1">
       <x:c r="A77" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-74211110370B</x:v>
+        <x:v>REGISTER-REFERENCE-15452EF50F15</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -3990,15 +3990,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="31.5" customHeight="1">
       <x:c r="A78" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-59446D8EB279</x:v>
+        <x:v>REGISTER-REFERENCE-9C7C0F0FD33F</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -4007,15 +4007,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="31.5" customHeight="1">
       <x:c r="A79" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-BFB2E2E1B4A3</x:v>
+        <x:v>REGISTER-REFERENCE-82A9C0A0E9C4</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -4024,15 +4024,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="31.5" customHeight="1">
       <x:c r="A80" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-D26C27B033B0</x:v>
+        <x:v>REGISTER-REFERENCE-25E2E410922F</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -4041,15 +4041,15 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="31.5" customHeight="1">
       <x:c r="A81" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
+        <x:v>REGISTER-REFERENCE-74211110370B</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
         <x:v>data-api.ecb.europa.eu</x:v>
@@ -4058,373 +4058,441 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="31.5" customHeight="1">
       <x:c r="A82" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
+        <x:v>REGISTER-REFERENCE-59446D8EB279</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
-        <x:v>data.ecb.europa.eu</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="31.5" customHeight="1">
       <x:c r="A83" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-2DA87527D51F</x:v>
+        <x:v>REGISTER-REFERENCE-BFB2E2E1B4A3</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
-        <x:v>datahelpdesk.worldbank.org</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="31.5" customHeight="1">
       <x:c r="A84" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-1208D3C8F46C</x:v>
+        <x:v>REGISTER-REFERENCE-D26C27B033B0</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
-        <x:v>douanes.public.lu</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>https://douanes.public.lu/dam-assets/fr/accises/signes-fiscaux/2024/s48/bareme-e-liquide-s48.pdf</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="31.5" customHeight="1">
       <x:c r="A85" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-25E8C2FC0150</x:v>
+        <x:v>REGISTER-REFERENCE-32690599750D</x:v>
       </x:c>
       <x:c r="B85" s="14" t="str">
-        <x:v>genesis.destatis.de</x:v>
+        <x:v>data-api.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003/</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="31.5" customHeight="1">
       <x:c r="A86" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
+        <x:v>REGISTER-REFERENCE-9B93C76EF890</x:v>
       </x:c>
       <x:c r="B86" s="14" t="str">
-        <x:v>laws-lois.justice.gc.ca</x:v>
+        <x:v>data.ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
+        <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="31.5" customHeight="1">
       <x:c r="A87" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
+        <x:v>REGISTER-REFERENCE-2DA87527D51F</x:v>
       </x:c>
       <x:c r="B87" s="14" t="str">
-        <x:v>adm.gov.it</x:v>
+        <x:v>datahelpdesk.worldbank.org</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
+        <x:v>https://datahelpdesk.worldbank.org/knowledgebase/articles/898581-api-basic-call-structures</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="31.5" customHeight="1">
       <x:c r="A88" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+        <x:v>REGISTER-REFERENCE-1208D3C8F46C</x:v>
       </x:c>
       <x:c r="B88" s="14" t="str">
-        <x:v>ecb.europa.eu</x:v>
+        <x:v>douanes.public.lu</x:v>
       </x:c>
       <x:c r="C88" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://douanes.public.lu/dam-assets/fr/accises/signes-fiscaux/2024/s48/bareme-e-liquide-s48.pdf</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="31.5" customHeight="1">
       <x:c r="A89" s="14" t="str">
-        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
+        <x:v>REGISTER-REFERENCE-25E8C2FC0150</x:v>
       </x:c>
       <x:c r="B89" s="14" t="str">
-        <x:v>Public Health Agency of Sweden</x:v>
+        <x:v>genesis.destatis.de</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
+        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003/</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="31.5" customHeight="1">
       <x:c r="A90" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
       </x:c>
       <x:c r="B90" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>laws-lois.justice.gc.ca</x:v>
       </x:c>
       <x:c r="C90" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D90" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E90" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="31.5" customHeight="1">
       <x:c r="A91" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
       </x:c>
       <x:c r="B91" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>adm.gov.it</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="31.5" customHeight="1">
       <x:c r="A92" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
+        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
       </x:c>
       <x:c r="B92" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C92" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D92" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E92" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="31.5" customHeight="1">
       <x:c r="A93" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-1766C84ECA96</x:v>
+        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
       </x:c>
       <x:c r="B93" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>Public Health Agency of Sweden</x:v>
       </x:c>
       <x:c r="C93" s="14" t="str">
-        <x:v>register_reference</x:v>
+        <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D93" s="14" t="str">
-        <x:v>https://www.health.govt.nz/system/files/2025-11/notifiable-products-annual-sales-return-2025-user-guide.pdf</x:v>
+        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E93" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="31.5" customHeight="1">
       <x:c r="A94" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-529570B0D6C7</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
       </x:c>
       <x:c r="B94" s="14" t="str">
-        <x:v>podatki.gov.pl</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C94" s="14" t="str">
-        <x:v>register_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D94" s="14" t="str">
-        <x:v>https://www.podatki.gov.pl/akcyza/komunikaty-w-zakresie-podatku-akcyzowego</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E94" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="31.5" customHeight="1">
       <x:c r="A95" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
       </x:c>
       <x:c r="B95" s="14" t="str">
-        <x:v>podatki.gov.pl</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C95" s="14" t="str">
-        <x:v>register_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D95" s="14" t="str">
-        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E95" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="31.5" customHeight="1">
       <x:c r="A96" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-645255DD4B34</x:v>
+        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
       </x:c>
       <x:c r="B96" s="14" t="str">
-        <x:v>stats.govt.nz</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C96" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D96" s="14" t="str">
-        <x:v>https://www.stats.govt.nz/large-datasets/csv-files-for-download/overseas-merchandise-trade-datasets/</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
       </x:c>
       <x:c r="E96" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="31.5" customHeight="1">
       <x:c r="A97" s="14" t="str">
-        <x:v>UN-MEMBER-STATES</x:v>
+        <x:v>REGISTER-REFERENCE-1766C84ECA96</x:v>
       </x:c>
       <x:c r="B97" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C97" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D97" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+        <x:v>https://www.health.govt.nz/system/files/2025-11/notifiable-products-annual-sales-return-2025-user-guide.pdf</x:v>
       </x:c>
       <x:c r="E97" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="31.5" customHeight="1">
       <x:c r="A98" s="14" t="str">
-        <x:v>UN-NON-MEMBER-STATES</x:v>
+        <x:v>REGISTER-REFERENCE-529570B0D6C7</x:v>
       </x:c>
       <x:c r="B98" s="14" t="str">
-        <x:v>United Nations</x:v>
+        <x:v>podatki.gov.pl</x:v>
       </x:c>
       <x:c r="C98" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D98" s="14" t="str">
-        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+        <x:v>https://www.podatki.gov.pl/akcyza/komunikaty-w-zakresie-podatku-akcyzowego</x:v>
       </x:c>
       <x:c r="E98" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="31.5" customHeight="1">
       <x:c r="A99" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
+        <x:v>REGISTER-REFERENCE-7AD3E1157197</x:v>
       </x:c>
       <x:c r="B99" s="14" t="str">
-        <x:v>www150.statcan.gc.ca</x:v>
+        <x:v>podatki.gov.pl</x:v>
       </x:c>
       <x:c r="C99" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D99" s="14" t="str">
-        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
+        <x:v>https://www.podatki.gov.pl/akcyza/stawki-podatkowe/</x:v>
       </x:c>
       <x:c r="E99" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="31.5" customHeight="1">
       <x:c r="A100" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-D61AFC87FA19</x:v>
+        <x:v>REGISTER-REFERENCE-645255DD4B34</x:v>
       </x:c>
       <x:c r="B100" s="14" t="str">
-        <x:v>www150.statcan.gc.ca</x:v>
+        <x:v>stats.govt.nz</x:v>
       </x:c>
       <x:c r="C100" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D100" s="14" t="str">
-        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
+        <x:v>https://www.stats.govt.nz/large-datasets/csv-files-for-download/overseas-merchandise-trade-datasets/</x:v>
       </x:c>
       <x:c r="E100" s="14" t="str">
-        <x:v>2026-08-02</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="31.5" customHeight="1">
       <x:c r="A101" s="14" t="str">
+        <x:v>UN-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B101" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C101" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D101" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/member-states</x:v>
+      </x:c>
+      <x:c r="E101" s="14" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="31.5" customHeight="1">
+      <x:c r="A102" s="14" t="str">
+        <x:v>UN-NON-MEMBER-STATES</x:v>
+      </x:c>
+      <x:c r="B102" s="14" t="str">
+        <x:v>United Nations</x:v>
+      </x:c>
+      <x:c r="C102" s="14" t="str">
+        <x:v>official_reference</x:v>
+      </x:c>
+      <x:c r="D102" s="14" t="str">
+        <x:v>https://www.un.org/en/about-us/non-member-states</x:v>
+      </x:c>
+      <x:c r="E102" s="14" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="31.5" customHeight="1">
+      <x:c r="A103" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-3332B0031C1D</x:v>
+      </x:c>
+      <x:c r="B103" s="14" t="str">
+        <x:v>www150.statcan.gc.ca</x:v>
+      </x:c>
+      <x:c r="C103" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D103" s="14" t="str">
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010007101</x:v>
+      </x:c>
+      <x:c r="E103" s="14" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="31.5" customHeight="1">
+      <x:c r="A104" s="14" t="str">
+        <x:v>REGISTER-REFERENCE-D61AFC87FA19</x:v>
+      </x:c>
+      <x:c r="B104" s="14" t="str">
+        <x:v>www150.statcan.gc.ca</x:v>
+      </x:c>
+      <x:c r="C104" s="14" t="str">
+        <x:v>register_reference</x:v>
+      </x:c>
+      <x:c r="D104" s="14" t="str">
+        <x:v>https://www150.statcan.gc.ca/t1/tbl1/en/tv.action?pid=2010008001</x:v>
+      </x:c>
+      <x:c r="E104" s="14" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="31.5" customHeight="1">
+      <x:c r="A105" s="14" t="str">
         <x:v>REGISTER-REFERENCE-9479B1548E50</x:v>
       </x:c>
-      <x:c r="B101" s="14" t="str">
+      <x:c r="B105" s="14" t="str">
         <x:v>www3.stats.govt.nz</x:v>
       </x:c>
-      <x:c r="C101" s="14" t="str">
+      <x:c r="C105" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D101" s="14" t="str">
+      <x:c r="D105" s="14" t="str">
         <x:v>https://www3.stats.govt.nz/HS10_by_Country/2024_Exports_HS10.zip</x:v>
       </x:c>
-      <x:c r="E101" s="14" t="str">
-        <x:v>2026-08-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="31.5" customHeight="1">
-      <x:c r="A102" s="15" t="str">
+      <x:c r="E105" s="14" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="31.5" customHeight="1">
+      <x:c r="A106" s="15" t="str">
         <x:v>REGISTER-REFERENCE-94B1312153E9</x:v>
       </x:c>
-      <x:c r="B102" s="15" t="str">
+      <x:c r="B106" s="15" t="str">
         <x:v>www3.stats.govt.nz</x:v>
       </x:c>
-      <x:c r="C102" s="15" t="str">
+      <x:c r="C106" s="15" t="str">
         <x:v>register_reference</x:v>
       </x:c>
-      <x:c r="D102" s="15" t="str">
+      <x:c r="D106" s="15" t="str">
         <x:v>https://www3.stats.govt.nz/HS10_by_Country/2024_Imports_HS10.zip</x:v>
       </x:c>
-      <x:c r="E102" s="15" t="str">
-        <x:v>2026-08-02</x:v>
+      <x:c r="E106" s="15" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6c4dc40110f477c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02e074c8a8dd4fe1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7281,266 +7349,266 @@
     </x:row>
     <x:row r="65" ht="25.5" customHeight="1">
       <x:c r="A65" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>ES-2025-AEAT-M573-ALL-EPIGRAPHS-ACCRUED-EXCISE-LIABILITY-EUR</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>low.specialistRetailNzd</x:v>
+        <x:v>accrued_excise_liability</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Spain</x:v>
       </x:c>
       <x:c r="E65" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F65" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G65" s="45" t="n">
-        <x:v>258327110.88</x:v>
+        <x:v>36151000</x:v>
       </x:c>
       <x:c r="H65" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I65" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J65" s="45" t="n">
-        <x:f>G65/I65</x:f>
-        <x:v>144474304.51375833</x:v>
+        <x:f>G65</x:f>
+        <x:v>36151000</x:v>
       </x:c>
       <x:c r="K65" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L65" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M65" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N65" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="25.5" customHeight="1">
       <x:c r="A66" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B66" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>ES-2025-AEAT-M573-ALL-EPIGRAPHS-GROSS-CASH-RECEIPTS-EUR</x:v>
       </x:c>
       <x:c r="C66" s="14" t="str">
-        <x:v>low.generalRetailRpsNzd</x:v>
+        <x:v>gross_excise_cash_receipts</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Spain</x:v>
       </x:c>
       <x:c r="E66" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F66" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G66" s="45" t="n">
-        <x:v>275335272.8</x:v>
+        <x:v>31797000</x:v>
       </x:c>
       <x:c r="H66" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I66" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J66" s="45" t="n">
-        <x:f>G66/I66</x:f>
-        <x:v>153986439.55865824</x:v>
+        <x:f>G66</x:f>
+        <x:v>31797000</x:v>
       </x:c>
       <x:c r="K66" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L66" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M66" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N66" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="25.5" customHeight="1">
       <x:c r="A67" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B67" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>ES-2025-AEAT-M573-ALL-EPIGRAPHS-NET-CASH-RECEIPTS-EUR</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
-        <x:v>low.combinedNzd</x:v>
+        <x:v>net_excise_cash_receipts</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Spain</x:v>
       </x:c>
       <x:c r="E67" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F67" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G67" s="45" t="n">
-        <x:v>533662383.68</x:v>
+        <x:v>29568000</x:v>
       </x:c>
       <x:c r="H67" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I67" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J67" s="45" t="n">
-        <x:f>G67/I67</x:f>
-        <x:v>298460744.0724166</x:v>
+        <x:f>G67</x:f>
+        <x:v>29568000</x:v>
       </x:c>
       <x:c r="K67" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L67" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M67" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N67" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="25.5" customHeight="1">
       <x:c r="A68" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B68" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>ES-2026-H1-AEAT-M573-ALL-EPIGRAPHS-GROSS-CASH-RECEIPTS-EUR</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
-        <x:v>base.specialistRetailNzd</x:v>
+        <x:v>gross_excise_cash_receipts</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Spain</x:v>
       </x:c>
       <x:c r="E68" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="F68" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>2026_h1</x:v>
       </x:c>
       <x:c r="G68" s="45" t="n">
-        <x:v>274180410.21</x:v>
+        <x:v>25726000</x:v>
       </x:c>
       <x:c r="H68" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I68" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J68" s="45" t="n">
-        <x:f>G68/I68</x:f>
-        <x:v>153340560.89369413</x:v>
+        <x:f>G68</x:f>
+        <x:v>25726000</x:v>
       </x:c>
       <x:c r="K68" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L68" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M68" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N68" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="25.5" customHeight="1">
       <x:c r="A69" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B69" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>ES-2026-H1-AEAT-M573-ALL-EPIGRAPHS-NET-CASH-RECEIPTS-EUR</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
-        <x:v>base.generalRetailRpsNzd</x:v>
+        <x:v>net_excise_cash_receipts</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Spain</x:v>
       </x:c>
       <x:c r="E69" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="F69" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>2026_h1</x:v>
       </x:c>
       <x:c r="G69" s="45" t="n">
-        <x:v>367631277.68</x:v>
+        <x:v>21776000</x:v>
       </x:c>
       <x:c r="H69" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>EUR</x:v>
       </x:c>
       <x:c r="I69" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J69" s="45" t="n">
-        <x:f>G69/I69</x:f>
-        <x:v>205604719.4558489</x:v>
+        <x:f>G69</x:f>
+        <x:v>21776000</x:v>
       </x:c>
       <x:c r="K69" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>EUR-IDENTITY</x:v>
       </x:c>
       <x:c r="L69" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M69" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>already_eur</x:v>
       </x:c>
       <x:c r="N69" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="25.5" customHeight="1">
       <x:c r="A70" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>JP-2022-854340000-E-CIGARETTE-DEVICE-IMPORT-CIF-VALUE-JPY</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
-        <x:v>base.combinedNzd</x:v>
+        <x:v>e_cigarette_device_customs_import_cif_value</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Japan</x:v>
       </x:c>
       <x:c r="E70" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="F70" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G70" s="45" t="n">
-        <x:v>641811687.89</x:v>
+        <x:v>70257202000</x:v>
       </x:c>
       <x:c r="H70" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>JPY</x:v>
       </x:c>
       <x:c r="I70" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>138.027392996109</x:v>
       </x:c>
       <x:c r="J70" s="45" t="n">
         <x:f>G70/I70</x:f>
-        <x:v>358945280.34954304</x:v>
+        <x:v>509009121.12409854</x:v>
       </x:c>
       <x:c r="K70" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-JPY-EUR-SP00-A-2022</x:v>
       </x:c>
       <x:c r="L70" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M70" s="14" t="str">
         <x:v>computed</x:v>
@@ -7551,41 +7619,41 @@
     </x:row>
     <x:row r="71" ht="25.5" customHeight="1">
       <x:c r="A71" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B71" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>JP-2023-854340000-E-CIGARETTE-DEVICE-IMPORT-CIF-VALUE-JPY</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
-        <x:v>high.specialistRetailNzd</x:v>
+        <x:v>e_cigarette_device_customs_import_cif_value</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Japan</x:v>
       </x:c>
       <x:c r="E71" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="F71" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G71" s="45" t="n">
-        <x:v>274180410.21</x:v>
+        <x:v>70496284000</x:v>
       </x:c>
       <x:c r="H71" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>JPY</x:v>
       </x:c>
       <x:c r="I71" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>151.9902745098038</x:v>
       </x:c>
       <x:c r="J71" s="45" t="n">
         <x:f>G71/I71</x:f>
-        <x:v>153340560.89369413</x:v>
+        <x:v>463821018.99192756</x:v>
       </x:c>
       <x:c r="K71" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-JPY-EUR-SP00-A-2023</x:v>
       </x:c>
       <x:c r="L71" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M71" s="14" t="str">
         <x:v>computed</x:v>
@@ -7596,16 +7664,16 @@
     </x:row>
     <x:row r="72" ht="25.5" customHeight="1">
       <x:c r="A72" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>JP-2024-854340000-E-CIGARETTE-DEVICE-IMPORT-CIF-VALUE-JPY</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
-        <x:v>high.generalRetailRpsNzd</x:v>
+        <x:v>e_cigarette_device_customs_import_cif_value</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Japan</x:v>
       </x:c>
       <x:c r="E72" s="14" t="n">
         <x:v>2024</x:v>
@@ -7614,23 +7682,23 @@
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G72" s="45" t="n">
-        <x:v>456995382.29</x:v>
+        <x:v>74526020000</x:v>
       </x:c>
       <x:c r="H72" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>JPY</x:v>
       </x:c>
       <x:c r="I72" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>163.8519140625</x:v>
       </x:c>
       <x:c r="J72" s="45" t="n">
         <x:f>G72/I72</x:f>
-        <x:v>255583278.88015154</x:v>
+        <x:v>454837652.80625683</x:v>
       </x:c>
       <x:c r="K72" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-JPY-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L72" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M72" s="14" t="str">
         <x:v>computed</x:v>
@@ -7641,41 +7709,41 @@
     </x:row>
     <x:row r="73" ht="25.5" customHeight="1">
       <x:c r="A73" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>market_observation</x:v>
       </x:c>
       <x:c r="B73" s="14" t="str">
-        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+        <x:v>JP-2025-854340000-E-CIGARETTE-DEVICE-IMPORT-CIF-VALUE-JPY</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
-        <x:v>high.combinedNzd</x:v>
+        <x:v>e_cigarette_device_customs_import_cif_value</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Japan</x:v>
       </x:c>
       <x:c r="E73" s="14" t="n">
-        <x:v>2024</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="F73" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G73" s="45" t="n">
-        <x:v>731175792.5</x:v>
+        <x:v>84361341000</x:v>
       </x:c>
       <x:c r="H73" s="45" t="str">
-        <x:v>NZD</x:v>
+        <x:v>JPY</x:v>
       </x:c>
       <x:c r="I73" s="45" t="n">
-        <x:v>1.788048828125</x:v>
+        <x:v>169.0434509803921</x:v>
       </x:c>
       <x:c r="J73" s="45" t="n">
         <x:f>G73/I73</x:f>
-        <x:v>408923839.7738457</x:v>
+        <x:v>499051223.2845113</x:v>
       </x:c>
       <x:c r="K73" s="14" t="str">
-        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+        <x:v>ECB-EXR-A-JPY-EUR-SP00-A-2025</x:v>
       </x:c>
       <x:c r="L73" s="14" t="str">
-        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M73" s="14" t="str">
         <x:v>computed</x:v>
@@ -7686,137 +7754,542 @@
     </x:row>
     <x:row r="74" ht="25.5" customHeight="1">
       <x:c r="A74" s="14" t="str">
-        <x:v>model</x:v>
+        <x:v>scenario_component</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
-        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
-        <x:v>low</x:v>
-      </x:c>
-      <x:c r="D74" s="14"/>
+        <x:v>low.specialistRetailNzd</x:v>
+      </x:c>
+      <x:c r="D74" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
       <x:c r="E74" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F74" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G74" s="45" t="n">
-        <x:v>667920000</x:v>
+        <x:v>258327110.88</x:v>
       </x:c>
       <x:c r="H74" s="45" t="str">
-        <x:v>EUR</x:v>
+        <x:v>NZD</x:v>
       </x:c>
       <x:c r="I74" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>1.788048828125</x:v>
       </x:c>
       <x:c r="J74" s="45" t="n">
-        <x:f>G74</x:f>
-        <x:v>667920000</x:v>
+        <x:f>G74/I74</x:f>
+        <x:v>144474304.51375833</x:v>
       </x:c>
       <x:c r="K74" s="14" t="str">
-        <x:v>EUR-IDENTITY</x:v>
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
       </x:c>
       <x:c r="L74" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M74" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>computed</x:v>
       </x:c>
       <x:c r="N74" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="25.5" customHeight="1">
       <x:c r="A75" s="14" t="str">
-        <x:v>model</x:v>
+        <x:v>scenario_component</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
-        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>central</x:v>
-      </x:c>
-      <x:c r="D75" s="14"/>
+        <x:v>low.generalRetailRpsNzd</x:v>
+      </x:c>
+      <x:c r="D75" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
       <x:c r="E75" s="14" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="F75" s="14" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
       <x:c r="G75" s="45" t="n">
+        <x:v>275335272.8</x:v>
+      </x:c>
+      <x:c r="H75" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I75" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J75" s="45" t="n">
+        <x:f>G75/I75</x:f>
+        <x:v>153986439.55865824</x:v>
+      </x:c>
+      <x:c r="K75" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L75" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M75" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N75" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="25.5" customHeight="1">
+      <x:c r="A76" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="str">
+        <x:v>low.combinedNzd</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E76" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F76" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G76" s="45" t="n">
+        <x:v>533662383.68</x:v>
+      </x:c>
+      <x:c r="H76" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I76" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J76" s="45" t="n">
+        <x:f>G76/I76</x:f>
+        <x:v>298460744.0724166</x:v>
+      </x:c>
+      <x:c r="K76" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L76" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M76" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N76" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="25.5" customHeight="1">
+      <x:c r="A77" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B77" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C77" s="14" t="str">
+        <x:v>base.specialistRetailNzd</x:v>
+      </x:c>
+      <x:c r="D77" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E77" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F77" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G77" s="45" t="n">
+        <x:v>274180410.21</x:v>
+      </x:c>
+      <x:c r="H77" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I77" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J77" s="45" t="n">
+        <x:f>G77/I77</x:f>
+        <x:v>153340560.89369413</x:v>
+      </x:c>
+      <x:c r="K77" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L77" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M77" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N77" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="25.5" customHeight="1">
+      <x:c r="A78" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B78" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C78" s="14" t="str">
+        <x:v>base.generalRetailRpsNzd</x:v>
+      </x:c>
+      <x:c r="D78" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E78" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F78" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G78" s="45" t="n">
+        <x:v>367631277.68</x:v>
+      </x:c>
+      <x:c r="H78" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I78" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J78" s="45" t="n">
+        <x:f>G78/I78</x:f>
+        <x:v>205604719.4558489</x:v>
+      </x:c>
+      <x:c r="K78" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L78" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M78" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N78" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="25.5" customHeight="1">
+      <x:c r="A79" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>base.combinedNzd</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E79" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F79" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G79" s="45" t="n">
+        <x:v>641811687.89</x:v>
+      </x:c>
+      <x:c r="H79" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I79" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J79" s="45" t="n">
+        <x:f>G79/I79</x:f>
+        <x:v>358945280.34954304</x:v>
+      </x:c>
+      <x:c r="K79" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L79" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M79" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N79" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="25.5" customHeight="1">
+      <x:c r="A80" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B80" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C80" s="14" t="str">
+        <x:v>high.specialistRetailNzd</x:v>
+      </x:c>
+      <x:c r="D80" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E80" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F80" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G80" s="45" t="n">
+        <x:v>274180410.21</x:v>
+      </x:c>
+      <x:c r="H80" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I80" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J80" s="45" t="n">
+        <x:f>G80/I80</x:f>
+        <x:v>153340560.89369413</x:v>
+      </x:c>
+      <x:c r="K80" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L80" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M80" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N80" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="25.5" customHeight="1">
+      <x:c r="A81" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B81" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>high.generalRetailRpsNzd</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E81" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F81" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G81" s="45" t="n">
+        <x:v>456995382.29</x:v>
+      </x:c>
+      <x:c r="H81" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I81" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J81" s="45" t="n">
+        <x:f>G81/I81</x:f>
+        <x:v>255583278.88015154</x:v>
+      </x:c>
+      <x:c r="K81" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L81" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M81" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N81" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="25.5" customHeight="1">
+      <x:c r="A82" s="14" t="str">
+        <x:v>scenario_component</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>NZ-2024-RETAIL-RANGE</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>high.combinedNzd</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>New Zealand</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F82" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G82" s="45" t="n">
+        <x:v>731175792.5</x:v>
+      </x:c>
+      <x:c r="H82" s="45" t="str">
+        <x:v>NZD</x:v>
+      </x:c>
+      <x:c r="I82" s="45" t="n">
+        <x:v>1.788048828125</x:v>
+      </x:c>
+      <x:c r="J82" s="45" t="n">
+        <x:f>G82/I82</x:f>
+        <x:v>408923839.7738457</x:v>
+      </x:c>
+      <x:c r="K82" s="14" t="str">
+        <x:v>ECB-EXR-A-NZD-EUR-SP00-A-2024</x:v>
+      </x:c>
+      <x:c r="L82" s="14" t="str">
+        <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
+      </x:c>
+      <x:c r="M82" s="14" t="str">
+        <x:v>computed</x:v>
+      </x:c>
+      <x:c r="N82" s="14" t="str">
+        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="25.5" customHeight="1">
+      <x:c r="A83" s="14" t="str">
+        <x:v>model</x:v>
+      </x:c>
+      <x:c r="B83" s="14" t="str">
+        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+      </x:c>
+      <x:c r="C83" s="14" t="str">
+        <x:v>low</x:v>
+      </x:c>
+      <x:c r="D83" s="14"/>
+      <x:c r="E83" s="14" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="F83" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G83" s="45" t="n">
+        <x:v>667920000</x:v>
+      </x:c>
+      <x:c r="H83" s="45" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I83" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J83" s="45" t="n">
+        <x:f>G83</x:f>
+        <x:v>667920000</x:v>
+      </x:c>
+      <x:c r="K83" s="14" t="str">
+        <x:v>EUR-IDENTITY</x:v>
+      </x:c>
+      <x:c r="L83" s="14" t="str">
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+      </x:c>
+      <x:c r="M83" s="14" t="str">
+        <x:v>already_eur</x:v>
+      </x:c>
+      <x:c r="N83" s="14" t="str">
+        <x:v>original_currency_already_eur</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="25.5" customHeight="1">
+      <x:c r="A84" s="14" t="str">
+        <x:v>model</x:v>
+      </x:c>
+      <x:c r="B84" s="14" t="str">
+        <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
+      </x:c>
+      <x:c r="C84" s="14" t="str">
+        <x:v>central</x:v>
+      </x:c>
+      <x:c r="D84" s="14"/>
+      <x:c r="E84" s="14" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="F84" s="14" t="str">
+        <x:v>calendar_year</x:v>
+      </x:c>
+      <x:c r="G84" s="45" t="n">
         <x:v>1199220000</x:v>
       </x:c>
-      <x:c r="H75" s="45" t="str">
+      <x:c r="H84" s="45" t="str">
         <x:v>EUR</x:v>
       </x:c>
-      <x:c r="I75" s="45" t="n">
+      <x:c r="I84" s="45" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J75" s="45" t="n">
-        <x:f>G75</x:f>
+      <x:c r="J84" s="45" t="n">
+        <x:f>G84</x:f>
         <x:v>1199220000</x:v>
       </x:c>
-      <x:c r="K75" s="14" t="str">
+      <x:c r="K84" s="14" t="str">
         <x:v>EUR-IDENTITY</x:v>
       </x:c>
-      <x:c r="L75" s="14" t="str">
+      <x:c r="L84" s="14" t="str">
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
-      <x:c r="M75" s="14" t="str">
+      <x:c r="M84" s="14" t="str">
         <x:v>already_eur</x:v>
       </x:c>
-      <x:c r="N75" s="14" t="str">
+      <x:c r="N84" s="14" t="str">
         <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="25.5" customHeight="1">
-      <x:c r="A76" s="15" t="str">
+    <x:row r="85" ht="25.5" customHeight="1">
+      <x:c r="A85" s="15" t="str">
         <x:v>model</x:v>
       </x:c>
-      <x:c r="B76" s="15" t="str">
+      <x:c r="B85" s="15" t="str">
         <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
       </x:c>
-      <x:c r="C76" s="15" t="str">
+      <x:c r="C85" s="15" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="D76" s="15"/>
-      <x:c r="E76" s="15" t="n">
+      <x:c r="D85" s="15"/>
+      <x:c r="E85" s="15" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F76" s="15" t="str">
+      <x:c r="F85" s="15" t="str">
         <x:v>calendar_year</x:v>
       </x:c>
-      <x:c r="G76" s="46" t="n">
+      <x:c r="G85" s="46" t="n">
         <x:v>1654620000</x:v>
       </x:c>
-      <x:c r="H76" s="46" t="str">
+      <x:c r="H85" s="46" t="str">
         <x:v>EUR</x:v>
       </x:c>
-      <x:c r="I76" s="46" t="n">
+      <x:c r="I85" s="46" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J76" s="46" t="n">
-        <x:f>G76</x:f>
+      <x:c r="J85" s="46" t="n">
+        <x:f>G85</x:f>
         <x:v>1654620000</x:v>
       </x:c>
-      <x:c r="K76" s="15" t="str">
+      <x:c r="K85" s="15" t="str">
         <x:v>EUR-IDENTITY</x:v>
       </x:c>
-      <x:c r="L76" s="15" t="str">
+      <x:c r="L85" s="15" t="str">
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
-      <x:c r="M76" s="15" t="str">
+      <x:c r="M85" s="15" t="str">
         <x:v>already_eur</x:v>
       </x:c>
-      <x:c r="N76" s="15" t="str">
+      <x:c r="N85" s="15" t="str">
         <x:v>original_currency_already_eur</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7242543625e42ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re46feb816db34858"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/downloads/pixan-bank-evidence-register-fi.xlsx
+++ b/site/downloads/pixan-bank-evidence-register-fi.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rf78f0f343c03432d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R4d7d4fdac86c4c45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="R9874534607d14a0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="R9471cf0fc7cf437b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="Rd7f57f1b00ba4d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="1" r:id="Rcb1333698efc4494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yhteenveto" sheetId="2" r:id="R32874bd3b4e641a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutkijan kysymykset" sheetId="3" r:id="Rc301d4a69b2c476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lähteet" sheetId="4" r:id="Rd1a8ef187fb74d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eurovastineet" sheetId="5" r:id="R8e317cc257c34849"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -308,8 +308,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EvidenceRegisterFI" displayName="EvidenceRegisterFI" ref="A1:I61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I61"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EvidenceRegisterFI" displayName="EvidenceRegisterFI" ref="A1:I63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I63"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Väite"/>
     <x:tableColumn id="2" name="Dia/osio"/>
@@ -355,16 +355,16 @@
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Tietuetyyppi"/>
     <x:tableColumn id="2" name="Tunniste"/>
-    <x:tableColumn id="3" name="Erä / komponentti"/>
+    <x:tableColumn id="3" name="Erätunniste / komponentti"/>
     <x:tableColumn id="4" name="Maa / maantiede"/>
     <x:tableColumn id="5" name="Vuosi"/>
-    <x:tableColumn id="6" name="Periodi"/>
+    <x:tableColumn id="6" name="Jakso"/>
     <x:tableColumn id="7" name="Alkuperäinen määrä"/>
     <x:tableColumn id="8" name="Valuutta"/>
-    <x:tableColumn id="9" name="ECB-kurssi (valuuttayksikköä / EUR)"/>
+    <x:tableColumn id="9" name="EKP-kurssi (valuuttayksikköä / EUR)"/>
     <x:tableColumn id="10" name="EUR-vasta-arvo (täysi tarkkuus)"/>
-    <x:tableColumn id="11" name="Rate ID"/>
-    <x:tableColumn id="12" name="ECB-lähde URL"/>
+    <x:tableColumn id="11" name="Kurssitunniste"/>
+    <x:tableColumn id="12" name="EKP-lähteen URL"/>
     <x:tableColumn id="13" name="Tila"/>
     <x:tableColumn id="14" name="Syy / menetelmä"/>
   </x:tableColumns>
@@ -714,7 +714,7 @@
         <x:v>B2-julkaisun vaatimusten lukumäärä.</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>Yleiskielinen tiivistelmä ei ole claim construction.</x:v>
+        <x:v>Yleiskielinen tiivistelmä ei ole patenttivaatimusten tulkinta.</x:v>
       </x:c>
       <x:c r="H5" s="14" t="str">
         <x:v>Vahvistettu</x:v>
@@ -818,7 +818,7 @@
         <x:v>Oikeudellinen näyttö</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>RPX merkitsee asian Kiinan patenttien uudelleentarkastuslautakunnan Review Request -menettelyksi. Reitti koskee hylätyn hakemuksen uudelleentarkastusta; kyse ei ole loukkaustuomiosta tai vastapuolen mitätöintiasiasta. Hakijan nimi esitetään muodossa Pixon Limited / 皮克森有限公司 ja vastaa vahvasti Pixanin kiinankielistä nimiversiota, mutta virallista päätöstä ei saatu haettua. CN105764365B julkaistiin myöhemmin myönnettynä 4.5.2021.</x:v>
+        <x:v>RPX merkitsee asian Kiinan patenttien uudelleentarkastuslautakunnan uudelleentarkastuspyyntömenettelyksi. Reitti koskee hylätyn hakemuksen uudelleentarkastusta; kyse ei ole loukkaustuomiosta tai vastapuolen mitätöintiasiasta. Hakijan nimi esitetään muodossa Pixon Limited / 皮克森有限公司 ja vastaa vahvasti Pixanin kiinankielistä nimiversiota, mutta virallista päätöstä ei saatu haettua. CN105764365B julkaistiin myöhemmin myönnettynä 4.5.2021.</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
         <x:v>https://litigation.rpxcorp.com/china/prb/5153434-picsen-company-v-pixan-oy-of-365 ; https://www.cnipa.gov.cn/art/2020/6/5/art_1517_92474.html ; https://register.epo.org/application?number=EP14836345&amp;lng=en&amp;tab=family</x:v>
@@ -827,7 +827,7 @@
         <x:v>2020-08-24</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
-        <x:v>Sekundäärisen docket-tiedon luokittelu virallisen prosessiohjeen avulla.</x:v>
+        <x:v>Sekundäärisen asiakirjarekisteritiedon luokittelu virallisen prosessiohjeen avulla.</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
         <x:v>Nimivastaavuus on vahva mutta virallista päätöstä ei saatu.</x:v>
@@ -923,7 +923,7 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I12" s="14" t="str">
-        <x:v>Kansallista vuosikoostetta, hintasarjaa, kattavuutta ja vähittäismyynnin sovitusta ei ole saatu; retailValueStatus on not_computed.</x:v>
+        <x:v>Kansallista vuosikoostetta, hintasarjaa, kattavuutta ja vähittäismyynnin sovitusta ei ole saatu; vähittäisarvon tila on not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58.5" customHeight="1">
@@ -981,7 +981,7 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I14" s="14" t="str">
-        <x:v>Luokkakohtaiset nettoverot tai millilitrat, oikaisut, nikotiinittomat täyttönesteet, hinnat ja kuluttajamyynti puuttuvat; retailValueStatus on not_computed.</x:v>
+        <x:v>Luokkakohtaiset nettoverot tai millilitrat, oikaisut, nikotiinittomat täyttönesteet, hinnat ja kuluttajamyynti puuttuvat; vähittäisarvon tila on not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="58.5" customHeight="1">
@@ -1010,7 +1010,7 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>Vuosittaiset veronalaiset millilitrat, verotuotto, veromerkkien pakkausmäärät, laitemäärät, sell-through ja kauden lopullisuus puuttuvat; retailValueStatus on not_computed.</x:v>
+        <x:v>Vuosittaiset veronalaiset millilitrat, verotuotto, veromerkkien pakkausmäärät, laitemäärät, sell-through ja kauden lopullisuus puuttuvat; vähittäisarvon tila on not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58.5" customHeight="1">
@@ -1039,7 +1039,7 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I16" s="14" t="str">
-        <x:v>Nikotiinittomien tuotteiden kuluttajamyynti, millilitrat, hinnat, kotimainen tuotanto, varastot, jälleenvienti ja laittomat kanavat puuttuvat; retailValueStatus on not_computed.</x:v>
+        <x:v>Nikotiinittomien tuotteiden kuluttajamyynti, millilitrat, hinnat, kotimainen tuotanto, varastot, jälleenvienti ja laittomat kanavat puuttuvat; vähittäisarvon tila on not_computed.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58.5" customHeight="1">
@@ -1207,7 +1207,7 @@
         <x:v>189 402 451,96 + 84 709 409,85 + 68 548,40 = 274 180 410,21 NZD. Viereiset ja ratkaisemattomat luokat käsitellään ennen vaping-summaa ja jätetään siitä pois. Kaikkien 29 tiedoston URL:t, koot ja SHA-256-tiivisteet validoidaan ennen aggregointia.</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>Deterministinen tuoterajaus on julkinen. RPS kerää tuotelajeja ja määriä mutta ei havaittua retail-arvoa. GST-perusta on tuntematon. Stats NZ:n lopullinen 2024 HS10 -kontrolli on tullivaiheen herkkyys eikä riippumaton retail-täsmäytys.</x:v>
+        <x:v>Deterministinen tuoterajaus on julkinen. RPS kerää tuotelajeja ja määriä mutta ei havaittua vähittäisarvoa. GST-perusta on tuntematon. Stats NZ:n lopullinen 2024 HS10 -kontrolli on tullivaiheen herkkyys eikä riippumaton vähittäismyynnin täsmäytys.</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str">
         <x:v>Tuettu</x:v>
@@ -1276,31 +1276,31 @@
     </x:row>
     <x:row r="25" ht="58.5" customHeight="1">
       <x:c r="A25" s="14" t="str">
-        <x:v>Saksan yksityinen DE-BLIND-1.0.0-audit läpäisi vuosien 2023 ja 2024 vuosirajat sekä yhdistetyn rajan; toimittaja-arvot ja tarkat poikkeamat pidetään salassa.</x:v>
+        <x:v>Saksan julkaistu ratkaisu on vain mahdollinen tapauskohtainen evidenssi ratkaistulle tuotteelle ja patenttivaatimukselle; se ei osoita maailmanlaajuista suojaa, loukkausta tai patentin arvoa.</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>Markkinakoko / Saksa</x:v>
+        <x:v>Patentin arvonmääritys / Saksa</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Viralliset lopulliset ankkurit ja ennalta rekisteröidyt vuosittaiset sekä yhdistetty numeerinen raja olivat julkisesti lukittuja ennen lisensoidun otteen yksityistä tarkastusta. Kaikki kolme numeerista testiä läpäistiin.</x:v>
+        <x:v>Siirtäminen toiseen tuotteeseen, vastapuoleen, ajanjaksoon tai maahan vaatii ajantasaisen patenttiasiantuntijan tarkastaman patenttivaatimusten vertailun ja prosessitilan vahvistuksen.</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003/ ; source/NZ_CA_DE_DONOR_CONTROL_SPRINT_2026-08-02.md ; source/GERMANY_VENDOR_AUDIT_BOUNDARY_2026-08-03.md</x:v>
+        <x:v>https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206 ; site/data/patent-history.json (monetisation.valuationControl.germanyRole)</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>Vuotuinen poikkeama = |toimittajan litrat / viralliset litrat − 1|; yhteispoikkeama = |toimittajan kahden vuoden summa / 2 525 000 − 1|.</x:v>
+        <x:v>Ei numeerista ekstrapolointia. Ratkaisua käytetään vain lähteistettynä tapauskohtaisena evidenssinä ja jokainen siirto käsitellään uutena tuloskohtaisena riippuvuutena.</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>Numeerinen osuma ei yksin osoita samaa tuotetta, veroperustaa, kanavaa, tapahtumavaihetta tai lähdelinjaa. Rajoja ei sovitettu yksityisiin arvoihin.</x:v>
+        <x:v>Tuomion julkaisu ei yksin vahvista lainvoimaisuutta, nykyistä prosessitilaa, toisen tuotteen patenttivaatimusten vertailuia, myyntiä, rojaltia, vahingonkorvausta tai arvoa.</x:v>
       </x:c>
       <x:c r="H25" s="14" t="str">
-        <x:v>Tuettu</x:v>
+        <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
-        <x:v>Julkinen lukija ei voi toisintaa lisensoitujen toimittaja-arvojen vertailua. Saksa ei ole donor, Euromonitor on 1/6 ja EI PISTEYTETTY, laajempi paketti HOLD ja Saksan retail-arvo not_computed.</x:v>
+        <x:v>Tarvitaan ajantasainen prosessitilan tarkistus, maakohtainen oikeusnäyttö, säilytetty tuotetodiste ja asiantuntijan patenttivaatimusten vertailu ennen käyttöä toisessa tapauksessa.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58.5" customHeight="1">
@@ -1416,7 +1416,7 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
-        <x:v>Toimitusosuuksia ei saa soveltaa retail-arvoon laite–neste-jaoksi eikä eri tapahtumatasoja summata.</x:v>
+        <x:v>Toimitusosuuksia ei saa soveltaa vähittäisarvoon laite–neste-jaoksi eikä eri tapahtumatasoja summata.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="58.5" customHeight="1">
@@ -1590,7 +1590,7 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I35" s="14" t="str">
-        <x:v>Tarvitaan AKC-4/R:n e-savuke–lämmitin–monitoimilaitejako, veron kuukausijakauma, vähittäishinnat, kanavapeitto ja riippumaton täsmäytys. Puolalle ei anneta donor-pistemäärää ilman maa–vuosi retail-arvoa.</x:v>
+        <x:v>Tarvitaan AKC-4/R:n e-savuke–lämmitin–monitoimilaitejako, veron kuukausijakauma, vähittäishinnat, kanavapeitto ja riippumaton täsmäytys. Puolalle ei anneta donor-pistemäärää ilman maa–vuosi vähittäisarvoa.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="58.5" customHeight="1">
@@ -1688,7 +1688,7 @@
         <x:v>Rahoitusteesi</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>research_dataset_not_valuation: Useimmista maista puuttuu virallinen vuosittainen laite- ja nestemyynti Markkinaevidenssiä ei ole vielä sidottu maakohtaiseen patenttistatukseen ja claim charteihin Aineisto ei sisällä riippumatonta IVS-arvonmääritystä eikä realisoitunutta lisenssi- tai vahingonkorvauskassavirtaa</x:v>
+        <x:v>research_dataset_not_valuation: Useimmista maista puuttuu virallinen vuosittainen laite- ja nestemyynti Markkinaevidenssiä ei ole vielä sidottu maakohtaiseen patenttistatukseen ja vaatimusvertailutaulukkoeihin Aineisto ei sisällä riippumatonta IVS-arvonmääritystä eikä realisoitunutta lisenssi- tai vahingonkorvauskassavirtaa</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
         <x:v>site/data/atlas.json (readiness)</x:v>
@@ -1842,7 +1842,7 @@
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="F44" s="14" t="str">
-        <x:v>Diligence-rajaus.</x:v>
+        <x:v>Tarkastusrajaus.</x:v>
       </x:c>
       <x:c r="G44" s="14" t="str">
         <x:v>Neljä kansallista rekisterijurisdiktiota ei kata koko perhettä.</x:v>
@@ -1862,7 +1862,7 @@
         <x:v>Tekninen erottautuminen</x:v>
       </x:c>
       <x:c r="C45" s="14" t="str">
-        <x:v>Patenttihistorian guardrail edellyttää counsel-reviewed claim chartia.</x:v>
+        <x:v>Patenttihistorian guardrail edellyttää asiamiehen tarkastamaa vaatimusvertailutaulukkoa.</x:v>
       </x:c>
       <x:c r="D45" s="14" t="str">
         <x:v>https://data.epo.org/publication-server/rest/v1.2/patents/EP3032975NWB2/document.pdf ; https://www.gesetze-bayern.de/Content/Document/Y-300-Z-BECKRS-B-2026-N-14206</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I45" s="14" t="str">
-        <x:v>Hanki tuotteet, säilytä hallussapitoketju, tee teardown ja asiamiehen tarkastama claim chart.</x:v>
+        <x:v>Hanki tuotteet, säilytä hallussapitoketju, tee purkuanalyysi ja asiamiehen tarkastama vaatimusvertailutaulukko.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="58.5" customHeight="1">
@@ -1909,7 +1909,7 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I46" s="14" t="str">
-        <x:v>Tarvitaan addressable/in-scope/claim-mapped sales -silta.</x:v>
+        <x:v>Tarvitaan osoitettavan ja rajaukseen kuuluvan vaatimuksiin kohdistetun myynnin silta.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="58.5" customHeight="1">
@@ -1949,7 +1949,7 @@
         <x:v>Kaupallistamismalli</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>Patenttihistorian vaiheistus suosittelee kovia portteja, claim chartia ja auditoitavaa yhteydenottoa.</x:v>
+        <x:v>Patenttihistorian vaiheistus suosittelee kovia portteja, vaatimusvertailutaulukkoia ja auditoitavaa yhteydenottoa.</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
         <x:v>https://www.wipo.int/ja/web/business/assignment-licensing ; https://www.wipo.int/en/web/business/settle-ip-disputes ; https://www.epo.org/en/searching-for-patents/business/ipscore</x:v>
@@ -1996,7 +1996,7 @@
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="I49" s="14" t="str">
-        <x:v>Tarvitaan riippumaton arvonmääritys, oikeuksien due diligence, toteutuneet tai sopimuspohjaiset kassavirrat ja downside-analyysi.</x:v>
+        <x:v>Tarvitaan riippumaton arvonmääritys, oikeuksien huolellisuustarkastus, toteutuneet tai sopimuspohjaiset kassavirrat ja alariskianalyysi.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="58.5" customHeight="1">
@@ -2016,7 +2016,7 @@
         <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
-        <x:v>Virallisen API-tiedon diligence-hälytys.</x:v>
+        <x:v>Virallisen API-tiedon tarkastushälytys.</x:v>
       </x:c>
       <x:c r="G50" s="14" t="str">
         <x:v>API:n in-force-through-päivä ei ole tässä lakisääteinen eräpäiväväite.</x:v>
@@ -2083,7 +2083,7 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I52" s="14" t="str">
-        <x:v>Yhdysvaltain patenttiasiamies: vahvistakaa entity status, summa ja maksu sekä arkistoikaa virallinen kuitti ja tuoreet ylläpito- ja siirtotiedot.</x:v>
+        <x:v>Yhdysvaltain patenttiasiamies: vahvistakaa toimijaluokka, summa ja maksu sekä arkistoikaa virallinen kuitti ja tuoreet ylläpito- ja siirtotiedot.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="58.5" customHeight="1">
@@ -2199,7 +2199,7 @@
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="I56" s="14" t="str">
-        <x:v>Laadi tuotteet, valmistajat, vaihtoehtoiset teknologiat, patenttiperheet, hinnat ja claim-map-status kattava vertailu.</x:v>
+        <x:v>Laadi tuotteet, valmistajat, vaihtoehtoiset teknologiat, patenttiperheet, hinnat ja vaatimusvertailun tila kattava vertailu.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="58.5" customHeight="1">
@@ -2257,7 +2257,7 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="I58" s="14" t="str">
-        <x:v>Laadi maakohtaiset oikeus- ja claim chart -paketit ennen yhteydenottoja.</x:v>
+        <x:v>Laadi maakohtaiset oikeus- ja vaatimusvertailutaulukko -paketit ennen yhteydenottoja.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="58.5" customHeight="1">
@@ -2319,49 +2319,107 @@
       </x:c>
     </x:row>
     <x:row r="61" ht="58.5" customHeight="1">
-      <x:c r="A61" s="15" t="str">
+      <x:c r="A61" s="14" t="str">
+        <x:v>Seitsemän perustekohtaista patenttiarvon tulosta ovat erillisiä, ei-yhteenlaskettavia ja null/NOT_COMPUTED-tilassa; kaikki seitsemän tuloskohtaista porttia ovat avoinna.</x:v>
+      </x:c>
+      <x:c r="B61" s="14" t="str">
+        <x:v>Patentin arvonmääritys</x:v>
+      </x:c>
+      <x:c r="C61" s="14" t="str">
+        <x:v>Markkinaosapuolen patentti-/perhearvo, omistajakohtainen strateginen arvo, RFR-/oman käytön arvo, kolmannen osapuolen lisensointiarvo, menneen täytäntöönpanon NPV, transaktioindikaatio ja vakuuden realisaatioarvo pysyvät erillään. BASIS-AND-SUBJECT lukitsee kohteen, käyttötarkoituksen ja perusteen ennen muita portteja.</x:v>
+      </x:c>
+      <x:c r="D61" s="14" t="str">
+        <x:v>site/data/patent-history.json (monetisation.valuationControl) ; site/schemas/patent-valuation-control.schema.json ; https://www.wipo.int/en/web/ip-financing ; https://www.ifrs.org/issued-standards/list-of-standards/ifrs-13-fair-value-measurement/</x:v>
+      </x:c>
+      <x:c r="E61" s="14" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="str">
+        <x:v>Kukin tulos voidaan laskea vain sen omien lähde- ja porttiriippuvuuksien sulkeuduttua. Nykytila: 7/7 OPEN; kaikki seitsemän tulostapausarvoa ja niiden painotetut arvot ovat null.</x:v>
+      </x:c>
+      <x:c r="G61" s="14" t="str">
+        <x:v>IFRS 13 määrittää vain markkinaosapuolen mittauspäivän exit price -perustetta; muita tuloksia ei nimetä IFRS-käyväksi arvoksi. Puuttuva ei ole nolla eikä tuloksia summata.</x:v>
+      </x:c>
+      <x:c r="H61" s="14" t="str">
+        <x:v>Vahvistettu</x:v>
+      </x:c>
+      <x:c r="I61" s="14" t="str">
+        <x:v>Tarvitaan allekirjoitettu peruste- ja kohdetaulukko, maaoikeusmatriisi, suojatun käytön ja patenttivaatimusten vertailu, kohdistettu SKU-myynti, reittikohtainen talousmalli, skenaarioiden summa-yhteen-QA ja vakuudelle erillinen realisaatiotapaus.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="58.5" customHeight="1">
+      <x:c r="A62" s="14" t="str">
+        <x:v>Seitsemän vaiheen menetelmä haarautuu katetun myynnin jälkeen RFR-/omaan käyttöön, kolmannen lisensointiin, menneeseen täytäntöönpanoon tai strategiseen optioarvoon; vain täytäntöönpanon haara vaatii loukkausmyyntiä.</x:v>
+      </x:c>
+      <x:c r="B62" s="14" t="str">
+        <x:v>Patentin arvonmääritys / menetelmä</x:v>
+      </x:c>
+      <x:c r="C62" s="14" t="str">
+        <x:v>Reitti tuottaa todennäköisyyspainotetut päivätyt kassavirrat; diskonttokorko ei sisällä erikseen mallinnettuja riskejä ja kukin riski kohdistetaan kerran. Donor 0/3 on vain markkinamallin evidenssivalmiuden syöte.</x:v>
+      </x:c>
+      <x:c r="D62" s="14" t="str">
+        <x:v>site/data/patent-history.json (monetisation.valuationControl) ; https://www.wipo.int/en/web/ip-financing</x:v>
+      </x:c>
+      <x:c r="E62" s="14" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="str">
+        <x:v>Täsmäytä tuote, maa, vastapuoli, ajanjakso ja taloudellinen hyöty; käytä Boolean-/aikamaskeja, mitattua SKU-kohdistusta ja asiantuntijan claim-tilaa ilman päällekkäisiä leikkureita.</x:v>
+      </x:c>
+      <x:c r="G62" s="14" t="str">
+        <x:v>Saksan ratkaisu on vain mahdollinen tapauskohtainen evidenssi ratkaistulle tuotteelle ja vaatimukselle; siirto vaatii ajantasaisen asiantuntijan mappingin ja prosessitilan tarkastuksen. Vakuusarvo ei ole arvo kerrottuna yleisellä leikkurilla.</x:v>
+      </x:c>
+      <x:c r="H62" s="14" t="str">
+        <x:v>Vahvistettu</x:v>
+      </x:c>
+      <x:c r="I62" s="14" t="str">
+        <x:v>Kaikki välivaiheet, seitsemän arvotulosta ja probabilityWeightedValueEUR pysyvät null/NOT_COMPUTED-tilassa, kunnes tuloskohtaiset riippuvuudet on suljettu lähteistetyllä näytöllä.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="58.5" customHeight="1">
+      <x:c r="A63" s="15" t="str">
         <x:v>Korkean luottamuksen rahoituspaketti vaatii suljetun datahuoneen julkisen paketin rinnalle.</x:v>
       </x:c>
-      <x:c r="B61" s="15" t="str">
+      <x:c r="B63" s="15" t="str">
         <x:v>Seuraavat vaiheet</x:v>
       </x:c>
-      <x:c r="C61" s="15" t="str">
+      <x:c r="C63" s="15" t="str">
         <x:v>Julkinen paketti osoittaa lähteet ja puutteet mutta ei sisällä luottamuksellista talous-, sopimus- tai omistusaineistoa.</x:v>
       </x:c>
-      <x:c r="D61" s="15" t="str">
+      <x:c r="D63" s="15" t="str">
         <x:v>Julkisen paketin rajaus</x:v>
       </x:c>
-      <x:c r="E61" s="15" t="str">
+      <x:c r="E63" s="15" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
-      <x:c r="F61" s="15" t="str">
-        <x:v>Diligence-arkkitehtuurin suositus.</x:v>
-      </x:c>
-      <x:c r="G61" s="15" t="str">
+      <x:c r="F63" s="15" t="str">
+        <x:v>Tarkastusarkkitehtuurin suositus.</x:v>
+      </x:c>
+      <x:c r="G63" s="15" t="str">
         <x:v>Pääsy rajataan ja lokitetaan.</x:v>
       </x:c>
-      <x:c r="H61" s="15" t="str">
+      <x:c r="H63" s="15" t="str">
         <x:v>Tuettu</x:v>
       </x:c>
-      <x:c r="I61" s="15" t="str">
+      <x:c r="I63" s="15" t="str">
         <x:v>Perusta indeksoitu datahuone: Corporate, IP, Legal, Commercial, Finance, Valuation, Security.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="H2:H61">
+  <x:conditionalFormatting sqref="H2:H63">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Vahvistettu"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Tuettu"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Oletus"/>
     <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Puuttuu"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H2:H61">
+    <x:dataValidation type="list" sqref="H2:H63">
       <x:formula1>"Vahvistettu,Tuettu,Oletus,Puuttuu"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ed77eb7ae4f4515"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49dc088729d04004"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2419,7 +2477,7 @@
         <x:v>Versio</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>2026.08.03-43</x:v>
+        <x:v>2026.08.03-44</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20.25" customHeight="1">
@@ -2443,8 +2501,8 @@
         <x:v>Evidenssirivejä</x:v>
       </x:c>
       <x:c r="B8" s="15" t="n">
-        <x:f>COUNTA('Evidence Register'!$A$2:$A$61)</x:f>
-        <x:v>60</x:v>
+        <x:f>COUNTA('Evidence Register'!$A$2:$A$63)</x:f>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20.25" customHeight="1"/>
@@ -2459,8 +2517,8 @@
         <x:v>Vahvistettu</x:v>
       </x:c>
       <x:c r="B11" s="13" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A11)</x:f>
-        <x:v>35</x:v>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$63,A11)</x:f>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20.25" customHeight="1">
@@ -2468,8 +2526,8 @@
         <x:v>Tuettu</x:v>
       </x:c>
       <x:c r="B12" s="14" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A12)</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$63,A12)</x:f>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20.25" customHeight="1">
@@ -2477,7 +2535,7 @@
         <x:v>Oletus</x:v>
       </x:c>
       <x:c r="B13" s="14" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A13)</x:f>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$63,A13)</x:f>
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -2486,7 +2544,7 @@
         <x:v>Puuttuu</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:f>COUNTIF('Evidence Register'!$H$2:$H$61,A14)</x:f>
+        <x:f>COUNTIF('Evidence Register'!$H$2:$H$63,A14)</x:f>
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -2543,7 +2601,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>Riippumattomat testit ja claim chartit priorisoiduille tuotteille.</x:v>
+        <x:v>Riippumattomat testit ja vaatimusvertailutaulukot priorisoiduille tuotteille.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="27" customHeight="1">
@@ -2559,7 +2617,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B27" s="15" t="str">
-        <x:v>Riippumaton arvonmääritys ja vakuuden downside-analyysi.</x:v>
+        <x:v>Riippumaton arvonmääritys ja vakuuden alariskianalyysi.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2620,7 +2678,7 @@
         <x:v>Mikä tuote täyttää mitkä patenttivaatimuksen rajat?</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>Riippumaton testi ja claim chart</x:v>
+        <x:v>Riippumaton testi ja vaatimusvertailutaulukko</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
         <x:v>Rajallinen Saksan näyttö</x:v>
@@ -2659,7 +2717,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>Mitä vakuudesta realisoidaan downside-tilanteessa?</x:v>
+        <x:v>Mitä vakuudesta realisoidaan alariskitilanteessa?</x:v>
       </x:c>
       <x:c r="C6" s="15" t="str">
         <x:v>Riippumaton arvo ja realisointipolku</x:v>
@@ -2671,7 +2729,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d812dee99214549"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R064785dd1d5e4ca0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4185,16 +4243,16 @@
     </x:row>
     <x:row r="89" ht="31.5" customHeight="1">
       <x:c r="A89" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-25E8C2FC0150</x:v>
+        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
       </x:c>
       <x:c r="B89" s="14" t="str">
-        <x:v>genesis.destatis.de</x:v>
+        <x:v>laws-lois.justice.gc.ca</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>https://genesis.destatis.de/datenbank/online/statistic/73411/table/73411-0003/</x:v>
+        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
         <x:v>2026-08-03</x:v>
@@ -4202,16 +4260,16 @@
     </x:row>
     <x:row r="90" ht="31.5" customHeight="1">
       <x:c r="A90" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-77110A089CB9</x:v>
+        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
       </x:c>
       <x:c r="B90" s="14" t="str">
-        <x:v>laws-lois.justice.gc.ca</x:v>
+        <x:v>adm.gov.it</x:v>
       </x:c>
       <x:c r="C90" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D90" s="14" t="str">
-        <x:v>https://laws-lois.justice.gc.ca/eng/regulations/SOR-2023-123/FullText.html</x:v>
+        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
       </x:c>
       <x:c r="E90" s="14" t="str">
         <x:v>2026-08-03</x:v>
@@ -4219,16 +4277,16 @@
     </x:row>
     <x:row r="91" ht="31.5" customHeight="1">
       <x:c r="A91" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-A3B80D981A8D</x:v>
+        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
       </x:c>
       <x:c r="B91" s="14" t="str">
-        <x:v>adm.gov.it</x:v>
+        <x:v>ecb.europa.eu</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>https://www.adm.gov.it/portale/documents/20182/261920520/Libro+blu+2024+-+Relazione.pdf/e46989ce-b39f-a404-3b4b-2af3196cba43</x:v>
+        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
         <x:v>2026-08-03</x:v>
@@ -4236,16 +4294,16 @@
     </x:row>
     <x:row r="92" ht="31.5" customHeight="1">
       <x:c r="A92" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-50ED634F402A</x:v>
+        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
       </x:c>
       <x:c r="B92" s="14" t="str">
-        <x:v>ecb.europa.eu</x:v>
+        <x:v>Public Health Agency of Sweden</x:v>
       </x:c>
       <x:c r="C92" s="14" t="str">
-        <x:v>register_reference</x:v>
+        <x:v>official_reference</x:v>
       </x:c>
       <x:c r="D92" s="14" t="str">
-        <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
+        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
       </x:c>
       <x:c r="E92" s="14" t="str">
         <x:v>2026-08-03</x:v>
@@ -4253,16 +4311,16 @@
     </x:row>
     <x:row r="93" ht="31.5" customHeight="1">
       <x:c r="A93" s="14" t="str">
-        <x:v>SE-FHM-PUBLIC-RECORD-RESPONSE-2026-07-24</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
       </x:c>
       <x:c r="B93" s="14" t="str">
-        <x:v>Public Health Agency of Sweden</x:v>
+        <x:v>Federal Trade Commission</x:v>
       </x:c>
       <x:c r="C93" s="14" t="str">
-        <x:v>official_reference</x:v>
+        <x:v>official_report</x:v>
       </x:c>
       <x:c r="D93" s="14" t="str">
-        <x:v>https://www.folkhalsomyndigheten.se/regler-och-tillsyn/tobak-och-nikotinprodukter-regler-for-tillverkning-handel-och-hantering/elektroniska-cigaretter-och-pafyllningsbehallare-sa-foljer-du-reglerna/</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
       </x:c>
       <x:c r="E93" s="14" t="str">
         <x:v>2026-08-03</x:v>
@@ -4270,7 +4328,7 @@
     </x:row>
     <x:row r="94" ht="31.5" customHeight="1">
       <x:c r="A94" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2015-2018</x:v>
+        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
       </x:c>
       <x:c r="B94" s="14" t="str">
         <x:v>Federal Trade Commission</x:v>
@@ -4279,7 +4337,7 @@
         <x:v>official_report</x:v>
       </x:c>
       <x:c r="D94" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2015-2018</x:v>
+        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
       </x:c>
       <x:c r="E94" s="14" t="str">
         <x:v>2026-08-03</x:v>
@@ -4287,16 +4345,16 @@
     </x:row>
     <x:row r="95" ht="31.5" customHeight="1">
       <x:c r="A95" s="14" t="str">
-        <x:v>US-FTC-E-CIGARETTE-REPORT-2021</x:v>
+        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
       </x:c>
       <x:c r="B95" s="14" t="str">
-        <x:v>Federal Trade Commission</x:v>
+        <x:v>health.govt.nz</x:v>
       </x:c>
       <x:c r="C95" s="14" t="str">
-        <x:v>official_report</x:v>
+        <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D95" s="14" t="str">
-        <x:v>https://www.ftc.gov/reports/e-cigarette-report-2021</x:v>
+        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
       </x:c>
       <x:c r="E95" s="14" t="str">
         <x:v>2026-08-03</x:v>
@@ -4304,7 +4362,7 @@
     </x:row>
     <x:row r="96" ht="31.5" customHeight="1">
       <x:c r="A96" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-E034CF64F670</x:v>
+        <x:v>REGISTER-REFERENCE-1766C84ECA96</x:v>
       </x:c>
       <x:c r="B96" s="14" t="str">
         <x:v>health.govt.nz</x:v>
@@ -4313,7 +4371,7 @@
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D96" s="14" t="str">
-        <x:v>https://www.health.govt.nz/regulation-legislation/vaping-herbal-smoking-and-smokeless-tobacco/requirements/complete-a-notifiable-product-annual-return</x:v>
+        <x:v>https://www.health.govt.nz/system/files/2025-11/notifiable-products-annual-sales-return-2025-user-guide.pdf</x:v>
       </x:c>
       <x:c r="E96" s="14" t="str">
         <x:v>2026-08-03</x:v>
@@ -4321,16 +4379,16 @@
     </x:row>
     <x:row r="97" ht="31.5" customHeight="1">
       <x:c r="A97" s="14" t="str">
-        <x:v>REGISTER-REFERENCE-1766C84ECA96</x:v>
+        <x:v>REGISTER-REFERENCE-096147286BEC</x:v>
       </x:c>
       <x:c r="B97" s="14" t="str">
-        <x:v>health.govt.nz</x:v>
+        <x:v>ifrs.org</x:v>
       </x:c>
       <x:c r="C97" s="14" t="str">
         <x:v>register_reference</x:v>
       </x:c>
       <x:c r="D97" s="14" t="str">
-        <x:v>https://www.health.govt.nz/system/files/2025-11/notifiable-products-annual-sales-return-2025-user-guide.pdf</x:v>
+        <x:v>https://www.ifrs.org/issued-standards/list-of-standards/ifrs-13-fair-value-measurement/</x:v>
       </x:c>
       <x:c r="E97" s="14" t="str">
         <x:v>2026-08-03</x:v>
@@ -4492,7 +4550,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02e074c8a8dd4fe1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re444d61bfc9e429e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4525,7 +4583,7 @@
         <x:v>Tunniste</x:v>
       </x:c>
       <x:c r="C1" s="5" t="str">
-        <x:v>Erä / komponentti</x:v>
+        <x:v>Erätunniste / komponentti</x:v>
       </x:c>
       <x:c r="D1" s="5" t="str">
         <x:v>Maa / maantiede</x:v>
@@ -4534,7 +4592,7 @@
         <x:v>Vuosi</x:v>
       </x:c>
       <x:c r="F1" s="5" t="str">
-        <x:v>Periodi</x:v>
+        <x:v>Jakso</x:v>
       </x:c>
       <x:c r="G1" s="5" t="str">
         <x:v>Alkuperäinen määrä</x:v>
@@ -4543,16 +4601,16 @@
         <x:v>Valuutta</x:v>
       </x:c>
       <x:c r="I1" s="5" t="str">
-        <x:v>ECB-kurssi (valuuttayksikköä / EUR)</x:v>
+        <x:v>EKP-kurssi (valuuttayksikköä / EUR)</x:v>
       </x:c>
       <x:c r="J1" s="5" t="str">
         <x:v>EUR-vasta-arvo (täysi tarkkuus)</x:v>
       </x:c>
       <x:c r="K1" s="5" t="str">
-        <x:v>Rate ID</x:v>
+        <x:v>Kurssitunniste</x:v>
       </x:c>
       <x:c r="L1" s="5" t="str">
-        <x:v>ECB-lähde URL</x:v>
+        <x:v>EKP-lähteen URL</x:v>
       </x:c>
       <x:c r="M1" s="5" t="str">
         <x:v>Tila</x:v>
@@ -4563,22 +4621,22 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="13" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B2" s="13" t="str">
         <x:v>CA-2024-MANUFACTURER-IMPORTER-SHIPMENTS-VALUE</x:v>
       </x:c>
       <x:c r="C2" s="13" t="str">
-        <x:v>manufacturer_importer_shipments_value</x:v>
+        <x:v>valmistajien ja maahantuojien toimitusarvo</x:v>
       </x:c>
       <x:c r="D2" s="13" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E2" s="13" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F2" s="13" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G2" s="44" t="n">
         <x:v>1160753796.78</x:v>
@@ -4600,30 +4658,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M2" s="13" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N2" s="13" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="25.5" customHeight="1">
       <x:c r="A3" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
         <x:v>CA-2019-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>statcan_rcs_vaping_retail_sales</x:v>
+        <x:v>Statistics Canadan sähkötupakkavähittäismyynti</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E3" s="14" t="n">
         <x:v>2019</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G3" s="45" t="n">
         <x:v>477077000</x:v>
@@ -4645,30 +4703,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M3" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N3" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25.5" customHeight="1">
       <x:c r="A4" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
         <x:v>CA-2020-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>statcan_rcs_vaping_retail_sales</x:v>
+        <x:v>Statistics Canadan sähkötupakkavähittäismyynti</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E4" s="14" t="n">
         <x:v>2020</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G4" s="45" t="n">
         <x:v>520647000</x:v>
@@ -4690,30 +4748,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M4" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N4" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25.5" customHeight="1">
       <x:c r="A5" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
         <x:v>CA-2021-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>statcan_rcs_vaping_retail_sales</x:v>
+        <x:v>Statistics Canadan sähkötupakkavähittäismyynti</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E5" s="14" t="n">
         <x:v>2021</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G5" s="45" t="n">
         <x:v>992732000</x:v>
@@ -4735,30 +4793,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M5" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N5" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25.5" customHeight="1">
       <x:c r="A6" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
         <x:v>CA-2022-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>statcan_rcs_vaping_retail_sales</x:v>
+        <x:v>Statistics Canadan sähkötupakkavähittäismyynti</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E6" s="14" t="n">
         <x:v>2022</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G6" s="45" t="n">
         <x:v>1277158000</x:v>
@@ -4780,30 +4838,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M6" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N6" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25.5" customHeight="1">
       <x:c r="A7" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
         <x:v>CA-2023-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>statcan_rcs_vaping_retail_sales</x:v>
+        <x:v>Statistics Canadan sähkötupakkavähittäismyynti</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E7" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G7" s="45" t="n">
         <x:v>1530758000</x:v>
@@ -4825,30 +4883,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M7" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N7" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="25.5" customHeight="1">
       <x:c r="A8" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
         <x:v>CA-2024-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>statcan_rcs_vaping_retail_sales</x:v>
+        <x:v>Statistics Canadan sähkötupakkavähittäismyynti</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E8" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G8" s="45" t="n">
         <x:v>1219160000</x:v>
@@ -4870,30 +4928,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M8" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N8" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="25.5" customHeight="1">
       <x:c r="A9" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
         <x:v>CA-2025-STATCAN-RCS-VAPING-RETAIL-SALES</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>statcan_rcs_vaping_retail_sales</x:v>
+        <x:v>Statistics Canadan sähkötupakkavähittäismyynti</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E9" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G9" s="45" t="n">
         <x:v>1266567000</x:v>
@@ -4915,30 +4973,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M9" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N9" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="25.5" customHeight="1">
       <x:c r="A10" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
         <x:v>NZ-2022-NOTIFIABLE-PRODUCT-REPORTED-REVENUE</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>official_reported_revenue_mixed_supply_stages</x:v>
+        <x:v>virallisesti ilmoitettu liikevaihto, sekalaiset toimitusvaiheet</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E10" s="14" t="n">
         <x:v>2022</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G10" s="45" t="n">
         <x:v>404000000</x:v>
@@ -4960,30 +5018,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M10" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N10" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="25.5" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>NZ-2023-NOTIFIABLE-PRODUCT-REPORTED-REVENUE-LOWER-BOUND</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>official_reported_revenue_mixed_supply_stages</x:v>
+        <x:v>virallisesti ilmoitettu liikevaihto, sekalaiset toimitusvaiheet</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E11" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G11" s="45" t="n">
         <x:v>374000000</x:v>
@@ -5005,30 +5063,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M11" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N11" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="25.5" customHeight="1">
       <x:c r="A12" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
         <x:v>NZ-2024-SPECIALIST-RETAIL-SALES-LOWER-BOUND</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>official_specialist_retail_sales_lower_bound</x:v>
+        <x:v>erikoisvähittäiskaupan virallinen myynnin alaraja</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E12" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G12" s="45" t="n">
         <x:v>280000000</x:v>
@@ -5050,30 +5108,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M12" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N12" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="25.5" customHeight="1">
       <x:c r="A13" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
         <x:v>NZ-2024-SPECIALIST-RETAIL-PRODUCT-SALES-RAW-FILE-SUM</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>derived_official_workbook_sales_raw_sum</x:v>
+        <x:v>virallisten työkirjojen johdettu myynnin raakasumma</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E13" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G13" s="45" t="n">
         <x:v>280684512.81</x:v>
@@ -5095,30 +5153,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M13" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N13" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="25.5" customHeight="1">
       <x:c r="A14" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
         <x:v>NZ-2024-IDENTIFIED-VAPING-PRODUCT-SALES-RAW-SUM</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>derived_identified_vaping_product_sales_raw_sum</x:v>
+        <x:v>tunnistettujen sähkötupakkatuotteiden johdettu myynnin raakasumma</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E14" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G14" s="45" t="n">
         <x:v>274180410.21</x:v>
@@ -5140,30 +5198,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M14" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N14" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="25.5" customHeight="1">
       <x:c r="A15" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
         <x:v>EU-2023-EC-E-CIGARETTE-MARKET-BENCHMARK</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>institutional_market_value_benchmark</x:v>
+        <x:v>institutionaalinen markkina-arvon vertailuarvo</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>European Union</x:v>
+        <x:v>Euroopan unioni</x:v>
       </x:c>
       <x:c r="E15" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G15" s="45" t="n">
         <x:v>4990000000</x:v>
@@ -5185,30 +5243,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M15" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N15" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="25.5" customHeight="1">
       <x:c r="A16" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
         <x:v>DE-2023-SUBSTITUTES-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>substitutes_excise_receipts</x:v>
+        <x:v>korvaavien tuotteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E16" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G16" s="45" t="n">
         <x:v>201000000</x:v>
@@ -5230,30 +5288,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M16" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N16" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="25.5" customHeight="1">
       <x:c r="A17" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
         <x:v>DE-2024-SUBSTITUTES-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>substitutes_excise_receipts</x:v>
+        <x:v>korvaavien tuotteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E17" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G17" s="45" t="n">
         <x:v>266000000</x:v>
@@ -5275,30 +5333,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M17" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N17" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="25.5" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
         <x:v>DE-2025-SUBSTITUTES-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>substitutes_excise_receipts</x:v>
+        <x:v>korvaavien tuotteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E18" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G18" s="45" t="n">
         <x:v>404000000</x:v>
@@ -5320,30 +5378,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M18" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N18" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="25.5" customHeight="1">
       <x:c r="A19" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
         <x:v>DE-2019-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
+        <x:v>WZ 47.26 -tupakkaerikoiskaupan verollinen liikevaihto</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E19" s="14" t="n">
         <x:v>2019</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G19" s="45" t="n">
         <x:v>2247267035</x:v>
@@ -5365,30 +5423,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M19" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N19" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="25.5" customHeight="1">
       <x:c r="A20" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
         <x:v>DE-2020-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
+        <x:v>WZ 47.26 -tupakkaerikoiskaupan verollinen liikevaihto</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E20" s="14" t="n">
         <x:v>2020</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G20" s="45" t="n">
         <x:v>2444948000</x:v>
@@ -5410,30 +5468,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M20" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N20" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="25.5" customHeight="1">
       <x:c r="A21" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
         <x:v>DE-2021-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
+        <x:v>WZ 47.26 -tupakkaerikoiskaupan verollinen liikevaihto</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E21" s="14" t="n">
         <x:v>2021</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G21" s="45" t="n">
         <x:v>2325648577</x:v>
@@ -5455,30 +5513,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M21" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N21" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="25.5" customHeight="1">
       <x:c r="A22" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
         <x:v>DE-2022-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
+        <x:v>WZ 47.26 -tupakkaerikoiskaupan verollinen liikevaihto</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E22" s="14" t="n">
         <x:v>2022</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G22" s="45" t="n">
         <x:v>2510888578</x:v>
@@ -5500,30 +5558,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M22" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="25.5" customHeight="1">
       <x:c r="A23" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
         <x:v>DE-2023-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
+        <x:v>WZ 47.26 -tupakkaerikoiskaupan verollinen liikevaihto</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E23" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G23" s="45" t="n">
         <x:v>2581608198</x:v>
@@ -5545,30 +5603,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M23" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="25.5" customHeight="1">
       <x:c r="A24" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
         <x:v>DE-2024-WZ4726-TAXABLE-TURNOVER-EUR</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>wz4726_tobacco_specialist_taxable_supplies_and_services_turnover</x:v>
+        <x:v>WZ 47.26 -tupakkaerikoiskaupan verollinen liikevaihto</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E24" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G24" s="45" t="n">
         <x:v>2687776000</x:v>
@@ -5590,30 +5648,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M24" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="25.5" customHeight="1">
       <x:c r="A25" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
         <x:v>FI-2025-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>nicotine_e_liquid_excise_receipts</x:v>
+        <x:v>nikotiinillisten e-nesteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>Finland</x:v>
+        <x:v>Suomi</x:v>
       </x:c>
       <x:c r="E25" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G25" s="45" t="n">
         <x:v>3540319</x:v>
@@ -5635,30 +5693,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M25" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="25.5" customHeight="1">
       <x:c r="A26" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
         <x:v>PL-2021-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>e_liquid_excise_receipts</x:v>
+        <x:v>e-nesteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Puola</x:v>
       </x:c>
       <x:c r="E26" s="14" t="n">
         <x:v>2021</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G26" s="45" t="n">
         <x:v>179500000</x:v>
@@ -5680,30 +5738,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M26" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N26" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="25.5" customHeight="1">
       <x:c r="A27" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
         <x:v>PL-2022-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>e_liquid_excise_receipts</x:v>
+        <x:v>e-nesteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Puola</x:v>
       </x:c>
       <x:c r="E27" s="14" t="n">
         <x:v>2022</x:v>
       </x:c>
       <x:c r="F27" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G27" s="45" t="n">
         <x:v>229900000</x:v>
@@ -5725,30 +5783,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M27" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N27" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="25.5" customHeight="1">
       <x:c r="A28" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
         <x:v>PL-2023-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>e_liquid_excise_receipts</x:v>
+        <x:v>e-nesteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Puola</x:v>
       </x:c>
       <x:c r="E28" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G28" s="45" t="n">
         <x:v>443600000</x:v>
@@ -5770,30 +5828,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M28" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N28" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="25.5" customHeight="1">
       <x:c r="A29" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
         <x:v>PL-2024-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>e_liquid_excise_receipts</x:v>
+        <x:v>e-nesteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Puola</x:v>
       </x:c>
       <x:c r="E29" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G29" s="45" t="n">
         <x:v>561400000</x:v>
@@ -5815,30 +5873,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M29" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N29" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="25.5" customHeight="1">
       <x:c r="A30" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
         <x:v>PL-2015-UOKIK-E-CIGARETTE-MARKET-VALUE-ESTIMATE</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>institutional_market_value_benchmark</x:v>
+        <x:v>institutionaalinen markkina-arvon vertailuarvo</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Puola</x:v>
       </x:c>
       <x:c r="E30" s="14" t="n">
         <x:v>2015</x:v>
       </x:c>
       <x:c r="F30" s="14" t="str">
-        <x:v>study_reference_period_may_2015</x:v>
+        <x:v>tutkimuksen viitejakso toukokuussa 2015</x:v>
       </x:c>
       <x:c r="G30" s="45" t="n">
         <x:v>500000000</x:v>
@@ -5853,30 +5911,30 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="M30" s="14" t="str">
-        <x:v>not_computed</x:v>
+        <x:v>ei laskettu</x:v>
       </x:c>
       <x:c r="N30" s="14" t="str">
-        <x:v>period_not_compatible_with_annual_average</x:v>
+        <x:v>jakso ei ole yhteensopiva vuotuisen keskikurssin kanssa</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="25.5" customHeight="1">
       <x:c r="A31" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
         <x:v>PL-2025-E-LIQUID-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>e_liquid_excise_receipts</x:v>
+        <x:v>e-nesteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Puola</x:v>
       </x:c>
       <x:c r="E31" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F31" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G31" s="45" t="n">
         <x:v>993100000</x:v>
@@ -5898,30 +5956,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M31" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N31" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="25.5" customHeight="1">
       <x:c r="A32" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
         <x:v>PL-2025-VAPING-DEVICE-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>vaporisation_device_broad_group_excise_amount</x:v>
+        <x:v>laajan höyrystyslaiteryhmän valmisteveron määrä</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Puola</x:v>
       </x:c>
       <x:c r="E32" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F32" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G32" s="45" t="n">
         <x:v>175300000</x:v>
@@ -5943,30 +6001,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M32" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N32" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="25.5" customHeight="1">
       <x:c r="A33" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
         <x:v>PL-2025-VAPING-COMPONENT-SETS-EXCISE-AMOUNT</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>vaporisation_device_component_sets_broad_group_excise_amount</x:v>
+        <x:v>laajan höyrystyslaitteiden osasarjaryhmän valmisteveron määrä</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Puola</x:v>
       </x:c>
       <x:c r="E33" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F33" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G33" s="45" t="n">
         <x:v>2500000</x:v>
@@ -5988,30 +6046,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M33" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N33" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="25.5" customHeight="1">
       <x:c r="A34" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
         <x:v>SE-2024-NICOTINE-E-LIQUID-EXCISE-RECEIPTS</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>nicotine_e_liquid_excise_receipts</x:v>
+        <x:v>nikotiinillisten e-nesteiden valmisteverotuotto</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
-        <x:v>Sweden</x:v>
+        <x:v>Ruotsi</x:v>
       </x:c>
       <x:c r="E34" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F34" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G34" s="45" t="n">
         <x:v>80000000</x:v>
@@ -6033,30 +6091,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.SEK.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M34" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N34" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="25.5" customHeight="1">
       <x:c r="A35" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
         <x:v>GLOBAL-2025-IMARC-COMMERCIAL-ESTIMATE</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>commercial_market_estimate</x:v>
+        <x:v>kaupallinen markkina-arvio</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>Global</x:v>
+        <x:v>Maailma</x:v>
       </x:c>
       <x:c r="E35" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F35" s="14" t="str">
-        <x:v>calendar_year_estimate</x:v>
+        <x:v>kalenterivuoden arvio</x:v>
       </x:c>
       <x:c r="G35" s="45" t="n">
         <x:v>26000000000</x:v>
@@ -6078,30 +6136,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M35" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N35" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="25.5" customHeight="1">
       <x:c r="A36" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B36" s="14" t="str">
         <x:v>GLOBAL-2025-GVR-COMMERCIAL-ESTIMATE</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>commercial_market_estimate</x:v>
+        <x:v>kaupallinen markkina-arvio</x:v>
       </x:c>
       <x:c r="D36" s="14" t="str">
-        <x:v>Global</x:v>
+        <x:v>Maailma</x:v>
       </x:c>
       <x:c r="E36" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
-        <x:v>calendar_year_estimate</x:v>
+        <x:v>kalenterivuoden arvio</x:v>
       </x:c>
       <x:c r="G36" s="45" t="n">
         <x:v>45700000000</x:v>
@@ -6123,30 +6181,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M36" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N36" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="25.5" customHeight="1">
       <x:c r="A37" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B37" s="14" t="str">
         <x:v>GLOBAL-2025-FORTUNE-COMMERCIAL-ESTIMATE</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>commercial_market_estimate</x:v>
+        <x:v>kaupallinen markkina-arvio</x:v>
       </x:c>
       <x:c r="D37" s="14" t="str">
-        <x:v>Global</x:v>
+        <x:v>Maailma</x:v>
       </x:c>
       <x:c r="E37" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F37" s="14" t="str">
-        <x:v>calendar_year_estimate</x:v>
+        <x:v>kalenterivuoden arvio</x:v>
       </x:c>
       <x:c r="G37" s="45" t="n">
         <x:v>46320000000</x:v>
@@ -6168,30 +6226,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M37" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N37" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="25.5" customHeight="1">
       <x:c r="A38" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B38" s="14" t="str">
         <x:v>US-2015-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>FTC:n ilmoittama kasetti- ja kertakäyttötuotteiden myynti</x:v>
       </x:c>
       <x:c r="D38" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Yhdysvallat</x:v>
       </x:c>
       <x:c r="E38" s="14" t="n">
         <x:v>2015</x:v>
       </x:c>
       <x:c r="F38" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G38" s="45" t="n">
         <x:v>304170046</x:v>
@@ -6213,30 +6271,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2015&amp;endPeriod=2015&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M38" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N38" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="25.5" customHeight="1">
       <x:c r="A39" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B39" s="14" t="str">
         <x:v>US-2016-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>FTC:n ilmoittama kasetti- ja kertakäyttötuotteiden myynti</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Yhdysvallat</x:v>
       </x:c>
       <x:c r="E39" s="14" t="n">
         <x:v>2016</x:v>
       </x:c>
       <x:c r="F39" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G39" s="45" t="n">
         <x:v>485707484</x:v>
@@ -6258,30 +6316,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2016&amp;endPeriod=2016&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M39" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N39" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="25.5" customHeight="1">
       <x:c r="A40" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B40" s="14" t="str">
         <x:v>US-2017-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>FTC:n ilmoittama kasetti- ja kertakäyttötuotteiden myynti</x:v>
       </x:c>
       <x:c r="D40" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Yhdysvallat</x:v>
       </x:c>
       <x:c r="E40" s="14" t="n">
         <x:v>2017</x:v>
       </x:c>
       <x:c r="F40" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G40" s="45" t="n">
         <x:v>779836399</x:v>
@@ -6303,30 +6361,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2017&amp;endPeriod=2017&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M40" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N40" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="25.5" customHeight="1">
       <x:c r="A41" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B41" s="14" t="str">
         <x:v>US-2018-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>FTC:n ilmoittama kasetti- ja kertakäyttötuotteiden myynti</x:v>
       </x:c>
       <x:c r="D41" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Yhdysvallat</x:v>
       </x:c>
       <x:c r="E41" s="14" t="n">
         <x:v>2018</x:v>
       </x:c>
       <x:c r="F41" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G41" s="45" t="n">
         <x:v>2043703005</x:v>
@@ -6348,30 +6406,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2018&amp;endPeriod=2018&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M41" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N41" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="25.5" customHeight="1">
       <x:c r="A42" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B42" s="14" t="str">
         <x:v>US-2019-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>FTC:n ilmoittama kasetti- ja kertakäyttötuotteiden myynti</x:v>
       </x:c>
       <x:c r="D42" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Yhdysvallat</x:v>
       </x:c>
       <x:c r="E42" s="14" t="n">
         <x:v>2019</x:v>
       </x:c>
       <x:c r="F42" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G42" s="45" t="n">
         <x:v>2702608307</x:v>
@@ -6393,30 +6451,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2019&amp;endPeriod=2019&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M42" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N42" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="25.5" customHeight="1">
       <x:c r="A43" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B43" s="14" t="str">
         <x:v>US-2020-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>FTC:n ilmoittama kasetti- ja kertakäyttötuotteiden myynti</x:v>
       </x:c>
       <x:c r="D43" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Yhdysvallat</x:v>
       </x:c>
       <x:c r="E43" s="14" t="n">
         <x:v>2020</x:v>
       </x:c>
       <x:c r="F43" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G43" s="45" t="n">
         <x:v>2394423105</x:v>
@@ -6438,30 +6496,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2020&amp;endPeriod=2020&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M43" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N43" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="25.5" customHeight="1">
       <x:c r="A44" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B44" s="14" t="str">
         <x:v>US-2021-FTC-CARTRIDGE-DISPOSABLE-REPORTED-SALES</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
-        <x:v>ftc_reported_cartridge_and_disposable_sales</x:v>
+        <x:v>FTC:n ilmoittama kasetti- ja kertakäyttötuotteiden myynti</x:v>
       </x:c>
       <x:c r="D44" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Yhdysvallat</x:v>
       </x:c>
       <x:c r="E44" s="14" t="n">
         <x:v>2021</x:v>
       </x:c>
       <x:c r="F44" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G44" s="45" t="n">
         <x:v>2763284338</x:v>
@@ -6483,30 +6541,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.USD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M44" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N44" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="25.5" customHeight="1">
       <x:c r="A45" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B45" s="14" t="str">
         <x:v>NZ-2019-HES-E-CIGARETTES-AND-REFILLS-EXPENDITURE-NZD</x:v>
       </x:c>
       <x:c r="C45" s="14" t="str">
-        <x:v>household_expenditure_estimate</x:v>
+        <x:v>kotitalouskulutuksen arvio</x:v>
       </x:c>
       <x:c r="D45" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E45" s="14" t="n">
         <x:v>2019</x:v>
       </x:c>
       <x:c r="F45" s="14" t="str">
-        <x:v>year_ended_june</x:v>
+        <x:v>kesäkuussa päättynyt vuosi</x:v>
       </x:c>
       <x:c r="G45" s="45" t="n">
         <x:v>42276000</x:v>
@@ -6521,30 +6579,30 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="M45" s="14" t="str">
-        <x:v>not_computed</x:v>
+        <x:v>ei laskettu</x:v>
       </x:c>
       <x:c r="N45" s="14" t="str">
-        <x:v>period_not_compatible_with_annual_average</x:v>
+        <x:v>jakso ei ole yhteensopiva vuotuisen keskikurssin kanssa</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="25.5" customHeight="1">
       <x:c r="A46" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B46" s="14" t="str">
         <x:v>NZ-2019-HES-E-CIGARETTE-DEVICES-EXPENDITURE-NZD</x:v>
       </x:c>
       <x:c r="C46" s="14" t="str">
-        <x:v>household_expenditure_estimate</x:v>
+        <x:v>kotitalouskulutuksen arvio</x:v>
       </x:c>
       <x:c r="D46" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E46" s="14" t="n">
         <x:v>2019</x:v>
       </x:c>
       <x:c r="F46" s="14" t="str">
-        <x:v>year_ended_june</x:v>
+        <x:v>kesäkuussa päättynyt vuosi</x:v>
       </x:c>
       <x:c r="G46" s="45" t="n">
         <x:v>18034000</x:v>
@@ -6559,30 +6617,30 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="M46" s="14" t="str">
-        <x:v>not_computed</x:v>
+        <x:v>ei laskettu</x:v>
       </x:c>
       <x:c r="N46" s="14" t="str">
-        <x:v>period_not_compatible_with_annual_average</x:v>
+        <x:v>jakso ei ole yhteensopiva vuotuisen keskikurssin kanssa</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="25.5" customHeight="1">
       <x:c r="A47" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B47" s="14" t="str">
         <x:v>NZ-2019-HES-E-CIGARETTE-REFILLS-EXPENDITURE-NZD</x:v>
       </x:c>
       <x:c r="C47" s="14" t="str">
-        <x:v>household_expenditure_estimate</x:v>
+        <x:v>kotitalouskulutuksen arvio</x:v>
       </x:c>
       <x:c r="D47" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E47" s="14" t="n">
         <x:v>2019</x:v>
       </x:c>
       <x:c r="F47" s="14" t="str">
-        <x:v>year_ended_june</x:v>
+        <x:v>kesäkuussa päättynyt vuosi</x:v>
       </x:c>
       <x:c r="G47" s="45" t="n">
         <x:v>24242000</x:v>
@@ -6597,30 +6655,30 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="M47" s="14" t="str">
-        <x:v>not_computed</x:v>
+        <x:v>ei laskettu</x:v>
       </x:c>
       <x:c r="N47" s="14" t="str">
-        <x:v>period_not_compatible_with_annual_average</x:v>
+        <x:v>jakso ei ole yhteensopiva vuotuisen keskikurssin kanssa</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="25.5" customHeight="1">
       <x:c r="A48" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B48" s="14" t="str">
         <x:v>NZ-2023-HES-E-CIGARETTES-AND-REFILLS-EXPENDITURE-NZD</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>household_expenditure_estimate</x:v>
+        <x:v>kotitalouskulutuksen arvio</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E48" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F48" s="14" t="str">
-        <x:v>year_ended_june</x:v>
+        <x:v>kesäkuussa päättynyt vuosi</x:v>
       </x:c>
       <x:c r="G48" s="45" t="n">
         <x:v>186980000</x:v>
@@ -6635,30 +6693,30 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="M48" s="14" t="str">
-        <x:v>not_computed</x:v>
+        <x:v>ei laskettu</x:v>
       </x:c>
       <x:c r="N48" s="14" t="str">
-        <x:v>period_not_compatible_with_annual_average</x:v>
+        <x:v>jakso ei ole yhteensopiva vuotuisen keskikurssin kanssa</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="25.5" customHeight="1">
       <x:c r="A49" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B49" s="14" t="str">
         <x:v>NZ-2023-HES-E-CIGARETTE-DEVICES-EXPENDITURE-NZD</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>household_expenditure_estimate</x:v>
+        <x:v>kotitalouskulutuksen arvio</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E49" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F49" s="14" t="str">
-        <x:v>year_ended_june</x:v>
+        <x:v>kesäkuussa päättynyt vuosi</x:v>
       </x:c>
       <x:c r="G49" s="45" t="n">
         <x:v>22488000</x:v>
@@ -6673,30 +6731,30 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="M49" s="14" t="str">
-        <x:v>not_computed</x:v>
+        <x:v>ei laskettu</x:v>
       </x:c>
       <x:c r="N49" s="14" t="str">
-        <x:v>period_not_compatible_with_annual_average</x:v>
+        <x:v>jakso ei ole yhteensopiva vuotuisen keskikurssin kanssa</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="25.5" customHeight="1">
       <x:c r="A50" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B50" s="14" t="str">
         <x:v>NZ-2023-HES-E-CIGARETTE-REFILLS-EXPENDITURE-NZD</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>household_expenditure_estimate</x:v>
+        <x:v>kotitalouskulutuksen arvio</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E50" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
-        <x:v>year_ended_june</x:v>
+        <x:v>kesäkuussa päättynyt vuosi</x:v>
       </x:c>
       <x:c r="G50" s="45" t="n">
         <x:v>164492000</x:v>
@@ -6711,30 +6769,30 @@
         <x:v>https://data.ecb.europa.eu/data/datasets/exr/data-information</x:v>
       </x:c>
       <x:c r="M50" s="14" t="str">
-        <x:v>not_computed</x:v>
+        <x:v>ei laskettu</x:v>
       </x:c>
       <x:c r="N50" s="14" t="str">
-        <x:v>period_not_compatible_with_annual_average</x:v>
+        <x:v>jakso ei ole yhteensopiva vuotuisen keskikurssin kanssa</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="25.5" customHeight="1">
       <x:c r="A51" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B51" s="14" t="str">
         <x:v>CA-2021-HC-VAPING-MARKET-BENCHMARK</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>institutional_market_value_benchmark</x:v>
+        <x:v>institutionaalinen markkina-arvon vertailuarvo</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E51" s="14" t="n">
         <x:v>2021</x:v>
       </x:c>
       <x:c r="F51" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G51" s="45" t="n">
         <x:v>2040000000</x:v>
@@ -6756,30 +6814,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M51" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N51" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="25.5" customHeight="1">
       <x:c r="A52" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
         <x:v>CA-2021-HC-GAS-CONVENIENCE-VAPING-SALES-BENCHMARK</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>institutional_channel_value_benchmark</x:v>
+        <x:v>institutionaalinen kanava-arvon vertailuarvo</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E52" s="14" t="n">
         <x:v>2021</x:v>
       </x:c>
       <x:c r="F52" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G52" s="45" t="n">
         <x:v>631000000</x:v>
@@ -6801,30 +6859,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M52" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N52" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="25.5" customHeight="1">
       <x:c r="A53" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
         <x:v>CA-2021-HC-ONLINE-VAPING-SALES-BENCHMARK</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>institutional_channel_value_benchmark</x:v>
+        <x:v>institutionaalinen kanava-arvon vertailuarvo</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Kanada</x:v>
       </x:c>
       <x:c r="E53" s="14" t="n">
         <x:v>2021</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G53" s="45" t="n">
         <x:v>436000000</x:v>
@@ -6846,30 +6904,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.CAD.EUR.SP00.A?startPeriod=2021&amp;endPeriod=2021&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M53" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N53" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="25.5" customHeight="1">
       <x:c r="A54" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B54" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-20595980-SOLD-PRODUCTION-EUR</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
-        <x:v>prodcom_20595980_sold_production_value</x:v>
+        <x:v>PRODCOM 20595980: myydyn tuotannon arvo</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E54" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F54" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G54" s="45" t="n">
         <x:v>39078000</x:v>
@@ -6891,30 +6949,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M54" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N54" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="25.5" customHeight="1">
       <x:c r="A55" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B55" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-20595980-IMPORTS-EUR</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
-        <x:v>prodcom_20595980_import_value</x:v>
+        <x:v>PRODCOM 20595980: tuonnin arvo</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E55" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F55" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G55" s="45" t="n">
         <x:v>400843037</x:v>
@@ -6936,30 +6994,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M55" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N55" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="25.5" customHeight="1">
       <x:c r="A56" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B56" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-20595980-EXPORTS-EUR</x:v>
       </x:c>
       <x:c r="C56" s="14" t="str">
-        <x:v>prodcom_20595980_export_value</x:v>
+        <x:v>PRODCOM 20595980: viennin arvo</x:v>
       </x:c>
       <x:c r="D56" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E56" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F56" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G56" s="45" t="n">
         <x:v>120676188</x:v>
@@ -6981,30 +7039,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M56" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N56" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="25.5" customHeight="1">
       <x:c r="A57" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B57" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-27901152-SOLD-PRODUCTION-EUR</x:v>
       </x:c>
       <x:c r="C57" s="14" t="str">
-        <x:v>prodcom_27901152_sold_production_value</x:v>
+        <x:v>PRODCOM 27901152: myydyn tuotannon arvo</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E57" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F57" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G57" s="45" t="n">
         <x:v>99890000</x:v>
@@ -7026,30 +7084,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M57" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N57" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="25.5" customHeight="1">
       <x:c r="A58" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B58" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-27901152-IMPORTS-EUR</x:v>
       </x:c>
       <x:c r="C58" s="14" t="str">
-        <x:v>prodcom_27901152_import_value</x:v>
+        <x:v>PRODCOM 27901152: tuonnin arvo</x:v>
       </x:c>
       <x:c r="D58" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E58" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F58" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G58" s="45" t="n">
         <x:v>490580247</x:v>
@@ -7071,30 +7129,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M58" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N58" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="25.5" customHeight="1">
       <x:c r="A59" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B59" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-27901152-EXPORTS-EUR</x:v>
       </x:c>
       <x:c r="C59" s="14" t="str">
-        <x:v>prodcom_27901152_export_value</x:v>
+        <x:v>PRODCOM 27901152: viennin arvo</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E59" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F59" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G59" s="45" t="n">
         <x:v>301380538</x:v>
@@ -7116,30 +7174,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M59" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N59" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="25.5" customHeight="1">
       <x:c r="A60" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B60" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-20595980-APPARENT-SUPPLY-EUR</x:v>
       </x:c>
       <x:c r="C60" s="14" t="str">
-        <x:v>prodcom_20595980_apparent_supply_value</x:v>
+        <x:v>PRODCOM 20595980: näennäisen tarjonnan arvo</x:v>
       </x:c>
       <x:c r="D60" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E60" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F60" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G60" s="45" t="n">
         <x:v>319244849</x:v>
@@ -7161,30 +7219,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M60" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N60" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="25.5" customHeight="1">
       <x:c r="A61" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B61" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-27901152-APPARENT-SUPPLY-EUR</x:v>
       </x:c>
       <x:c r="C61" s="14" t="str">
-        <x:v>prodcom_27901152_apparent_supply_value</x:v>
+        <x:v>PRODCOM 27901152: näennäisen tarjonnan arvo</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E61" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F61" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G61" s="45" t="n">
         <x:v>289089709</x:v>
@@ -7206,30 +7264,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M61" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N61" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="25.5" customHeight="1">
       <x:c r="A62" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B62" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-COMBINED-APPARENT-SUPPLY-EUR</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>combined_prodcom_apparent_supply_value</x:v>
+        <x:v>yhdistetty PRODCOM-näennäisen tarjonnan arvo</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E62" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F62" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G62" s="45" t="n">
         <x:v>608334558</x:v>
@@ -7251,30 +7309,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M62" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N62" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="25.5" customHeight="1">
       <x:c r="A63" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
         <x:v>DE-2024-EUROSTAT-APPARENT-SUPPLY-EXCISE-VAT-BRIDGE-EUR</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>mechanical_apparent_supply_excise_vat_bridge</x:v>
+        <x:v>mekaaninen näennäisen tarjonnan valmistevero- ja ALV-silta</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>Germany</x:v>
+        <x:v>Saksa</x:v>
       </x:c>
       <x:c r="E63" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F63" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G63" s="45" t="n">
         <x:v>1040458124.02</x:v>
@@ -7296,30 +7354,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M63" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N63" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="25.5" customHeight="1">
       <x:c r="A64" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
         <x:v>PL-2023-CMR-DISPOSABLE-E-CIGARETTE-RETAIL-SALES-VALUE</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>commercial_disposable_e_cigarette_retail_sales_value</x:v>
+        <x:v>kaupallinen kertakäyttöisten sähkötupakoiden vähittäismyyntiarvo</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>Poland</x:v>
+        <x:v>Puola</x:v>
       </x:c>
       <x:c r="E64" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F64" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G64" s="45" t="n">
         <x:v>2000000000</x:v>
@@ -7341,30 +7399,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.PLN.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M64" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N64" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="25.5" customHeight="1">
       <x:c r="A65" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
         <x:v>ES-2025-AEAT-M573-ALL-EPIGRAPHS-ACCRUED-EXCISE-LIABILITY-EUR</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>accrued_excise_liability</x:v>
+        <x:v>kertynyt valmisteverovelka</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>Spain</x:v>
+        <x:v>Espanja</x:v>
       </x:c>
       <x:c r="E65" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F65" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G65" s="45" t="n">
         <x:v>36151000</x:v>
@@ -7386,30 +7444,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M65" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N65" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="25.5" customHeight="1">
       <x:c r="A66" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B66" s="14" t="str">
         <x:v>ES-2025-AEAT-M573-ALL-EPIGRAPHS-GROSS-CASH-RECEIPTS-EUR</x:v>
       </x:c>
       <x:c r="C66" s="14" t="str">
-        <x:v>gross_excise_cash_receipts</x:v>
+        <x:v>valmisteveron bruttokassakertymä</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>Spain</x:v>
+        <x:v>Espanja</x:v>
       </x:c>
       <x:c r="E66" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F66" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G66" s="45" t="n">
         <x:v>31797000</x:v>
@@ -7431,30 +7489,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M66" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N66" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="25.5" customHeight="1">
       <x:c r="A67" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B67" s="14" t="str">
         <x:v>ES-2025-AEAT-M573-ALL-EPIGRAPHS-NET-CASH-RECEIPTS-EUR</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
-        <x:v>net_excise_cash_receipts</x:v>
+        <x:v>valmisteveron nettokassakertymä</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>Spain</x:v>
+        <x:v>Espanja</x:v>
       </x:c>
       <x:c r="E67" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F67" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G67" s="45" t="n">
         <x:v>29568000</x:v>
@@ -7476,30 +7534,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M67" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N67" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="25.5" customHeight="1">
       <x:c r="A68" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B68" s="14" t="str">
         <x:v>ES-2026-H1-AEAT-M573-ALL-EPIGRAPHS-GROSS-CASH-RECEIPTS-EUR</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
-        <x:v>gross_excise_cash_receipts</x:v>
+        <x:v>valmisteveron bruttokassakertymä</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>Spain</x:v>
+        <x:v>Espanja</x:v>
       </x:c>
       <x:c r="E68" s="14" t="n">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="F68" s="14" t="str">
-        <x:v>2026_h1</x:v>
+        <x:v>vuoden 2026 ensimmäinen puolisko</x:v>
       </x:c>
       <x:c r="G68" s="45" t="n">
         <x:v>25726000</x:v>
@@ -7521,30 +7579,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M68" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N68" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="25.5" customHeight="1">
       <x:c r="A69" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B69" s="14" t="str">
         <x:v>ES-2026-H1-AEAT-M573-ALL-EPIGRAPHS-NET-CASH-RECEIPTS-EUR</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
-        <x:v>net_excise_cash_receipts</x:v>
+        <x:v>valmisteveron nettokassakertymä</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>Spain</x:v>
+        <x:v>Espanja</x:v>
       </x:c>
       <x:c r="E69" s="14" t="n">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="F69" s="14" t="str">
-        <x:v>2026_h1</x:v>
+        <x:v>vuoden 2026 ensimmäinen puolisko</x:v>
       </x:c>
       <x:c r="G69" s="45" t="n">
         <x:v>21776000</x:v>
@@ -7566,30 +7624,30 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M69" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N69" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="25.5" customHeight="1">
       <x:c r="A70" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
         <x:v>JP-2022-854340000-E-CIGARETTE-DEVICE-IMPORT-CIF-VALUE-JPY</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
-        <x:v>e_cigarette_device_customs_import_cif_value</x:v>
+        <x:v>sähkötupakkalaitteiden tullituonnin CIF-arvo</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>Japan</x:v>
+        <x:v>Japani</x:v>
       </x:c>
       <x:c r="E70" s="14" t="n">
         <x:v>2022</x:v>
       </x:c>
       <x:c r="F70" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G70" s="45" t="n">
         <x:v>70257202000</x:v>
@@ -7611,30 +7669,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2022&amp;endPeriod=2022&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M70" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N70" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="25.5" customHeight="1">
       <x:c r="A71" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B71" s="14" t="str">
         <x:v>JP-2023-854340000-E-CIGARETTE-DEVICE-IMPORT-CIF-VALUE-JPY</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
-        <x:v>e_cigarette_device_customs_import_cif_value</x:v>
+        <x:v>sähkötupakkalaitteiden tullituonnin CIF-arvo</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>Japan</x:v>
+        <x:v>Japani</x:v>
       </x:c>
       <x:c r="E71" s="14" t="n">
         <x:v>2023</x:v>
       </x:c>
       <x:c r="F71" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G71" s="45" t="n">
         <x:v>70496284000</x:v>
@@ -7656,30 +7714,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2023&amp;endPeriod=2023&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M71" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N71" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="25.5" customHeight="1">
       <x:c r="A72" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
         <x:v>JP-2024-854340000-E-CIGARETTE-DEVICE-IMPORT-CIF-VALUE-JPY</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
-        <x:v>e_cigarette_device_customs_import_cif_value</x:v>
+        <x:v>sähkötupakkalaitteiden tullituonnin CIF-arvo</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>Japan</x:v>
+        <x:v>Japani</x:v>
       </x:c>
       <x:c r="E72" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F72" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G72" s="45" t="n">
         <x:v>74526020000</x:v>
@@ -7701,30 +7759,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M72" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N72" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="25.5" customHeight="1">
       <x:c r="A73" s="14" t="str">
-        <x:v>market_observation</x:v>
+        <x:v>markkinahavainto</x:v>
       </x:c>
       <x:c r="B73" s="14" t="str">
         <x:v>JP-2025-854340000-E-CIGARETTE-DEVICE-IMPORT-CIF-VALUE-JPY</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
-        <x:v>e_cigarette_device_customs_import_cif_value</x:v>
+        <x:v>sähkötupakkalaitteiden tullituonnin CIF-arvo</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>Japan</x:v>
+        <x:v>Japani</x:v>
       </x:c>
       <x:c r="E73" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F73" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G73" s="45" t="n">
         <x:v>84361341000</x:v>
@@ -7746,30 +7804,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.JPY.EUR.SP00.A?startPeriod=2025&amp;endPeriod=2025&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M73" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N73" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="25.5" customHeight="1">
       <x:c r="A74" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>skenaariokomponentti</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
-        <x:v>low.specialistRetailNzd</x:v>
+        <x:v>ala: erikoisvähittäiskauppa, NZD</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E74" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F74" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G74" s="45" t="n">
         <x:v>258327110.88</x:v>
@@ -7791,30 +7849,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M74" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N74" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="25.5" customHeight="1">
       <x:c r="A75" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>skenaariokomponentti</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>low.generalRetailRpsNzd</x:v>
+        <x:v>ala: yleisvähittäiskaupan RPS-malli, NZD</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E75" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F75" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G75" s="45" t="n">
         <x:v>275335272.8</x:v>
@@ -7836,30 +7894,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M75" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N75" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="25.5" customHeight="1">
       <x:c r="A76" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>skenaariokomponentti</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>low.combinedNzd</x:v>
+        <x:v>ala: yhdistetty, NZD</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E76" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F76" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G76" s="45" t="n">
         <x:v>533662383.68</x:v>
@@ -7881,30 +7939,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M76" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N76" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="25.5" customHeight="1">
       <x:c r="A77" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>skenaariokomponentti</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>base.specialistRetailNzd</x:v>
+        <x:v>perus: erikoisvähittäiskauppa, NZD</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E77" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F77" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G77" s="45" t="n">
         <x:v>274180410.21</x:v>
@@ -7926,30 +7984,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M77" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N77" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="25.5" customHeight="1">
       <x:c r="A78" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>skenaariokomponentti</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>base.generalRetailRpsNzd</x:v>
+        <x:v>perus: yleisvähittäiskaupan RPS-malli, NZD</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E78" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F78" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G78" s="45" t="n">
         <x:v>367631277.68</x:v>
@@ -7971,30 +8029,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M78" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N78" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="25.5" customHeight="1">
       <x:c r="A79" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>skenaariokomponentti</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
-        <x:v>base.combinedNzd</x:v>
+        <x:v>perus: yhdistetty, NZD</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E79" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F79" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G79" s="45" t="n">
         <x:v>641811687.89</x:v>
@@ -8016,30 +8074,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M79" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N79" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="25.5" customHeight="1">
       <x:c r="A80" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>skenaariokomponentti</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>high.specialistRetailNzd</x:v>
+        <x:v>ylä: erikoisvähittäiskauppa, NZD</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E80" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F80" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G80" s="45" t="n">
         <x:v>274180410.21</x:v>
@@ -8061,30 +8119,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M80" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N80" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="25.5" customHeight="1">
       <x:c r="A81" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>skenaariokomponentti</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>high.generalRetailRpsNzd</x:v>
+        <x:v>ylä: yleisvähittäiskaupan RPS-malli, NZD</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E81" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F81" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G81" s="45" t="n">
         <x:v>456995382.29</x:v>
@@ -8106,30 +8164,30 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M81" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N81" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="25.5" customHeight="1">
       <x:c r="A82" s="14" t="str">
-        <x:v>scenario_component</x:v>
+        <x:v>skenaariokomponentti</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
         <x:v>NZ-2024-RETAIL-RANGE</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>high.combinedNzd</x:v>
+        <x:v>ylä: yhdistetty, NZD</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>New Zealand</x:v>
+        <x:v>Uusi-Seelanti</x:v>
       </x:c>
       <x:c r="E82" s="14" t="n">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="F82" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G82" s="45" t="n">
         <x:v>731175792.5</x:v>
@@ -8151,28 +8209,28 @@
         <x:v>https://data-api.ecb.europa.eu/service/data/EXR/A.NZD.EUR.SP00.A?startPeriod=2024&amp;endPeriod=2024&amp;format=csvdata</x:v>
       </x:c>
       <x:c r="M82" s="14" t="str">
-        <x:v>computed</x:v>
+        <x:v>laskettu</x:v>
       </x:c>
       <x:c r="N82" s="14" t="str">
-        <x:v>original_amount_divided_by_ecb_annual_average</x:v>
+        <x:v>alkuperäinen määrä jaettuna EKP:n vuotuisella keskikurssilla</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="25.5" customHeight="1">
       <x:c r="A83" s="14" t="str">
-        <x:v>model</x:v>
+        <x:v>malli</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
         <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>low</x:v>
+        <x:v>ala</x:v>
       </x:c>
       <x:c r="D83" s="14"/>
       <x:c r="E83" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F83" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G83" s="45" t="n">
         <x:v>667920000</x:v>
@@ -8194,28 +8252,28 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M83" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N83" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="25.5" customHeight="1">
       <x:c r="A84" s="14" t="str">
-        <x:v>model</x:v>
+        <x:v>malli</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
         <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>central</x:v>
+        <x:v>keskitaso</x:v>
       </x:c>
       <x:c r="D84" s="14"/>
       <x:c r="E84" s="14" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F84" s="14" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G84" s="45" t="n">
         <x:v>1199220000</x:v>
@@ -8237,28 +8295,28 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M84" s="14" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N84" s="14" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="25.5" customHeight="1">
       <x:c r="A85" s="15" t="str">
-        <x:v>model</x:v>
+        <x:v>malli</x:v>
       </x:c>
       <x:c r="B85" s="15" t="str">
         <x:v>DE-2025-LIQUID-RETAIL-EQUIVALENT-RANGE</x:v>
       </x:c>
       <x:c r="C85" s="15" t="str">
-        <x:v>high</x:v>
+        <x:v>ylä</x:v>
       </x:c>
       <x:c r="D85" s="15"/>
       <x:c r="E85" s="15" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F85" s="15" t="str">
-        <x:v>calendar_year</x:v>
+        <x:v>kalenterivuosi</x:v>
       </x:c>
       <x:c r="G85" s="46" t="n">
         <x:v>1654620000</x:v>
@@ -8280,16 +8338,16 @@
         <x:v>https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/index.en.html</x:v>
       </x:c>
       <x:c r="M85" s="15" t="str">
-        <x:v>already_eur</x:v>
+        <x:v>valmiiksi euroina</x:v>
       </x:c>
       <x:c r="N85" s="15" t="str">
-        <x:v>original_currency_already_eur</x:v>
+        <x:v>alkuperäinen valuutta on jo euro</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re46feb816db34858"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebe85c15f540431a"/>
   </x:tableParts>
 </x:worksheet>
 </file>